--- a/data/main/mlb.xlsx
+++ b/data/main/mlb.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ41" headerRowCount="1">
-  <autoFilter ref="A1:CQ41"/>
-  <tableColumns count="95">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CR68" headerRowCount="1">
+  <autoFilter ref="A1:CR68"/>
+  <tableColumns count="96">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -392,12 +392,13 @@
     <tableColumn id="87" name="unavailable_features"/>
     <tableColumn id="88" name="defensive_trend_gap"/>
     <tableColumn id="89" name="neutral_elo_rating_difference"/>
-    <tableColumn id="90" name="rest_disparity"/>
-    <tableColumn id="91" name="back_to_back_gap"/>
-    <tableColumn id="92" name="games_last_7_gap"/>
-    <tableColumn id="93" name="schedule_missingness"/>
-    <tableColumn id="94" name="market_residual_probability"/>
-    <tableColumn id="95" name="trade_candidate"/>
+    <tableColumn id="90" name="bullpen_weakness_gap"/>
+    <tableColumn id="91" name="rest_disparity"/>
+    <tableColumn id="92" name="back_to_back_gap"/>
+    <tableColumn id="93" name="games_last_7_gap"/>
+    <tableColumn id="94" name="schedule_missingness"/>
+    <tableColumn id="95" name="market_residual_probability"/>
+    <tableColumn id="96" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -754,19 +755,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$41)</f>
+        <f>COUNTA('Picks'!$A$2:$A$68)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$41,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$68,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$41,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$68,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$41,"settled",'Picks'!$V$2:$V$41,"win")+COUNTIFS('Picks'!$U$2:$U$41,"settled",'Picks'!$V$2:$V$41,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$68,"settled",'Picks'!$V$2:$V$68,"win")+COUNTIFS('Picks'!$U$2:$U$68,"settled",'Picks'!$V$2:$V$68,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +795,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$41,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$68,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$41,"&gt;0",'Picks'!$V$2:$V$41,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$41,"&gt;0",'Picks'!$V$2:$V$41,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$68,"&gt;0",'Picks'!$V$2:$V$68,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$68,"&gt;0",'Picks'!$V$2:$V$68,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$41,"&gt;0",'Picks'!$V$2:$V$41,"win")/(COUNTIFS('Picks'!$BX$2:$BX$41,"&gt;0",'Picks'!$V$2:$V$41,"win")+COUNTIFS('Picks'!$BX$2:$BX$41,"&gt;0",'Picks'!$V$2:$V$41,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$68,"&gt;0",'Picks'!$V$2:$V$68,"win")/(COUNTIFS('Picks'!$BX$2:$BX$68,"&gt;0",'Picks'!$V$2:$V$68,"win")+COUNTIFS('Picks'!$BX$2:$BX$68,"&gt;0",'Picks'!$V$2:$V$68,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$41)/SUM('Picks'!$BX$2:$BX$41),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$68)/SUM('Picks'!$BX$2:$BX$68),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +835,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$41)</f>
+        <f>SUM('Picks'!$BY$2:$BY$68)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$41,"&lt;&gt;",'Picks'!$AB$2:$AB$41),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$68,"&lt;&gt;",'Picks'!$AB$2:$AB$68),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$41,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$41,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$68,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$68,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$41,'Picks'!$AM$2:$AM$41,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$68,'Picks'!$AM$2:$AM$68,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +902,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$41,$A14,'Picks'!$U$2:$U$41,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$68,$A14,'Picks'!$U$2:$U$68,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$41,$A14,'Picks'!$U$2:$U$41,"settled",'Picks'!$V$2:$V$41,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$68,$A14,'Picks'!$U$2:$U$68,"settled",'Picks'!$V$2:$V$68,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$41,$A14,'Picks'!$U$2:$U$41,"settled",'Picks'!$V$2:$V$41,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$68,$A14,'Picks'!$U$2:$U$68,"settled",'Picks'!$V$2:$V$68,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +918,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$41,'Picks'!$H$2:$H$41,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$68,'Picks'!$H$2:$H$68,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$41,'Picks'!$H$2:$H$41,$A14,'Picks'!$U$2:$U$41,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$68,'Picks'!$H$2:$H$68,$A14,'Picks'!$U$2:$U$68,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +933,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$41,$A15,'Picks'!$U$2:$U$41,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$68,$A15,'Picks'!$U$2:$U$68,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$41,$A15,'Picks'!$U$2:$U$41,"settled",'Picks'!$V$2:$V$41,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$68,$A15,'Picks'!$U$2:$U$68,"settled",'Picks'!$V$2:$V$68,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$41,$A15,'Picks'!$U$2:$U$41,"settled",'Picks'!$V$2:$V$41,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$68,$A15,'Picks'!$U$2:$U$68,"settled",'Picks'!$V$2:$V$68,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +949,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$41,'Picks'!$H$2:$H$41,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$68,'Picks'!$H$2:$H$68,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$41,'Picks'!$H$2:$H$41,$A15,'Picks'!$U$2:$U$41,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$68,'Picks'!$H$2:$H$68,$A15,'Picks'!$U$2:$U$68,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +964,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$41,$A16,'Picks'!$U$2:$U$41,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$68,$A16,'Picks'!$U$2:$U$68,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$41,$A16,'Picks'!$U$2:$U$41,"settled",'Picks'!$V$2:$V$41,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$68,$A16,'Picks'!$U$2:$U$68,"settled",'Picks'!$V$2:$V$68,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$41,$A16,'Picks'!$U$2:$U$41,"settled",'Picks'!$V$2:$V$41,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$68,$A16,'Picks'!$U$2:$U$68,"settled",'Picks'!$V$2:$V$68,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +980,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$41,'Picks'!$H$2:$H$41,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$68,'Picks'!$H$2:$H$68,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$41,'Picks'!$H$2:$H$41,$A16,'Picks'!$U$2:$U$41,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$68,'Picks'!$H$2:$H$68,$A16,'Picks'!$U$2:$U$68,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ41"/>
+  <dimension ref="A1:CR68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1104,12 +1105,13 @@
     <col width="22" customWidth="1" min="87" max="87"/>
     <col width="21" customWidth="1" min="88" max="88"/>
     <col width="22" customWidth="1" min="89" max="89"/>
-    <col width="16" customWidth="1" min="90" max="90"/>
-    <col width="18" customWidth="1" min="91" max="91"/>
+    <col width="22" customWidth="1" min="90" max="90"/>
+    <col width="16" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
-    <col width="22" customWidth="1" min="93" max="93"/>
+    <col width="18" customWidth="1" min="93" max="93"/>
     <col width="22" customWidth="1" min="94" max="94"/>
-    <col width="17" customWidth="1" min="95" max="95"/>
+    <col width="22" customWidth="1" min="95" max="95"/>
+    <col width="17" customWidth="1" min="96" max="96"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1560,30 +1562,35 @@
       </c>
       <c r="CL1" s="23" t="inlineStr">
         <is>
+          <t>bullpen_weakness_gap</t>
+        </is>
+      </c>
+      <c r="CM1" s="23" t="inlineStr">
+        <is>
           <t>rest_disparity</t>
         </is>
       </c>
-      <c r="CM1" s="23" t="inlineStr">
+      <c r="CN1" s="23" t="inlineStr">
         <is>
           <t>back_to_back_gap</t>
         </is>
       </c>
-      <c r="CN1" s="23" t="inlineStr">
+      <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>games_last_7_gap</t>
         </is>
       </c>
-      <c r="CO1" s="23" t="inlineStr">
+      <c r="CP1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
         </is>
       </c>
-      <c r="CP1" s="23" t="inlineStr">
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>market_residual_probability</t>
         </is>
       </c>
-      <c r="CQ1" s="23" t="inlineStr">
+      <c r="CR1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
@@ -1884,7 +1891,8 @@
       <c r="CN2" s="24" t="n"/>
       <c r="CO2" s="24" t="n"/>
       <c r="CP2" s="24" t="n"/>
-      <c r="CQ2" s="24" t="inlineStr">
+      <c r="CQ2" s="24" t="n"/>
+      <c r="CR2" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -2185,7 +2193,8 @@
       <c r="CN3" s="24" t="n"/>
       <c r="CO3" s="24" t="n"/>
       <c r="CP3" s="24" t="n"/>
-      <c r="CQ3" s="24" t="inlineStr">
+      <c r="CQ3" s="24" t="n"/>
+      <c r="CR3" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -2486,7 +2495,8 @@
       <c r="CN4" s="24" t="n"/>
       <c r="CO4" s="24" t="n"/>
       <c r="CP4" s="24" t="n"/>
-      <c r="CQ4" s="24" t="inlineStr">
+      <c r="CQ4" s="24" t="n"/>
+      <c r="CR4" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2787,7 +2797,8 @@
       <c r="CN5" s="24" t="n"/>
       <c r="CO5" s="24" t="n"/>
       <c r="CP5" s="24" t="n"/>
-      <c r="CQ5" s="24" t="inlineStr">
+      <c r="CQ5" s="24" t="n"/>
+      <c r="CR5" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3088,7 +3099,8 @@
       <c r="CN6" s="24" t="n"/>
       <c r="CO6" s="24" t="n"/>
       <c r="CP6" s="24" t="n"/>
-      <c r="CQ6" s="24" t="inlineStr">
+      <c r="CQ6" s="24" t="n"/>
+      <c r="CR6" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3389,7 +3401,8 @@
       <c r="CN7" s="24" t="n"/>
       <c r="CO7" s="24" t="n"/>
       <c r="CP7" s="24" t="n"/>
-      <c r="CQ7" s="24" t="inlineStr">
+      <c r="CQ7" s="24" t="n"/>
+      <c r="CR7" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3690,7 +3703,8 @@
       <c r="CN8" s="24" t="n"/>
       <c r="CO8" s="24" t="n"/>
       <c r="CP8" s="24" t="n"/>
-      <c r="CQ8" s="24" t="inlineStr">
+      <c r="CQ8" s="24" t="n"/>
+      <c r="CR8" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3991,7 +4005,8 @@
       <c r="CN9" s="24" t="n"/>
       <c r="CO9" s="24" t="n"/>
       <c r="CP9" s="24" t="n"/>
-      <c r="CQ9" s="24" t="inlineStr">
+      <c r="CQ9" s="24" t="n"/>
+      <c r="CR9" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4292,7 +4307,8 @@
       <c r="CN10" s="24" t="n"/>
       <c r="CO10" s="24" t="n"/>
       <c r="CP10" s="24" t="n"/>
-      <c r="CQ10" s="24" t="inlineStr">
+      <c r="CQ10" s="24" t="n"/>
+      <c r="CR10" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4593,7 +4609,8 @@
       <c r="CN11" s="24" t="n"/>
       <c r="CO11" s="24" t="n"/>
       <c r="CP11" s="24" t="n"/>
-      <c r="CQ11" s="24" t="inlineStr">
+      <c r="CQ11" s="24" t="n"/>
+      <c r="CR11" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4905,12 +4922,13 @@
       <c r="CM12" s="24" t="n"/>
       <c r="CN12" s="24" t="n"/>
       <c r="CO12" s="24" t="n"/>
-      <c r="CP12" s="24" t="inlineStr">
+      <c r="CP12" s="24" t="n"/>
+      <c r="CQ12" s="24" t="inlineStr">
         <is>
           <t>0.625602</t>
         </is>
       </c>
-      <c r="CQ12" s="24" t="inlineStr">
+      <c r="CR12" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5211,7 +5229,8 @@
       <c r="CN13" s="24" t="n"/>
       <c r="CO13" s="24" t="n"/>
       <c r="CP13" s="24" t="n"/>
-      <c r="CQ13" s="24" t="inlineStr">
+      <c r="CQ13" s="24" t="n"/>
+      <c r="CR13" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5512,7 +5531,8 @@
       <c r="CN14" s="24" t="n"/>
       <c r="CO14" s="24" t="n"/>
       <c r="CP14" s="24" t="n"/>
-      <c r="CQ14" s="24" t="inlineStr">
+      <c r="CQ14" s="24" t="n"/>
+      <c r="CR14" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5813,7 +5833,8 @@
       <c r="CN15" s="24" t="n"/>
       <c r="CO15" s="24" t="n"/>
       <c r="CP15" s="24" t="n"/>
-      <c r="CQ15" s="24" t="inlineStr">
+      <c r="CQ15" s="24" t="n"/>
+      <c r="CR15" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -6114,7 +6135,8 @@
       <c r="CN16" s="24" t="n"/>
       <c r="CO16" s="24" t="n"/>
       <c r="CP16" s="24" t="n"/>
-      <c r="CQ16" s="24" t="inlineStr">
+      <c r="CQ16" s="24" t="n"/>
+      <c r="CR16" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -6415,7 +6437,8 @@
       <c r="CN17" s="24" t="n"/>
       <c r="CO17" s="24" t="n"/>
       <c r="CP17" s="24" t="n"/>
-      <c r="CQ17" s="24" t="inlineStr">
+      <c r="CQ17" s="24" t="n"/>
+      <c r="CR17" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -6716,7 +6739,8 @@
       <c r="CN18" s="24" t="n"/>
       <c r="CO18" s="24" t="n"/>
       <c r="CP18" s="24" t="n"/>
-      <c r="CQ18" s="24" t="inlineStr">
+      <c r="CQ18" s="24" t="n"/>
+      <c r="CR18" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -7017,7 +7041,8 @@
       <c r="CN19" s="24" t="n"/>
       <c r="CO19" s="24" t="n"/>
       <c r="CP19" s="24" t="n"/>
-      <c r="CQ19" s="24" t="inlineStr">
+      <c r="CQ19" s="24" t="n"/>
+      <c r="CR19" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -7318,7 +7343,8 @@
       <c r="CN20" s="24" t="n"/>
       <c r="CO20" s="24" t="n"/>
       <c r="CP20" s="24" t="n"/>
-      <c r="CQ20" s="24" t="inlineStr">
+      <c r="CQ20" s="24" t="n"/>
+      <c r="CR20" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -7619,7 +7645,8 @@
       <c r="CN21" s="24" t="n"/>
       <c r="CO21" s="24" t="n"/>
       <c r="CP21" s="24" t="n"/>
-      <c r="CQ21" s="24" t="inlineStr">
+      <c r="CQ21" s="24" t="n"/>
+      <c r="CR21" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -7920,7 +7947,8 @@
       <c r="CN22" s="24" t="n"/>
       <c r="CO22" s="24" t="n"/>
       <c r="CP22" s="24" t="n"/>
-      <c r="CQ22" s="24" t="inlineStr">
+      <c r="CQ22" s="24" t="n"/>
+      <c r="CR22" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -8221,7 +8249,8 @@
       <c r="CN23" s="24" t="n"/>
       <c r="CO23" s="24" t="n"/>
       <c r="CP23" s="24" t="n"/>
-      <c r="CQ23" s="24" t="inlineStr">
+      <c r="CQ23" s="24" t="n"/>
+      <c r="CR23" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -8522,7 +8551,8 @@
       <c r="CN24" s="24" t="n"/>
       <c r="CO24" s="24" t="n"/>
       <c r="CP24" s="24" t="n"/>
-      <c r="CQ24" s="24" t="inlineStr">
+      <c r="CQ24" s="24" t="n"/>
+      <c r="CR24" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -8823,7 +8853,8 @@
       <c r="CN25" s="24" t="n"/>
       <c r="CO25" s="24" t="n"/>
       <c r="CP25" s="24" t="n"/>
-      <c r="CQ25" s="24" t="inlineStr">
+      <c r="CQ25" s="24" t="n"/>
+      <c r="CR25" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -9124,7 +9155,8 @@
       <c r="CN26" s="24" t="n"/>
       <c r="CO26" s="24" t="n"/>
       <c r="CP26" s="24" t="n"/>
-      <c r="CQ26" s="24" t="inlineStr">
+      <c r="CQ26" s="24" t="n"/>
+      <c r="CR26" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -9436,12 +9468,13 @@
       <c r="CM27" s="24" t="n"/>
       <c r="CN27" s="24" t="n"/>
       <c r="CO27" s="24" t="n"/>
-      <c r="CP27" s="24" t="inlineStr">
+      <c r="CP27" s="24" t="n"/>
+      <c r="CQ27" s="24" t="inlineStr">
         <is>
           <t>0.648206</t>
         </is>
       </c>
-      <c r="CQ27" s="24" t="inlineStr">
+      <c r="CR27" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -9742,7 +9775,8 @@
       <c r="CN28" s="24" t="n"/>
       <c r="CO28" s="24" t="n"/>
       <c r="CP28" s="24" t="n"/>
-      <c r="CQ28" s="24" t="inlineStr">
+      <c r="CQ28" s="24" t="n"/>
+      <c r="CR28" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -10043,7 +10077,8 @@
       <c r="CN29" s="24" t="n"/>
       <c r="CO29" s="24" t="n"/>
       <c r="CP29" s="24" t="n"/>
-      <c r="CQ29" s="24" t="inlineStr">
+      <c r="CQ29" s="24" t="n"/>
+      <c r="CR29" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -10344,7 +10379,8 @@
       <c r="CN30" s="24" t="n"/>
       <c r="CO30" s="24" t="n"/>
       <c r="CP30" s="24" t="n"/>
-      <c r="CQ30" s="24" t="inlineStr">
+      <c r="CQ30" s="24" t="n"/>
+      <c r="CR30" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -10645,7 +10681,8 @@
       <c r="CN31" s="24" t="n"/>
       <c r="CO31" s="24" t="n"/>
       <c r="CP31" s="24" t="n"/>
-      <c r="CQ31" s="24" t="inlineStr">
+      <c r="CQ31" s="24" t="n"/>
+      <c r="CR31" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -10946,7 +10983,8 @@
       <c r="CN32" s="24" t="n"/>
       <c r="CO32" s="24" t="n"/>
       <c r="CP32" s="24" t="n"/>
-      <c r="CQ32" s="24" t="inlineStr">
+      <c r="CQ32" s="24" t="n"/>
+      <c r="CR32" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -11247,7 +11285,8 @@
       <c r="CN33" s="24" t="n"/>
       <c r="CO33" s="24" t="n"/>
       <c r="CP33" s="24" t="n"/>
-      <c r="CQ33" s="24" t="inlineStr">
+      <c r="CQ33" s="24" t="n"/>
+      <c r="CR33" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -11548,7 +11587,8 @@
       <c r="CN34" s="24" t="n"/>
       <c r="CO34" s="24" t="n"/>
       <c r="CP34" s="24" t="n"/>
-      <c r="CQ34" s="24" t="inlineStr">
+      <c r="CQ34" s="24" t="n"/>
+      <c r="CR34" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -11849,7 +11889,8 @@
       <c r="CN35" s="24" t="n"/>
       <c r="CO35" s="24" t="n"/>
       <c r="CP35" s="24" t="n"/>
-      <c r="CQ35" s="24" t="inlineStr">
+      <c r="CQ35" s="24" t="n"/>
+      <c r="CR35" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -12150,7 +12191,8 @@
       <c r="CN36" s="24" t="n"/>
       <c r="CO36" s="24" t="n"/>
       <c r="CP36" s="24" t="n"/>
-      <c r="CQ36" s="24" t="inlineStr">
+      <c r="CQ36" s="24" t="n"/>
+      <c r="CR36" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -12451,7 +12493,8 @@
       <c r="CN37" s="24" t="n"/>
       <c r="CO37" s="24" t="n"/>
       <c r="CP37" s="24" t="n"/>
-      <c r="CQ37" s="24" t="inlineStr">
+      <c r="CQ37" s="24" t="n"/>
+      <c r="CR37" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -12752,7 +12795,8 @@
       <c r="CN38" s="24" t="n"/>
       <c r="CO38" s="24" t="n"/>
       <c r="CP38" s="24" t="n"/>
-      <c r="CQ38" s="24" t="inlineStr">
+      <c r="CQ38" s="24" t="n"/>
+      <c r="CR38" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -13053,7 +13097,8 @@
       <c r="CN39" s="24" t="n"/>
       <c r="CO39" s="24" t="n"/>
       <c r="CP39" s="24" t="n"/>
-      <c r="CQ39" s="24" t="inlineStr">
+      <c r="CQ39" s="24" t="n"/>
+      <c r="CR39" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -13144,18 +13189,40 @@
       </c>
       <c r="U40" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V40" s="24" t="n"/>
-      <c r="W40" s="26" t="n"/>
-      <c r="X40" s="26" t="n"/>
-      <c r="Y40" s="25" t="n"/>
-      <c r="Z40" s="26" t="n"/>
-      <c r="AA40" s="28" t="n"/>
-      <c r="AB40" s="28" t="n"/>
-      <c r="AC40" s="30" t="n"/>
-      <c r="AD40" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V40" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W40" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X40" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y40" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z40" s="26" t="n">
+        <v>-174</v>
+      </c>
+      <c r="AA40" s="28" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="AB40" s="28" t="n">
+        <v>-3.6e-05</v>
+      </c>
+      <c r="AC40" s="30" t="n">
+        <v>0.8621</v>
+      </c>
+      <c r="AD40" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:15:15.052080Z</t>
+        </is>
+      </c>
       <c r="AE40" s="31" t="inlineStr">
         <is>
           <t>Measured Edge Margin: Trend Engine projected 4.26-4.48; raw selected-side p=0.6917, calibrated p=0.6258.</t>
@@ -13302,8 +13369,12 @@
       </c>
       <c r="BO40" s="28" t="n"/>
       <c r="BP40" s="25" t="n"/>
-      <c r="BQ40" s="27" t="n"/>
-      <c r="BR40" s="28" t="n"/>
+      <c r="BQ40" s="27" t="n">
+        <v>1.574713</v>
+      </c>
+      <c r="BR40" s="28" t="n">
+        <v>0.635</v>
+      </c>
       <c r="BS40" s="28" t="n"/>
       <c r="BT40" s="28" t="n"/>
       <c r="BU40" s="25" t="n"/>
@@ -13328,7 +13399,8 @@
       <c r="CN40" s="24" t="n"/>
       <c r="CO40" s="24" t="n"/>
       <c r="CP40" s="24" t="n"/>
-      <c r="CQ40" s="24" t="inlineStr">
+      <c r="CQ40" s="24" t="n"/>
+      <c r="CR40" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -13419,18 +13491,40 @@
       </c>
       <c r="U41" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V41" s="24" t="n"/>
-      <c r="W41" s="26" t="n"/>
-      <c r="X41" s="26" t="n"/>
-      <c r="Y41" s="25" t="n"/>
-      <c r="Z41" s="26" t="n"/>
-      <c r="AA41" s="28" t="n"/>
-      <c r="AB41" s="28" t="n"/>
-      <c r="AC41" s="30" t="n"/>
-      <c r="AD41" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V41" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W41" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X41" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y41" s="25" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z41" s="26" t="n">
+        <v>115</v>
+      </c>
+      <c r="AA41" s="28" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="AB41" s="28" t="n">
+        <v>-0.000116</v>
+      </c>
+      <c r="AC41" s="30" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD41" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:15:15.302651Z</t>
+        </is>
+      </c>
       <c r="AE41" s="31" t="inlineStr">
         <is>
           <t>Measured Edge Totals: Trend Engine projected 4.26-4.48; raw selected-side p=0.5085, calibrated p=0.5109.</t>
@@ -13577,8 +13671,12 @@
       </c>
       <c r="BO41" s="28" t="n"/>
       <c r="BP41" s="25" t="n"/>
-      <c r="BQ41" s="27" t="n"/>
-      <c r="BR41" s="28" t="n"/>
+      <c r="BQ41" s="27" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BR41" s="28" t="n">
+        <v>0.465</v>
+      </c>
       <c r="BS41" s="28" t="n"/>
       <c r="BT41" s="28" t="n"/>
       <c r="BU41" s="25" t="n"/>
@@ -13603,7 +13701,7486 @@
       <c r="CN41" s="24" t="n"/>
       <c r="CO41" s="24" t="n"/>
       <c r="CP41" s="24" t="n"/>
-      <c r="CQ41" s="24" t="inlineStr">
+      <c r="CQ41" s="24" t="n"/>
+      <c r="CR41" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="36" customHeight="1">
+      <c r="A42" s="24" t="inlineStr">
+        <is>
+          <t>46630ec118fc4a81</t>
+        </is>
+      </c>
+      <c r="B42" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:42.290404Z</t>
+        </is>
+      </c>
+      <c r="C42" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T20:40:00-0400</t>
+        </is>
+      </c>
+      <c r="D42" s="24" t="inlineStr">
+        <is>
+          <t>401816396</t>
+        </is>
+      </c>
+      <c r="E42" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F42" s="24" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays</t>
+        </is>
+      </c>
+      <c r="G42" s="24" t="inlineStr">
+        <is>
+          <t>Colorado Rockies</t>
+        </is>
+      </c>
+      <c r="H42" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I42" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J42" s="25" t="n"/>
+      <c r="K42" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L42" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="M42" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="N42" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="O42" s="28" t="n">
+        <v>0.651997</v>
+      </c>
+      <c r="P42" s="28" t="n"/>
+      <c r="Q42" s="28" t="n">
+        <v>0.07216500000000001</v>
+      </c>
+      <c r="R42" s="26" t="n">
+        <v>57</v>
+      </c>
+      <c r="S42" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T42" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="U42" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V42" s="24" t="n"/>
+      <c r="W42" s="26" t="n"/>
+      <c r="X42" s="26" t="n"/>
+      <c r="Y42" s="25" t="n"/>
+      <c r="Z42" s="26" t="n"/>
+      <c r="AA42" s="28" t="n"/>
+      <c r="AB42" s="28" t="n"/>
+      <c r="AC42" s="30" t="n"/>
+      <c r="AD42" s="24" t="n"/>
+      <c r="AE42" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.6242; executable ask 0.5800 (aec-mlb-tb-col-2026-08-04); model edge vs ask +0.0720.</t>
+        </is>
+      </c>
+      <c r="AF42" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG42" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH42" s="24" t="n"/>
+      <c r="AI42" s="31" t="n"/>
+      <c r="AJ42" s="31" t="n"/>
+      <c r="AK42" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL42" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM42" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN42" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO42" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP42" s="24" t="inlineStr">
+        <is>
+          <t>mlb-tb</t>
+        </is>
+      </c>
+      <c r="AQ42" s="24" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays</t>
+        </is>
+      </c>
+      <c r="AR42" s="24" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays</t>
+        </is>
+      </c>
+      <c r="AS42" s="24" t="inlineStr">
+        <is>
+          <t>mlb-col</t>
+        </is>
+      </c>
+      <c r="AT42" s="24" t="inlineStr">
+        <is>
+          <t>Colorado Rockies</t>
+        </is>
+      </c>
+      <c r="AU42" s="24" t="inlineStr">
+        <is>
+          <t>Colorado Rockies</t>
+        </is>
+      </c>
+      <c r="AV42" s="24" t="n"/>
+      <c r="AW42" s="24" t="n"/>
+      <c r="AX42" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY42" s="24" t="n"/>
+      <c r="AZ42" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA42" s="24" t="inlineStr">
+        <is>
+          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+        </is>
+      </c>
+      <c r="BB42" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC42" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="BD42" s="24" t="inlineStr">
+        <is>
+          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+        </is>
+      </c>
+      <c r="BE42" s="24" t="inlineStr">
+        <is>
+          <t>aa1550043d30dddf</t>
+        </is>
+      </c>
+      <c r="BF42" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG42" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v7</t>
+        </is>
+      </c>
+      <c r="BH42" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:24.205568Z</t>
+        </is>
+      </c>
+      <c r="BI42" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ42" s="25" t="n"/>
+      <c r="BK42" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="BL42" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BM42" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="BN42" s="28" t="n">
+        <v>0.577114</v>
+      </c>
+      <c r="BO42" s="28" t="n"/>
+      <c r="BP42" s="25" t="n"/>
+      <c r="BQ42" s="27" t="n"/>
+      <c r="BR42" s="28" t="n"/>
+      <c r="BS42" s="28" t="n"/>
+      <c r="BT42" s="28" t="n"/>
+      <c r="BU42" s="25" t="n"/>
+      <c r="BV42" s="29" t="n"/>
+      <c r="BW42" s="24" t="n"/>
+      <c r="BX42" s="30" t="n"/>
+      <c r="BY42" s="27" t="n"/>
+      <c r="BZ42" s="24" t="n"/>
+      <c r="CA42" s="31" t="n"/>
+      <c r="CB42" s="24" t="n"/>
+      <c r="CC42" s="24" t="inlineStr">
+        <is>
+          <t>0.3759904491</t>
+        </is>
+      </c>
+      <c r="CD42" s="24" t="inlineStr">
+        <is>
+          <t>1.914708</t>
+        </is>
+      </c>
+      <c r="CE42" s="24" t="inlineStr">
+        <is>
+          <t>1.193</t>
+        </is>
+      </c>
+      <c r="CF42" s="24" t="inlineStr">
+        <is>
+          <t>1.0086</t>
+        </is>
+      </c>
+      <c r="CG42" s="24" t="inlineStr">
+        <is>
+          <t>-0.4</t>
+        </is>
+      </c>
+      <c r="CH42" s="24" t="n"/>
+      <c r="CI42" s="24" t="n"/>
+      <c r="CJ42" s="24" t="inlineStr">
+        <is>
+          <t>0.686906</t>
+        </is>
+      </c>
+      <c r="CK42" s="24" t="n"/>
+      <c r="CL42" s="24" t="inlineStr">
+        <is>
+          <t>0.056981</t>
+        </is>
+      </c>
+      <c r="CM42" s="24" t="n"/>
+      <c r="CN42" s="24" t="n"/>
+      <c r="CO42" s="24" t="n"/>
+      <c r="CP42" s="24" t="n"/>
+      <c r="CQ42" s="24" t="inlineStr">
+        <is>
+          <t>0.651997</t>
+        </is>
+      </c>
+      <c r="CR42" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="36" customHeight="1">
+      <c r="A43" s="24" t="inlineStr">
+        <is>
+          <t>7bcb1e9699d34e7c</t>
+        </is>
+      </c>
+      <c r="B43" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="C43" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:40Z</t>
+        </is>
+      </c>
+      <c r="D43" s="24" t="inlineStr">
+        <is>
+          <t>401816385</t>
+        </is>
+      </c>
+      <c r="E43" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F43" s="24" t="inlineStr">
+        <is>
+          <t>Athletics</t>
+        </is>
+      </c>
+      <c r="G43" s="24" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds</t>
+        </is>
+      </c>
+      <c r="H43" s="24" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="I43" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J43" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K43" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L43" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="M43" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="N43" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="O43" s="28" t="n">
+        <v>0.559361</v>
+      </c>
+      <c r="P43" s="28" t="n">
+        <v>0.042131</v>
+      </c>
+      <c r="Q43" s="28" t="n">
+        <v>-0.060411</v>
+      </c>
+      <c r="R43" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T43" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v2</t>
+        </is>
+      </c>
+      <c r="U43" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V43" s="24" t="n"/>
+      <c r="W43" s="26" t="n"/>
+      <c r="X43" s="26" t="n"/>
+      <c r="Y43" s="25" t="n"/>
+      <c r="Z43" s="26" t="n"/>
+      <c r="AA43" s="28" t="n"/>
+      <c r="AB43" s="28" t="n"/>
+      <c r="AC43" s="30" t="n"/>
+      <c r="AD43" s="24" t="n"/>
+      <c r="AE43" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Margin: Trend Engine projected 3.87-4.68; raw selected-side p=0.5904, calibrated p=0.5594.</t>
+        </is>
+      </c>
+      <c r="AF43" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG43" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH43" s="24" t="n"/>
+      <c r="AI43" s="31" t="n"/>
+      <c r="AJ43" s="31" t="n"/>
+      <c r="AK43" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL43" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM43" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN43" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO43" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP43" s="24" t="inlineStr">
+        <is>
+          <t>mlb-ath</t>
+        </is>
+      </c>
+      <c r="AQ43" s="24" t="inlineStr">
+        <is>
+          <t>Athletics</t>
+        </is>
+      </c>
+      <c r="AR43" s="24" t="inlineStr">
+        <is>
+          <t>Athletics</t>
+        </is>
+      </c>
+      <c r="AS43" s="24" t="inlineStr">
+        <is>
+          <t>mlb-cin</t>
+        </is>
+      </c>
+      <c r="AT43" s="24" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds</t>
+        </is>
+      </c>
+      <c r="AU43" s="24" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds</t>
+        </is>
+      </c>
+      <c r="AV43" s="24" t="n"/>
+      <c r="AW43" s="24" t="n"/>
+      <c r="AX43" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY43" s="24" t="n"/>
+      <c r="AZ43" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA43" s="24" t="inlineStr">
+        <is>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+        </is>
+      </c>
+      <c r="BB43" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC43" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v2</t>
+        </is>
+      </c>
+      <c r="BD43" s="24" t="inlineStr">
+        <is>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+        </is>
+      </c>
+      <c r="BE43" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF43" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG43" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH43" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="BI43" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ43" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK43" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="BL43" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="BM43" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="BN43" s="28" t="n">
+        <v>0.616915</v>
+      </c>
+      <c r="BO43" s="28" t="n"/>
+      <c r="BP43" s="25" t="n"/>
+      <c r="BQ43" s="27" t="n"/>
+      <c r="BR43" s="28" t="n"/>
+      <c r="BS43" s="28" t="n"/>
+      <c r="BT43" s="28" t="n"/>
+      <c r="BU43" s="25" t="n"/>
+      <c r="BV43" s="29" t="n"/>
+      <c r="BW43" s="24" t="n"/>
+      <c r="BX43" s="30" t="n"/>
+      <c r="BY43" s="27" t="n"/>
+      <c r="BZ43" s="24" t="n"/>
+      <c r="CA43" s="31" t="n"/>
+      <c r="CB43" s="24" t="n"/>
+      <c r="CC43" s="24" t="n"/>
+      <c r="CD43" s="24" t="n"/>
+      <c r="CE43" s="24" t="n"/>
+      <c r="CF43" s="24" t="n"/>
+      <c r="CG43" s="24" t="n"/>
+      <c r="CH43" s="24" t="n"/>
+      <c r="CI43" s="24" t="n"/>
+      <c r="CJ43" s="24" t="n"/>
+      <c r="CK43" s="24" t="n"/>
+      <c r="CL43" s="24" t="n"/>
+      <c r="CM43" s="24" t="n"/>
+      <c r="CN43" s="24" t="n"/>
+      <c r="CO43" s="24" t="n"/>
+      <c r="CP43" s="24" t="n"/>
+      <c r="CQ43" s="24" t="n"/>
+      <c r="CR43" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="36" customHeight="1">
+      <c r="A44" s="24" t="inlineStr">
+        <is>
+          <t>33826a4332194433</t>
+        </is>
+      </c>
+      <c r="B44" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="C44" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:40Z</t>
+        </is>
+      </c>
+      <c r="D44" s="24" t="inlineStr">
+        <is>
+          <t>401816385</t>
+        </is>
+      </c>
+      <c r="E44" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F44" s="24" t="inlineStr">
+        <is>
+          <t>Athletics</t>
+        </is>
+      </c>
+      <c r="G44" s="24" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds</t>
+        </is>
+      </c>
+      <c r="H44" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I44" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J44" s="25" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K44" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L44" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="M44" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="N44" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="O44" s="28" t="n">
+        <v>0.5548650000000001</v>
+      </c>
+      <c r="P44" s="28" t="n">
+        <v>0.042131</v>
+      </c>
+      <c r="Q44" s="28" t="n">
+        <v>0.024349</v>
+      </c>
+      <c r="R44" s="26" t="n">
+        <v>38</v>
+      </c>
+      <c r="S44" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T44" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v2</t>
+        </is>
+      </c>
+      <c r="U44" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V44" s="24" t="n"/>
+      <c r="W44" s="26" t="n"/>
+      <c r="X44" s="26" t="n"/>
+      <c r="Y44" s="25" t="n"/>
+      <c r="Z44" s="26" t="n"/>
+      <c r="AA44" s="28" t="n"/>
+      <c r="AB44" s="28" t="n"/>
+      <c r="AC44" s="30" t="n"/>
+      <c r="AD44" s="24" t="n"/>
+      <c r="AE44" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Totals: Trend Engine projected 3.87-4.68; raw selected-side p=0.6373, calibrated p=0.5549.</t>
+        </is>
+      </c>
+      <c r="AF44" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG44" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH44" s="24" t="n"/>
+      <c r="AI44" s="31" t="n"/>
+      <c r="AJ44" s="31" t="n"/>
+      <c r="AK44" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL44" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM44" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN44" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO44" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP44" s="24" t="inlineStr">
+        <is>
+          <t>mlb-ath</t>
+        </is>
+      </c>
+      <c r="AQ44" s="24" t="inlineStr">
+        <is>
+          <t>Athletics</t>
+        </is>
+      </c>
+      <c r="AR44" s="24" t="inlineStr">
+        <is>
+          <t>Athletics</t>
+        </is>
+      </c>
+      <c r="AS44" s="24" t="inlineStr">
+        <is>
+          <t>mlb-cin</t>
+        </is>
+      </c>
+      <c r="AT44" s="24" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds</t>
+        </is>
+      </c>
+      <c r="AU44" s="24" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds</t>
+        </is>
+      </c>
+      <c r="AV44" s="24" t="n"/>
+      <c r="AW44" s="24" t="n"/>
+      <c r="AX44" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY44" s="24" t="n"/>
+      <c r="AZ44" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA44" s="24" t="inlineStr">
+        <is>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+        </is>
+      </c>
+      <c r="BB44" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC44" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v2</t>
+        </is>
+      </c>
+      <c r="BD44" s="24" t="inlineStr">
+        <is>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+        </is>
+      </c>
+      <c r="BE44" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF44" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG44" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH44" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="BI44" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ44" s="25" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BK44" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="BL44" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BM44" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="BN44" s="28" t="n">
+        <v>0.527363</v>
+      </c>
+      <c r="BO44" s="28" t="n"/>
+      <c r="BP44" s="25" t="n"/>
+      <c r="BQ44" s="27" t="n"/>
+      <c r="BR44" s="28" t="n"/>
+      <c r="BS44" s="28" t="n"/>
+      <c r="BT44" s="28" t="n"/>
+      <c r="BU44" s="25" t="n"/>
+      <c r="BV44" s="29" t="n"/>
+      <c r="BW44" s="24" t="n"/>
+      <c r="BX44" s="30" t="n"/>
+      <c r="BY44" s="27" t="n"/>
+      <c r="BZ44" s="24" t="n"/>
+      <c r="CA44" s="31" t="n"/>
+      <c r="CB44" s="24" t="n"/>
+      <c r="CC44" s="24" t="n"/>
+      <c r="CD44" s="24" t="n"/>
+      <c r="CE44" s="24" t="n"/>
+      <c r="CF44" s="24" t="n"/>
+      <c r="CG44" s="24" t="n"/>
+      <c r="CH44" s="24" t="n"/>
+      <c r="CI44" s="24" t="n"/>
+      <c r="CJ44" s="24" t="n"/>
+      <c r="CK44" s="24" t="n"/>
+      <c r="CL44" s="24" t="n"/>
+      <c r="CM44" s="24" t="n"/>
+      <c r="CN44" s="24" t="n"/>
+      <c r="CO44" s="24" t="n"/>
+      <c r="CP44" s="24" t="n"/>
+      <c r="CQ44" s="24" t="n"/>
+      <c r="CR44" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="36" customHeight="1">
+      <c r="A45" s="24" t="inlineStr">
+        <is>
+          <t>af4975d4ff6c4b78</t>
+        </is>
+      </c>
+      <c r="B45" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="C45" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:40Z</t>
+        </is>
+      </c>
+      <c r="D45" s="24" t="inlineStr">
+        <is>
+          <t>401816388</t>
+        </is>
+      </c>
+      <c r="E45" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F45" s="24" t="inlineStr">
+        <is>
+          <t>New York Mets</t>
+        </is>
+      </c>
+      <c r="G45" s="24" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="H45" s="24" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="I45" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J45" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K45" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L45" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="M45" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="N45" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="O45" s="28" t="n">
+        <v>0.602336</v>
+      </c>
+      <c r="P45" s="28" t="n">
+        <v>0.042131</v>
+      </c>
+      <c r="Q45" s="28" t="n">
+        <v>-0.017436</v>
+      </c>
+      <c r="R45" s="26" t="n">
+        <v>17</v>
+      </c>
+      <c r="S45" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T45" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v2</t>
+        </is>
+      </c>
+      <c r="U45" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V45" s="24" t="n"/>
+      <c r="W45" s="26" t="n"/>
+      <c r="X45" s="26" t="n"/>
+      <c r="Y45" s="25" t="n"/>
+      <c r="Z45" s="26" t="n"/>
+      <c r="AA45" s="28" t="n"/>
+      <c r="AB45" s="28" t="n"/>
+      <c r="AC45" s="30" t="n"/>
+      <c r="AD45" s="24" t="n"/>
+      <c r="AE45" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Margin: Trend Engine projected 4.10-4.32; raw selected-side p=0.6559, calibrated p=0.6023.</t>
+        </is>
+      </c>
+      <c r="AF45" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG45" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH45" s="24" t="n"/>
+      <c r="AI45" s="31" t="n"/>
+      <c r="AJ45" s="31" t="n"/>
+      <c r="AK45" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL45" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM45" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN45" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO45" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP45" s="24" t="inlineStr">
+        <is>
+          <t>mlb-nym</t>
+        </is>
+      </c>
+      <c r="AQ45" s="24" t="inlineStr">
+        <is>
+          <t>New York Mets</t>
+        </is>
+      </c>
+      <c r="AR45" s="24" t="inlineStr">
+        <is>
+          <t>New York Mets</t>
+        </is>
+      </c>
+      <c r="AS45" s="24" t="inlineStr">
+        <is>
+          <t>mlb-cle</t>
+        </is>
+      </c>
+      <c r="AT45" s="24" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="AU45" s="24" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="AV45" s="24" t="n"/>
+      <c r="AW45" s="24" t="n"/>
+      <c r="AX45" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY45" s="24" t="n"/>
+      <c r="AZ45" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA45" s="24" t="inlineStr">
+        <is>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+        </is>
+      </c>
+      <c r="BB45" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC45" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v2</t>
+        </is>
+      </c>
+      <c r="BD45" s="24" t="inlineStr">
+        <is>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+        </is>
+      </c>
+      <c r="BE45" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF45" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG45" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH45" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="BI45" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ45" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK45" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="BL45" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="BM45" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="BN45" s="28" t="n">
+        <v>0.616915</v>
+      </c>
+      <c r="BO45" s="28" t="n"/>
+      <c r="BP45" s="25" t="n"/>
+      <c r="BQ45" s="27" t="n"/>
+      <c r="BR45" s="28" t="n"/>
+      <c r="BS45" s="28" t="n"/>
+      <c r="BT45" s="28" t="n"/>
+      <c r="BU45" s="25" t="n"/>
+      <c r="BV45" s="29" t="n"/>
+      <c r="BW45" s="24" t="n"/>
+      <c r="BX45" s="30" t="n"/>
+      <c r="BY45" s="27" t="n"/>
+      <c r="BZ45" s="24" t="n"/>
+      <c r="CA45" s="31" t="n"/>
+      <c r="CB45" s="24" t="n"/>
+      <c r="CC45" s="24" t="n"/>
+      <c r="CD45" s="24" t="n"/>
+      <c r="CE45" s="24" t="n"/>
+      <c r="CF45" s="24" t="n"/>
+      <c r="CG45" s="24" t="n"/>
+      <c r="CH45" s="24" t="n"/>
+      <c r="CI45" s="24" t="n"/>
+      <c r="CJ45" s="24" t="n"/>
+      <c r="CK45" s="24" t="n"/>
+      <c r="CL45" s="24" t="n"/>
+      <c r="CM45" s="24" t="n"/>
+      <c r="CN45" s="24" t="n"/>
+      <c r="CO45" s="24" t="n"/>
+      <c r="CP45" s="24" t="n"/>
+      <c r="CQ45" s="24" t="n"/>
+      <c r="CR45" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="36" customHeight="1">
+      <c r="A46" s="24" t="inlineStr">
+        <is>
+          <t>342b4720b837407b</t>
+        </is>
+      </c>
+      <c r="B46" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="C46" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:40Z</t>
+        </is>
+      </c>
+      <c r="D46" s="24" t="inlineStr">
+        <is>
+          <t>401816388</t>
+        </is>
+      </c>
+      <c r="E46" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F46" s="24" t="inlineStr">
+        <is>
+          <t>New York Mets</t>
+        </is>
+      </c>
+      <c r="G46" s="24" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="H46" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I46" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J46" s="25" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="K46" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L46" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="M46" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="N46" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="O46" s="28" t="n">
+        <v>0.523634</v>
+      </c>
+      <c r="P46" s="28" t="n">
+        <v>0.042131</v>
+      </c>
+      <c r="Q46" s="28" t="n">
+        <v>0.01383</v>
+      </c>
+      <c r="R46" s="26" t="n">
+        <v>33</v>
+      </c>
+      <c r="S46" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T46" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v2</t>
+        </is>
+      </c>
+      <c r="U46" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V46" s="24" t="n"/>
+      <c r="W46" s="26" t="n"/>
+      <c r="X46" s="26" t="n"/>
+      <c r="Y46" s="25" t="n"/>
+      <c r="Z46" s="26" t="n"/>
+      <c r="AA46" s="28" t="n"/>
+      <c r="AB46" s="28" t="n"/>
+      <c r="AC46" s="30" t="n"/>
+      <c r="AD46" s="24" t="n"/>
+      <c r="AE46" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Totals: Trend Engine projected 4.10-4.32; raw selected-side p=0.5459, calibrated p=0.5236.</t>
+        </is>
+      </c>
+      <c r="AF46" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG46" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH46" s="24" t="n"/>
+      <c r="AI46" s="31" t="n"/>
+      <c r="AJ46" s="31" t="n"/>
+      <c r="AK46" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL46" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM46" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN46" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO46" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP46" s="24" t="inlineStr">
+        <is>
+          <t>mlb-nym</t>
+        </is>
+      </c>
+      <c r="AQ46" s="24" t="inlineStr">
+        <is>
+          <t>New York Mets</t>
+        </is>
+      </c>
+      <c r="AR46" s="24" t="inlineStr">
+        <is>
+          <t>New York Mets</t>
+        </is>
+      </c>
+      <c r="AS46" s="24" t="inlineStr">
+        <is>
+          <t>mlb-cle</t>
+        </is>
+      </c>
+      <c r="AT46" s="24" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="AU46" s="24" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="AV46" s="24" t="n"/>
+      <c r="AW46" s="24" t="n"/>
+      <c r="AX46" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY46" s="24" t="n"/>
+      <c r="AZ46" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA46" s="24" t="inlineStr">
+        <is>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+        </is>
+      </c>
+      <c r="BB46" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC46" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v2</t>
+        </is>
+      </c>
+      <c r="BD46" s="24" t="inlineStr">
+        <is>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+        </is>
+      </c>
+      <c r="BE46" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF46" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG46" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH46" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="BI46" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ46" s="25" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BK46" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="BL46" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="BM46" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="BN46" s="28" t="n">
+        <v>0.507463</v>
+      </c>
+      <c r="BO46" s="28" t="n"/>
+      <c r="BP46" s="25" t="n"/>
+      <c r="BQ46" s="27" t="n"/>
+      <c r="BR46" s="28" t="n"/>
+      <c r="BS46" s="28" t="n"/>
+      <c r="BT46" s="28" t="n"/>
+      <c r="BU46" s="25" t="n"/>
+      <c r="BV46" s="29" t="n"/>
+      <c r="BW46" s="24" t="n"/>
+      <c r="BX46" s="30" t="n"/>
+      <c r="BY46" s="27" t="n"/>
+      <c r="BZ46" s="24" t="n"/>
+      <c r="CA46" s="31" t="n"/>
+      <c r="CB46" s="24" t="n"/>
+      <c r="CC46" s="24" t="n"/>
+      <c r="CD46" s="24" t="n"/>
+      <c r="CE46" s="24" t="n"/>
+      <c r="CF46" s="24" t="n"/>
+      <c r="CG46" s="24" t="n"/>
+      <c r="CH46" s="24" t="n"/>
+      <c r="CI46" s="24" t="n"/>
+      <c r="CJ46" s="24" t="n"/>
+      <c r="CK46" s="24" t="n"/>
+      <c r="CL46" s="24" t="n"/>
+      <c r="CM46" s="24" t="n"/>
+      <c r="CN46" s="24" t="n"/>
+      <c r="CO46" s="24" t="n"/>
+      <c r="CP46" s="24" t="n"/>
+      <c r="CQ46" s="24" t="n"/>
+      <c r="CR46" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="36" customHeight="1">
+      <c r="A47" s="24" t="inlineStr">
+        <is>
+          <t>164e21d243c84d21</t>
+        </is>
+      </c>
+      <c r="B47" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="C47" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:40Z</t>
+        </is>
+      </c>
+      <c r="D47" s="24" t="inlineStr">
+        <is>
+          <t>401816390</t>
+        </is>
+      </c>
+      <c r="E47" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F47" s="24" t="inlineStr">
+        <is>
+          <t>Washington Nationals</t>
+        </is>
+      </c>
+      <c r="G47" s="24" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies</t>
+        </is>
+      </c>
+      <c r="H47" s="24" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="I47" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J47" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K47" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L47" s="26" t="n">
+        <v>111</v>
+      </c>
+      <c r="M47" s="27" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="N47" s="28" t="n">
+        <v>0.473934</v>
+      </c>
+      <c r="O47" s="28" t="n">
+        <v>0.537481</v>
+      </c>
+      <c r="P47" s="28" t="n">
+        <v>0.042131</v>
+      </c>
+      <c r="Q47" s="28" t="n">
+        <v>0.06354700000000001</v>
+      </c>
+      <c r="R47" s="26" t="n">
+        <v>57</v>
+      </c>
+      <c r="S47" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T47" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v2</t>
+        </is>
+      </c>
+      <c r="U47" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V47" s="24" t="n"/>
+      <c r="W47" s="26" t="n"/>
+      <c r="X47" s="26" t="n"/>
+      <c r="Y47" s="25" t="n"/>
+      <c r="Z47" s="26" t="n"/>
+      <c r="AA47" s="28" t="n"/>
+      <c r="AB47" s="28" t="n"/>
+      <c r="AC47" s="30" t="n"/>
+      <c r="AD47" s="24" t="n"/>
+      <c r="AE47" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Margin: Trend Engine projected 3.92-5.03; raw selected-side p=0.5571, calibrated p=0.5375.</t>
+        </is>
+      </c>
+      <c r="AF47" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG47" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH47" s="24" t="n"/>
+      <c r="AI47" s="31" t="n"/>
+      <c r="AJ47" s="31" t="n"/>
+      <c r="AK47" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL47" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM47" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN47" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO47" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP47" s="24" t="inlineStr">
+        <is>
+          <t>mlb-wsh</t>
+        </is>
+      </c>
+      <c r="AQ47" s="24" t="inlineStr">
+        <is>
+          <t>Washington Nationals</t>
+        </is>
+      </c>
+      <c r="AR47" s="24" t="inlineStr">
+        <is>
+          <t>Washington Nationals</t>
+        </is>
+      </c>
+      <c r="AS47" s="24" t="inlineStr">
+        <is>
+          <t>mlb-phi</t>
+        </is>
+      </c>
+      <c r="AT47" s="24" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies</t>
+        </is>
+      </c>
+      <c r="AU47" s="24" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies</t>
+        </is>
+      </c>
+      <c r="AV47" s="24" t="n"/>
+      <c r="AW47" s="24" t="n"/>
+      <c r="AX47" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY47" s="24" t="n"/>
+      <c r="AZ47" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA47" s="24" t="inlineStr">
+        <is>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+        </is>
+      </c>
+      <c r="BB47" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC47" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v2</t>
+        </is>
+      </c>
+      <c r="BD47" s="24" t="inlineStr">
+        <is>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+        </is>
+      </c>
+      <c r="BE47" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF47" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG47" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH47" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="BI47" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ47" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK47" s="26" t="n">
+        <v>111</v>
+      </c>
+      <c r="BL47" s="27" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BM47" s="28" t="n">
+        <v>0.473934</v>
+      </c>
+      <c r="BN47" s="28" t="n">
+        <v>0.472637</v>
+      </c>
+      <c r="BO47" s="28" t="n"/>
+      <c r="BP47" s="25" t="n"/>
+      <c r="BQ47" s="27" t="n"/>
+      <c r="BR47" s="28" t="n"/>
+      <c r="BS47" s="28" t="n"/>
+      <c r="BT47" s="28" t="n"/>
+      <c r="BU47" s="25" t="n"/>
+      <c r="BV47" s="29" t="n"/>
+      <c r="BW47" s="24" t="n"/>
+      <c r="BX47" s="30" t="n"/>
+      <c r="BY47" s="27" t="n"/>
+      <c r="BZ47" s="24" t="n"/>
+      <c r="CA47" s="31" t="n"/>
+      <c r="CB47" s="24" t="n"/>
+      <c r="CC47" s="24" t="n"/>
+      <c r="CD47" s="24" t="n"/>
+      <c r="CE47" s="24" t="n"/>
+      <c r="CF47" s="24" t="n"/>
+      <c r="CG47" s="24" t="n"/>
+      <c r="CH47" s="24" t="n"/>
+      <c r="CI47" s="24" t="n"/>
+      <c r="CJ47" s="24" t="n"/>
+      <c r="CK47" s="24" t="n"/>
+      <c r="CL47" s="24" t="n"/>
+      <c r="CM47" s="24" t="n"/>
+      <c r="CN47" s="24" t="n"/>
+      <c r="CO47" s="24" t="n"/>
+      <c r="CP47" s="24" t="n"/>
+      <c r="CQ47" s="24" t="n"/>
+      <c r="CR47" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="36" customHeight="1">
+      <c r="A48" s="24" t="inlineStr">
+        <is>
+          <t>823c22f90c7c4b5d</t>
+        </is>
+      </c>
+      <c r="B48" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="C48" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:40Z</t>
+        </is>
+      </c>
+      <c r="D48" s="24" t="inlineStr">
+        <is>
+          <t>401816390</t>
+        </is>
+      </c>
+      <c r="E48" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F48" s="24" t="inlineStr">
+        <is>
+          <t>Washington Nationals</t>
+        </is>
+      </c>
+      <c r="G48" s="24" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies</t>
+        </is>
+      </c>
+      <c r="H48" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I48" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J48" s="25" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K48" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L48" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="M48" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="N48" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="O48" s="28" t="n">
+        <v>0.511111</v>
+      </c>
+      <c r="P48" s="28" t="n">
+        <v>0.042131</v>
+      </c>
+      <c r="Q48" s="28" t="n">
+        <v>-0.019405</v>
+      </c>
+      <c r="R48" s="26" t="n">
+        <v>17</v>
+      </c>
+      <c r="S48" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T48" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v2</t>
+        </is>
+      </c>
+      <c r="U48" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V48" s="24" t="n"/>
+      <c r="W48" s="26" t="n"/>
+      <c r="X48" s="26" t="n"/>
+      <c r="Y48" s="25" t="n"/>
+      <c r="Z48" s="26" t="n"/>
+      <c r="AA48" s="28" t="n"/>
+      <c r="AB48" s="28" t="n"/>
+      <c r="AC48" s="30" t="n"/>
+      <c r="AD48" s="24" t="n"/>
+      <c r="AE48" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Totals: Trend Engine projected 3.92-5.03; raw selected-side p=0.5092, calibrated p=0.5111.</t>
+        </is>
+      </c>
+      <c r="AF48" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG48" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH48" s="24" t="n"/>
+      <c r="AI48" s="31" t="n"/>
+      <c r="AJ48" s="31" t="n"/>
+      <c r="AK48" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL48" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM48" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN48" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO48" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP48" s="24" t="inlineStr">
+        <is>
+          <t>mlb-wsh</t>
+        </is>
+      </c>
+      <c r="AQ48" s="24" t="inlineStr">
+        <is>
+          <t>Washington Nationals</t>
+        </is>
+      </c>
+      <c r="AR48" s="24" t="inlineStr">
+        <is>
+          <t>Washington Nationals</t>
+        </is>
+      </c>
+      <c r="AS48" s="24" t="inlineStr">
+        <is>
+          <t>mlb-phi</t>
+        </is>
+      </c>
+      <c r="AT48" s="24" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies</t>
+        </is>
+      </c>
+      <c r="AU48" s="24" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies</t>
+        </is>
+      </c>
+      <c r="AV48" s="24" t="n"/>
+      <c r="AW48" s="24" t="n"/>
+      <c r="AX48" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY48" s="24" t="n"/>
+      <c r="AZ48" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA48" s="24" t="inlineStr">
+        <is>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+        </is>
+      </c>
+      <c r="BB48" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC48" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v2</t>
+        </is>
+      </c>
+      <c r="BD48" s="24" t="inlineStr">
+        <is>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+        </is>
+      </c>
+      <c r="BE48" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF48" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG48" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH48" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="BI48" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ48" s="25" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BK48" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="BL48" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BM48" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="BN48" s="28" t="n">
+        <v>0.527363</v>
+      </c>
+      <c r="BO48" s="28" t="n"/>
+      <c r="BP48" s="25" t="n"/>
+      <c r="BQ48" s="27" t="n"/>
+      <c r="BR48" s="28" t="n"/>
+      <c r="BS48" s="28" t="n"/>
+      <c r="BT48" s="28" t="n"/>
+      <c r="BU48" s="25" t="n"/>
+      <c r="BV48" s="29" t="n"/>
+      <c r="BW48" s="24" t="n"/>
+      <c r="BX48" s="30" t="n"/>
+      <c r="BY48" s="27" t="n"/>
+      <c r="BZ48" s="24" t="n"/>
+      <c r="CA48" s="31" t="n"/>
+      <c r="CB48" s="24" t="n"/>
+      <c r="CC48" s="24" t="n"/>
+      <c r="CD48" s="24" t="n"/>
+      <c r="CE48" s="24" t="n"/>
+      <c r="CF48" s="24" t="n"/>
+      <c r="CG48" s="24" t="n"/>
+      <c r="CH48" s="24" t="n"/>
+      <c r="CI48" s="24" t="n"/>
+      <c r="CJ48" s="24" t="n"/>
+      <c r="CK48" s="24" t="n"/>
+      <c r="CL48" s="24" t="n"/>
+      <c r="CM48" s="24" t="n"/>
+      <c r="CN48" s="24" t="n"/>
+      <c r="CO48" s="24" t="n"/>
+      <c r="CP48" s="24" t="n"/>
+      <c r="CQ48" s="24" t="n"/>
+      <c r="CR48" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="36" customHeight="1">
+      <c r="A49" s="24" t="inlineStr">
+        <is>
+          <t>36a8e843485741c2</t>
+        </is>
+      </c>
+      <c r="B49" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="C49" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T23:05Z</t>
+        </is>
+      </c>
+      <c r="D49" s="24" t="inlineStr">
+        <is>
+          <t>401816389</t>
+        </is>
+      </c>
+      <c r="E49" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F49" s="24" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="G49" s="24" t="inlineStr">
+        <is>
+          <t>New York Yankees</t>
+        </is>
+      </c>
+      <c r="H49" s="24" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="I49" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J49" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K49" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L49" s="26" t="n">
+        <v>-135</v>
+      </c>
+      <c r="M49" s="27" t="n">
+        <v>1.740741</v>
+      </c>
+      <c r="N49" s="28" t="n">
+        <v>0.574468</v>
+      </c>
+      <c r="O49" s="28" t="n">
+        <v>0.611882</v>
+      </c>
+      <c r="P49" s="28" t="n">
+        <v>0.05172</v>
+      </c>
+      <c r="Q49" s="28" t="n">
+        <v>0.037414</v>
+      </c>
+      <c r="R49" s="26" t="n">
+        <v>39</v>
+      </c>
+      <c r="S49" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T49" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v2</t>
+        </is>
+      </c>
+      <c r="U49" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V49" s="24" t="n"/>
+      <c r="W49" s="26" t="n"/>
+      <c r="X49" s="26" t="n"/>
+      <c r="Y49" s="25" t="n"/>
+      <c r="Z49" s="26" t="n"/>
+      <c r="AA49" s="28" t="n"/>
+      <c r="AB49" s="28" t="n"/>
+      <c r="AC49" s="30" t="n"/>
+      <c r="AD49" s="24" t="n"/>
+      <c r="AE49" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Margin: Trend Engine projected 4.35-4.35; raw selected-side p=0.6704, calibrated p=0.6119.</t>
+        </is>
+      </c>
+      <c r="AF49" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG49" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH49" s="24" t="n"/>
+      <c r="AI49" s="31" t="n"/>
+      <c r="AJ49" s="31" t="n"/>
+      <c r="AK49" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL49" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM49" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN49" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO49" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP49" s="24" t="inlineStr">
+        <is>
+          <t>mlb-stl</t>
+        </is>
+      </c>
+      <c r="AQ49" s="24" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="AR49" s="24" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="AS49" s="24" t="inlineStr">
+        <is>
+          <t>mlb-nyy</t>
+        </is>
+      </c>
+      <c r="AT49" s="24" t="inlineStr">
+        <is>
+          <t>New York Yankees</t>
+        </is>
+      </c>
+      <c r="AU49" s="24" t="inlineStr">
+        <is>
+          <t>New York Yankees</t>
+        </is>
+      </c>
+      <c r="AV49" s="24" t="n"/>
+      <c r="AW49" s="24" t="n"/>
+      <c r="AX49" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY49" s="24" t="n"/>
+      <c r="AZ49" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA49" s="24" t="inlineStr">
+        <is>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+        </is>
+      </c>
+      <c r="BB49" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC49" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v2</t>
+        </is>
+      </c>
+      <c r="BD49" s="24" t="inlineStr">
+        <is>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+        </is>
+      </c>
+      <c r="BE49" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF49" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG49" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH49" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="BI49" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ49" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK49" s="26" t="n">
+        <v>-135</v>
+      </c>
+      <c r="BL49" s="27" t="n">
+        <v>1.740741</v>
+      </c>
+      <c r="BM49" s="28" t="n">
+        <v>0.574468</v>
+      </c>
+      <c r="BN49" s="28" t="n">
+        <v>0.572139</v>
+      </c>
+      <c r="BO49" s="28" t="n"/>
+      <c r="BP49" s="25" t="n"/>
+      <c r="BQ49" s="27" t="n"/>
+      <c r="BR49" s="28" t="n"/>
+      <c r="BS49" s="28" t="n"/>
+      <c r="BT49" s="28" t="n"/>
+      <c r="BU49" s="25" t="n"/>
+      <c r="BV49" s="29" t="n"/>
+      <c r="BW49" s="24" t="n"/>
+      <c r="BX49" s="30" t="n"/>
+      <c r="BY49" s="27" t="n"/>
+      <c r="BZ49" s="24" t="n"/>
+      <c r="CA49" s="31" t="n"/>
+      <c r="CB49" s="24" t="n"/>
+      <c r="CC49" s="24" t="n"/>
+      <c r="CD49" s="24" t="n"/>
+      <c r="CE49" s="24" t="n"/>
+      <c r="CF49" s="24" t="n"/>
+      <c r="CG49" s="24" t="n"/>
+      <c r="CH49" s="24" t="n"/>
+      <c r="CI49" s="24" t="n"/>
+      <c r="CJ49" s="24" t="n"/>
+      <c r="CK49" s="24" t="n"/>
+      <c r="CL49" s="24" t="n"/>
+      <c r="CM49" s="24" t="n"/>
+      <c r="CN49" s="24" t="n"/>
+      <c r="CO49" s="24" t="n"/>
+      <c r="CP49" s="24" t="n"/>
+      <c r="CQ49" s="24" t="n"/>
+      <c r="CR49" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="36" customHeight="1">
+      <c r="A50" s="24" t="inlineStr">
+        <is>
+          <t>c992438407204be4</t>
+        </is>
+      </c>
+      <c r="B50" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="C50" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T23:05Z</t>
+        </is>
+      </c>
+      <c r="D50" s="24" t="inlineStr">
+        <is>
+          <t>401816389</t>
+        </is>
+      </c>
+      <c r="E50" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F50" s="24" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="G50" s="24" t="inlineStr">
+        <is>
+          <t>New York Yankees</t>
+        </is>
+      </c>
+      <c r="H50" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I50" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J50" s="25" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K50" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L50" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="M50" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="N50" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="O50" s="28" t="n">
+        <v>0.513093</v>
+      </c>
+      <c r="P50" s="28" t="n">
+        <v>0.05172</v>
+      </c>
+      <c r="Q50" s="28" t="n">
+        <v>-0.006138</v>
+      </c>
+      <c r="R50" s="26" t="n">
+        <v>17</v>
+      </c>
+      <c r="S50" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T50" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v2</t>
+        </is>
+      </c>
+      <c r="U50" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V50" s="24" t="n"/>
+      <c r="W50" s="26" t="n"/>
+      <c r="X50" s="26" t="n"/>
+      <c r="Y50" s="25" t="n"/>
+      <c r="Z50" s="26" t="n"/>
+      <c r="AA50" s="28" t="n"/>
+      <c r="AB50" s="28" t="n"/>
+      <c r="AC50" s="30" t="n"/>
+      <c r="AD50" s="24" t="n"/>
+      <c r="AE50" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Totals: Trend Engine projected 4.35-4.35; raw selected-side p=0.5151, calibrated p=0.5131.</t>
+        </is>
+      </c>
+      <c r="AF50" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG50" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH50" s="24" t="n"/>
+      <c r="AI50" s="31" t="n"/>
+      <c r="AJ50" s="31" t="n"/>
+      <c r="AK50" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL50" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM50" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN50" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO50" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP50" s="24" t="inlineStr">
+        <is>
+          <t>mlb-stl</t>
+        </is>
+      </c>
+      <c r="AQ50" s="24" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="AR50" s="24" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="AS50" s="24" t="inlineStr">
+        <is>
+          <t>mlb-nyy</t>
+        </is>
+      </c>
+      <c r="AT50" s="24" t="inlineStr">
+        <is>
+          <t>New York Yankees</t>
+        </is>
+      </c>
+      <c r="AU50" s="24" t="inlineStr">
+        <is>
+          <t>New York Yankees</t>
+        </is>
+      </c>
+      <c r="AV50" s="24" t="n"/>
+      <c r="AW50" s="24" t="n"/>
+      <c r="AX50" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY50" s="24" t="n"/>
+      <c r="AZ50" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA50" s="24" t="inlineStr">
+        <is>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+        </is>
+      </c>
+      <c r="BB50" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC50" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v2</t>
+        </is>
+      </c>
+      <c r="BD50" s="24" t="inlineStr">
+        <is>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+        </is>
+      </c>
+      <c r="BE50" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF50" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG50" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH50" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="BI50" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ50" s="25" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BK50" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="BL50" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="BM50" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="BN50" s="28" t="n">
+        <v>0.517413</v>
+      </c>
+      <c r="BO50" s="28" t="n"/>
+      <c r="BP50" s="25" t="n"/>
+      <c r="BQ50" s="27" t="n"/>
+      <c r="BR50" s="28" t="n"/>
+      <c r="BS50" s="28" t="n"/>
+      <c r="BT50" s="28" t="n"/>
+      <c r="BU50" s="25" t="n"/>
+      <c r="BV50" s="29" t="n"/>
+      <c r="BW50" s="24" t="n"/>
+      <c r="BX50" s="30" t="n"/>
+      <c r="BY50" s="27" t="n"/>
+      <c r="BZ50" s="24" t="n"/>
+      <c r="CA50" s="31" t="n"/>
+      <c r="CB50" s="24" t="n"/>
+      <c r="CC50" s="24" t="n"/>
+      <c r="CD50" s="24" t="n"/>
+      <c r="CE50" s="24" t="n"/>
+      <c r="CF50" s="24" t="n"/>
+      <c r="CG50" s="24" t="n"/>
+      <c r="CH50" s="24" t="n"/>
+      <c r="CI50" s="24" t="n"/>
+      <c r="CJ50" s="24" t="n"/>
+      <c r="CK50" s="24" t="n"/>
+      <c r="CL50" s="24" t="n"/>
+      <c r="CM50" s="24" t="n"/>
+      <c r="CN50" s="24" t="n"/>
+      <c r="CO50" s="24" t="n"/>
+      <c r="CP50" s="24" t="n"/>
+      <c r="CQ50" s="24" t="n"/>
+      <c r="CR50" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="36" customHeight="1">
+      <c r="A51" s="24" t="inlineStr">
+        <is>
+          <t>e9ddc697bb5c4a01</t>
+        </is>
+      </c>
+      <c r="B51" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="C51" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T23:10Z</t>
+        </is>
+      </c>
+      <c r="D51" s="24" t="inlineStr">
+        <is>
+          <t>401816386</t>
+        </is>
+      </c>
+      <c r="E51" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F51" s="24" t="inlineStr">
+        <is>
+          <t>Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="G51" s="24" t="inlineStr">
+        <is>
+          <t>Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="H51" s="24" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="I51" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J51" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K51" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L51" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="M51" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="N51" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="O51" s="28" t="n">
+        <v>0.561067</v>
+      </c>
+      <c r="P51" s="28" t="n">
+        <v>0.05172</v>
+      </c>
+      <c r="Q51" s="28" t="n">
+        <v>-0.079221</v>
+      </c>
+      <c r="R51" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T51" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v2</t>
+        </is>
+      </c>
+      <c r="U51" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V51" s="24" t="n"/>
+      <c r="W51" s="26" t="n"/>
+      <c r="X51" s="26" t="n"/>
+      <c r="Y51" s="25" t="n"/>
+      <c r="Z51" s="26" t="n"/>
+      <c r="AA51" s="28" t="n"/>
+      <c r="AB51" s="28" t="n"/>
+      <c r="AC51" s="30" t="n"/>
+      <c r="AD51" s="24" t="n"/>
+      <c r="AE51" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Margin: Trend Engine projected 4.37-5.16; raw selected-side p=0.5930, calibrated p=0.5611.</t>
+        </is>
+      </c>
+      <c r="AF51" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG51" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH51" s="24" t="n"/>
+      <c r="AI51" s="31" t="n"/>
+      <c r="AJ51" s="31" t="n"/>
+      <c r="AK51" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL51" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM51" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN51" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO51" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP51" s="24" t="inlineStr">
+        <is>
+          <t>mlb-cws</t>
+        </is>
+      </c>
+      <c r="AQ51" s="24" t="inlineStr">
+        <is>
+          <t>Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="AR51" s="24" t="inlineStr">
+        <is>
+          <t>Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="AS51" s="24" t="inlineStr">
+        <is>
+          <t>mlb-bos</t>
+        </is>
+      </c>
+      <c r="AT51" s="24" t="inlineStr">
+        <is>
+          <t>Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="AU51" s="24" t="inlineStr">
+        <is>
+          <t>Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="AV51" s="24" t="n"/>
+      <c r="AW51" s="24" t="n"/>
+      <c r="AX51" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY51" s="24" t="n"/>
+      <c r="AZ51" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA51" s="24" t="inlineStr">
+        <is>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+        </is>
+      </c>
+      <c r="BB51" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC51" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v2</t>
+        </is>
+      </c>
+      <c r="BD51" s="24" t="inlineStr">
+        <is>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+        </is>
+      </c>
+      <c r="BE51" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF51" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG51" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH51" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="BI51" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ51" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK51" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="BL51" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="BM51" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="BN51" s="28" t="n">
+        <v>0.636816</v>
+      </c>
+      <c r="BO51" s="28" t="n"/>
+      <c r="BP51" s="25" t="n"/>
+      <c r="BQ51" s="27" t="n"/>
+      <c r="BR51" s="28" t="n"/>
+      <c r="BS51" s="28" t="n"/>
+      <c r="BT51" s="28" t="n"/>
+      <c r="BU51" s="25" t="n"/>
+      <c r="BV51" s="29" t="n"/>
+      <c r="BW51" s="24" t="n"/>
+      <c r="BX51" s="30" t="n"/>
+      <c r="BY51" s="27" t="n"/>
+      <c r="BZ51" s="24" t="n"/>
+      <c r="CA51" s="31" t="n"/>
+      <c r="CB51" s="24" t="n"/>
+      <c r="CC51" s="24" t="n"/>
+      <c r="CD51" s="24" t="n"/>
+      <c r="CE51" s="24" t="n"/>
+      <c r="CF51" s="24" t="n"/>
+      <c r="CG51" s="24" t="n"/>
+      <c r="CH51" s="24" t="n"/>
+      <c r="CI51" s="24" t="n"/>
+      <c r="CJ51" s="24" t="n"/>
+      <c r="CK51" s="24" t="n"/>
+      <c r="CL51" s="24" t="n"/>
+      <c r="CM51" s="24" t="n"/>
+      <c r="CN51" s="24" t="n"/>
+      <c r="CO51" s="24" t="n"/>
+      <c r="CP51" s="24" t="n"/>
+      <c r="CQ51" s="24" t="n"/>
+      <c r="CR51" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="36" customHeight="1">
+      <c r="A52" s="24" t="inlineStr">
+        <is>
+          <t>9fe44a3d5c074b0c</t>
+        </is>
+      </c>
+      <c r="B52" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="C52" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T23:10Z</t>
+        </is>
+      </c>
+      <c r="D52" s="24" t="inlineStr">
+        <is>
+          <t>401816386</t>
+        </is>
+      </c>
+      <c r="E52" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F52" s="24" t="inlineStr">
+        <is>
+          <t>Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="G52" s="24" t="inlineStr">
+        <is>
+          <t>Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="H52" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I52" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J52" s="25" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K52" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L52" s="26" t="n">
+        <v>-125</v>
+      </c>
+      <c r="M52" s="27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N52" s="28" t="n">
+        <v>0.555556</v>
+      </c>
+      <c r="O52" s="28" t="n">
+        <v>0.530246</v>
+      </c>
+      <c r="P52" s="28" t="n">
+        <v>0.05172</v>
+      </c>
+      <c r="Q52" s="28" t="n">
+        <v>-0.02531</v>
+      </c>
+      <c r="R52" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="S52" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T52" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v2</t>
+        </is>
+      </c>
+      <c r="U52" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V52" s="24" t="n"/>
+      <c r="W52" s="26" t="n"/>
+      <c r="X52" s="26" t="n"/>
+      <c r="Y52" s="25" t="n"/>
+      <c r="Z52" s="26" t="n"/>
+      <c r="AA52" s="28" t="n"/>
+      <c r="AB52" s="28" t="n"/>
+      <c r="AC52" s="30" t="n"/>
+      <c r="AD52" s="24" t="n"/>
+      <c r="AE52" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Totals: Trend Engine projected 4.37-5.16; raw selected-side p=0.5653, calibrated p=0.5302.</t>
+        </is>
+      </c>
+      <c r="AF52" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG52" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH52" s="24" t="n"/>
+      <c r="AI52" s="31" t="n"/>
+      <c r="AJ52" s="31" t="n"/>
+      <c r="AK52" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL52" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM52" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN52" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO52" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP52" s="24" t="inlineStr">
+        <is>
+          <t>mlb-cws</t>
+        </is>
+      </c>
+      <c r="AQ52" s="24" t="inlineStr">
+        <is>
+          <t>Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="AR52" s="24" t="inlineStr">
+        <is>
+          <t>Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="AS52" s="24" t="inlineStr">
+        <is>
+          <t>mlb-bos</t>
+        </is>
+      </c>
+      <c r="AT52" s="24" t="inlineStr">
+        <is>
+          <t>Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="AU52" s="24" t="inlineStr">
+        <is>
+          <t>Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="AV52" s="24" t="n"/>
+      <c r="AW52" s="24" t="n"/>
+      <c r="AX52" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY52" s="24" t="n"/>
+      <c r="AZ52" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA52" s="24" t="inlineStr">
+        <is>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+        </is>
+      </c>
+      <c r="BB52" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC52" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v2</t>
+        </is>
+      </c>
+      <c r="BD52" s="24" t="inlineStr">
+        <is>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+        </is>
+      </c>
+      <c r="BE52" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF52" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG52" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH52" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="BI52" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ52" s="25" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BK52" s="26" t="n">
+        <v>-125</v>
+      </c>
+      <c r="BL52" s="27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM52" s="28" t="n">
+        <v>0.555556</v>
+      </c>
+      <c r="BN52" s="28" t="n">
+        <v>0.552239</v>
+      </c>
+      <c r="BO52" s="28" t="n"/>
+      <c r="BP52" s="25" t="n"/>
+      <c r="BQ52" s="27" t="n"/>
+      <c r="BR52" s="28" t="n"/>
+      <c r="BS52" s="28" t="n"/>
+      <c r="BT52" s="28" t="n"/>
+      <c r="BU52" s="25" t="n"/>
+      <c r="BV52" s="29" t="n"/>
+      <c r="BW52" s="24" t="n"/>
+      <c r="BX52" s="30" t="n"/>
+      <c r="BY52" s="27" t="n"/>
+      <c r="BZ52" s="24" t="n"/>
+      <c r="CA52" s="31" t="n"/>
+      <c r="CB52" s="24" t="n"/>
+      <c r="CC52" s="24" t="n"/>
+      <c r="CD52" s="24" t="n"/>
+      <c r="CE52" s="24" t="n"/>
+      <c r="CF52" s="24" t="n"/>
+      <c r="CG52" s="24" t="n"/>
+      <c r="CH52" s="24" t="n"/>
+      <c r="CI52" s="24" t="n"/>
+      <c r="CJ52" s="24" t="n"/>
+      <c r="CK52" s="24" t="n"/>
+      <c r="CL52" s="24" t="n"/>
+      <c r="CM52" s="24" t="n"/>
+      <c r="CN52" s="24" t="n"/>
+      <c r="CO52" s="24" t="n"/>
+      <c r="CP52" s="24" t="n"/>
+      <c r="CQ52" s="24" t="n"/>
+      <c r="CR52" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="36" customHeight="1">
+      <c r="A53" s="24" t="inlineStr">
+        <is>
+          <t>930434e105a343cf</t>
+        </is>
+      </c>
+      <c r="B53" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="C53" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T23:15Z</t>
+        </is>
+      </c>
+      <c r="D53" s="24" t="inlineStr">
+        <is>
+          <t>401816387</t>
+        </is>
+      </c>
+      <c r="E53" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F53" s="24" t="inlineStr">
+        <is>
+          <t>Miami Marlins</t>
+        </is>
+      </c>
+      <c r="G53" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Braves</t>
+        </is>
+      </c>
+      <c r="H53" s="24" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="I53" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J53" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K53" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L53" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M53" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="N53" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O53" s="28" t="n">
+        <v>0.563298</v>
+      </c>
+      <c r="P53" s="28" t="n">
+        <v>0.042131</v>
+      </c>
+      <c r="Q53" s="28" t="n">
+        <v>-0.036702</v>
+      </c>
+      <c r="R53" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="S53" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T53" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v2</t>
+        </is>
+      </c>
+      <c r="U53" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V53" s="24" t="n"/>
+      <c r="W53" s="26" t="n"/>
+      <c r="X53" s="26" t="n"/>
+      <c r="Y53" s="25" t="n"/>
+      <c r="Z53" s="26" t="n"/>
+      <c r="AA53" s="28" t="n"/>
+      <c r="AB53" s="28" t="n"/>
+      <c r="AC53" s="30" t="n"/>
+      <c r="AD53" s="24" t="n"/>
+      <c r="AE53" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Margin: Trend Engine projected 4.10-4.82; raw selected-side p=0.5964, calibrated p=0.5633.</t>
+        </is>
+      </c>
+      <c r="AF53" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG53" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH53" s="24" t="n"/>
+      <c r="AI53" s="31" t="n"/>
+      <c r="AJ53" s="31" t="n"/>
+      <c r="AK53" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL53" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM53" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN53" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO53" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP53" s="24" t="inlineStr">
+        <is>
+          <t>mlb-mia</t>
+        </is>
+      </c>
+      <c r="AQ53" s="24" t="inlineStr">
+        <is>
+          <t>Miami Marlins</t>
+        </is>
+      </c>
+      <c r="AR53" s="24" t="inlineStr">
+        <is>
+          <t>Miami Marlins</t>
+        </is>
+      </c>
+      <c r="AS53" s="24" t="inlineStr">
+        <is>
+          <t>mlb-atl</t>
+        </is>
+      </c>
+      <c r="AT53" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Braves</t>
+        </is>
+      </c>
+      <c r="AU53" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Braves</t>
+        </is>
+      </c>
+      <c r="AV53" s="24" t="n"/>
+      <c r="AW53" s="24" t="n"/>
+      <c r="AX53" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY53" s="24" t="n"/>
+      <c r="AZ53" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA53" s="24" t="inlineStr">
+        <is>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+        </is>
+      </c>
+      <c r="BB53" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC53" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v2</t>
+        </is>
+      </c>
+      <c r="BD53" s="24" t="inlineStr">
+        <is>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+        </is>
+      </c>
+      <c r="BE53" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF53" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG53" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH53" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="BI53" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ53" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK53" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BL53" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BM53" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN53" s="28" t="n">
+        <v>0.597015</v>
+      </c>
+      <c r="BO53" s="28" t="n"/>
+      <c r="BP53" s="25" t="n"/>
+      <c r="BQ53" s="27" t="n"/>
+      <c r="BR53" s="28" t="n"/>
+      <c r="BS53" s="28" t="n"/>
+      <c r="BT53" s="28" t="n"/>
+      <c r="BU53" s="25" t="n"/>
+      <c r="BV53" s="29" t="n"/>
+      <c r="BW53" s="24" t="n"/>
+      <c r="BX53" s="30" t="n"/>
+      <c r="BY53" s="27" t="n"/>
+      <c r="BZ53" s="24" t="n"/>
+      <c r="CA53" s="31" t="n"/>
+      <c r="CB53" s="24" t="n"/>
+      <c r="CC53" s="24" t="n"/>
+      <c r="CD53" s="24" t="n"/>
+      <c r="CE53" s="24" t="n"/>
+      <c r="CF53" s="24" t="n"/>
+      <c r="CG53" s="24" t="n"/>
+      <c r="CH53" s="24" t="n"/>
+      <c r="CI53" s="24" t="n"/>
+      <c r="CJ53" s="24" t="n"/>
+      <c r="CK53" s="24" t="n"/>
+      <c r="CL53" s="24" t="n"/>
+      <c r="CM53" s="24" t="n"/>
+      <c r="CN53" s="24" t="n"/>
+      <c r="CO53" s="24" t="n"/>
+      <c r="CP53" s="24" t="n"/>
+      <c r="CQ53" s="24" t="n"/>
+      <c r="CR53" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="36" customHeight="1">
+      <c r="A54" s="24" t="inlineStr">
+        <is>
+          <t>e529811f2e5c408d</t>
+        </is>
+      </c>
+      <c r="B54" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="C54" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T23:15Z</t>
+        </is>
+      </c>
+      <c r="D54" s="24" t="inlineStr">
+        <is>
+          <t>401816387</t>
+        </is>
+      </c>
+      <c r="E54" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F54" s="24" t="inlineStr">
+        <is>
+          <t>Miami Marlins</t>
+        </is>
+      </c>
+      <c r="G54" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Braves</t>
+        </is>
+      </c>
+      <c r="H54" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I54" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J54" s="25" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K54" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L54" s="26" t="n">
+        <v>-120</v>
+      </c>
+      <c r="M54" s="27" t="n">
+        <v>1.833333</v>
+      </c>
+      <c r="N54" s="28" t="n">
+        <v>0.545455</v>
+      </c>
+      <c r="O54" s="28" t="n">
+        <v>0.542496</v>
+      </c>
+      <c r="P54" s="28" t="n">
+        <v>0.042131</v>
+      </c>
+      <c r="Q54" s="28" t="n">
+        <v>-0.002959</v>
+      </c>
+      <c r="R54" s="26" t="n">
+        <v>25</v>
+      </c>
+      <c r="S54" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T54" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v2</t>
+        </is>
+      </c>
+      <c r="U54" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V54" s="24" t="n"/>
+      <c r="W54" s="26" t="n"/>
+      <c r="X54" s="26" t="n"/>
+      <c r="Y54" s="25" t="n"/>
+      <c r="Z54" s="26" t="n"/>
+      <c r="AA54" s="28" t="n"/>
+      <c r="AB54" s="28" t="n"/>
+      <c r="AC54" s="30" t="n"/>
+      <c r="AD54" s="24" t="n"/>
+      <c r="AE54" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Totals: Trend Engine projected 4.10-4.82; raw selected-side p=0.6011, calibrated p=0.5425.</t>
+        </is>
+      </c>
+      <c r="AF54" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG54" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH54" s="24" t="n"/>
+      <c r="AI54" s="31" t="n"/>
+      <c r="AJ54" s="31" t="n"/>
+      <c r="AK54" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL54" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM54" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN54" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO54" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP54" s="24" t="inlineStr">
+        <is>
+          <t>mlb-mia</t>
+        </is>
+      </c>
+      <c r="AQ54" s="24" t="inlineStr">
+        <is>
+          <t>Miami Marlins</t>
+        </is>
+      </c>
+      <c r="AR54" s="24" t="inlineStr">
+        <is>
+          <t>Miami Marlins</t>
+        </is>
+      </c>
+      <c r="AS54" s="24" t="inlineStr">
+        <is>
+          <t>mlb-atl</t>
+        </is>
+      </c>
+      <c r="AT54" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Braves</t>
+        </is>
+      </c>
+      <c r="AU54" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Braves</t>
+        </is>
+      </c>
+      <c r="AV54" s="24" t="n"/>
+      <c r="AW54" s="24" t="n"/>
+      <c r="AX54" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY54" s="24" t="n"/>
+      <c r="AZ54" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA54" s="24" t="inlineStr">
+        <is>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+        </is>
+      </c>
+      <c r="BB54" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC54" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v2</t>
+        </is>
+      </c>
+      <c r="BD54" s="24" t="inlineStr">
+        <is>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+        </is>
+      </c>
+      <c r="BE54" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF54" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG54" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH54" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="BI54" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ54" s="25" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BK54" s="26" t="n">
+        <v>-120</v>
+      </c>
+      <c r="BL54" s="27" t="n">
+        <v>1.833333</v>
+      </c>
+      <c r="BM54" s="28" t="n">
+        <v>0.545455</v>
+      </c>
+      <c r="BN54" s="28" t="n">
+        <v>0.542289</v>
+      </c>
+      <c r="BO54" s="28" t="n"/>
+      <c r="BP54" s="25" t="n"/>
+      <c r="BQ54" s="27" t="n"/>
+      <c r="BR54" s="28" t="n"/>
+      <c r="BS54" s="28" t="n"/>
+      <c r="BT54" s="28" t="n"/>
+      <c r="BU54" s="25" t="n"/>
+      <c r="BV54" s="29" t="n"/>
+      <c r="BW54" s="24" t="n"/>
+      <c r="BX54" s="30" t="n"/>
+      <c r="BY54" s="27" t="n"/>
+      <c r="BZ54" s="24" t="n"/>
+      <c r="CA54" s="31" t="n"/>
+      <c r="CB54" s="24" t="n"/>
+      <c r="CC54" s="24" t="n"/>
+      <c r="CD54" s="24" t="n"/>
+      <c r="CE54" s="24" t="n"/>
+      <c r="CF54" s="24" t="n"/>
+      <c r="CG54" s="24" t="n"/>
+      <c r="CH54" s="24" t="n"/>
+      <c r="CI54" s="24" t="n"/>
+      <c r="CJ54" s="24" t="n"/>
+      <c r="CK54" s="24" t="n"/>
+      <c r="CL54" s="24" t="n"/>
+      <c r="CM54" s="24" t="n"/>
+      <c r="CN54" s="24" t="n"/>
+      <c r="CO54" s="24" t="n"/>
+      <c r="CP54" s="24" t="n"/>
+      <c r="CQ54" s="24" t="n"/>
+      <c r="CR54" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="36" customHeight="1">
+      <c r="A55" s="24" t="inlineStr">
+        <is>
+          <t>f2ced1650ff241d4</t>
+        </is>
+      </c>
+      <c r="B55" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="C55" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T23:40Z</t>
+        </is>
+      </c>
+      <c r="D55" s="24" t="inlineStr">
+        <is>
+          <t>401816392</t>
+        </is>
+      </c>
+      <c r="E55" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F55" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="G55" s="24" t="inlineStr">
+        <is>
+          <t>Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="H55" s="24" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="I55" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J55" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K55" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L55" s="26" t="n">
+        <v>-120</v>
+      </c>
+      <c r="M55" s="27" t="n">
+        <v>1.833333</v>
+      </c>
+      <c r="N55" s="28" t="n">
+        <v>0.545455</v>
+      </c>
+      <c r="O55" s="28" t="n">
+        <v>0.702982</v>
+      </c>
+      <c r="P55" s="28" t="n">
+        <v>0.05172</v>
+      </c>
+      <c r="Q55" s="28" t="n">
+        <v>0.157527</v>
+      </c>
+      <c r="R55" s="26" t="n">
+        <v>99</v>
+      </c>
+      <c r="S55" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T55" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v2</t>
+        </is>
+      </c>
+      <c r="U55" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V55" s="24" t="n"/>
+      <c r="W55" s="26" t="n"/>
+      <c r="X55" s="26" t="n"/>
+      <c r="Y55" s="25" t="n"/>
+      <c r="Z55" s="26" t="n"/>
+      <c r="AA55" s="28" t="n"/>
+      <c r="AB55" s="28" t="n"/>
+      <c r="AC55" s="30" t="n"/>
+      <c r="AD55" s="24" t="n"/>
+      <c r="AE55" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Margin: Trend Engine projected 3.16-4.32; raw selected-side p=0.8093, calibrated p=0.7030.</t>
+        </is>
+      </c>
+      <c r="AF55" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG55" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH55" s="24" t="n"/>
+      <c r="AI55" s="31" t="n"/>
+      <c r="AJ55" s="31" t="n"/>
+      <c r="AK55" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL55" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM55" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN55" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO55" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP55" s="24" t="inlineStr">
+        <is>
+          <t>mlb-min</t>
+        </is>
+      </c>
+      <c r="AQ55" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="AR55" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="AS55" s="24" t="inlineStr">
+        <is>
+          <t>mlb-kc</t>
+        </is>
+      </c>
+      <c r="AT55" s="24" t="inlineStr">
+        <is>
+          <t>Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="AU55" s="24" t="inlineStr">
+        <is>
+          <t>Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="AV55" s="24" t="n"/>
+      <c r="AW55" s="24" t="n"/>
+      <c r="AX55" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY55" s="24" t="n"/>
+      <c r="AZ55" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA55" s="24" t="inlineStr">
+        <is>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+        </is>
+      </c>
+      <c r="BB55" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC55" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v2</t>
+        </is>
+      </c>
+      <c r="BD55" s="24" t="inlineStr">
+        <is>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+        </is>
+      </c>
+      <c r="BE55" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF55" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG55" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH55" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="BI55" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ55" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK55" s="26" t="n">
+        <v>-120</v>
+      </c>
+      <c r="BL55" s="27" t="n">
+        <v>1.833333</v>
+      </c>
+      <c r="BM55" s="28" t="n">
+        <v>0.545455</v>
+      </c>
+      <c r="BN55" s="28" t="n">
+        <v>0.542289</v>
+      </c>
+      <c r="BO55" s="28" t="n"/>
+      <c r="BP55" s="25" t="n"/>
+      <c r="BQ55" s="27" t="n"/>
+      <c r="BR55" s="28" t="n"/>
+      <c r="BS55" s="28" t="n"/>
+      <c r="BT55" s="28" t="n"/>
+      <c r="BU55" s="25" t="n"/>
+      <c r="BV55" s="29" t="n"/>
+      <c r="BW55" s="24" t="n"/>
+      <c r="BX55" s="30" t="n"/>
+      <c r="BY55" s="27" t="n"/>
+      <c r="BZ55" s="24" t="n"/>
+      <c r="CA55" s="31" t="n"/>
+      <c r="CB55" s="24" t="n"/>
+      <c r="CC55" s="24" t="n"/>
+      <c r="CD55" s="24" t="n"/>
+      <c r="CE55" s="24" t="n"/>
+      <c r="CF55" s="24" t="n"/>
+      <c r="CG55" s="24" t="n"/>
+      <c r="CH55" s="24" t="n"/>
+      <c r="CI55" s="24" t="n"/>
+      <c r="CJ55" s="24" t="n"/>
+      <c r="CK55" s="24" t="n"/>
+      <c r="CL55" s="24" t="n"/>
+      <c r="CM55" s="24" t="n"/>
+      <c r="CN55" s="24" t="n"/>
+      <c r="CO55" s="24" t="n"/>
+      <c r="CP55" s="24" t="n"/>
+      <c r="CQ55" s="24" t="n"/>
+      <c r="CR55" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="36" customHeight="1">
+      <c r="A56" s="24" t="inlineStr">
+        <is>
+          <t>e68c58bbc7d74d97</t>
+        </is>
+      </c>
+      <c r="B56" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="C56" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T23:40Z</t>
+        </is>
+      </c>
+      <c r="D56" s="24" t="inlineStr">
+        <is>
+          <t>401816392</t>
+        </is>
+      </c>
+      <c r="E56" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F56" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="G56" s="24" t="inlineStr">
+        <is>
+          <t>Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="H56" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I56" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J56" s="25" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K56" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L56" s="26" t="n">
+        <v>-120</v>
+      </c>
+      <c r="M56" s="27" t="n">
+        <v>1.833333</v>
+      </c>
+      <c r="N56" s="28" t="n">
+        <v>0.545455</v>
+      </c>
+      <c r="O56" s="28" t="n">
+        <v>0.590214</v>
+      </c>
+      <c r="P56" s="28" t="n">
+        <v>0.05172</v>
+      </c>
+      <c r="Q56" s="28" t="n">
+        <v>0.044759</v>
+      </c>
+      <c r="R56" s="26" t="n">
+        <v>43</v>
+      </c>
+      <c r="S56" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T56" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v2</t>
+        </is>
+      </c>
+      <c r="U56" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V56" s="24" t="n"/>
+      <c r="W56" s="26" t="n"/>
+      <c r="X56" s="26" t="n"/>
+      <c r="Y56" s="25" t="n"/>
+      <c r="Z56" s="26" t="n"/>
+      <c r="AA56" s="28" t="n"/>
+      <c r="AB56" s="28" t="n"/>
+      <c r="AC56" s="30" t="n"/>
+      <c r="AD56" s="24" t="n"/>
+      <c r="AE56" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Totals: Trend Engine projected 3.16-4.32; raw selected-side p=0.7408, calibrated p=0.5902.</t>
+        </is>
+      </c>
+      <c r="AF56" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG56" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH56" s="24" t="n"/>
+      <c r="AI56" s="31" t="n"/>
+      <c r="AJ56" s="31" t="n"/>
+      <c r="AK56" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL56" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM56" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN56" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO56" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP56" s="24" t="inlineStr">
+        <is>
+          <t>mlb-min</t>
+        </is>
+      </c>
+      <c r="AQ56" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="AR56" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="AS56" s="24" t="inlineStr">
+        <is>
+          <t>mlb-kc</t>
+        </is>
+      </c>
+      <c r="AT56" s="24" t="inlineStr">
+        <is>
+          <t>Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="AU56" s="24" t="inlineStr">
+        <is>
+          <t>Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="AV56" s="24" t="n"/>
+      <c r="AW56" s="24" t="n"/>
+      <c r="AX56" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY56" s="24" t="n"/>
+      <c r="AZ56" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA56" s="24" t="inlineStr">
+        <is>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+        </is>
+      </c>
+      <c r="BB56" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC56" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v2</t>
+        </is>
+      </c>
+      <c r="BD56" s="24" t="inlineStr">
+        <is>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+        </is>
+      </c>
+      <c r="BE56" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF56" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG56" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH56" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="BI56" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ56" s="25" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BK56" s="26" t="n">
+        <v>-120</v>
+      </c>
+      <c r="BL56" s="27" t="n">
+        <v>1.833333</v>
+      </c>
+      <c r="BM56" s="28" t="n">
+        <v>0.545455</v>
+      </c>
+      <c r="BN56" s="28" t="n">
+        <v>0.542289</v>
+      </c>
+      <c r="BO56" s="28" t="n"/>
+      <c r="BP56" s="25" t="n"/>
+      <c r="BQ56" s="27" t="n"/>
+      <c r="BR56" s="28" t="n"/>
+      <c r="BS56" s="28" t="n"/>
+      <c r="BT56" s="28" t="n"/>
+      <c r="BU56" s="25" t="n"/>
+      <c r="BV56" s="29" t="n"/>
+      <c r="BW56" s="24" t="n"/>
+      <c r="BX56" s="30" t="n"/>
+      <c r="BY56" s="27" t="n"/>
+      <c r="BZ56" s="24" t="n"/>
+      <c r="CA56" s="31" t="n"/>
+      <c r="CB56" s="24" t="n"/>
+      <c r="CC56" s="24" t="n"/>
+      <c r="CD56" s="24" t="n"/>
+      <c r="CE56" s="24" t="n"/>
+      <c r="CF56" s="24" t="n"/>
+      <c r="CG56" s="24" t="n"/>
+      <c r="CH56" s="24" t="n"/>
+      <c r="CI56" s="24" t="n"/>
+      <c r="CJ56" s="24" t="n"/>
+      <c r="CK56" s="24" t="n"/>
+      <c r="CL56" s="24" t="n"/>
+      <c r="CM56" s="24" t="n"/>
+      <c r="CN56" s="24" t="n"/>
+      <c r="CO56" s="24" t="n"/>
+      <c r="CP56" s="24" t="n"/>
+      <c r="CQ56" s="24" t="n"/>
+      <c r="CR56" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="36" customHeight="1">
+      <c r="A57" s="24" t="inlineStr">
+        <is>
+          <t>a8a0293973dd4f21</t>
+        </is>
+      </c>
+      <c r="B57" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="C57" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T23:40Z</t>
+        </is>
+      </c>
+      <c r="D57" s="24" t="inlineStr">
+        <is>
+          <t>401816393</t>
+        </is>
+      </c>
+      <c r="E57" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F57" s="24" t="inlineStr">
+        <is>
+          <t>Pittsburgh Pirates</t>
+        </is>
+      </c>
+      <c r="G57" s="24" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="H57" s="24" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="I57" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J57" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K57" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L57" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M57" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="N57" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O57" s="28" t="n">
+        <v>0.593511</v>
+      </c>
+      <c r="P57" s="28" t="n">
+        <v>0.05172</v>
+      </c>
+      <c r="Q57" s="28" t="n">
+        <v>-0.006489</v>
+      </c>
+      <c r="R57" s="26" t="n">
+        <v>17</v>
+      </c>
+      <c r="S57" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T57" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v2</t>
+        </is>
+      </c>
+      <c r="U57" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V57" s="24" t="n"/>
+      <c r="W57" s="26" t="n"/>
+      <c r="X57" s="26" t="n"/>
+      <c r="Y57" s="25" t="n"/>
+      <c r="Z57" s="26" t="n"/>
+      <c r="AA57" s="28" t="n"/>
+      <c r="AB57" s="28" t="n"/>
+      <c r="AC57" s="30" t="n"/>
+      <c r="AD57" s="24" t="n"/>
+      <c r="AE57" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Margin: Trend Engine projected 3.58-4.00; raw selected-side p=0.6424, calibrated p=0.5935.</t>
+        </is>
+      </c>
+      <c r="AF57" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG57" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH57" s="24" t="n"/>
+      <c r="AI57" s="31" t="n"/>
+      <c r="AJ57" s="31" t="n"/>
+      <c r="AK57" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL57" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM57" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN57" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO57" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP57" s="24" t="inlineStr">
+        <is>
+          <t>mlb-pit</t>
+        </is>
+      </c>
+      <c r="AQ57" s="24" t="inlineStr">
+        <is>
+          <t>Pittsburgh Pirates</t>
+        </is>
+      </c>
+      <c r="AR57" s="24" t="inlineStr">
+        <is>
+          <t>Pittsburgh Pirates</t>
+        </is>
+      </c>
+      <c r="AS57" s="24" t="inlineStr">
+        <is>
+          <t>mlb-mil</t>
+        </is>
+      </c>
+      <c r="AT57" s="24" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="AU57" s="24" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="AV57" s="24" t="n"/>
+      <c r="AW57" s="24" t="n"/>
+      <c r="AX57" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY57" s="24" t="n"/>
+      <c r="AZ57" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA57" s="24" t="inlineStr">
+        <is>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+        </is>
+      </c>
+      <c r="BB57" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC57" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v2</t>
+        </is>
+      </c>
+      <c r="BD57" s="24" t="inlineStr">
+        <is>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+        </is>
+      </c>
+      <c r="BE57" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF57" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG57" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH57" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="BI57" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ57" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK57" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BL57" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BM57" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN57" s="28" t="n">
+        <v>0.597015</v>
+      </c>
+      <c r="BO57" s="28" t="n"/>
+      <c r="BP57" s="25" t="n"/>
+      <c r="BQ57" s="27" t="n"/>
+      <c r="BR57" s="28" t="n"/>
+      <c r="BS57" s="28" t="n"/>
+      <c r="BT57" s="28" t="n"/>
+      <c r="BU57" s="25" t="n"/>
+      <c r="BV57" s="29" t="n"/>
+      <c r="BW57" s="24" t="n"/>
+      <c r="BX57" s="30" t="n"/>
+      <c r="BY57" s="27" t="n"/>
+      <c r="BZ57" s="24" t="n"/>
+      <c r="CA57" s="31" t="n"/>
+      <c r="CB57" s="24" t="n"/>
+      <c r="CC57" s="24" t="n"/>
+      <c r="CD57" s="24" t="n"/>
+      <c r="CE57" s="24" t="n"/>
+      <c r="CF57" s="24" t="n"/>
+      <c r="CG57" s="24" t="n"/>
+      <c r="CH57" s="24" t="n"/>
+      <c r="CI57" s="24" t="n"/>
+      <c r="CJ57" s="24" t="n"/>
+      <c r="CK57" s="24" t="n"/>
+      <c r="CL57" s="24" t="n"/>
+      <c r="CM57" s="24" t="n"/>
+      <c r="CN57" s="24" t="n"/>
+      <c r="CO57" s="24" t="n"/>
+      <c r="CP57" s="24" t="n"/>
+      <c r="CQ57" s="24" t="n"/>
+      <c r="CR57" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="36" customHeight="1">
+      <c r="A58" s="24" t="inlineStr">
+        <is>
+          <t>967686712a774c57</t>
+        </is>
+      </c>
+      <c r="B58" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="C58" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T23:40Z</t>
+        </is>
+      </c>
+      <c r="D58" s="24" t="inlineStr">
+        <is>
+          <t>401816393</t>
+        </is>
+      </c>
+      <c r="E58" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F58" s="24" t="inlineStr">
+        <is>
+          <t>Pittsburgh Pirates</t>
+        </is>
+      </c>
+      <c r="G58" s="24" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="H58" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I58" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J58" s="25" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="K58" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L58" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="M58" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N58" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O58" s="28" t="n">
+        <v>0.52237</v>
+      </c>
+      <c r="P58" s="28" t="n">
+        <v>0.05172</v>
+      </c>
+      <c r="Q58" s="28" t="n">
+        <v>0.02237</v>
+      </c>
+      <c r="R58" s="26" t="n">
+        <v>31</v>
+      </c>
+      <c r="S58" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T58" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v2</t>
+        </is>
+      </c>
+      <c r="U58" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V58" s="24" t="n"/>
+      <c r="W58" s="26" t="n"/>
+      <c r="X58" s="26" t="n"/>
+      <c r="Y58" s="25" t="n"/>
+      <c r="Z58" s="26" t="n"/>
+      <c r="AA58" s="28" t="n"/>
+      <c r="AB58" s="28" t="n"/>
+      <c r="AC58" s="30" t="n"/>
+      <c r="AD58" s="24" t="n"/>
+      <c r="AE58" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Totals: Trend Engine projected 3.58-4.00; raw selected-side p=0.5422, calibrated p=0.5224.</t>
+        </is>
+      </c>
+      <c r="AF58" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG58" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH58" s="24" t="n"/>
+      <c r="AI58" s="31" t="n"/>
+      <c r="AJ58" s="31" t="n"/>
+      <c r="AK58" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL58" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM58" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN58" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO58" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP58" s="24" t="inlineStr">
+        <is>
+          <t>mlb-pit</t>
+        </is>
+      </c>
+      <c r="AQ58" s="24" t="inlineStr">
+        <is>
+          <t>Pittsburgh Pirates</t>
+        </is>
+      </c>
+      <c r="AR58" s="24" t="inlineStr">
+        <is>
+          <t>Pittsburgh Pirates</t>
+        </is>
+      </c>
+      <c r="AS58" s="24" t="inlineStr">
+        <is>
+          <t>mlb-mil</t>
+        </is>
+      </c>
+      <c r="AT58" s="24" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="AU58" s="24" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="AV58" s="24" t="n"/>
+      <c r="AW58" s="24" t="n"/>
+      <c r="AX58" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY58" s="24" t="n"/>
+      <c r="AZ58" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA58" s="24" t="inlineStr">
+        <is>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+        </is>
+      </c>
+      <c r="BB58" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC58" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v2</t>
+        </is>
+      </c>
+      <c r="BD58" s="24" t="inlineStr">
+        <is>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+        </is>
+      </c>
+      <c r="BE58" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF58" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG58" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH58" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="BI58" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ58" s="25" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BK58" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="BL58" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM58" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN58" s="28" t="n">
+        <v>0.497512</v>
+      </c>
+      <c r="BO58" s="28" t="n"/>
+      <c r="BP58" s="25" t="n"/>
+      <c r="BQ58" s="27" t="n"/>
+      <c r="BR58" s="28" t="n"/>
+      <c r="BS58" s="28" t="n"/>
+      <c r="BT58" s="28" t="n"/>
+      <c r="BU58" s="25" t="n"/>
+      <c r="BV58" s="29" t="n"/>
+      <c r="BW58" s="24" t="n"/>
+      <c r="BX58" s="30" t="n"/>
+      <c r="BY58" s="27" t="n"/>
+      <c r="BZ58" s="24" t="n"/>
+      <c r="CA58" s="31" t="n"/>
+      <c r="CB58" s="24" t="n"/>
+      <c r="CC58" s="24" t="n"/>
+      <c r="CD58" s="24" t="n"/>
+      <c r="CE58" s="24" t="n"/>
+      <c r="CF58" s="24" t="n"/>
+      <c r="CG58" s="24" t="n"/>
+      <c r="CH58" s="24" t="n"/>
+      <c r="CI58" s="24" t="n"/>
+      <c r="CJ58" s="24" t="n"/>
+      <c r="CK58" s="24" t="n"/>
+      <c r="CL58" s="24" t="n"/>
+      <c r="CM58" s="24" t="n"/>
+      <c r="CN58" s="24" t="n"/>
+      <c r="CO58" s="24" t="n"/>
+      <c r="CP58" s="24" t="n"/>
+      <c r="CQ58" s="24" t="n"/>
+      <c r="CR58" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="36" customHeight="1">
+      <c r="A59" s="24" t="inlineStr">
+        <is>
+          <t>5234f00872d54269</t>
+        </is>
+      </c>
+      <c r="B59" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="C59" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T00:05Z</t>
+        </is>
+      </c>
+      <c r="D59" s="24" t="inlineStr">
+        <is>
+          <t>401816391</t>
+        </is>
+      </c>
+      <c r="E59" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F59" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="G59" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Cubs</t>
+        </is>
+      </c>
+      <c r="H59" s="24" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="I59" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J59" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K59" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L59" s="26" t="n">
+        <v>120</v>
+      </c>
+      <c r="M59" s="27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N59" s="28" t="n">
+        <v>0.454545</v>
+      </c>
+      <c r="O59" s="28" t="n">
+        <v>0.626973</v>
+      </c>
+      <c r="P59" s="28" t="n">
+        <v>0.042131</v>
+      </c>
+      <c r="Q59" s="28" t="n">
+        <v>0.172428</v>
+      </c>
+      <c r="R59" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S59" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T59" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v2</t>
+        </is>
+      </c>
+      <c r="U59" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V59" s="24" t="n"/>
+      <c r="W59" s="26" t="n"/>
+      <c r="X59" s="26" t="n"/>
+      <c r="Y59" s="25" t="n"/>
+      <c r="Z59" s="26" t="n"/>
+      <c r="AA59" s="28" t="n"/>
+      <c r="AB59" s="28" t="n"/>
+      <c r="AC59" s="30" t="n"/>
+      <c r="AD59" s="24" t="n"/>
+      <c r="AE59" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Margin: Trend Engine projected 3.82-3.91; raw selected-side p=0.6935, calibrated p=0.6270.</t>
+        </is>
+      </c>
+      <c r="AF59" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG59" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH59" s="24" t="n"/>
+      <c r="AI59" s="31" t="n"/>
+      <c r="AJ59" s="31" t="n"/>
+      <c r="AK59" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL59" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM59" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN59" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO59" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP59" s="24" t="inlineStr">
+        <is>
+          <t>mlb-lad</t>
+        </is>
+      </c>
+      <c r="AQ59" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="AR59" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="AS59" s="24" t="inlineStr">
+        <is>
+          <t>mlb-chc</t>
+        </is>
+      </c>
+      <c r="AT59" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Cubs</t>
+        </is>
+      </c>
+      <c r="AU59" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Cubs</t>
+        </is>
+      </c>
+      <c r="AV59" s="24" t="n"/>
+      <c r="AW59" s="24" t="n"/>
+      <c r="AX59" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY59" s="24" t="n"/>
+      <c r="AZ59" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA59" s="24" t="inlineStr">
+        <is>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+        </is>
+      </c>
+      <c r="BB59" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC59" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v2</t>
+        </is>
+      </c>
+      <c r="BD59" s="24" t="inlineStr">
+        <is>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+        </is>
+      </c>
+      <c r="BE59" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF59" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG59" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH59" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="BI59" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ59" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK59" s="26" t="n">
+        <v>120</v>
+      </c>
+      <c r="BL59" s="27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BM59" s="28" t="n">
+        <v>0.454545</v>
+      </c>
+      <c r="BN59" s="28" t="n">
+        <v>0.452736</v>
+      </c>
+      <c r="BO59" s="28" t="n"/>
+      <c r="BP59" s="25" t="n"/>
+      <c r="BQ59" s="27" t="n"/>
+      <c r="BR59" s="28" t="n"/>
+      <c r="BS59" s="28" t="n"/>
+      <c r="BT59" s="28" t="n"/>
+      <c r="BU59" s="25" t="n"/>
+      <c r="BV59" s="29" t="n"/>
+      <c r="BW59" s="24" t="n"/>
+      <c r="BX59" s="30" t="n"/>
+      <c r="BY59" s="27" t="n"/>
+      <c r="BZ59" s="24" t="n"/>
+      <c r="CA59" s="31" t="n"/>
+      <c r="CB59" s="24" t="n"/>
+      <c r="CC59" s="24" t="n"/>
+      <c r="CD59" s="24" t="n"/>
+      <c r="CE59" s="24" t="n"/>
+      <c r="CF59" s="24" t="n"/>
+      <c r="CG59" s="24" t="n"/>
+      <c r="CH59" s="24" t="n"/>
+      <c r="CI59" s="24" t="n"/>
+      <c r="CJ59" s="24" t="n"/>
+      <c r="CK59" s="24" t="n"/>
+      <c r="CL59" s="24" t="n"/>
+      <c r="CM59" s="24" t="n"/>
+      <c r="CN59" s="24" t="n"/>
+      <c r="CO59" s="24" t="n"/>
+      <c r="CP59" s="24" t="n"/>
+      <c r="CQ59" s="24" t="n"/>
+      <c r="CR59" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="36" customHeight="1">
+      <c r="A60" s="24" t="inlineStr">
+        <is>
+          <t>4d77dd83a07c4a3f</t>
+        </is>
+      </c>
+      <c r="B60" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="C60" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T00:05Z</t>
+        </is>
+      </c>
+      <c r="D60" s="24" t="inlineStr">
+        <is>
+          <t>401816391</t>
+        </is>
+      </c>
+      <c r="E60" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F60" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="G60" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Cubs</t>
+        </is>
+      </c>
+      <c r="H60" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I60" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J60" s="25" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K60" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L60" s="26" t="n">
+        <v>111</v>
+      </c>
+      <c r="M60" s="27" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="N60" s="28" t="n">
+        <v>0.473934</v>
+      </c>
+      <c r="O60" s="28" t="n">
+        <v>0.546255</v>
+      </c>
+      <c r="P60" s="28" t="n">
+        <v>0.042131</v>
+      </c>
+      <c r="Q60" s="28" t="n">
+        <v>0.072321</v>
+      </c>
+      <c r="R60" s="26" t="n">
+        <v>62</v>
+      </c>
+      <c r="S60" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T60" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v2</t>
+        </is>
+      </c>
+      <c r="U60" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V60" s="24" t="n"/>
+      <c r="W60" s="26" t="n"/>
+      <c r="X60" s="26" t="n"/>
+      <c r="Y60" s="25" t="n"/>
+      <c r="Z60" s="26" t="n"/>
+      <c r="AA60" s="28" t="n"/>
+      <c r="AB60" s="28" t="n"/>
+      <c r="AC60" s="30" t="n"/>
+      <c r="AD60" s="24" t="n"/>
+      <c r="AE60" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Totals: Trend Engine projected 3.82-3.91; raw selected-side p=0.6121, calibrated p=0.5463.</t>
+        </is>
+      </c>
+      <c r="AF60" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG60" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH60" s="24" t="n"/>
+      <c r="AI60" s="31" t="n"/>
+      <c r="AJ60" s="31" t="n"/>
+      <c r="AK60" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL60" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM60" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN60" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO60" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP60" s="24" t="inlineStr">
+        <is>
+          <t>mlb-lad</t>
+        </is>
+      </c>
+      <c r="AQ60" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="AR60" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="AS60" s="24" t="inlineStr">
+        <is>
+          <t>mlb-chc</t>
+        </is>
+      </c>
+      <c r="AT60" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Cubs</t>
+        </is>
+      </c>
+      <c r="AU60" s="24" t="inlineStr">
+        <is>
+          <t>Chicago Cubs</t>
+        </is>
+      </c>
+      <c r="AV60" s="24" t="n"/>
+      <c r="AW60" s="24" t="n"/>
+      <c r="AX60" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY60" s="24" t="n"/>
+      <c r="AZ60" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA60" s="24" t="inlineStr">
+        <is>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+        </is>
+      </c>
+      <c r="BB60" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC60" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v2</t>
+        </is>
+      </c>
+      <c r="BD60" s="24" t="inlineStr">
+        <is>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+        </is>
+      </c>
+      <c r="BE60" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF60" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG60" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH60" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="BI60" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ60" s="25" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BK60" s="26" t="n">
+        <v>111</v>
+      </c>
+      <c r="BL60" s="27" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BM60" s="28" t="n">
+        <v>0.473934</v>
+      </c>
+      <c r="BN60" s="28" t="n">
+        <v>0.472637</v>
+      </c>
+      <c r="BO60" s="28" t="n"/>
+      <c r="BP60" s="25" t="n"/>
+      <c r="BQ60" s="27" t="n"/>
+      <c r="BR60" s="28" t="n"/>
+      <c r="BS60" s="28" t="n"/>
+      <c r="BT60" s="28" t="n"/>
+      <c r="BU60" s="25" t="n"/>
+      <c r="BV60" s="29" t="n"/>
+      <c r="BW60" s="24" t="n"/>
+      <c r="BX60" s="30" t="n"/>
+      <c r="BY60" s="27" t="n"/>
+      <c r="BZ60" s="24" t="n"/>
+      <c r="CA60" s="31" t="n"/>
+      <c r="CB60" s="24" t="n"/>
+      <c r="CC60" s="24" t="n"/>
+      <c r="CD60" s="24" t="n"/>
+      <c r="CE60" s="24" t="n"/>
+      <c r="CF60" s="24" t="n"/>
+      <c r="CG60" s="24" t="n"/>
+      <c r="CH60" s="24" t="n"/>
+      <c r="CI60" s="24" t="n"/>
+      <c r="CJ60" s="24" t="n"/>
+      <c r="CK60" s="24" t="n"/>
+      <c r="CL60" s="24" t="n"/>
+      <c r="CM60" s="24" t="n"/>
+      <c r="CN60" s="24" t="n"/>
+      <c r="CO60" s="24" t="n"/>
+      <c r="CP60" s="24" t="n"/>
+      <c r="CQ60" s="24" t="n"/>
+      <c r="CR60" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="36" customHeight="1">
+      <c r="A61" s="24" t="inlineStr">
+        <is>
+          <t>a43107e1fc0542b5</t>
+        </is>
+      </c>
+      <c r="B61" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="C61" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T00:05Z</t>
+        </is>
+      </c>
+      <c r="D61" s="24" t="inlineStr">
+        <is>
+          <t>401816394</t>
+        </is>
+      </c>
+      <c r="E61" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F61" s="24" t="inlineStr">
+        <is>
+          <t>San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="G61" s="24" t="inlineStr">
+        <is>
+          <t>Texas Rangers</t>
+        </is>
+      </c>
+      <c r="H61" s="24" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="I61" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J61" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K61" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L61" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="M61" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="N61" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="O61" s="28" t="n">
+        <v>0.6599739999999999</v>
+      </c>
+      <c r="P61" s="28" t="n">
+        <v>0.05172</v>
+      </c>
+      <c r="Q61" s="28" t="n">
+        <v>0.110424</v>
+      </c>
+      <c r="R61" s="26" t="n">
+        <v>75</v>
+      </c>
+      <c r="S61" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T61" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v2</t>
+        </is>
+      </c>
+      <c r="U61" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V61" s="24" t="n"/>
+      <c r="W61" s="26" t="n"/>
+      <c r="X61" s="26" t="n"/>
+      <c r="Y61" s="25" t="n"/>
+      <c r="Z61" s="26" t="n"/>
+      <c r="AA61" s="28" t="n"/>
+      <c r="AB61" s="28" t="n"/>
+      <c r="AC61" s="30" t="n"/>
+      <c r="AD61" s="24" t="n"/>
+      <c r="AE61" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Margin: Trend Engine projected 4.98-4.16; raw selected-side p=0.7438, calibrated p=0.6600.</t>
+        </is>
+      </c>
+      <c r="AF61" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG61" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH61" s="24" t="n"/>
+      <c r="AI61" s="31" t="n"/>
+      <c r="AJ61" s="31" t="n"/>
+      <c r="AK61" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL61" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM61" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN61" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO61" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP61" s="24" t="inlineStr">
+        <is>
+          <t>mlb-sf</t>
+        </is>
+      </c>
+      <c r="AQ61" s="24" t="inlineStr">
+        <is>
+          <t>San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="AR61" s="24" t="inlineStr">
+        <is>
+          <t>San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="AS61" s="24" t="inlineStr">
+        <is>
+          <t>mlb-tex</t>
+        </is>
+      </c>
+      <c r="AT61" s="24" t="inlineStr">
+        <is>
+          <t>Texas Rangers</t>
+        </is>
+      </c>
+      <c r="AU61" s="24" t="inlineStr">
+        <is>
+          <t>Texas Rangers</t>
+        </is>
+      </c>
+      <c r="AV61" s="24" t="n"/>
+      <c r="AW61" s="24" t="n"/>
+      <c r="AX61" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY61" s="24" t="n"/>
+      <c r="AZ61" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA61" s="24" t="inlineStr">
+        <is>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+        </is>
+      </c>
+      <c r="BB61" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC61" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v2</t>
+        </is>
+      </c>
+      <c r="BD61" s="24" t="inlineStr">
+        <is>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+        </is>
+      </c>
+      <c r="BE61" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF61" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG61" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH61" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="BI61" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ61" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK61" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="BL61" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="BM61" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="BN61" s="28" t="n">
+        <v>0.547264</v>
+      </c>
+      <c r="BO61" s="28" t="n"/>
+      <c r="BP61" s="25" t="n"/>
+      <c r="BQ61" s="27" t="n"/>
+      <c r="BR61" s="28" t="n"/>
+      <c r="BS61" s="28" t="n"/>
+      <c r="BT61" s="28" t="n"/>
+      <c r="BU61" s="25" t="n"/>
+      <c r="BV61" s="29" t="n"/>
+      <c r="BW61" s="24" t="n"/>
+      <c r="BX61" s="30" t="n"/>
+      <c r="BY61" s="27" t="n"/>
+      <c r="BZ61" s="24" t="n"/>
+      <c r="CA61" s="31" t="n"/>
+      <c r="CB61" s="24" t="n"/>
+      <c r="CC61" s="24" t="n"/>
+      <c r="CD61" s="24" t="n"/>
+      <c r="CE61" s="24" t="n"/>
+      <c r="CF61" s="24" t="n"/>
+      <c r="CG61" s="24" t="n"/>
+      <c r="CH61" s="24" t="n"/>
+      <c r="CI61" s="24" t="n"/>
+      <c r="CJ61" s="24" t="n"/>
+      <c r="CK61" s="24" t="n"/>
+      <c r="CL61" s="24" t="n"/>
+      <c r="CM61" s="24" t="n"/>
+      <c r="CN61" s="24" t="n"/>
+      <c r="CO61" s="24" t="n"/>
+      <c r="CP61" s="24" t="n"/>
+      <c r="CQ61" s="24" t="n"/>
+      <c r="CR61" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="36" customHeight="1">
+      <c r="A62" s="24" t="inlineStr">
+        <is>
+          <t>8338675c774948c1</t>
+        </is>
+      </c>
+      <c r="B62" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="C62" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T00:05Z</t>
+        </is>
+      </c>
+      <c r="D62" s="24" t="inlineStr">
+        <is>
+          <t>401816394</t>
+        </is>
+      </c>
+      <c r="E62" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F62" s="24" t="inlineStr">
+        <is>
+          <t>San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="G62" s="24" t="inlineStr">
+        <is>
+          <t>Texas Rangers</t>
+        </is>
+      </c>
+      <c r="H62" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I62" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J62" s="25" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="K62" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L62" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="M62" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="N62" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="O62" s="28" t="n">
+        <v>0.544324</v>
+      </c>
+      <c r="P62" s="28" t="n">
+        <v>0.05172</v>
+      </c>
+      <c r="Q62" s="28" t="n">
+        <v>0.013808</v>
+      </c>
+      <c r="R62" s="26" t="n">
+        <v>27</v>
+      </c>
+      <c r="S62" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T62" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v2</t>
+        </is>
+      </c>
+      <c r="U62" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V62" s="24" t="n"/>
+      <c r="W62" s="26" t="n"/>
+      <c r="X62" s="26" t="n"/>
+      <c r="Y62" s="25" t="n"/>
+      <c r="Z62" s="26" t="n"/>
+      <c r="AA62" s="28" t="n"/>
+      <c r="AB62" s="28" t="n"/>
+      <c r="AC62" s="30" t="n"/>
+      <c r="AD62" s="24" t="n"/>
+      <c r="AE62" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Totals: Trend Engine projected 4.98-4.16; raw selected-side p=0.6065, calibrated p=0.5443.</t>
+        </is>
+      </c>
+      <c r="AF62" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG62" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH62" s="24" t="n"/>
+      <c r="AI62" s="31" t="n"/>
+      <c r="AJ62" s="31" t="n"/>
+      <c r="AK62" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL62" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM62" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN62" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO62" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP62" s="24" t="inlineStr">
+        <is>
+          <t>mlb-sf</t>
+        </is>
+      </c>
+      <c r="AQ62" s="24" t="inlineStr">
+        <is>
+          <t>San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="AR62" s="24" t="inlineStr">
+        <is>
+          <t>San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="AS62" s="24" t="inlineStr">
+        <is>
+          <t>mlb-tex</t>
+        </is>
+      </c>
+      <c r="AT62" s="24" t="inlineStr">
+        <is>
+          <t>Texas Rangers</t>
+        </is>
+      </c>
+      <c r="AU62" s="24" t="inlineStr">
+        <is>
+          <t>Texas Rangers</t>
+        </is>
+      </c>
+      <c r="AV62" s="24" t="n"/>
+      <c r="AW62" s="24" t="n"/>
+      <c r="AX62" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY62" s="24" t="n"/>
+      <c r="AZ62" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA62" s="24" t="inlineStr">
+        <is>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+        </is>
+      </c>
+      <c r="BB62" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC62" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v2</t>
+        </is>
+      </c>
+      <c r="BD62" s="24" t="inlineStr">
+        <is>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+        </is>
+      </c>
+      <c r="BE62" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF62" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG62" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH62" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="BI62" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ62" s="25" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BK62" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="BL62" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BM62" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="BN62" s="28" t="n">
+        <v>0.527363</v>
+      </c>
+      <c r="BO62" s="28" t="n"/>
+      <c r="BP62" s="25" t="n"/>
+      <c r="BQ62" s="27" t="n"/>
+      <c r="BR62" s="28" t="n"/>
+      <c r="BS62" s="28" t="n"/>
+      <c r="BT62" s="28" t="n"/>
+      <c r="BU62" s="25" t="n"/>
+      <c r="BV62" s="29" t="n"/>
+      <c r="BW62" s="24" t="n"/>
+      <c r="BX62" s="30" t="n"/>
+      <c r="BY62" s="27" t="n"/>
+      <c r="BZ62" s="24" t="n"/>
+      <c r="CA62" s="31" t="n"/>
+      <c r="CB62" s="24" t="n"/>
+      <c r="CC62" s="24" t="n"/>
+      <c r="CD62" s="24" t="n"/>
+      <c r="CE62" s="24" t="n"/>
+      <c r="CF62" s="24" t="n"/>
+      <c r="CG62" s="24" t="n"/>
+      <c r="CH62" s="24" t="n"/>
+      <c r="CI62" s="24" t="n"/>
+      <c r="CJ62" s="24" t="n"/>
+      <c r="CK62" s="24" t="n"/>
+      <c r="CL62" s="24" t="n"/>
+      <c r="CM62" s="24" t="n"/>
+      <c r="CN62" s="24" t="n"/>
+      <c r="CO62" s="24" t="n"/>
+      <c r="CP62" s="24" t="n"/>
+      <c r="CQ62" s="24" t="n"/>
+      <c r="CR62" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="36" customHeight="1">
+      <c r="A63" s="24" t="inlineStr">
+        <is>
+          <t>5f01a74edfff4cf0</t>
+        </is>
+      </c>
+      <c r="B63" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="C63" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T00:10Z</t>
+        </is>
+      </c>
+      <c r="D63" s="24" t="inlineStr">
+        <is>
+          <t>401816395</t>
+        </is>
+      </c>
+      <c r="E63" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F63" s="24" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays</t>
+        </is>
+      </c>
+      <c r="G63" s="24" t="inlineStr">
+        <is>
+          <t>Houston Astros</t>
+        </is>
+      </c>
+      <c r="H63" s="24" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="I63" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J63" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K63" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L63" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="M63" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="N63" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="O63" s="28" t="n">
+        <v>0.577995</v>
+      </c>
+      <c r="P63" s="28" t="n">
+        <v>0.05172</v>
+      </c>
+      <c r="Q63" s="28" t="n">
+        <v>-0.062293</v>
+      </c>
+      <c r="R63" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T63" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v2</t>
+        </is>
+      </c>
+      <c r="U63" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V63" s="24" t="n"/>
+      <c r="W63" s="26" t="n"/>
+      <c r="X63" s="26" t="n"/>
+      <c r="Y63" s="25" t="n"/>
+      <c r="Z63" s="26" t="n"/>
+      <c r="AA63" s="28" t="n"/>
+      <c r="AB63" s="28" t="n"/>
+      <c r="AC63" s="30" t="n"/>
+      <c r="AD63" s="24" t="n"/>
+      <c r="AE63" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Margin: Trend Engine projected 4.31-4.86; raw selected-side p=0.6188, calibrated p=0.5780.</t>
+        </is>
+      </c>
+      <c r="AF63" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG63" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH63" s="24" t="n"/>
+      <c r="AI63" s="31" t="n"/>
+      <c r="AJ63" s="31" t="n"/>
+      <c r="AK63" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL63" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM63" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN63" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO63" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP63" s="24" t="inlineStr">
+        <is>
+          <t>mlb-tor</t>
+        </is>
+      </c>
+      <c r="AQ63" s="24" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays</t>
+        </is>
+      </c>
+      <c r="AR63" s="24" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays</t>
+        </is>
+      </c>
+      <c r="AS63" s="24" t="inlineStr">
+        <is>
+          <t>mlb-hou</t>
+        </is>
+      </c>
+      <c r="AT63" s="24" t="inlineStr">
+        <is>
+          <t>Houston Astros</t>
+        </is>
+      </c>
+      <c r="AU63" s="24" t="inlineStr">
+        <is>
+          <t>Houston Astros</t>
+        </is>
+      </c>
+      <c r="AV63" s="24" t="n"/>
+      <c r="AW63" s="24" t="n"/>
+      <c r="AX63" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY63" s="24" t="n"/>
+      <c r="AZ63" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA63" s="24" t="inlineStr">
+        <is>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+        </is>
+      </c>
+      <c r="BB63" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC63" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v2</t>
+        </is>
+      </c>
+      <c r="BD63" s="24" t="inlineStr">
+        <is>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+        </is>
+      </c>
+      <c r="BE63" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF63" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG63" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH63" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="BI63" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ63" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK63" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="BL63" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="BM63" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="BN63" s="28" t="n">
+        <v>0.636816</v>
+      </c>
+      <c r="BO63" s="28" t="n"/>
+      <c r="BP63" s="25" t="n"/>
+      <c r="BQ63" s="27" t="n"/>
+      <c r="BR63" s="28" t="n"/>
+      <c r="BS63" s="28" t="n"/>
+      <c r="BT63" s="28" t="n"/>
+      <c r="BU63" s="25" t="n"/>
+      <c r="BV63" s="29" t="n"/>
+      <c r="BW63" s="24" t="n"/>
+      <c r="BX63" s="30" t="n"/>
+      <c r="BY63" s="27" t="n"/>
+      <c r="BZ63" s="24" t="n"/>
+      <c r="CA63" s="31" t="n"/>
+      <c r="CB63" s="24" t="n"/>
+      <c r="CC63" s="24" t="n"/>
+      <c r="CD63" s="24" t="n"/>
+      <c r="CE63" s="24" t="n"/>
+      <c r="CF63" s="24" t="n"/>
+      <c r="CG63" s="24" t="n"/>
+      <c r="CH63" s="24" t="n"/>
+      <c r="CI63" s="24" t="n"/>
+      <c r="CJ63" s="24" t="n"/>
+      <c r="CK63" s="24" t="n"/>
+      <c r="CL63" s="24" t="n"/>
+      <c r="CM63" s="24" t="n"/>
+      <c r="CN63" s="24" t="n"/>
+      <c r="CO63" s="24" t="n"/>
+      <c r="CP63" s="24" t="n"/>
+      <c r="CQ63" s="24" t="n"/>
+      <c r="CR63" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="36" customHeight="1">
+      <c r="A64" s="24" t="inlineStr">
+        <is>
+          <t>11bdcee0bebc494a</t>
+        </is>
+      </c>
+      <c r="B64" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="C64" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T00:10Z</t>
+        </is>
+      </c>
+      <c r="D64" s="24" t="inlineStr">
+        <is>
+          <t>401816395</t>
+        </is>
+      </c>
+      <c r="E64" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F64" s="24" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays</t>
+        </is>
+      </c>
+      <c r="G64" s="24" t="inlineStr">
+        <is>
+          <t>Houston Astros</t>
+        </is>
+      </c>
+      <c r="H64" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I64" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J64" s="25" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K64" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L64" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="M64" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="N64" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="O64" s="28" t="n">
+        <v>0.515724</v>
+      </c>
+      <c r="P64" s="28" t="n">
+        <v>0.05172</v>
+      </c>
+      <c r="Q64" s="28" t="n">
+        <v>0.025528</v>
+      </c>
+      <c r="R64" s="26" t="n">
+        <v>33</v>
+      </c>
+      <c r="S64" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T64" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v2</t>
+        </is>
+      </c>
+      <c r="U64" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V64" s="24" t="n"/>
+      <c r="W64" s="26" t="n"/>
+      <c r="X64" s="26" t="n"/>
+      <c r="Y64" s="25" t="n"/>
+      <c r="Z64" s="26" t="n"/>
+      <c r="AA64" s="28" t="n"/>
+      <c r="AB64" s="28" t="n"/>
+      <c r="AC64" s="30" t="n"/>
+      <c r="AD64" s="24" t="n"/>
+      <c r="AE64" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Totals: Trend Engine projected 4.31-4.86; raw selected-side p=0.5228, calibrated p=0.5157.</t>
+        </is>
+      </c>
+      <c r="AF64" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG64" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH64" s="24" t="n"/>
+      <c r="AI64" s="31" t="n"/>
+      <c r="AJ64" s="31" t="n"/>
+      <c r="AK64" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL64" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM64" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN64" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO64" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP64" s="24" t="inlineStr">
+        <is>
+          <t>mlb-tor</t>
+        </is>
+      </c>
+      <c r="AQ64" s="24" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays</t>
+        </is>
+      </c>
+      <c r="AR64" s="24" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays</t>
+        </is>
+      </c>
+      <c r="AS64" s="24" t="inlineStr">
+        <is>
+          <t>mlb-hou</t>
+        </is>
+      </c>
+      <c r="AT64" s="24" t="inlineStr">
+        <is>
+          <t>Houston Astros</t>
+        </is>
+      </c>
+      <c r="AU64" s="24" t="inlineStr">
+        <is>
+          <t>Houston Astros</t>
+        </is>
+      </c>
+      <c r="AV64" s="24" t="n"/>
+      <c r="AW64" s="24" t="n"/>
+      <c r="AX64" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY64" s="24" t="n"/>
+      <c r="AZ64" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA64" s="24" t="inlineStr">
+        <is>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+        </is>
+      </c>
+      <c r="BB64" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC64" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v2</t>
+        </is>
+      </c>
+      <c r="BD64" s="24" t="inlineStr">
+        <is>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+        </is>
+      </c>
+      <c r="BE64" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF64" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG64" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH64" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="BI64" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ64" s="25" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BK64" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="BL64" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BM64" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="BN64" s="28" t="n">
+        <v>0.487562</v>
+      </c>
+      <c r="BO64" s="28" t="n"/>
+      <c r="BP64" s="25" t="n"/>
+      <c r="BQ64" s="27" t="n"/>
+      <c r="BR64" s="28" t="n"/>
+      <c r="BS64" s="28" t="n"/>
+      <c r="BT64" s="28" t="n"/>
+      <c r="BU64" s="25" t="n"/>
+      <c r="BV64" s="29" t="n"/>
+      <c r="BW64" s="24" t="n"/>
+      <c r="BX64" s="30" t="n"/>
+      <c r="BY64" s="27" t="n"/>
+      <c r="BZ64" s="24" t="n"/>
+      <c r="CA64" s="31" t="n"/>
+      <c r="CB64" s="24" t="n"/>
+      <c r="CC64" s="24" t="n"/>
+      <c r="CD64" s="24" t="n"/>
+      <c r="CE64" s="24" t="n"/>
+      <c r="CF64" s="24" t="n"/>
+      <c r="CG64" s="24" t="n"/>
+      <c r="CH64" s="24" t="n"/>
+      <c r="CI64" s="24" t="n"/>
+      <c r="CJ64" s="24" t="n"/>
+      <c r="CK64" s="24" t="n"/>
+      <c r="CL64" s="24" t="n"/>
+      <c r="CM64" s="24" t="n"/>
+      <c r="CN64" s="24" t="n"/>
+      <c r="CO64" s="24" t="n"/>
+      <c r="CP64" s="24" t="n"/>
+      <c r="CQ64" s="24" t="n"/>
+      <c r="CR64" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="36" customHeight="1">
+      <c r="A65" s="24" t="inlineStr">
+        <is>
+          <t>42347c86496a4115</t>
+        </is>
+      </c>
+      <c r="B65" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="C65" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T00:40Z</t>
+        </is>
+      </c>
+      <c r="D65" s="24" t="inlineStr">
+        <is>
+          <t>401816396</t>
+        </is>
+      </c>
+      <c r="E65" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F65" s="24" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays</t>
+        </is>
+      </c>
+      <c r="G65" s="24" t="inlineStr">
+        <is>
+          <t>Colorado Rockies</t>
+        </is>
+      </c>
+      <c r="H65" s="24" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="I65" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J65" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K65" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L65" s="26" t="n">
+        <v>-120</v>
+      </c>
+      <c r="M65" s="27" t="n">
+        <v>1.833333</v>
+      </c>
+      <c r="N65" s="28" t="n">
+        <v>0.545455</v>
+      </c>
+      <c r="O65" s="28" t="n">
+        <v>0.687662</v>
+      </c>
+      <c r="P65" s="28" t="n">
+        <v>0.05172</v>
+      </c>
+      <c r="Q65" s="28" t="n">
+        <v>0.142207</v>
+      </c>
+      <c r="R65" s="26" t="n">
+        <v>92</v>
+      </c>
+      <c r="S65" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T65" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v2</t>
+        </is>
+      </c>
+      <c r="U65" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V65" s="24" t="n"/>
+      <c r="W65" s="26" t="n"/>
+      <c r="X65" s="26" t="n"/>
+      <c r="Y65" s="25" t="n"/>
+      <c r="Z65" s="26" t="n"/>
+      <c r="AA65" s="28" t="n"/>
+      <c r="AB65" s="28" t="n"/>
+      <c r="AC65" s="30" t="n"/>
+      <c r="AD65" s="24" t="n"/>
+      <c r="AE65" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Margin: Trend Engine projected 4.49-6.29; raw selected-side p=0.7860, calibrated p=0.6877.</t>
+        </is>
+      </c>
+      <c r="AF65" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG65" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH65" s="24" t="n"/>
+      <c r="AI65" s="31" t="n"/>
+      <c r="AJ65" s="31" t="n"/>
+      <c r="AK65" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL65" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM65" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN65" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO65" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP65" s="24" t="inlineStr">
+        <is>
+          <t>mlb-tb</t>
+        </is>
+      </c>
+      <c r="AQ65" s="24" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays</t>
+        </is>
+      </c>
+      <c r="AR65" s="24" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays</t>
+        </is>
+      </c>
+      <c r="AS65" s="24" t="inlineStr">
+        <is>
+          <t>mlb-col</t>
+        </is>
+      </c>
+      <c r="AT65" s="24" t="inlineStr">
+        <is>
+          <t>Colorado Rockies</t>
+        </is>
+      </c>
+      <c r="AU65" s="24" t="inlineStr">
+        <is>
+          <t>Colorado Rockies</t>
+        </is>
+      </c>
+      <c r="AV65" s="24" t="n"/>
+      <c r="AW65" s="24" t="n"/>
+      <c r="AX65" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY65" s="24" t="n"/>
+      <c r="AZ65" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA65" s="24" t="inlineStr">
+        <is>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+        </is>
+      </c>
+      <c r="BB65" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC65" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v2</t>
+        </is>
+      </c>
+      <c r="BD65" s="24" t="inlineStr">
+        <is>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+        </is>
+      </c>
+      <c r="BE65" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF65" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG65" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH65" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="BI65" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ65" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK65" s="26" t="n">
+        <v>-120</v>
+      </c>
+      <c r="BL65" s="27" t="n">
+        <v>1.833333</v>
+      </c>
+      <c r="BM65" s="28" t="n">
+        <v>0.545455</v>
+      </c>
+      <c r="BN65" s="28" t="n">
+        <v>0.542289</v>
+      </c>
+      <c r="BO65" s="28" t="n"/>
+      <c r="BP65" s="25" t="n"/>
+      <c r="BQ65" s="27" t="n"/>
+      <c r="BR65" s="28" t="n"/>
+      <c r="BS65" s="28" t="n"/>
+      <c r="BT65" s="28" t="n"/>
+      <c r="BU65" s="25" t="n"/>
+      <c r="BV65" s="29" t="n"/>
+      <c r="BW65" s="24" t="n"/>
+      <c r="BX65" s="30" t="n"/>
+      <c r="BY65" s="27" t="n"/>
+      <c r="BZ65" s="24" t="n"/>
+      <c r="CA65" s="31" t="n"/>
+      <c r="CB65" s="24" t="n"/>
+      <c r="CC65" s="24" t="n"/>
+      <c r="CD65" s="24" t="n"/>
+      <c r="CE65" s="24" t="n"/>
+      <c r="CF65" s="24" t="n"/>
+      <c r="CG65" s="24" t="n"/>
+      <c r="CH65" s="24" t="n"/>
+      <c r="CI65" s="24" t="n"/>
+      <c r="CJ65" s="24" t="n"/>
+      <c r="CK65" s="24" t="n"/>
+      <c r="CL65" s="24" t="n"/>
+      <c r="CM65" s="24" t="n"/>
+      <c r="CN65" s="24" t="n"/>
+      <c r="CO65" s="24" t="n"/>
+      <c r="CP65" s="24" t="n"/>
+      <c r="CQ65" s="24" t="n"/>
+      <c r="CR65" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="36" customHeight="1">
+      <c r="A66" s="24" t="inlineStr">
+        <is>
+          <t>f3472920e7b045eb</t>
+        </is>
+      </c>
+      <c r="B66" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="C66" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T00:40Z</t>
+        </is>
+      </c>
+      <c r="D66" s="24" t="inlineStr">
+        <is>
+          <t>401816396</t>
+        </is>
+      </c>
+      <c r="E66" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F66" s="24" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays</t>
+        </is>
+      </c>
+      <c r="G66" s="24" t="inlineStr">
+        <is>
+          <t>Colorado Rockies</t>
+        </is>
+      </c>
+      <c r="H66" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I66" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J66" s="25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="K66" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L66" s="26" t="n">
+        <v>-120</v>
+      </c>
+      <c r="M66" s="27" t="n">
+        <v>1.833333</v>
+      </c>
+      <c r="N66" s="28" t="n">
+        <v>0.545455</v>
+      </c>
+      <c r="O66" s="28" t="n">
+        <v>0.544956</v>
+      </c>
+      <c r="P66" s="28" t="n">
+        <v>0.05172</v>
+      </c>
+      <c r="Q66" s="28" t="n">
+        <v>-0.000499</v>
+      </c>
+      <c r="R66" s="26" t="n">
+        <v>20</v>
+      </c>
+      <c r="S66" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T66" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v2</t>
+        </is>
+      </c>
+      <c r="U66" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V66" s="24" t="n"/>
+      <c r="W66" s="26" t="n"/>
+      <c r="X66" s="26" t="n"/>
+      <c r="Y66" s="25" t="n"/>
+      <c r="Z66" s="26" t="n"/>
+      <c r="AA66" s="28" t="n"/>
+      <c r="AB66" s="28" t="n"/>
+      <c r="AC66" s="30" t="n"/>
+      <c r="AD66" s="24" t="n"/>
+      <c r="AE66" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Totals: Trend Engine projected 4.49-6.29; raw selected-side p=0.6083, calibrated p=0.5450.</t>
+        </is>
+      </c>
+      <c r="AF66" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG66" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH66" s="24" t="n"/>
+      <c r="AI66" s="31" t="n"/>
+      <c r="AJ66" s="31" t="n"/>
+      <c r="AK66" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL66" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM66" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN66" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO66" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP66" s="24" t="inlineStr">
+        <is>
+          <t>mlb-tb</t>
+        </is>
+      </c>
+      <c r="AQ66" s="24" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays</t>
+        </is>
+      </c>
+      <c r="AR66" s="24" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays</t>
+        </is>
+      </c>
+      <c r="AS66" s="24" t="inlineStr">
+        <is>
+          <t>mlb-col</t>
+        </is>
+      </c>
+      <c r="AT66" s="24" t="inlineStr">
+        <is>
+          <t>Colorado Rockies</t>
+        </is>
+      </c>
+      <c r="AU66" s="24" t="inlineStr">
+        <is>
+          <t>Colorado Rockies</t>
+        </is>
+      </c>
+      <c r="AV66" s="24" t="n"/>
+      <c r="AW66" s="24" t="n"/>
+      <c r="AX66" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY66" s="24" t="n"/>
+      <c r="AZ66" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA66" s="24" t="inlineStr">
+        <is>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+        </is>
+      </c>
+      <c r="BB66" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC66" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v2</t>
+        </is>
+      </c>
+      <c r="BD66" s="24" t="inlineStr">
+        <is>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+        </is>
+      </c>
+      <c r="BE66" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF66" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG66" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH66" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="BI66" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ66" s="25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK66" s="26" t="n">
+        <v>-120</v>
+      </c>
+      <c r="BL66" s="27" t="n">
+        <v>1.833333</v>
+      </c>
+      <c r="BM66" s="28" t="n">
+        <v>0.545455</v>
+      </c>
+      <c r="BN66" s="28" t="n">
+        <v>0.542289</v>
+      </c>
+      <c r="BO66" s="28" t="n"/>
+      <c r="BP66" s="25" t="n"/>
+      <c r="BQ66" s="27" t="n"/>
+      <c r="BR66" s="28" t="n"/>
+      <c r="BS66" s="28" t="n"/>
+      <c r="BT66" s="28" t="n"/>
+      <c r="BU66" s="25" t="n"/>
+      <c r="BV66" s="29" t="n"/>
+      <c r="BW66" s="24" t="n"/>
+      <c r="BX66" s="30" t="n"/>
+      <c r="BY66" s="27" t="n"/>
+      <c r="BZ66" s="24" t="n"/>
+      <c r="CA66" s="31" t="n"/>
+      <c r="CB66" s="24" t="n"/>
+      <c r="CC66" s="24" t="n"/>
+      <c r="CD66" s="24" t="n"/>
+      <c r="CE66" s="24" t="n"/>
+      <c r="CF66" s="24" t="n"/>
+      <c r="CG66" s="24" t="n"/>
+      <c r="CH66" s="24" t="n"/>
+      <c r="CI66" s="24" t="n"/>
+      <c r="CJ66" s="24" t="n"/>
+      <c r="CK66" s="24" t="n"/>
+      <c r="CL66" s="24" t="n"/>
+      <c r="CM66" s="24" t="n"/>
+      <c r="CN66" s="24" t="n"/>
+      <c r="CO66" s="24" t="n"/>
+      <c r="CP66" s="24" t="n"/>
+      <c r="CQ66" s="24" t="n"/>
+      <c r="CR66" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="36" customHeight="1">
+      <c r="A67" s="24" t="inlineStr">
+        <is>
+          <t>183c547310514240</t>
+        </is>
+      </c>
+      <c r="B67" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="C67" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T01:40Z</t>
+        </is>
+      </c>
+      <c r="D67" s="24" t="inlineStr">
+        <is>
+          <t>401816398</t>
+        </is>
+      </c>
+      <c r="E67" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F67" s="24" t="inlineStr">
+        <is>
+          <t>San Diego Padres</t>
+        </is>
+      </c>
+      <c r="G67" s="24" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="H67" s="24" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="I67" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J67" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K67" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L67" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="M67" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="N67" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="O67" s="28" t="n">
+        <v>0.5404330000000001</v>
+      </c>
+      <c r="P67" s="28" t="n">
+        <v>0.042131</v>
+      </c>
+      <c r="Q67" s="28" t="n">
+        <v>-0.099855</v>
+      </c>
+      <c r="R67" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T67" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v2</t>
+        </is>
+      </c>
+      <c r="U67" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V67" s="24" t="n"/>
+      <c r="W67" s="26" t="n"/>
+      <c r="X67" s="26" t="n"/>
+      <c r="Y67" s="25" t="n"/>
+      <c r="Z67" s="26" t="n"/>
+      <c r="AA67" s="28" t="n"/>
+      <c r="AB67" s="28" t="n"/>
+      <c r="AC67" s="30" t="n"/>
+      <c r="AD67" s="24" t="n"/>
+      <c r="AE67" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Margin: Trend Engine projected 4.09-5.16; raw selected-side p=0.5615, calibrated p=0.5404.</t>
+        </is>
+      </c>
+      <c r="AF67" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG67" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH67" s="24" t="n"/>
+      <c r="AI67" s="31" t="n"/>
+      <c r="AJ67" s="31" t="n"/>
+      <c r="AK67" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL67" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM67" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN67" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO67" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP67" s="24" t="inlineStr">
+        <is>
+          <t>mlb-sd</t>
+        </is>
+      </c>
+      <c r="AQ67" s="24" t="inlineStr">
+        <is>
+          <t>San Diego Padres</t>
+        </is>
+      </c>
+      <c r="AR67" s="24" t="inlineStr">
+        <is>
+          <t>San Diego Padres</t>
+        </is>
+      </c>
+      <c r="AS67" s="24" t="inlineStr">
+        <is>
+          <t>mlb-ari</t>
+        </is>
+      </c>
+      <c r="AT67" s="24" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="AU67" s="24" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="AV67" s="24" t="n"/>
+      <c r="AW67" s="24" t="n"/>
+      <c r="AX67" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY67" s="24" t="n"/>
+      <c r="AZ67" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA67" s="24" t="inlineStr">
+        <is>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+        </is>
+      </c>
+      <c r="BB67" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC67" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v2</t>
+        </is>
+      </c>
+      <c r="BD67" s="24" t="inlineStr">
+        <is>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+        </is>
+      </c>
+      <c r="BE67" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF67" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG67" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH67" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="BI67" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ67" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK67" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="BL67" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="BM67" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="BN67" s="28" t="n">
+        <v>0.636816</v>
+      </c>
+      <c r="BO67" s="28" t="n"/>
+      <c r="BP67" s="25" t="n"/>
+      <c r="BQ67" s="27" t="n"/>
+      <c r="BR67" s="28" t="n"/>
+      <c r="BS67" s="28" t="n"/>
+      <c r="BT67" s="28" t="n"/>
+      <c r="BU67" s="25" t="n"/>
+      <c r="BV67" s="29" t="n"/>
+      <c r="BW67" s="24" t="n"/>
+      <c r="BX67" s="30" t="n"/>
+      <c r="BY67" s="27" t="n"/>
+      <c r="BZ67" s="24" t="n"/>
+      <c r="CA67" s="31" t="n"/>
+      <c r="CB67" s="24" t="n"/>
+      <c r="CC67" s="24" t="n"/>
+      <c r="CD67" s="24" t="n"/>
+      <c r="CE67" s="24" t="n"/>
+      <c r="CF67" s="24" t="n"/>
+      <c r="CG67" s="24" t="n"/>
+      <c r="CH67" s="24" t="n"/>
+      <c r="CI67" s="24" t="n"/>
+      <c r="CJ67" s="24" t="n"/>
+      <c r="CK67" s="24" t="n"/>
+      <c r="CL67" s="24" t="n"/>
+      <c r="CM67" s="24" t="n"/>
+      <c r="CN67" s="24" t="n"/>
+      <c r="CO67" s="24" t="n"/>
+      <c r="CP67" s="24" t="n"/>
+      <c r="CQ67" s="24" t="n"/>
+      <c r="CR67" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="36" customHeight="1">
+      <c r="A68" s="24" t="inlineStr">
+        <is>
+          <t>3323c6ba254a4283</t>
+        </is>
+      </c>
+      <c r="B68" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="C68" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T01:40Z</t>
+        </is>
+      </c>
+      <c r="D68" s="24" t="inlineStr">
+        <is>
+          <t>401816398</t>
+        </is>
+      </c>
+      <c r="E68" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F68" s="24" t="inlineStr">
+        <is>
+          <t>San Diego Padres</t>
+        </is>
+      </c>
+      <c r="G68" s="24" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="H68" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I68" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J68" s="25" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K68" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L68" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="M68" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="N68" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="O68" s="28" t="n">
+        <v>0.520815</v>
+      </c>
+      <c r="P68" s="28" t="n">
+        <v>0.042131</v>
+      </c>
+      <c r="Q68" s="28" t="n">
+        <v>0.011011</v>
+      </c>
+      <c r="R68" s="26" t="n">
+        <v>31</v>
+      </c>
+      <c r="S68" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T68" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v2</t>
+        </is>
+      </c>
+      <c r="U68" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V68" s="24" t="n"/>
+      <c r="W68" s="26" t="n"/>
+      <c r="X68" s="26" t="n"/>
+      <c r="Y68" s="25" t="n"/>
+      <c r="Z68" s="26" t="n"/>
+      <c r="AA68" s="28" t="n"/>
+      <c r="AB68" s="28" t="n"/>
+      <c r="AC68" s="30" t="n"/>
+      <c r="AD68" s="24" t="n"/>
+      <c r="AE68" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Totals: Trend Engine projected 4.09-5.16; raw selected-side p=0.5376, calibrated p=0.5208.</t>
+        </is>
+      </c>
+      <c r="AF68" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG68" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH68" s="24" t="n"/>
+      <c r="AI68" s="31" t="n"/>
+      <c r="AJ68" s="31" t="n"/>
+      <c r="AK68" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL68" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM68" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN68" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO68" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP68" s="24" t="inlineStr">
+        <is>
+          <t>mlb-sd</t>
+        </is>
+      </c>
+      <c r="AQ68" s="24" t="inlineStr">
+        <is>
+          <t>San Diego Padres</t>
+        </is>
+      </c>
+      <c r="AR68" s="24" t="inlineStr">
+        <is>
+          <t>San Diego Padres</t>
+        </is>
+      </c>
+      <c r="AS68" s="24" t="inlineStr">
+        <is>
+          <t>mlb-ari</t>
+        </is>
+      </c>
+      <c r="AT68" s="24" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="AU68" s="24" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="AV68" s="24" t="n"/>
+      <c r="AW68" s="24" t="n"/>
+      <c r="AX68" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY68" s="24" t="n"/>
+      <c r="AZ68" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA68" s="24" t="inlineStr">
+        <is>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+        </is>
+      </c>
+      <c r="BB68" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC68" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v2</t>
+        </is>
+      </c>
+      <c r="BD68" s="24" t="inlineStr">
+        <is>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+        </is>
+      </c>
+      <c r="BE68" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF68" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG68" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH68" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:54:58.120999Z</t>
+        </is>
+      </c>
+      <c r="BI68" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ68" s="25" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BK68" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="BL68" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="BM68" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="BN68" s="28" t="n">
+        <v>0.507463</v>
+      </c>
+      <c r="BO68" s="28" t="n"/>
+      <c r="BP68" s="25" t="n"/>
+      <c r="BQ68" s="27" t="n"/>
+      <c r="BR68" s="28" t="n"/>
+      <c r="BS68" s="28" t="n"/>
+      <c r="BT68" s="28" t="n"/>
+      <c r="BU68" s="25" t="n"/>
+      <c r="BV68" s="29" t="n"/>
+      <c r="BW68" s="24" t="n"/>
+      <c r="BX68" s="30" t="n"/>
+      <c r="BY68" s="27" t="n"/>
+      <c r="BZ68" s="24" t="n"/>
+      <c r="CA68" s="31" t="n"/>
+      <c r="CB68" s="24" t="n"/>
+      <c r="CC68" s="24" t="n"/>
+      <c r="CD68" s="24" t="n"/>
+      <c r="CE68" s="24" t="n"/>
+      <c r="CF68" s="24" t="n"/>
+      <c r="CG68" s="24" t="n"/>
+      <c r="CH68" s="24" t="n"/>
+      <c r="CI68" s="24" t="n"/>
+      <c r="CJ68" s="24" t="n"/>
+      <c r="CK68" s="24" t="n"/>
+      <c r="CL68" s="24" t="n"/>
+      <c r="CM68" s="24" t="n"/>
+      <c r="CN68" s="24" t="n"/>
+      <c r="CO68" s="24" t="n"/>
+      <c r="CP68" s="24" t="n"/>
+      <c r="CQ68" s="24" t="n"/>
+      <c r="CR68" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>

--- a/data/main/mlb.xlsx
+++ b/data/main/mlb.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CR68" headerRowCount="1">
-  <autoFilter ref="A1:CR68"/>
-  <tableColumns count="96">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS67" headerRowCount="1">
+  <autoFilter ref="A1:CS67"/>
+  <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -393,12 +393,13 @@
     <tableColumn id="88" name="defensive_trend_gap"/>
     <tableColumn id="89" name="neutral_elo_rating_difference"/>
     <tableColumn id="90" name="bullpen_weakness_gap"/>
-    <tableColumn id="91" name="rest_disparity"/>
-    <tableColumn id="92" name="back_to_back_gap"/>
-    <tableColumn id="93" name="games_last_7_gap"/>
-    <tableColumn id="94" name="schedule_missingness"/>
-    <tableColumn id="95" name="market_residual_probability"/>
-    <tableColumn id="96" name="trade_candidate"/>
+    <tableColumn id="91" name="starter_era_gap"/>
+    <tableColumn id="92" name="rest_disparity"/>
+    <tableColumn id="93" name="back_to_back_gap"/>
+    <tableColumn id="94" name="games_last_7_gap"/>
+    <tableColumn id="95" name="schedule_missingness"/>
+    <tableColumn id="96" name="market_residual_probability"/>
+    <tableColumn id="97" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -755,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$68)</f>
+        <f>COUNTA('Picks'!$A$2:$A$67)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$68,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$67,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$68,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$67,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$68,"settled",'Picks'!$V$2:$V$68,"win")+COUNTIFS('Picks'!$U$2:$U$68,"settled",'Picks'!$V$2:$V$68,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"win")+COUNTIFS('Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -795,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$68,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$67,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$68,"&gt;0",'Picks'!$V$2:$V$68,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$68,"&gt;0",'Picks'!$V$2:$V$68,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$67,"&gt;0",'Picks'!$V$2:$V$67,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$67,"&gt;0",'Picks'!$V$2:$V$67,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$68,"&gt;0",'Picks'!$V$2:$V$68,"win")/(COUNTIFS('Picks'!$BX$2:$BX$68,"&gt;0",'Picks'!$V$2:$V$68,"win")+COUNTIFS('Picks'!$BX$2:$BX$68,"&gt;0",'Picks'!$V$2:$V$68,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$67,"&gt;0",'Picks'!$V$2:$V$67,"win")/(COUNTIFS('Picks'!$BX$2:$BX$67,"&gt;0",'Picks'!$V$2:$V$67,"win")+COUNTIFS('Picks'!$BX$2:$BX$67,"&gt;0",'Picks'!$V$2:$V$67,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$68)/SUM('Picks'!$BX$2:$BX$68),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$67)/SUM('Picks'!$BX$2:$BX$67),0)</f>
         <v/>
       </c>
     </row>
@@ -835,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$68)</f>
+        <f>SUM('Picks'!$BY$2:$BY$67)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$68,"&lt;&gt;",'Picks'!$AB$2:$AB$68),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$67,"&lt;&gt;",'Picks'!$AB$2:$AB$67),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$68,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$68,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$67,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$67,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$68,'Picks'!$AM$2:$AM$68,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$67,'Picks'!$AM$2:$AM$67,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -902,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$68,$A14,'Picks'!$U$2:$U$68,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$67,$A14,'Picks'!$U$2:$U$67,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$68,$A14,'Picks'!$U$2:$U$68,"settled",'Picks'!$V$2:$V$68,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$67,$A14,'Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$68,$A14,'Picks'!$U$2:$U$68,"settled",'Picks'!$V$2:$V$68,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$67,$A14,'Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -918,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$68,'Picks'!$H$2:$H$68,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$67,'Picks'!$H$2:$H$67,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$68,'Picks'!$H$2:$H$68,$A14,'Picks'!$U$2:$U$68,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$67,'Picks'!$H$2:$H$67,$A14,'Picks'!$U$2:$U$67,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -933,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$68,$A15,'Picks'!$U$2:$U$68,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$67,$A15,'Picks'!$U$2:$U$67,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$68,$A15,'Picks'!$U$2:$U$68,"settled",'Picks'!$V$2:$V$68,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$67,$A15,'Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$68,$A15,'Picks'!$U$2:$U$68,"settled",'Picks'!$V$2:$V$68,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$67,$A15,'Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -949,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$68,'Picks'!$H$2:$H$68,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$67,'Picks'!$H$2:$H$67,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$68,'Picks'!$H$2:$H$68,$A15,'Picks'!$U$2:$U$68,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$67,'Picks'!$H$2:$H$67,$A15,'Picks'!$U$2:$U$67,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -964,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$68,$A16,'Picks'!$U$2:$U$68,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$67,$A16,'Picks'!$U$2:$U$67,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$68,$A16,'Picks'!$U$2:$U$68,"settled",'Picks'!$V$2:$V$68,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$67,$A16,'Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$68,$A16,'Picks'!$U$2:$U$68,"settled",'Picks'!$V$2:$V$68,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$67,$A16,'Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -980,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$68,'Picks'!$H$2:$H$68,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$67,'Picks'!$H$2:$H$67,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$68,'Picks'!$H$2:$H$68,$A16,'Picks'!$U$2:$U$68,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$67,'Picks'!$H$2:$H$67,$A16,'Picks'!$U$2:$U$67,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1013,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CR68"/>
+  <dimension ref="A1:CS67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1106,12 +1107,13 @@
     <col width="21" customWidth="1" min="88" max="88"/>
     <col width="22" customWidth="1" min="89" max="89"/>
     <col width="22" customWidth="1" min="90" max="90"/>
-    <col width="16" customWidth="1" min="91" max="91"/>
-    <col width="18" customWidth="1" min="92" max="92"/>
+    <col width="17" customWidth="1" min="91" max="91"/>
+    <col width="16" customWidth="1" min="92" max="92"/>
     <col width="18" customWidth="1" min="93" max="93"/>
-    <col width="22" customWidth="1" min="94" max="94"/>
+    <col width="18" customWidth="1" min="94" max="94"/>
     <col width="22" customWidth="1" min="95" max="95"/>
-    <col width="17" customWidth="1" min="96" max="96"/>
+    <col width="22" customWidth="1" min="96" max="96"/>
+    <col width="17" customWidth="1" min="97" max="97"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1567,30 +1569,35 @@
       </c>
       <c r="CM1" s="23" t="inlineStr">
         <is>
+          <t>starter_era_gap</t>
+        </is>
+      </c>
+      <c r="CN1" s="23" t="inlineStr">
+        <is>
           <t>rest_disparity</t>
         </is>
       </c>
-      <c r="CN1" s="23" t="inlineStr">
+      <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>back_to_back_gap</t>
         </is>
       </c>
-      <c r="CO1" s="23" t="inlineStr">
+      <c r="CP1" s="23" t="inlineStr">
         <is>
           <t>games_last_7_gap</t>
         </is>
       </c>
-      <c r="CP1" s="23" t="inlineStr">
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
         </is>
       </c>
-      <c r="CQ1" s="23" t="inlineStr">
+      <c r="CR1" s="23" t="inlineStr">
         <is>
           <t>market_residual_probability</t>
         </is>
       </c>
-      <c r="CR1" s="23" t="inlineStr">
+      <c r="CS1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
@@ -1892,7 +1899,8 @@
       <c r="CO2" s="24" t="n"/>
       <c r="CP2" s="24" t="n"/>
       <c r="CQ2" s="24" t="n"/>
-      <c r="CR2" s="24" t="inlineStr">
+      <c r="CR2" s="24" t="n"/>
+      <c r="CS2" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -2194,7 +2202,8 @@
       <c r="CO3" s="24" t="n"/>
       <c r="CP3" s="24" t="n"/>
       <c r="CQ3" s="24" t="n"/>
-      <c r="CR3" s="24" t="inlineStr">
+      <c r="CR3" s="24" t="n"/>
+      <c r="CS3" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -2496,7 +2505,8 @@
       <c r="CO4" s="24" t="n"/>
       <c r="CP4" s="24" t="n"/>
       <c r="CQ4" s="24" t="n"/>
-      <c r="CR4" s="24" t="inlineStr">
+      <c r="CR4" s="24" t="n"/>
+      <c r="CS4" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2798,7 +2808,8 @@
       <c r="CO5" s="24" t="n"/>
       <c r="CP5" s="24" t="n"/>
       <c r="CQ5" s="24" t="n"/>
-      <c r="CR5" s="24" t="inlineStr">
+      <c r="CR5" s="24" t="n"/>
+      <c r="CS5" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3100,7 +3111,8 @@
       <c r="CO6" s="24" t="n"/>
       <c r="CP6" s="24" t="n"/>
       <c r="CQ6" s="24" t="n"/>
-      <c r="CR6" s="24" t="inlineStr">
+      <c r="CR6" s="24" t="n"/>
+      <c r="CS6" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3402,7 +3414,8 @@
       <c r="CO7" s="24" t="n"/>
       <c r="CP7" s="24" t="n"/>
       <c r="CQ7" s="24" t="n"/>
-      <c r="CR7" s="24" t="inlineStr">
+      <c r="CR7" s="24" t="n"/>
+      <c r="CS7" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3704,7 +3717,8 @@
       <c r="CO8" s="24" t="n"/>
       <c r="CP8" s="24" t="n"/>
       <c r="CQ8" s="24" t="n"/>
-      <c r="CR8" s="24" t="inlineStr">
+      <c r="CR8" s="24" t="n"/>
+      <c r="CS8" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4006,7 +4020,8 @@
       <c r="CO9" s="24" t="n"/>
       <c r="CP9" s="24" t="n"/>
       <c r="CQ9" s="24" t="n"/>
-      <c r="CR9" s="24" t="inlineStr">
+      <c r="CR9" s="24" t="n"/>
+      <c r="CS9" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4308,7 +4323,8 @@
       <c r="CO10" s="24" t="n"/>
       <c r="CP10" s="24" t="n"/>
       <c r="CQ10" s="24" t="n"/>
-      <c r="CR10" s="24" t="inlineStr">
+      <c r="CR10" s="24" t="n"/>
+      <c r="CS10" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4610,7 +4626,8 @@
       <c r="CO11" s="24" t="n"/>
       <c r="CP11" s="24" t="n"/>
       <c r="CQ11" s="24" t="n"/>
-      <c r="CR11" s="24" t="inlineStr">
+      <c r="CR11" s="24" t="n"/>
+      <c r="CS11" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4923,12 +4940,13 @@
       <c r="CN12" s="24" t="n"/>
       <c r="CO12" s="24" t="n"/>
       <c r="CP12" s="24" t="n"/>
-      <c r="CQ12" s="24" t="inlineStr">
+      <c r="CQ12" s="24" t="n"/>
+      <c r="CR12" s="24" t="inlineStr">
         <is>
           <t>0.625602</t>
         </is>
       </c>
-      <c r="CR12" s="24" t="inlineStr">
+      <c r="CS12" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5230,7 +5248,8 @@
       <c r="CO13" s="24" t="n"/>
       <c r="CP13" s="24" t="n"/>
       <c r="CQ13" s="24" t="n"/>
-      <c r="CR13" s="24" t="inlineStr">
+      <c r="CR13" s="24" t="n"/>
+      <c r="CS13" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5532,7 +5551,8 @@
       <c r="CO14" s="24" t="n"/>
       <c r="CP14" s="24" t="n"/>
       <c r="CQ14" s="24" t="n"/>
-      <c r="CR14" s="24" t="inlineStr">
+      <c r="CR14" s="24" t="n"/>
+      <c r="CS14" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5834,7 +5854,8 @@
       <c r="CO15" s="24" t="n"/>
       <c r="CP15" s="24" t="n"/>
       <c r="CQ15" s="24" t="n"/>
-      <c r="CR15" s="24" t="inlineStr">
+      <c r="CR15" s="24" t="n"/>
+      <c r="CS15" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -6136,7 +6157,8 @@
       <c r="CO16" s="24" t="n"/>
       <c r="CP16" s="24" t="n"/>
       <c r="CQ16" s="24" t="n"/>
-      <c r="CR16" s="24" t="inlineStr">
+      <c r="CR16" s="24" t="n"/>
+      <c r="CS16" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -6438,7 +6460,8 @@
       <c r="CO17" s="24" t="n"/>
       <c r="CP17" s="24" t="n"/>
       <c r="CQ17" s="24" t="n"/>
-      <c r="CR17" s="24" t="inlineStr">
+      <c r="CR17" s="24" t="n"/>
+      <c r="CS17" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -6740,7 +6763,8 @@
       <c r="CO18" s="24" t="n"/>
       <c r="CP18" s="24" t="n"/>
       <c r="CQ18" s="24" t="n"/>
-      <c r="CR18" s="24" t="inlineStr">
+      <c r="CR18" s="24" t="n"/>
+      <c r="CS18" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -7042,7 +7066,8 @@
       <c r="CO19" s="24" t="n"/>
       <c r="CP19" s="24" t="n"/>
       <c r="CQ19" s="24" t="n"/>
-      <c r="CR19" s="24" t="inlineStr">
+      <c r="CR19" s="24" t="n"/>
+      <c r="CS19" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -7344,7 +7369,8 @@
       <c r="CO20" s="24" t="n"/>
       <c r="CP20" s="24" t="n"/>
       <c r="CQ20" s="24" t="n"/>
-      <c r="CR20" s="24" t="inlineStr">
+      <c r="CR20" s="24" t="n"/>
+      <c r="CS20" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -7646,7 +7672,8 @@
       <c r="CO21" s="24" t="n"/>
       <c r="CP21" s="24" t="n"/>
       <c r="CQ21" s="24" t="n"/>
-      <c r="CR21" s="24" t="inlineStr">
+      <c r="CR21" s="24" t="n"/>
+      <c r="CS21" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -7948,7 +7975,8 @@
       <c r="CO22" s="24" t="n"/>
       <c r="CP22" s="24" t="n"/>
       <c r="CQ22" s="24" t="n"/>
-      <c r="CR22" s="24" t="inlineStr">
+      <c r="CR22" s="24" t="n"/>
+      <c r="CS22" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -8250,7 +8278,8 @@
       <c r="CO23" s="24" t="n"/>
       <c r="CP23" s="24" t="n"/>
       <c r="CQ23" s="24" t="n"/>
-      <c r="CR23" s="24" t="inlineStr">
+      <c r="CR23" s="24" t="n"/>
+      <c r="CS23" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -8552,7 +8581,8 @@
       <c r="CO24" s="24" t="n"/>
       <c r="CP24" s="24" t="n"/>
       <c r="CQ24" s="24" t="n"/>
-      <c r="CR24" s="24" t="inlineStr">
+      <c r="CR24" s="24" t="n"/>
+      <c r="CS24" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -8854,7 +8884,8 @@
       <c r="CO25" s="24" t="n"/>
       <c r="CP25" s="24" t="n"/>
       <c r="CQ25" s="24" t="n"/>
-      <c r="CR25" s="24" t="inlineStr">
+      <c r="CR25" s="24" t="n"/>
+      <c r="CS25" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -9156,7 +9187,8 @@
       <c r="CO26" s="24" t="n"/>
       <c r="CP26" s="24" t="n"/>
       <c r="CQ26" s="24" t="n"/>
-      <c r="CR26" s="24" t="inlineStr">
+      <c r="CR26" s="24" t="n"/>
+      <c r="CS26" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -9469,12 +9501,13 @@
       <c r="CN27" s="24" t="n"/>
       <c r="CO27" s="24" t="n"/>
       <c r="CP27" s="24" t="n"/>
-      <c r="CQ27" s="24" t="inlineStr">
+      <c r="CQ27" s="24" t="n"/>
+      <c r="CR27" s="24" t="inlineStr">
         <is>
           <t>0.648206</t>
         </is>
       </c>
-      <c r="CR27" s="24" t="inlineStr">
+      <c r="CS27" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -9776,7 +9809,8 @@
       <c r="CO28" s="24" t="n"/>
       <c r="CP28" s="24" t="n"/>
       <c r="CQ28" s="24" t="n"/>
-      <c r="CR28" s="24" t="inlineStr">
+      <c r="CR28" s="24" t="n"/>
+      <c r="CS28" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -10078,7 +10112,8 @@
       <c r="CO29" s="24" t="n"/>
       <c r="CP29" s="24" t="n"/>
       <c r="CQ29" s="24" t="n"/>
-      <c r="CR29" s="24" t="inlineStr">
+      <c r="CR29" s="24" t="n"/>
+      <c r="CS29" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -10380,7 +10415,8 @@
       <c r="CO30" s="24" t="n"/>
       <c r="CP30" s="24" t="n"/>
       <c r="CQ30" s="24" t="n"/>
-      <c r="CR30" s="24" t="inlineStr">
+      <c r="CR30" s="24" t="n"/>
+      <c r="CS30" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -10682,7 +10718,8 @@
       <c r="CO31" s="24" t="n"/>
       <c r="CP31" s="24" t="n"/>
       <c r="CQ31" s="24" t="n"/>
-      <c r="CR31" s="24" t="inlineStr">
+      <c r="CR31" s="24" t="n"/>
+      <c r="CS31" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -10984,7 +11021,8 @@
       <c r="CO32" s="24" t="n"/>
       <c r="CP32" s="24" t="n"/>
       <c r="CQ32" s="24" t="n"/>
-      <c r="CR32" s="24" t="inlineStr">
+      <c r="CR32" s="24" t="n"/>
+      <c r="CS32" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -11286,7 +11324,8 @@
       <c r="CO33" s="24" t="n"/>
       <c r="CP33" s="24" t="n"/>
       <c r="CQ33" s="24" t="n"/>
-      <c r="CR33" s="24" t="inlineStr">
+      <c r="CR33" s="24" t="n"/>
+      <c r="CS33" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -11588,7 +11627,8 @@
       <c r="CO34" s="24" t="n"/>
       <c r="CP34" s="24" t="n"/>
       <c r="CQ34" s="24" t="n"/>
-      <c r="CR34" s="24" t="inlineStr">
+      <c r="CR34" s="24" t="n"/>
+      <c r="CS34" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -11890,7 +11930,8 @@
       <c r="CO35" s="24" t="n"/>
       <c r="CP35" s="24" t="n"/>
       <c r="CQ35" s="24" t="n"/>
-      <c r="CR35" s="24" t="inlineStr">
+      <c r="CR35" s="24" t="n"/>
+      <c r="CS35" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -12192,7 +12233,8 @@
       <c r="CO36" s="24" t="n"/>
       <c r="CP36" s="24" t="n"/>
       <c r="CQ36" s="24" t="n"/>
-      <c r="CR36" s="24" t="inlineStr">
+      <c r="CR36" s="24" t="n"/>
+      <c r="CS36" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -12494,7 +12536,8 @@
       <c r="CO37" s="24" t="n"/>
       <c r="CP37" s="24" t="n"/>
       <c r="CQ37" s="24" t="n"/>
-      <c r="CR37" s="24" t="inlineStr">
+      <c r="CR37" s="24" t="n"/>
+      <c r="CS37" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -12796,7 +12839,8 @@
       <c r="CO38" s="24" t="n"/>
       <c r="CP38" s="24" t="n"/>
       <c r="CQ38" s="24" t="n"/>
-      <c r="CR38" s="24" t="inlineStr">
+      <c r="CR38" s="24" t="n"/>
+      <c r="CS38" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -13098,7 +13142,8 @@
       <c r="CO39" s="24" t="n"/>
       <c r="CP39" s="24" t="n"/>
       <c r="CQ39" s="24" t="n"/>
-      <c r="CR39" s="24" t="inlineStr">
+      <c r="CR39" s="24" t="n"/>
+      <c r="CS39" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -13400,7 +13445,8 @@
       <c r="CO40" s="24" t="n"/>
       <c r="CP40" s="24" t="n"/>
       <c r="CQ40" s="24" t="n"/>
-      <c r="CR40" s="24" t="inlineStr">
+      <c r="CR40" s="24" t="n"/>
+      <c r="CS40" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -13702,7 +13748,8 @@
       <c r="CO41" s="24" t="n"/>
       <c r="CP41" s="24" t="n"/>
       <c r="CQ41" s="24" t="n"/>
-      <c r="CR41" s="24" t="inlineStr">
+      <c r="CR41" s="24" t="n"/>
+      <c r="CS41" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -13711,22 +13758,22 @@
     <row r="42" ht="36" customHeight="1">
       <c r="A42" s="24" t="inlineStr">
         <is>
-          <t>46630ec118fc4a81</t>
+          <t>97896ce4943849be</t>
         </is>
       </c>
       <c r="B42" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:42.290404Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C42" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T20:40:00-0400</t>
+          <t>2026-08-04T22:40Z</t>
         </is>
       </c>
       <c r="D42" s="24" t="inlineStr">
         <is>
-          <t>401816396</t>
+          <t>401816385</t>
         </is>
       </c>
       <c r="E42" s="24" t="inlineStr">
@@ -13736,17 +13783,17 @@
       </c>
       <c r="F42" s="24" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="G42" s="24" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="H42" s="24" t="inlineStr">
         <is>
-          <t>moneyline</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="I42" s="24" t="inlineStr">
@@ -13754,37 +13801,41 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J42" s="25" t="n"/>
+      <c r="J42" s="25" t="n">
+        <v>1.5</v>
+      </c>
       <c r="K42" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L42" s="26" t="n">
-        <v>-138</v>
+        <v>-163</v>
       </c>
       <c r="M42" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.613497</v>
       </c>
       <c r="N42" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.619772</v>
       </c>
       <c r="O42" s="28" t="n">
-        <v>0.651997</v>
-      </c>
-      <c r="P42" s="28" t="n"/>
+        <v>0.56005</v>
+      </c>
+      <c r="P42" s="28" t="n">
+        <v>0.042131</v>
+      </c>
       <c r="Q42" s="28" t="n">
-        <v>0.07216500000000001</v>
+        <v>-0.059722</v>
       </c>
       <c r="R42" s="26" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="S42" s="29" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="T42" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v7</t>
+          <t>measured-edge-margin-v2</t>
         </is>
       </c>
       <c r="U42" s="24" t="inlineStr">
@@ -13803,12 +13854,12 @@
       <c r="AD42" s="24" t="n"/>
       <c r="AE42" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.6242; executable ask 0.5800 (aec-mlb-tb-col-2026-08-04); model edge vs ask +0.0720.</t>
+          <t>Measured Edge Margin: Trend Engine projected 3.87-4.68; raw selected-side p=0.5915, calibrated p=0.5601.</t>
         </is>
       </c>
       <c r="AF42" s="31" t="inlineStr">
         <is>
-          <t>Learned model; shadow-qualified via operator override.</t>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
         </is>
       </c>
       <c r="AG42" s="24" t="inlineStr">
@@ -13844,32 +13895,32 @@
       </c>
       <c r="AP42" s="24" t="inlineStr">
         <is>
-          <t>mlb-tb</t>
+          <t>mlb-ath</t>
         </is>
       </c>
       <c r="AQ42" s="24" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="AR42" s="24" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="AS42" s="24" t="inlineStr">
         <is>
-          <t>mlb-col</t>
+          <t>mlb-cin</t>
         </is>
       </c>
       <c r="AT42" s="24" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="AU42" s="24" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="AV42" s="24" t="n"/>
@@ -13882,32 +13933,32 @@
       <c r="AY42" s="24" t="n"/>
       <c r="AZ42" s="24" t="inlineStr">
         <is>
-          <t>shadow_qualified</t>
+          <t>research</t>
         </is>
       </c>
       <c r="BA42" s="24" t="inlineStr">
         <is>
-          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
         </is>
       </c>
       <c r="BB42" s="24" t="inlineStr">
         <is>
-          <t>learned_lr</t>
+          <t>flat_probability_shrinkage_toward_half</t>
         </is>
       </c>
       <c r="BC42" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v7</t>
+          <t>measured-edge-margin-v2</t>
         </is>
       </c>
       <c r="BD42" s="24" t="inlineStr">
         <is>
-          <t>464eef695bfbbdaa819ec6f5e4c5bd1068ed20b92915fb2677220ae91e20d8b6</t>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
         </is>
       </c>
       <c r="BE42" s="24" t="inlineStr">
         <is>
-          <t>aa1550043d30dddf</t>
+          <t>v3</t>
         </is>
       </c>
       <c r="BF42" s="24" t="inlineStr">
@@ -13917,12 +13968,12 @@
       </c>
       <c r="BG42" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v7</t>
+          <t>measured-edge-paired-v1</t>
         </is>
       </c>
       <c r="BH42" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:53:24.205568Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI42" s="24" t="inlineStr">
@@ -13930,18 +13981,20 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ42" s="25" t="n"/>
+      <c r="BJ42" s="25" t="n">
+        <v>1.5</v>
+      </c>
       <c r="BK42" s="26" t="n">
-        <v>-138</v>
+        <v>-163</v>
       </c>
       <c r="BL42" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.613497</v>
       </c>
       <c r="BM42" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.619772</v>
       </c>
       <c r="BN42" s="28" t="n">
-        <v>0.577114</v>
+        <v>0.616915</v>
       </c>
       <c r="BO42" s="28" t="n"/>
       <c r="BP42" s="25" t="n"/>
@@ -13957,68 +14010,37 @@
       <c r="BZ42" s="24" t="n"/>
       <c r="CA42" s="31" t="n"/>
       <c r="CB42" s="24" t="n"/>
-      <c r="CC42" s="24" t="inlineStr">
-        <is>
-          <t>0.3759904491</t>
-        </is>
-      </c>
-      <c r="CD42" s="24" t="inlineStr">
-        <is>
-          <t>1.914708</t>
-        </is>
-      </c>
-      <c r="CE42" s="24" t="inlineStr">
-        <is>
-          <t>1.193</t>
-        </is>
-      </c>
-      <c r="CF42" s="24" t="inlineStr">
-        <is>
-          <t>1.0086</t>
-        </is>
-      </c>
-      <c r="CG42" s="24" t="inlineStr">
-        <is>
-          <t>-0.4</t>
-        </is>
-      </c>
+      <c r="CC42" s="24" t="n"/>
+      <c r="CD42" s="24" t="n"/>
+      <c r="CE42" s="24" t="n"/>
+      <c r="CF42" s="24" t="n"/>
+      <c r="CG42" s="24" t="n"/>
       <c r="CH42" s="24" t="n"/>
       <c r="CI42" s="24" t="n"/>
-      <c r="CJ42" s="24" t="inlineStr">
-        <is>
-          <t>0.686906</t>
-        </is>
-      </c>
+      <c r="CJ42" s="24" t="n"/>
       <c r="CK42" s="24" t="n"/>
-      <c r="CL42" s="24" t="inlineStr">
-        <is>
-          <t>0.056981</t>
-        </is>
-      </c>
+      <c r="CL42" s="24" t="n"/>
       <c r="CM42" s="24" t="n"/>
       <c r="CN42" s="24" t="n"/>
       <c r="CO42" s="24" t="n"/>
       <c r="CP42" s="24" t="n"/>
-      <c r="CQ42" s="24" t="inlineStr">
-        <is>
-          <t>0.651997</t>
-        </is>
-      </c>
-      <c r="CR42" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
+      <c r="CQ42" s="24" t="n"/>
+      <c r="CR42" s="24" t="n"/>
+      <c r="CS42" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="43" ht="36" customHeight="1">
       <c r="A43" s="24" t="inlineStr">
         <is>
-          <t>7bcb1e9699d34e7c</t>
+          <t>ddeb2a337c46426e</t>
         </is>
       </c>
       <c r="B43" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C43" s="24" t="inlineStr">
@@ -14048,16 +14070,16 @@
       </c>
       <c r="H43" s="24" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="I43" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>under</t>
         </is>
       </c>
       <c r="J43" s="25" t="n">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="K43" s="24" t="inlineStr">
         <is>
@@ -14065,32 +14087,32 @@
         </is>
       </c>
       <c r="L43" s="26" t="n">
-        <v>-163</v>
+        <v>122</v>
       </c>
       <c r="M43" s="27" t="n">
-        <v>1.613497</v>
+        <v>2.22</v>
       </c>
       <c r="N43" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.45045</v>
       </c>
       <c r="O43" s="28" t="n">
-        <v>0.559361</v>
+        <v>0.514254</v>
       </c>
       <c r="P43" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q43" s="28" t="n">
-        <v>-0.060411</v>
+        <v>0.063804</v>
       </c>
       <c r="R43" s="26" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="S43" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T43" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-totals-v2</t>
         </is>
       </c>
       <c r="U43" s="24" t="inlineStr">
@@ -14109,7 +14131,7 @@
       <c r="AD43" s="24" t="n"/>
       <c r="AE43" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 3.87-4.68; raw selected-side p=0.5904, calibrated p=0.5594.</t>
+          <t>Measured Edge Totals: Trend Engine projected 3.87-4.68; raw selected-side p=0.5184, calibrated p=0.5143.</t>
         </is>
       </c>
       <c r="AF43" s="31" t="inlineStr">
@@ -14193,7 +14215,7 @@
       </c>
       <c r="BA43" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
         </is>
       </c>
       <c r="BB43" s="24" t="inlineStr">
@@ -14203,12 +14225,12 @@
       </c>
       <c r="BC43" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-totals-v2</t>
         </is>
       </c>
       <c r="BD43" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
         </is>
       </c>
       <c r="BE43" s="24" t="inlineStr">
@@ -14228,7 +14250,7 @@
       </c>
       <c r="BH43" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI43" s="24" t="inlineStr">
@@ -14237,19 +14259,19 @@
         </is>
       </c>
       <c r="BJ43" s="25" t="n">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="BK43" s="26" t="n">
-        <v>-163</v>
+        <v>122</v>
       </c>
       <c r="BL43" s="27" t="n">
-        <v>1.613497</v>
+        <v>2.22</v>
       </c>
       <c r="BM43" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.45045</v>
       </c>
       <c r="BN43" s="28" t="n">
-        <v>0.616915</v>
+        <v>0.447761</v>
       </c>
       <c r="BO43" s="28" t="n"/>
       <c r="BP43" s="25" t="n"/>
@@ -14280,21 +14302,22 @@
       <c r="CO43" s="24" t="n"/>
       <c r="CP43" s="24" t="n"/>
       <c r="CQ43" s="24" t="n"/>
-      <c r="CR43" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
+      <c r="CR43" s="24" t="n"/>
+      <c r="CS43" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="44" ht="36" customHeight="1">
       <c r="A44" s="24" t="inlineStr">
         <is>
-          <t>33826a4332194433</t>
+          <t>6811d5d9494c4c1f</t>
         </is>
       </c>
       <c r="B44" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C44" s="24" t="inlineStr">
@@ -14304,7 +14327,7 @@
       </c>
       <c r="D44" s="24" t="inlineStr">
         <is>
-          <t>401816385</t>
+          <t>401816388</t>
         </is>
       </c>
       <c r="E44" s="24" t="inlineStr">
@@ -14314,26 +14337,26 @@
       </c>
       <c r="F44" s="24" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="G44" s="24" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Cleveland Guardians</t>
         </is>
       </c>
       <c r="H44" s="24" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="I44" s="24" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J44" s="25" t="n">
-        <v>9.5</v>
+        <v>1.5</v>
       </c>
       <c r="K44" s="24" t="inlineStr">
         <is>
@@ -14341,32 +14364,32 @@
         </is>
       </c>
       <c r="L44" s="26" t="n">
-        <v>-113</v>
+        <v>-163</v>
       </c>
       <c r="M44" s="27" t="n">
-        <v>1.884956</v>
+        <v>1.613497</v>
       </c>
       <c r="N44" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.619772</v>
       </c>
       <c r="O44" s="28" t="n">
-        <v>0.5548650000000001</v>
+        <v>0.600007</v>
       </c>
       <c r="P44" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q44" s="28" t="n">
-        <v>0.024349</v>
+        <v>-0.019765</v>
       </c>
       <c r="R44" s="26" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="S44" s="29" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="T44" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-margin-v2</t>
         </is>
       </c>
       <c r="U44" s="24" t="inlineStr">
@@ -14385,7 +14408,7 @@
       <c r="AD44" s="24" t="n"/>
       <c r="AE44" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 3.87-4.68; raw selected-side p=0.6373, calibrated p=0.5549.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.10-4.32; raw selected-side p=0.6523, calibrated p=0.6000.</t>
         </is>
       </c>
       <c r="AF44" s="31" t="inlineStr">
@@ -14426,32 +14449,32 @@
       </c>
       <c r="AP44" s="24" t="inlineStr">
         <is>
-          <t>mlb-ath</t>
+          <t>mlb-nym</t>
         </is>
       </c>
       <c r="AQ44" s="24" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="AR44" s="24" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="AS44" s="24" t="inlineStr">
         <is>
-          <t>mlb-cin</t>
+          <t>mlb-cle</t>
         </is>
       </c>
       <c r="AT44" s="24" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Cleveland Guardians</t>
         </is>
       </c>
       <c r="AU44" s="24" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Cleveland Guardians</t>
         </is>
       </c>
       <c r="AV44" s="24" t="n"/>
@@ -14469,7 +14492,7 @@
       </c>
       <c r="BA44" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
         </is>
       </c>
       <c r="BB44" s="24" t="inlineStr">
@@ -14479,12 +14502,12 @@
       </c>
       <c r="BC44" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-margin-v2</t>
         </is>
       </c>
       <c r="BD44" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
         </is>
       </c>
       <c r="BE44" s="24" t="inlineStr">
@@ -14504,7 +14527,7 @@
       </c>
       <c r="BH44" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI44" s="24" t="inlineStr">
@@ -14513,19 +14536,19 @@
         </is>
       </c>
       <c r="BJ44" s="25" t="n">
-        <v>9.5</v>
+        <v>1.5</v>
       </c>
       <c r="BK44" s="26" t="n">
-        <v>-113</v>
+        <v>-163</v>
       </c>
       <c r="BL44" s="27" t="n">
-        <v>1.884956</v>
+        <v>1.613497</v>
       </c>
       <c r="BM44" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.619772</v>
       </c>
       <c r="BN44" s="28" t="n">
-        <v>0.527363</v>
+        <v>0.616915</v>
       </c>
       <c r="BO44" s="28" t="n"/>
       <c r="BP44" s="25" t="n"/>
@@ -14556,21 +14579,22 @@
       <c r="CO44" s="24" t="n"/>
       <c r="CP44" s="24" t="n"/>
       <c r="CQ44" s="24" t="n"/>
-      <c r="CR44" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
+      <c r="CR44" s="24" t="n"/>
+      <c r="CS44" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="45" ht="36" customHeight="1">
       <c r="A45" s="24" t="inlineStr">
         <is>
-          <t>af4975d4ff6c4b78</t>
+          <t>c7b77c0e4f0b4e4a</t>
         </is>
       </c>
       <c r="B45" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C45" s="24" t="inlineStr">
@@ -14600,16 +14624,16 @@
       </c>
       <c r="H45" s="24" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="I45" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>over</t>
         </is>
       </c>
       <c r="J45" s="25" t="n">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="K45" s="24" t="inlineStr">
         <is>
@@ -14617,32 +14641,32 @@
         </is>
       </c>
       <c r="L45" s="26" t="n">
-        <v>-163</v>
+        <v>-106</v>
       </c>
       <c r="M45" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.943396</v>
       </c>
       <c r="N45" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.514563</v>
       </c>
       <c r="O45" s="28" t="n">
-        <v>0.602336</v>
+        <v>0.521567</v>
       </c>
       <c r="P45" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q45" s="28" t="n">
-        <v>-0.017436</v>
+        <v>0.007004</v>
       </c>
       <c r="R45" s="26" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="S45" s="29" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="T45" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-totals-v2</t>
         </is>
       </c>
       <c r="U45" s="24" t="inlineStr">
@@ -14661,7 +14685,7 @@
       <c r="AD45" s="24" t="n"/>
       <c r="AE45" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.10-4.32; raw selected-side p=0.6559, calibrated p=0.6023.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.10-4.32; raw selected-side p=0.5399, calibrated p=0.5216.</t>
         </is>
       </c>
       <c r="AF45" s="31" t="inlineStr">
@@ -14745,7 +14769,7 @@
       </c>
       <c r="BA45" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
         </is>
       </c>
       <c r="BB45" s="24" t="inlineStr">
@@ -14755,12 +14779,12 @@
       </c>
       <c r="BC45" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-totals-v2</t>
         </is>
       </c>
       <c r="BD45" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
         </is>
       </c>
       <c r="BE45" s="24" t="inlineStr">
@@ -14780,7 +14804,7 @@
       </c>
       <c r="BH45" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI45" s="24" t="inlineStr">
@@ -14789,19 +14813,19 @@
         </is>
       </c>
       <c r="BJ45" s="25" t="n">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="BK45" s="26" t="n">
-        <v>-163</v>
+        <v>-106</v>
       </c>
       <c r="BL45" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.943396</v>
       </c>
       <c r="BM45" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.514563</v>
       </c>
       <c r="BN45" s="28" t="n">
-        <v>0.616915</v>
+        <v>0.5124379999999999</v>
       </c>
       <c r="BO45" s="28" t="n"/>
       <c r="BP45" s="25" t="n"/>
@@ -14832,21 +14856,22 @@
       <c r="CO45" s="24" t="n"/>
       <c r="CP45" s="24" t="n"/>
       <c r="CQ45" s="24" t="n"/>
-      <c r="CR45" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
+      <c r="CR45" s="24" t="n"/>
+      <c r="CS45" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="46" ht="36" customHeight="1">
       <c r="A46" s="24" t="inlineStr">
         <is>
-          <t>342b4720b837407b</t>
+          <t>d21c466f2c6e41c8</t>
         </is>
       </c>
       <c r="B46" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C46" s="24" t="inlineStr">
@@ -14856,7 +14881,7 @@
       </c>
       <c r="D46" s="24" t="inlineStr">
         <is>
-          <t>401816388</t>
+          <t>401816390</t>
         </is>
       </c>
       <c r="E46" s="24" t="inlineStr">
@@ -14866,26 +14891,26 @@
       </c>
       <c r="F46" s="24" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="G46" s="24" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="H46" s="24" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="I46" s="24" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J46" s="25" t="n">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
       <c r="K46" s="24" t="inlineStr">
         <is>
@@ -14893,32 +14918,32 @@
         </is>
       </c>
       <c r="L46" s="26" t="n">
-        <v>-104</v>
+        <v>117</v>
       </c>
       <c r="M46" s="27" t="n">
-        <v>1.961538</v>
+        <v>2.17</v>
       </c>
       <c r="N46" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.460829</v>
       </c>
       <c r="O46" s="28" t="n">
-        <v>0.523634</v>
+        <v>0.540597</v>
       </c>
       <c r="P46" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q46" s="28" t="n">
-        <v>0.01383</v>
+        <v>0.07976800000000001</v>
       </c>
       <c r="R46" s="26" t="n">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="S46" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T46" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-margin-v2</t>
         </is>
       </c>
       <c r="U46" s="24" t="inlineStr">
@@ -14937,7 +14962,7 @@
       <c r="AD46" s="24" t="n"/>
       <c r="AE46" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.10-4.32; raw selected-side p=0.5459, calibrated p=0.5236.</t>
+          <t>Measured Edge Margin: Trend Engine projected 3.92-5.03; raw selected-side p=0.5618, calibrated p=0.5406.</t>
         </is>
       </c>
       <c r="AF46" s="31" t="inlineStr">
@@ -14978,32 +15003,32 @@
       </c>
       <c r="AP46" s="24" t="inlineStr">
         <is>
-          <t>mlb-nym</t>
+          <t>mlb-wsh</t>
         </is>
       </c>
       <c r="AQ46" s="24" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="AR46" s="24" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="AS46" s="24" t="inlineStr">
         <is>
-          <t>mlb-cle</t>
+          <t>mlb-phi</t>
         </is>
       </c>
       <c r="AT46" s="24" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="AU46" s="24" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="AV46" s="24" t="n"/>
@@ -15021,7 +15046,7 @@
       </c>
       <c r="BA46" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
         </is>
       </c>
       <c r="BB46" s="24" t="inlineStr">
@@ -15031,12 +15056,12 @@
       </c>
       <c r="BC46" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-margin-v2</t>
         </is>
       </c>
       <c r="BD46" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
         </is>
       </c>
       <c r="BE46" s="24" t="inlineStr">
@@ -15056,7 +15081,7 @@
       </c>
       <c r="BH46" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI46" s="24" t="inlineStr">
@@ -15065,19 +15090,19 @@
         </is>
       </c>
       <c r="BJ46" s="25" t="n">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
       <c r="BK46" s="26" t="n">
-        <v>-104</v>
+        <v>117</v>
       </c>
       <c r="BL46" s="27" t="n">
-        <v>1.961538</v>
+        <v>2.17</v>
       </c>
       <c r="BM46" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.460829</v>
       </c>
       <c r="BN46" s="28" t="n">
-        <v>0.507463</v>
+        <v>0.457711</v>
       </c>
       <c r="BO46" s="28" t="n"/>
       <c r="BP46" s="25" t="n"/>
@@ -15108,7 +15133,8 @@
       <c r="CO46" s="24" t="n"/>
       <c r="CP46" s="24" t="n"/>
       <c r="CQ46" s="24" t="n"/>
-      <c r="CR46" s="24" t="inlineStr">
+      <c r="CR46" s="24" t="n"/>
+      <c r="CS46" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -15117,12 +15143,12 @@
     <row r="47" ht="36" customHeight="1">
       <c r="A47" s="24" t="inlineStr">
         <is>
-          <t>164e21d243c84d21</t>
+          <t>24ac0a3e828e402a</t>
         </is>
       </c>
       <c r="B47" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C47" s="24" t="inlineStr">
@@ -15152,16 +15178,16 @@
       </c>
       <c r="H47" s="24" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="I47" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>over</t>
         </is>
       </c>
       <c r="J47" s="25" t="n">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="K47" s="24" t="inlineStr">
         <is>
@@ -15169,32 +15195,32 @@
         </is>
       </c>
       <c r="L47" s="26" t="n">
-        <v>111</v>
+        <v>-117</v>
       </c>
       <c r="M47" s="27" t="n">
-        <v>2.11</v>
+        <v>1.854701</v>
       </c>
       <c r="N47" s="28" t="n">
-        <v>0.473934</v>
+        <v>0.539171</v>
       </c>
       <c r="O47" s="28" t="n">
-        <v>0.537481</v>
+        <v>0.511059</v>
       </c>
       <c r="P47" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q47" s="28" t="n">
-        <v>0.06354700000000001</v>
+        <v>-0.028112</v>
       </c>
       <c r="R47" s="26" t="n">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="S47" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T47" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-totals-v2</t>
         </is>
       </c>
       <c r="U47" s="24" t="inlineStr">
@@ -15213,7 +15239,7 @@
       <c r="AD47" s="24" t="n"/>
       <c r="AE47" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 3.92-5.03; raw selected-side p=0.5571, calibrated p=0.5375.</t>
+          <t>Measured Edge Totals: Trend Engine projected 3.92-5.03; raw selected-side p=0.5091, calibrated p=0.5111.</t>
         </is>
       </c>
       <c r="AF47" s="31" t="inlineStr">
@@ -15297,7 +15323,7 @@
       </c>
       <c r="BA47" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
         </is>
       </c>
       <c r="BB47" s="24" t="inlineStr">
@@ -15307,12 +15333,12 @@
       </c>
       <c r="BC47" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-totals-v2</t>
         </is>
       </c>
       <c r="BD47" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
         </is>
       </c>
       <c r="BE47" s="24" t="inlineStr">
@@ -15332,7 +15358,7 @@
       </c>
       <c r="BH47" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI47" s="24" t="inlineStr">
@@ -15341,19 +15367,19 @@
         </is>
       </c>
       <c r="BJ47" s="25" t="n">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="BK47" s="26" t="n">
-        <v>111</v>
+        <v>-117</v>
       </c>
       <c r="BL47" s="27" t="n">
-        <v>2.11</v>
+        <v>1.854701</v>
       </c>
       <c r="BM47" s="28" t="n">
-        <v>0.473934</v>
+        <v>0.539171</v>
       </c>
       <c r="BN47" s="28" t="n">
-        <v>0.472637</v>
+        <v>0.537313</v>
       </c>
       <c r="BO47" s="28" t="n"/>
       <c r="BP47" s="25" t="n"/>
@@ -15384,31 +15410,32 @@
       <c r="CO47" s="24" t="n"/>
       <c r="CP47" s="24" t="n"/>
       <c r="CQ47" s="24" t="n"/>
-      <c r="CR47" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
+      <c r="CR47" s="24" t="n"/>
+      <c r="CS47" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="48" ht="36" customHeight="1">
       <c r="A48" s="24" t="inlineStr">
         <is>
-          <t>823c22f90c7c4b5d</t>
+          <t>4269da3d4eca4177</t>
         </is>
       </c>
       <c r="B48" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C48" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T22:40Z</t>
+          <t>2026-08-04T23:05Z</t>
         </is>
       </c>
       <c r="D48" s="24" t="inlineStr">
         <is>
-          <t>401816390</t>
+          <t>401816389</t>
         </is>
       </c>
       <c r="E48" s="24" t="inlineStr">
@@ -15418,26 +15445,26 @@
       </c>
       <c r="F48" s="24" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="G48" s="24" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="H48" s="24" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="I48" s="24" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J48" s="25" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="K48" s="24" t="inlineStr">
         <is>
@@ -15445,32 +15472,32 @@
         </is>
       </c>
       <c r="L48" s="26" t="n">
-        <v>-113</v>
+        <v>-120</v>
       </c>
       <c r="M48" s="27" t="n">
-        <v>1.884956</v>
+        <v>1.833333</v>
       </c>
       <c r="N48" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.545455</v>
       </c>
       <c r="O48" s="28" t="n">
-        <v>0.511111</v>
+        <v>0.612998</v>
       </c>
       <c r="P48" s="28" t="n">
-        <v>0.042131</v>
+        <v>0.05172</v>
       </c>
       <c r="Q48" s="28" t="n">
-        <v>-0.019405</v>
+        <v>0.06754300000000001</v>
       </c>
       <c r="R48" s="26" t="n">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="S48" s="29" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="T48" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-margin-v2</t>
         </is>
       </c>
       <c r="U48" s="24" t="inlineStr">
@@ -15489,7 +15516,7 @@
       <c r="AD48" s="24" t="n"/>
       <c r="AE48" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 3.92-5.03; raw selected-side p=0.5092, calibrated p=0.5111.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.35-4.35; raw selected-side p=0.6722, calibrated p=0.6130.</t>
         </is>
       </c>
       <c r="AF48" s="31" t="inlineStr">
@@ -15530,32 +15557,32 @@
       </c>
       <c r="AP48" s="24" t="inlineStr">
         <is>
-          <t>mlb-wsh</t>
+          <t>mlb-stl</t>
         </is>
       </c>
       <c r="AQ48" s="24" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="AR48" s="24" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="AS48" s="24" t="inlineStr">
         <is>
-          <t>mlb-phi</t>
+          <t>mlb-nyy</t>
         </is>
       </c>
       <c r="AT48" s="24" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="AU48" s="24" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="AV48" s="24" t="n"/>
@@ -15573,7 +15600,7 @@
       </c>
       <c r="BA48" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
         </is>
       </c>
       <c r="BB48" s="24" t="inlineStr">
@@ -15583,12 +15610,12 @@
       </c>
       <c r="BC48" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-margin-v2</t>
         </is>
       </c>
       <c r="BD48" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
         </is>
       </c>
       <c r="BE48" s="24" t="inlineStr">
@@ -15608,7 +15635,7 @@
       </c>
       <c r="BH48" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI48" s="24" t="inlineStr">
@@ -15617,19 +15644,19 @@
         </is>
       </c>
       <c r="BJ48" s="25" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="BK48" s="26" t="n">
-        <v>-113</v>
+        <v>-120</v>
       </c>
       <c r="BL48" s="27" t="n">
-        <v>1.884956</v>
+        <v>1.833333</v>
       </c>
       <c r="BM48" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.545455</v>
       </c>
       <c r="BN48" s="28" t="n">
-        <v>0.527363</v>
+        <v>0.542289</v>
       </c>
       <c r="BO48" s="28" t="n"/>
       <c r="BP48" s="25" t="n"/>
@@ -15660,21 +15687,22 @@
       <c r="CO48" s="24" t="n"/>
       <c r="CP48" s="24" t="n"/>
       <c r="CQ48" s="24" t="n"/>
-      <c r="CR48" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
+      <c r="CR48" s="24" t="n"/>
+      <c r="CS48" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="49" ht="36" customHeight="1">
       <c r="A49" s="24" t="inlineStr">
         <is>
-          <t>36a8e843485741c2</t>
+          <t>7447a7a90b074319</t>
         </is>
       </c>
       <c r="B49" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C49" s="24" t="inlineStr">
@@ -15704,16 +15732,16 @@
       </c>
       <c r="H49" s="24" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="I49" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>under</t>
         </is>
       </c>
       <c r="J49" s="25" t="n">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="K49" s="24" t="inlineStr">
         <is>
@@ -15721,32 +15749,32 @@
         </is>
       </c>
       <c r="L49" s="26" t="n">
-        <v>-135</v>
+        <v>-111</v>
       </c>
       <c r="M49" s="27" t="n">
-        <v>1.740741</v>
+        <v>1.900901</v>
       </c>
       <c r="N49" s="28" t="n">
-        <v>0.574468</v>
+        <v>0.526066</v>
       </c>
       <c r="O49" s="28" t="n">
-        <v>0.611882</v>
+        <v>0.510786</v>
       </c>
       <c r="P49" s="28" t="n">
         <v>0.05172</v>
       </c>
       <c r="Q49" s="28" t="n">
-        <v>0.037414</v>
+        <v>-0.01528</v>
       </c>
       <c r="R49" s="26" t="n">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="S49" s="29" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="T49" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-totals-v2</t>
         </is>
       </c>
       <c r="U49" s="24" t="inlineStr">
@@ -15765,7 +15793,7 @@
       <c r="AD49" s="24" t="n"/>
       <c r="AE49" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.35-4.35; raw selected-side p=0.6704, calibrated p=0.6119.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.35-4.35; raw selected-side p=0.5083, calibrated p=0.5108.</t>
         </is>
       </c>
       <c r="AF49" s="31" t="inlineStr">
@@ -15849,7 +15877,7 @@
       </c>
       <c r="BA49" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
         </is>
       </c>
       <c r="BB49" s="24" t="inlineStr">
@@ -15859,12 +15887,12 @@
       </c>
       <c r="BC49" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-totals-v2</t>
         </is>
       </c>
       <c r="BD49" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
         </is>
       </c>
       <c r="BE49" s="24" t="inlineStr">
@@ -15884,7 +15912,7 @@
       </c>
       <c r="BH49" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI49" s="24" t="inlineStr">
@@ -15893,19 +15921,19 @@
         </is>
       </c>
       <c r="BJ49" s="25" t="n">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="BK49" s="26" t="n">
-        <v>-135</v>
+        <v>-111</v>
       </c>
       <c r="BL49" s="27" t="n">
-        <v>1.740741</v>
+        <v>1.900901</v>
       </c>
       <c r="BM49" s="28" t="n">
-        <v>0.574468</v>
+        <v>0.526066</v>
       </c>
       <c r="BN49" s="28" t="n">
-        <v>0.572139</v>
+        <v>0.522388</v>
       </c>
       <c r="BO49" s="28" t="n"/>
       <c r="BP49" s="25" t="n"/>
@@ -15936,31 +15964,32 @@
       <c r="CO49" s="24" t="n"/>
       <c r="CP49" s="24" t="n"/>
       <c r="CQ49" s="24" t="n"/>
-      <c r="CR49" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
+      <c r="CR49" s="24" t="n"/>
+      <c r="CS49" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="50" ht="36" customHeight="1">
       <c r="A50" s="24" t="inlineStr">
         <is>
-          <t>c992438407204be4</t>
+          <t>74826e5d920a490b</t>
         </is>
       </c>
       <c r="B50" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C50" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T23:05Z</t>
+          <t>2026-08-04T23:10Z</t>
         </is>
       </c>
       <c r="D50" s="24" t="inlineStr">
         <is>
-          <t>401816389</t>
+          <t>401816386</t>
         </is>
       </c>
       <c r="E50" s="24" t="inlineStr">
@@ -15970,26 +15999,26 @@
       </c>
       <c r="F50" s="24" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="G50" s="24" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="H50" s="24" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="I50" s="24" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J50" s="25" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="K50" s="24" t="inlineStr">
         <is>
@@ -15997,32 +16026,32 @@
         </is>
       </c>
       <c r="L50" s="26" t="n">
-        <v>-108</v>
+        <v>-174</v>
       </c>
       <c r="M50" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.574713</v>
       </c>
       <c r="N50" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.635036</v>
       </c>
       <c r="O50" s="28" t="n">
-        <v>0.513093</v>
+        <v>0.558902</v>
       </c>
       <c r="P50" s="28" t="n">
         <v>0.05172</v>
       </c>
       <c r="Q50" s="28" t="n">
-        <v>-0.006138</v>
+        <v>-0.07613399999999999</v>
       </c>
       <c r="R50" s="26" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="S50" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T50" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-margin-v2</t>
         </is>
       </c>
       <c r="U50" s="24" t="inlineStr">
@@ -16041,7 +16070,7 @@
       <c r="AD50" s="24" t="n"/>
       <c r="AE50" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.35-4.35; raw selected-side p=0.5151, calibrated p=0.5131.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.37-5.16; raw selected-side p=0.5897, calibrated p=0.5589.</t>
         </is>
       </c>
       <c r="AF50" s="31" t="inlineStr">
@@ -16082,32 +16111,32 @@
       </c>
       <c r="AP50" s="24" t="inlineStr">
         <is>
-          <t>mlb-stl</t>
+          <t>mlb-cws</t>
         </is>
       </c>
       <c r="AQ50" s="24" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="AR50" s="24" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="AS50" s="24" t="inlineStr">
         <is>
-          <t>mlb-nyy</t>
+          <t>mlb-bos</t>
         </is>
       </c>
       <c r="AT50" s="24" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="AU50" s="24" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="AV50" s="24" t="n"/>
@@ -16125,7 +16154,7 @@
       </c>
       <c r="BA50" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
         </is>
       </c>
       <c r="BB50" s="24" t="inlineStr">
@@ -16135,12 +16164,12 @@
       </c>
       <c r="BC50" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-margin-v2</t>
         </is>
       </c>
       <c r="BD50" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
         </is>
       </c>
       <c r="BE50" s="24" t="inlineStr">
@@ -16160,7 +16189,7 @@
       </c>
       <c r="BH50" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI50" s="24" t="inlineStr">
@@ -16169,19 +16198,19 @@
         </is>
       </c>
       <c r="BJ50" s="25" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="BK50" s="26" t="n">
-        <v>-108</v>
+        <v>-174</v>
       </c>
       <c r="BL50" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.574713</v>
       </c>
       <c r="BM50" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.635036</v>
       </c>
       <c r="BN50" s="28" t="n">
-        <v>0.517413</v>
+        <v>0.631841</v>
       </c>
       <c r="BO50" s="28" t="n"/>
       <c r="BP50" s="25" t="n"/>
@@ -16212,7 +16241,8 @@
       <c r="CO50" s="24" t="n"/>
       <c r="CP50" s="24" t="n"/>
       <c r="CQ50" s="24" t="n"/>
-      <c r="CR50" s="24" t="inlineStr">
+      <c r="CR50" s="24" t="n"/>
+      <c r="CS50" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -16221,12 +16251,12 @@
     <row r="51" ht="36" customHeight="1">
       <c r="A51" s="24" t="inlineStr">
         <is>
-          <t>e9ddc697bb5c4a01</t>
+          <t>8e58043a780a4849</t>
         </is>
       </c>
       <c r="B51" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C51" s="24" t="inlineStr">
@@ -16256,16 +16286,16 @@
       </c>
       <c r="H51" s="24" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="I51" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>over</t>
         </is>
       </c>
       <c r="J51" s="25" t="n">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="K51" s="24" t="inlineStr">
         <is>
@@ -16273,32 +16303,32 @@
         </is>
       </c>
       <c r="L51" s="26" t="n">
-        <v>-178</v>
+        <v>-122</v>
       </c>
       <c r="M51" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.819672</v>
       </c>
       <c r="N51" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.54955</v>
       </c>
       <c r="O51" s="28" t="n">
-        <v>0.561067</v>
+        <v>0.529648</v>
       </c>
       <c r="P51" s="28" t="n">
         <v>0.05172</v>
       </c>
       <c r="Q51" s="28" t="n">
-        <v>-0.079221</v>
+        <v>-0.019902</v>
       </c>
       <c r="R51" s="26" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S51" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T51" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-totals-v2</t>
         </is>
       </c>
       <c r="U51" s="24" t="inlineStr">
@@ -16317,7 +16347,7 @@
       <c r="AD51" s="24" t="n"/>
       <c r="AE51" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.37-5.16; raw selected-side p=0.5930, calibrated p=0.5611.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.37-5.16; raw selected-side p=0.5635, calibrated p=0.5296.</t>
         </is>
       </c>
       <c r="AF51" s="31" t="inlineStr">
@@ -16401,7 +16431,7 @@
       </c>
       <c r="BA51" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
         </is>
       </c>
       <c r="BB51" s="24" t="inlineStr">
@@ -16411,12 +16441,12 @@
       </c>
       <c r="BC51" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-totals-v2</t>
         </is>
       </c>
       <c r="BD51" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
         </is>
       </c>
       <c r="BE51" s="24" t="inlineStr">
@@ -16436,7 +16466,7 @@
       </c>
       <c r="BH51" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI51" s="24" t="inlineStr">
@@ -16445,19 +16475,19 @@
         </is>
       </c>
       <c r="BJ51" s="25" t="n">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="BK51" s="26" t="n">
-        <v>-178</v>
+        <v>-122</v>
       </c>
       <c r="BL51" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.819672</v>
       </c>
       <c r="BM51" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.54955</v>
       </c>
       <c r="BN51" s="28" t="n">
-        <v>0.636816</v>
+        <v>0.547264</v>
       </c>
       <c r="BO51" s="28" t="n"/>
       <c r="BP51" s="25" t="n"/>
@@ -16488,7 +16518,8 @@
       <c r="CO51" s="24" t="n"/>
       <c r="CP51" s="24" t="n"/>
       <c r="CQ51" s="24" t="n"/>
-      <c r="CR51" s="24" t="inlineStr">
+      <c r="CR51" s="24" t="n"/>
+      <c r="CS51" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -16497,22 +16528,22 @@
     <row r="52" ht="36" customHeight="1">
       <c r="A52" s="24" t="inlineStr">
         <is>
-          <t>9fe44a3d5c074b0c</t>
+          <t>8c1d1d3f571d4025</t>
         </is>
       </c>
       <c r="B52" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C52" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T23:10Z</t>
+          <t>2026-08-04T23:15Z</t>
         </is>
       </c>
       <c r="D52" s="24" t="inlineStr">
         <is>
-          <t>401816386</t>
+          <t>401816387</t>
         </is>
       </c>
       <c r="E52" s="24" t="inlineStr">
@@ -16522,26 +16553,26 @@
       </c>
       <c r="F52" s="24" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="G52" s="24" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="H52" s="24" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="I52" s="24" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J52" s="25" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="K52" s="24" t="inlineStr">
         <is>
@@ -16549,32 +16580,32 @@
         </is>
       </c>
       <c r="L52" s="26" t="n">
-        <v>-125</v>
+        <v>-150</v>
       </c>
       <c r="M52" s="27" t="n">
-        <v>1.8</v>
+        <v>1.666667</v>
       </c>
       <c r="N52" s="28" t="n">
-        <v>0.555556</v>
+        <v>0.6</v>
       </c>
       <c r="O52" s="28" t="n">
-        <v>0.530246</v>
+        <v>0.567661</v>
       </c>
       <c r="P52" s="28" t="n">
-        <v>0.05172</v>
+        <v>0.042131</v>
       </c>
       <c r="Q52" s="28" t="n">
-        <v>-0.02531</v>
+        <v>-0.032339</v>
       </c>
       <c r="R52" s="26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S52" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T52" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-margin-v2</t>
         </is>
       </c>
       <c r="U52" s="24" t="inlineStr">
@@ -16593,7 +16624,7 @@
       <c r="AD52" s="24" t="n"/>
       <c r="AE52" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.37-5.16; raw selected-side p=0.5653, calibrated p=0.5302.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.10-4.82; raw selected-side p=0.6030, calibrated p=0.5677.</t>
         </is>
       </c>
       <c r="AF52" s="31" t="inlineStr">
@@ -16634,32 +16665,32 @@
       </c>
       <c r="AP52" s="24" t="inlineStr">
         <is>
-          <t>mlb-cws</t>
+          <t>mlb-mia</t>
         </is>
       </c>
       <c r="AQ52" s="24" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="AR52" s="24" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="AS52" s="24" t="inlineStr">
         <is>
-          <t>mlb-bos</t>
+          <t>mlb-atl</t>
         </is>
       </c>
       <c r="AT52" s="24" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="AU52" s="24" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="AV52" s="24" t="n"/>
@@ -16677,7 +16708,7 @@
       </c>
       <c r="BA52" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
         </is>
       </c>
       <c r="BB52" s="24" t="inlineStr">
@@ -16687,12 +16718,12 @@
       </c>
       <c r="BC52" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-margin-v2</t>
         </is>
       </c>
       <c r="BD52" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
         </is>
       </c>
       <c r="BE52" s="24" t="inlineStr">
@@ -16712,7 +16743,7 @@
       </c>
       <c r="BH52" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI52" s="24" t="inlineStr">
@@ -16721,19 +16752,19 @@
         </is>
       </c>
       <c r="BJ52" s="25" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="BK52" s="26" t="n">
-        <v>-125</v>
+        <v>-150</v>
       </c>
       <c r="BL52" s="27" t="n">
-        <v>1.8</v>
+        <v>1.666667</v>
       </c>
       <c r="BM52" s="28" t="n">
-        <v>0.555556</v>
+        <v>0.6</v>
       </c>
       <c r="BN52" s="28" t="n">
-        <v>0.552239</v>
+        <v>0.597015</v>
       </c>
       <c r="BO52" s="28" t="n"/>
       <c r="BP52" s="25" t="n"/>
@@ -16764,7 +16795,8 @@
       <c r="CO52" s="24" t="n"/>
       <c r="CP52" s="24" t="n"/>
       <c r="CQ52" s="24" t="n"/>
-      <c r="CR52" s="24" t="inlineStr">
+      <c r="CR52" s="24" t="n"/>
+      <c r="CS52" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -16773,12 +16805,12 @@
     <row r="53" ht="36" customHeight="1">
       <c r="A53" s="24" t="inlineStr">
         <is>
-          <t>930434e105a343cf</t>
+          <t>1f9fb77aaf164589</t>
         </is>
       </c>
       <c r="B53" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C53" s="24" t="inlineStr">
@@ -16808,16 +16840,16 @@
       </c>
       <c r="H53" s="24" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="I53" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>under</t>
         </is>
       </c>
       <c r="J53" s="25" t="n">
-        <v>1.5</v>
+        <v>9.5</v>
       </c>
       <c r="K53" s="24" t="inlineStr">
         <is>
@@ -16825,32 +16857,32 @@
         </is>
       </c>
       <c r="L53" s="26" t="n">
-        <v>-150</v>
+        <v>-113</v>
       </c>
       <c r="M53" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.884956</v>
       </c>
       <c r="N53" s="28" t="n">
-        <v>0.6</v>
+        <v>0.530516</v>
       </c>
       <c r="O53" s="28" t="n">
-        <v>0.563298</v>
+        <v>0.54376</v>
       </c>
       <c r="P53" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q53" s="28" t="n">
-        <v>-0.036702</v>
+        <v>0.013244</v>
       </c>
       <c r="R53" s="26" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="S53" s="29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T53" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-totals-v2</t>
         </is>
       </c>
       <c r="U53" s="24" t="inlineStr">
@@ -16869,7 +16901,7 @@
       <c r="AD53" s="24" t="n"/>
       <c r="AE53" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.10-4.82; raw selected-side p=0.5964, calibrated p=0.5633.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.10-4.82; raw selected-side p=0.6048, calibrated p=0.5438.</t>
         </is>
       </c>
       <c r="AF53" s="31" t="inlineStr">
@@ -16953,7 +16985,7 @@
       </c>
       <c r="BA53" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
         </is>
       </c>
       <c r="BB53" s="24" t="inlineStr">
@@ -16963,12 +16995,12 @@
       </c>
       <c r="BC53" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-totals-v2</t>
         </is>
       </c>
       <c r="BD53" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
         </is>
       </c>
       <c r="BE53" s="24" t="inlineStr">
@@ -16988,7 +17020,7 @@
       </c>
       <c r="BH53" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI53" s="24" t="inlineStr">
@@ -16997,19 +17029,19 @@
         </is>
       </c>
       <c r="BJ53" s="25" t="n">
-        <v>1.5</v>
+        <v>9.5</v>
       </c>
       <c r="BK53" s="26" t="n">
-        <v>-150</v>
+        <v>-113</v>
       </c>
       <c r="BL53" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.884956</v>
       </c>
       <c r="BM53" s="28" t="n">
-        <v>0.6</v>
+        <v>0.530516</v>
       </c>
       <c r="BN53" s="28" t="n">
-        <v>0.597015</v>
+        <v>0.527363</v>
       </c>
       <c r="BO53" s="28" t="n"/>
       <c r="BP53" s="25" t="n"/>
@@ -17040,31 +17072,32 @@
       <c r="CO53" s="24" t="n"/>
       <c r="CP53" s="24" t="n"/>
       <c r="CQ53" s="24" t="n"/>
-      <c r="CR53" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
+      <c r="CR53" s="24" t="n"/>
+      <c r="CS53" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="54" ht="36" customHeight="1">
       <c r="A54" s="24" t="inlineStr">
         <is>
-          <t>e529811f2e5c408d</t>
+          <t>032ac8c42bb54932</t>
         </is>
       </c>
       <c r="B54" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C54" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T23:15Z</t>
+          <t>2026-08-04T23:40Z</t>
         </is>
       </c>
       <c r="D54" s="24" t="inlineStr">
         <is>
-          <t>401816387</t>
+          <t>401816392</t>
         </is>
       </c>
       <c r="E54" s="24" t="inlineStr">
@@ -17074,26 +17107,26 @@
       </c>
       <c r="F54" s="24" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="G54" s="24" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="H54" s="24" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="I54" s="24" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J54" s="25" t="n">
-        <v>9.5</v>
+        <v>1.5</v>
       </c>
       <c r="K54" s="24" t="inlineStr">
         <is>
@@ -17101,32 +17134,32 @@
         </is>
       </c>
       <c r="L54" s="26" t="n">
-        <v>-120</v>
+        <v>-122</v>
       </c>
       <c r="M54" s="27" t="n">
-        <v>1.833333</v>
+        <v>1.819672</v>
       </c>
       <c r="N54" s="28" t="n">
-        <v>0.545455</v>
+        <v>0.54955</v>
       </c>
       <c r="O54" s="28" t="n">
-        <v>0.542496</v>
+        <v>0.700193</v>
       </c>
       <c r="P54" s="28" t="n">
-        <v>0.042131</v>
+        <v>0.05172</v>
       </c>
       <c r="Q54" s="28" t="n">
-        <v>-0.002959</v>
+        <v>0.150643</v>
       </c>
       <c r="R54" s="26" t="n">
-        <v>25</v>
+        <v>95</v>
       </c>
       <c r="S54" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T54" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-margin-v2</t>
         </is>
       </c>
       <c r="U54" s="24" t="inlineStr">
@@ -17145,7 +17178,7 @@
       <c r="AD54" s="24" t="n"/>
       <c r="AE54" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.10-4.82; raw selected-side p=0.6011, calibrated p=0.5425.</t>
+          <t>Measured Edge Margin: Trend Engine projected 3.16-4.32; raw selected-side p=0.8051, calibrated p=0.7002.</t>
         </is>
       </c>
       <c r="AF54" s="31" t="inlineStr">
@@ -17186,32 +17219,32 @@
       </c>
       <c r="AP54" s="24" t="inlineStr">
         <is>
-          <t>mlb-mia</t>
+          <t>mlb-min</t>
         </is>
       </c>
       <c r="AQ54" s="24" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="AR54" s="24" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="AS54" s="24" t="inlineStr">
         <is>
-          <t>mlb-atl</t>
+          <t>mlb-kc</t>
         </is>
       </c>
       <c r="AT54" s="24" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="AU54" s="24" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="AV54" s="24" t="n"/>
@@ -17229,7 +17262,7 @@
       </c>
       <c r="BA54" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
         </is>
       </c>
       <c r="BB54" s="24" t="inlineStr">
@@ -17239,12 +17272,12 @@
       </c>
       <c r="BC54" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-margin-v2</t>
         </is>
       </c>
       <c r="BD54" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
         </is>
       </c>
       <c r="BE54" s="24" t="inlineStr">
@@ -17264,7 +17297,7 @@
       </c>
       <c r="BH54" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI54" s="24" t="inlineStr">
@@ -17273,19 +17306,19 @@
         </is>
       </c>
       <c r="BJ54" s="25" t="n">
-        <v>9.5</v>
+        <v>1.5</v>
       </c>
       <c r="BK54" s="26" t="n">
-        <v>-120</v>
+        <v>-122</v>
       </c>
       <c r="BL54" s="27" t="n">
-        <v>1.833333</v>
+        <v>1.819672</v>
       </c>
       <c r="BM54" s="28" t="n">
-        <v>0.545455</v>
+        <v>0.54955</v>
       </c>
       <c r="BN54" s="28" t="n">
-        <v>0.542289</v>
+        <v>0.547264</v>
       </c>
       <c r="BO54" s="28" t="n"/>
       <c r="BP54" s="25" t="n"/>
@@ -17316,21 +17349,22 @@
       <c r="CO54" s="24" t="n"/>
       <c r="CP54" s="24" t="n"/>
       <c r="CQ54" s="24" t="n"/>
-      <c r="CR54" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
+      <c r="CR54" s="24" t="n"/>
+      <c r="CS54" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="55" ht="36" customHeight="1">
       <c r="A55" s="24" t="inlineStr">
         <is>
-          <t>f2ced1650ff241d4</t>
+          <t>352ff4cb49064cdb</t>
         </is>
       </c>
       <c r="B55" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C55" s="24" t="inlineStr">
@@ -17360,16 +17394,16 @@
       </c>
       <c r="H55" s="24" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="I55" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>under</t>
         </is>
       </c>
       <c r="J55" s="25" t="n">
-        <v>1.5</v>
+        <v>9.5</v>
       </c>
       <c r="K55" s="24" t="inlineStr">
         <is>
@@ -17386,23 +17420,23 @@
         <v>0.545455</v>
       </c>
       <c r="O55" s="28" t="n">
-        <v>0.702982</v>
+        <v>0.587703</v>
       </c>
       <c r="P55" s="28" t="n">
         <v>0.05172</v>
       </c>
       <c r="Q55" s="28" t="n">
-        <v>0.157527</v>
+        <v>0.042248</v>
       </c>
       <c r="R55" s="26" t="n">
-        <v>99</v>
+        <v>42</v>
       </c>
       <c r="S55" s="29" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="T55" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-totals-v2</t>
         </is>
       </c>
       <c r="U55" s="24" t="inlineStr">
@@ -17421,7 +17455,7 @@
       <c r="AD55" s="24" t="n"/>
       <c r="AE55" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 3.16-4.32; raw selected-side p=0.8093, calibrated p=0.7030.</t>
+          <t>Measured Edge Totals: Trend Engine projected 3.16-4.32; raw selected-side p=0.7334, calibrated p=0.5877.</t>
         </is>
       </c>
       <c r="AF55" s="31" t="inlineStr">
@@ -17505,7 +17539,7 @@
       </c>
       <c r="BA55" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
         </is>
       </c>
       <c r="BB55" s="24" t="inlineStr">
@@ -17515,12 +17549,12 @@
       </c>
       <c r="BC55" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-totals-v2</t>
         </is>
       </c>
       <c r="BD55" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
         </is>
       </c>
       <c r="BE55" s="24" t="inlineStr">
@@ -17540,7 +17574,7 @@
       </c>
       <c r="BH55" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI55" s="24" t="inlineStr">
@@ -17549,7 +17583,7 @@
         </is>
       </c>
       <c r="BJ55" s="25" t="n">
-        <v>1.5</v>
+        <v>9.5</v>
       </c>
       <c r="BK55" s="26" t="n">
         <v>-120</v>
@@ -17592,7 +17626,8 @@
       <c r="CO55" s="24" t="n"/>
       <c r="CP55" s="24" t="n"/>
       <c r="CQ55" s="24" t="n"/>
-      <c r="CR55" s="24" t="inlineStr">
+      <c r="CR55" s="24" t="n"/>
+      <c r="CS55" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -17601,12 +17636,12 @@
     <row r="56" ht="36" customHeight="1">
       <c r="A56" s="24" t="inlineStr">
         <is>
-          <t>e68c58bbc7d74d97</t>
+          <t>72db7fcab77e4e00</t>
         </is>
       </c>
       <c r="B56" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C56" s="24" t="inlineStr">
@@ -17616,7 +17651,7 @@
       </c>
       <c r="D56" s="24" t="inlineStr">
         <is>
-          <t>401816392</t>
+          <t>401816393</t>
         </is>
       </c>
       <c r="E56" s="24" t="inlineStr">
@@ -17626,26 +17661,26 @@
       </c>
       <c r="F56" s="24" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="G56" s="24" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="H56" s="24" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="I56" s="24" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J56" s="25" t="n">
-        <v>9.5</v>
+        <v>1.5</v>
       </c>
       <c r="K56" s="24" t="inlineStr">
         <is>
@@ -17653,32 +17688,32 @@
         </is>
       </c>
       <c r="L56" s="26" t="n">
-        <v>-120</v>
+        <v>-147</v>
       </c>
       <c r="M56" s="27" t="n">
-        <v>1.833333</v>
+        <v>1.680272</v>
       </c>
       <c r="N56" s="28" t="n">
-        <v>0.545455</v>
+        <v>0.5951419999999999</v>
       </c>
       <c r="O56" s="28" t="n">
-        <v>0.590214</v>
+        <v>0.597054</v>
       </c>
       <c r="P56" s="28" t="n">
         <v>0.05172</v>
       </c>
       <c r="Q56" s="28" t="n">
-        <v>0.044759</v>
+        <v>0.001912</v>
       </c>
       <c r="R56" s="26" t="n">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="S56" s="29" t="n">
         <v>1.25</v>
       </c>
       <c r="T56" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-margin-v2</t>
         </is>
       </c>
       <c r="U56" s="24" t="inlineStr">
@@ -17697,7 +17732,7 @@
       <c r="AD56" s="24" t="n"/>
       <c r="AE56" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 3.16-4.32; raw selected-side p=0.7408, calibrated p=0.5902.</t>
+          <t>Measured Edge Margin: Trend Engine projected 3.58-4.00; raw selected-side p=0.6479, calibrated p=0.5971.</t>
         </is>
       </c>
       <c r="AF56" s="31" t="inlineStr">
@@ -17738,32 +17773,32 @@
       </c>
       <c r="AP56" s="24" t="inlineStr">
         <is>
-          <t>mlb-min</t>
+          <t>mlb-pit</t>
         </is>
       </c>
       <c r="AQ56" s="24" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="AR56" s="24" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="AS56" s="24" t="inlineStr">
         <is>
-          <t>mlb-kc</t>
+          <t>mlb-mil</t>
         </is>
       </c>
       <c r="AT56" s="24" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="AU56" s="24" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="AV56" s="24" t="n"/>
@@ -17781,7 +17816,7 @@
       </c>
       <c r="BA56" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
         </is>
       </c>
       <c r="BB56" s="24" t="inlineStr">
@@ -17791,12 +17826,12 @@
       </c>
       <c r="BC56" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-margin-v2</t>
         </is>
       </c>
       <c r="BD56" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
         </is>
       </c>
       <c r="BE56" s="24" t="inlineStr">
@@ -17816,7 +17851,7 @@
       </c>
       <c r="BH56" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI56" s="24" t="inlineStr">
@@ -17825,19 +17860,19 @@
         </is>
       </c>
       <c r="BJ56" s="25" t="n">
-        <v>9.5</v>
+        <v>1.5</v>
       </c>
       <c r="BK56" s="26" t="n">
-        <v>-120</v>
+        <v>-147</v>
       </c>
       <c r="BL56" s="27" t="n">
-        <v>1.833333</v>
+        <v>1.680272</v>
       </c>
       <c r="BM56" s="28" t="n">
-        <v>0.545455</v>
+        <v>0.5951419999999999</v>
       </c>
       <c r="BN56" s="28" t="n">
-        <v>0.542289</v>
+        <v>0.59204</v>
       </c>
       <c r="BO56" s="28" t="n"/>
       <c r="BP56" s="25" t="n"/>
@@ -17868,7 +17903,8 @@
       <c r="CO56" s="24" t="n"/>
       <c r="CP56" s="24" t="n"/>
       <c r="CQ56" s="24" t="n"/>
-      <c r="CR56" s="24" t="inlineStr">
+      <c r="CR56" s="24" t="n"/>
+      <c r="CS56" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -17877,12 +17913,12 @@
     <row r="57" ht="36" customHeight="1">
       <c r="A57" s="24" t="inlineStr">
         <is>
-          <t>a8a0293973dd4f21</t>
+          <t>3aaaf6eb6eef4eb1</t>
         </is>
       </c>
       <c r="B57" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C57" s="24" t="inlineStr">
@@ -17912,16 +17948,16 @@
       </c>
       <c r="H57" s="24" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="I57" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>under</t>
         </is>
       </c>
       <c r="J57" s="25" t="n">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="K57" s="24" t="inlineStr">
         <is>
@@ -17929,32 +17965,32 @@
         </is>
       </c>
       <c r="L57" s="26" t="n">
-        <v>-150</v>
+        <v>-106</v>
       </c>
       <c r="M57" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.943396</v>
       </c>
       <c r="N57" s="28" t="n">
-        <v>0.6</v>
+        <v>0.514563</v>
       </c>
       <c r="O57" s="28" t="n">
-        <v>0.593511</v>
+        <v>0.523429</v>
       </c>
       <c r="P57" s="28" t="n">
         <v>0.05172</v>
       </c>
       <c r="Q57" s="28" t="n">
-        <v>-0.006489</v>
+        <v>0.008866000000000001</v>
       </c>
       <c r="R57" s="26" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="S57" s="29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T57" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-totals-v2</t>
         </is>
       </c>
       <c r="U57" s="24" t="inlineStr">
@@ -17973,7 +18009,7 @@
       <c r="AD57" s="24" t="n"/>
       <c r="AE57" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 3.58-4.00; raw selected-side p=0.6424, calibrated p=0.5935.</t>
+          <t>Measured Edge Totals: Trend Engine projected 3.58-4.00; raw selected-side p=0.5453, calibrated p=0.5234.</t>
         </is>
       </c>
       <c r="AF57" s="31" t="inlineStr">
@@ -18057,7 +18093,7 @@
       </c>
       <c r="BA57" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
         </is>
       </c>
       <c r="BB57" s="24" t="inlineStr">
@@ -18067,12 +18103,12 @@
       </c>
       <c r="BC57" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-totals-v2</t>
         </is>
       </c>
       <c r="BD57" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
         </is>
       </c>
       <c r="BE57" s="24" t="inlineStr">
@@ -18092,7 +18128,7 @@
       </c>
       <c r="BH57" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI57" s="24" t="inlineStr">
@@ -18101,19 +18137,19 @@
         </is>
       </c>
       <c r="BJ57" s="25" t="n">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="BK57" s="26" t="n">
-        <v>-150</v>
+        <v>-106</v>
       </c>
       <c r="BL57" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.943396</v>
       </c>
       <c r="BM57" s="28" t="n">
-        <v>0.6</v>
+        <v>0.514563</v>
       </c>
       <c r="BN57" s="28" t="n">
-        <v>0.597015</v>
+        <v>0.509901</v>
       </c>
       <c r="BO57" s="28" t="n"/>
       <c r="BP57" s="25" t="n"/>
@@ -18144,31 +18180,32 @@
       <c r="CO57" s="24" t="n"/>
       <c r="CP57" s="24" t="n"/>
       <c r="CQ57" s="24" t="n"/>
-      <c r="CR57" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
+      <c r="CR57" s="24" t="n"/>
+      <c r="CS57" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="58" ht="36" customHeight="1">
       <c r="A58" s="24" t="inlineStr">
         <is>
-          <t>967686712a774c57</t>
+          <t>efd57fffe90f4d98</t>
         </is>
       </c>
       <c r="B58" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C58" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T23:40Z</t>
+          <t>2026-08-05T00:05Z</t>
         </is>
       </c>
       <c r="D58" s="24" t="inlineStr">
         <is>
-          <t>401816393</t>
+          <t>401816391</t>
         </is>
       </c>
       <c r="E58" s="24" t="inlineStr">
@@ -18178,26 +18215,26 @@
       </c>
       <c r="F58" s="24" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="G58" s="24" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="H58" s="24" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="I58" s="24" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J58" s="25" t="n">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
       <c r="K58" s="24" t="inlineStr">
         <is>
@@ -18205,32 +18242,32 @@
         </is>
       </c>
       <c r="L58" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="M58" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="N58" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="O58" s="28" t="n">
+        <v>0.62835</v>
+      </c>
+      <c r="P58" s="28" t="n">
+        <v>0.042131</v>
+      </c>
+      <c r="Q58" s="28" t="n">
+        <v>0.167521</v>
+      </c>
+      <c r="R58" s="26" t="n">
         <v>100</v>
       </c>
-      <c r="M58" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="N58" s="28" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O58" s="28" t="n">
-        <v>0.52237</v>
-      </c>
-      <c r="P58" s="28" t="n">
-        <v>0.05172</v>
-      </c>
-      <c r="Q58" s="28" t="n">
-        <v>0.02237</v>
-      </c>
-      <c r="R58" s="26" t="n">
-        <v>31</v>
-      </c>
       <c r="S58" s="29" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="T58" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-margin-v2</t>
         </is>
       </c>
       <c r="U58" s="24" t="inlineStr">
@@ -18249,7 +18286,7 @@
       <c r="AD58" s="24" t="n"/>
       <c r="AE58" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 3.58-4.00; raw selected-side p=0.5422, calibrated p=0.5224.</t>
+          <t>Measured Edge Margin: Trend Engine projected 3.82-3.91; raw selected-side p=0.6956, calibrated p=0.6284.</t>
         </is>
       </c>
       <c r="AF58" s="31" t="inlineStr">
@@ -18290,32 +18327,32 @@
       </c>
       <c r="AP58" s="24" t="inlineStr">
         <is>
-          <t>mlb-pit</t>
+          <t>mlb-lad</t>
         </is>
       </c>
       <c r="AQ58" s="24" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="AR58" s="24" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="AS58" s="24" t="inlineStr">
         <is>
-          <t>mlb-mil</t>
+          <t>mlb-chc</t>
         </is>
       </c>
       <c r="AT58" s="24" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="AU58" s="24" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="AV58" s="24" t="n"/>
@@ -18333,7 +18370,7 @@
       </c>
       <c r="BA58" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
         </is>
       </c>
       <c r="BB58" s="24" t="inlineStr">
@@ -18343,12 +18380,12 @@
       </c>
       <c r="BC58" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-margin-v2</t>
         </is>
       </c>
       <c r="BD58" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
         </is>
       </c>
       <c r="BE58" s="24" t="inlineStr">
@@ -18368,7 +18405,7 @@
       </c>
       <c r="BH58" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI58" s="24" t="inlineStr">
@@ -18377,19 +18414,19 @@
         </is>
       </c>
       <c r="BJ58" s="25" t="n">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
       <c r="BK58" s="26" t="n">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="BL58" s="27" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="BM58" s="28" t="n">
-        <v>0.5</v>
+        <v>0.460829</v>
       </c>
       <c r="BN58" s="28" t="n">
-        <v>0.497512</v>
+        <v>0.455446</v>
       </c>
       <c r="BO58" s="28" t="n"/>
       <c r="BP58" s="25" t="n"/>
@@ -18420,7 +18457,8 @@
       <c r="CO58" s="24" t="n"/>
       <c r="CP58" s="24" t="n"/>
       <c r="CQ58" s="24" t="n"/>
-      <c r="CR58" s="24" t="inlineStr">
+      <c r="CR58" s="24" t="n"/>
+      <c r="CS58" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -18429,12 +18467,12 @@
     <row r="59" ht="36" customHeight="1">
       <c r="A59" s="24" t="inlineStr">
         <is>
-          <t>5234f00872d54269</t>
+          <t>5afdfe6a6e5342e0</t>
         </is>
       </c>
       <c r="B59" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C59" s="24" t="inlineStr">
@@ -18464,16 +18502,16 @@
       </c>
       <c r="H59" s="24" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="I59" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>under</t>
         </is>
       </c>
       <c r="J59" s="25" t="n">
-        <v>1.5</v>
+        <v>9.5</v>
       </c>
       <c r="K59" s="24" t="inlineStr">
         <is>
@@ -18481,32 +18519,32 @@
         </is>
       </c>
       <c r="L59" s="26" t="n">
-        <v>120</v>
+        <v>-122</v>
       </c>
       <c r="M59" s="27" t="n">
-        <v>2.2</v>
+        <v>1.819672</v>
       </c>
       <c r="N59" s="28" t="n">
-        <v>0.454545</v>
+        <v>0.54955</v>
       </c>
       <c r="O59" s="28" t="n">
-        <v>0.626973</v>
+        <v>0.579434</v>
       </c>
       <c r="P59" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q59" s="28" t="n">
-        <v>0.172428</v>
+        <v>0.029884</v>
       </c>
       <c r="R59" s="26" t="n">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="S59" s="29" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="T59" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-totals-v2</t>
         </is>
       </c>
       <c r="U59" s="24" t="inlineStr">
@@ -18525,7 +18563,7 @@
       <c r="AD59" s="24" t="n"/>
       <c r="AE59" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 3.82-3.91; raw selected-side p=0.6935, calibrated p=0.6270.</t>
+          <t>Measured Edge Totals: Trend Engine projected 3.82-3.91; raw selected-side p=0.7092, calibrated p=0.5794.</t>
         </is>
       </c>
       <c r="AF59" s="31" t="inlineStr">
@@ -18609,7 +18647,7 @@
       </c>
       <c r="BA59" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
         </is>
       </c>
       <c r="BB59" s="24" t="inlineStr">
@@ -18619,12 +18657,12 @@
       </c>
       <c r="BC59" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-totals-v2</t>
         </is>
       </c>
       <c r="BD59" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
         </is>
       </c>
       <c r="BE59" s="24" t="inlineStr">
@@ -18644,7 +18682,7 @@
       </c>
       <c r="BH59" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI59" s="24" t="inlineStr">
@@ -18653,19 +18691,19 @@
         </is>
       </c>
       <c r="BJ59" s="25" t="n">
-        <v>1.5</v>
+        <v>9.5</v>
       </c>
       <c r="BK59" s="26" t="n">
-        <v>120</v>
+        <v>-122</v>
       </c>
       <c r="BL59" s="27" t="n">
-        <v>2.2</v>
+        <v>1.819672</v>
       </c>
       <c r="BM59" s="28" t="n">
-        <v>0.454545</v>
+        <v>0.54955</v>
       </c>
       <c r="BN59" s="28" t="n">
-        <v>0.452736</v>
+        <v>0.547264</v>
       </c>
       <c r="BO59" s="28" t="n"/>
       <c r="BP59" s="25" t="n"/>
@@ -18696,7 +18734,8 @@
       <c r="CO59" s="24" t="n"/>
       <c r="CP59" s="24" t="n"/>
       <c r="CQ59" s="24" t="n"/>
-      <c r="CR59" s="24" t="inlineStr">
+      <c r="CR59" s="24" t="n"/>
+      <c r="CS59" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -18705,12 +18744,12 @@
     <row r="60" ht="36" customHeight="1">
       <c r="A60" s="24" t="inlineStr">
         <is>
-          <t>4d77dd83a07c4a3f</t>
+          <t>19c2aae4fb7046a6</t>
         </is>
       </c>
       <c r="B60" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C60" s="24" t="inlineStr">
@@ -18720,7 +18759,7 @@
       </c>
       <c r="D60" s="24" t="inlineStr">
         <is>
-          <t>401816391</t>
+          <t>401816394</t>
         </is>
       </c>
       <c r="E60" s="24" t="inlineStr">
@@ -18730,26 +18769,26 @@
       </c>
       <c r="F60" s="24" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>San Francisco Giants</t>
         </is>
       </c>
       <c r="G60" s="24" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="H60" s="24" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="I60" s="24" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J60" s="25" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="K60" s="24" t="inlineStr">
         <is>
@@ -18757,32 +18796,32 @@
         </is>
       </c>
       <c r="L60" s="26" t="n">
-        <v>111</v>
+        <v>-120</v>
       </c>
       <c r="M60" s="27" t="n">
-        <v>2.11</v>
+        <v>1.833333</v>
       </c>
       <c r="N60" s="28" t="n">
-        <v>0.473934</v>
+        <v>0.545455</v>
       </c>
       <c r="O60" s="28" t="n">
-        <v>0.546255</v>
+        <v>0.657612</v>
       </c>
       <c r="P60" s="28" t="n">
-        <v>0.042131</v>
+        <v>0.05172</v>
       </c>
       <c r="Q60" s="28" t="n">
-        <v>0.072321</v>
+        <v>0.112157</v>
       </c>
       <c r="R60" s="26" t="n">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="S60" s="29" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="T60" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-margin-v2</t>
         </is>
       </c>
       <c r="U60" s="24" t="inlineStr">
@@ -18801,7 +18840,7 @@
       <c r="AD60" s="24" t="n"/>
       <c r="AE60" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 3.82-3.91; raw selected-side p=0.6121, calibrated p=0.5463.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.98-4.16; raw selected-side p=0.7401, calibrated p=0.6576.</t>
         </is>
       </c>
       <c r="AF60" s="31" t="inlineStr">
@@ -18842,32 +18881,32 @@
       </c>
       <c r="AP60" s="24" t="inlineStr">
         <is>
-          <t>mlb-lad</t>
+          <t>mlb-sf</t>
         </is>
       </c>
       <c r="AQ60" s="24" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>San Francisco Giants</t>
         </is>
       </c>
       <c r="AR60" s="24" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>San Francisco Giants</t>
         </is>
       </c>
       <c r="AS60" s="24" t="inlineStr">
         <is>
-          <t>mlb-chc</t>
+          <t>mlb-tex</t>
         </is>
       </c>
       <c r="AT60" s="24" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="AU60" s="24" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="AV60" s="24" t="n"/>
@@ -18885,7 +18924,7 @@
       </c>
       <c r="BA60" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
         </is>
       </c>
       <c r="BB60" s="24" t="inlineStr">
@@ -18895,12 +18934,12 @@
       </c>
       <c r="BC60" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-margin-v2</t>
         </is>
       </c>
       <c r="BD60" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
         </is>
       </c>
       <c r="BE60" s="24" t="inlineStr">
@@ -18920,7 +18959,7 @@
       </c>
       <c r="BH60" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI60" s="24" t="inlineStr">
@@ -18929,19 +18968,19 @@
         </is>
       </c>
       <c r="BJ60" s="25" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="BK60" s="26" t="n">
-        <v>111</v>
+        <v>-120</v>
       </c>
       <c r="BL60" s="27" t="n">
-        <v>2.11</v>
+        <v>1.833333</v>
       </c>
       <c r="BM60" s="28" t="n">
-        <v>0.473934</v>
+        <v>0.545455</v>
       </c>
       <c r="BN60" s="28" t="n">
-        <v>0.472637</v>
+        <v>0.542289</v>
       </c>
       <c r="BO60" s="28" t="n"/>
       <c r="BP60" s="25" t="n"/>
@@ -18972,7 +19011,8 @@
       <c r="CO60" s="24" t="n"/>
       <c r="CP60" s="24" t="n"/>
       <c r="CQ60" s="24" t="n"/>
-      <c r="CR60" s="24" t="inlineStr">
+      <c r="CR60" s="24" t="n"/>
+      <c r="CS60" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -18981,12 +19021,12 @@
     <row r="61" ht="36" customHeight="1">
       <c r="A61" s="24" t="inlineStr">
         <is>
-          <t>a43107e1fc0542b5</t>
+          <t>57aef3476be84083</t>
         </is>
       </c>
       <c r="B61" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C61" s="24" t="inlineStr">
@@ -19016,16 +19056,16 @@
       </c>
       <c r="H61" s="24" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="I61" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>over</t>
         </is>
       </c>
       <c r="J61" s="25" t="n">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="K61" s="24" t="inlineStr">
         <is>
@@ -19033,32 +19073,32 @@
         </is>
       </c>
       <c r="L61" s="26" t="n">
-        <v>-122</v>
+        <v>-115</v>
       </c>
       <c r="M61" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.869565</v>
       </c>
       <c r="N61" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.534884</v>
       </c>
       <c r="O61" s="28" t="n">
-        <v>0.6599739999999999</v>
+        <v>0.543008</v>
       </c>
       <c r="P61" s="28" t="n">
         <v>0.05172</v>
       </c>
       <c r="Q61" s="28" t="n">
-        <v>0.110424</v>
+        <v>0.008123999999999999</v>
       </c>
       <c r="R61" s="26" t="n">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="S61" s="29" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="T61" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-totals-v2</t>
         </is>
       </c>
       <c r="U61" s="24" t="inlineStr">
@@ -19077,7 +19117,7 @@
       <c r="AD61" s="24" t="n"/>
       <c r="AE61" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.98-4.16; raw selected-side p=0.7438, calibrated p=0.6600.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.98-4.16; raw selected-side p=0.6026, calibrated p=0.5430.</t>
         </is>
       </c>
       <c r="AF61" s="31" t="inlineStr">
@@ -19161,7 +19201,7 @@
       </c>
       <c r="BA61" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
         </is>
       </c>
       <c r="BB61" s="24" t="inlineStr">
@@ -19171,12 +19211,12 @@
       </c>
       <c r="BC61" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-totals-v2</t>
         </is>
       </c>
       <c r="BD61" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
         </is>
       </c>
       <c r="BE61" s="24" t="inlineStr">
@@ -19196,7 +19236,7 @@
       </c>
       <c r="BH61" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI61" s="24" t="inlineStr">
@@ -19205,19 +19245,19 @@
         </is>
       </c>
       <c r="BJ61" s="25" t="n">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="BK61" s="26" t="n">
-        <v>-122</v>
+        <v>-115</v>
       </c>
       <c r="BL61" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.869565</v>
       </c>
       <c r="BM61" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.534884</v>
       </c>
       <c r="BN61" s="28" t="n">
-        <v>0.547264</v>
+        <v>0.532338</v>
       </c>
       <c r="BO61" s="28" t="n"/>
       <c r="BP61" s="25" t="n"/>
@@ -19248,7 +19288,8 @@
       <c r="CO61" s="24" t="n"/>
       <c r="CP61" s="24" t="n"/>
       <c r="CQ61" s="24" t="n"/>
-      <c r="CR61" s="24" t="inlineStr">
+      <c r="CR61" s="24" t="n"/>
+      <c r="CS61" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -19257,22 +19298,22 @@
     <row r="62" ht="36" customHeight="1">
       <c r="A62" s="24" t="inlineStr">
         <is>
-          <t>8338675c774948c1</t>
+          <t>8bdbed487f214c46</t>
         </is>
       </c>
       <c r="B62" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C62" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T00:05Z</t>
+          <t>2026-08-05T00:10Z</t>
         </is>
       </c>
       <c r="D62" s="24" t="inlineStr">
         <is>
-          <t>401816394</t>
+          <t>401816395</t>
         </is>
       </c>
       <c r="E62" s="24" t="inlineStr">
@@ -19282,26 +19323,26 @@
       </c>
       <c r="F62" s="24" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Toronto Blue Jays</t>
         </is>
       </c>
       <c r="G62" s="24" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="H62" s="24" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="I62" s="24" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J62" s="25" t="n">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
       <c r="K62" s="24" t="inlineStr">
         <is>
@@ -19309,32 +19350,32 @@
         </is>
       </c>
       <c r="L62" s="26" t="n">
-        <v>-113</v>
+        <v>-178</v>
       </c>
       <c r="M62" s="27" t="n">
-        <v>1.884956</v>
+        <v>1.561798</v>
       </c>
       <c r="N62" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.640288</v>
       </c>
       <c r="O62" s="28" t="n">
-        <v>0.544324</v>
+        <v>0.577535</v>
       </c>
       <c r="P62" s="28" t="n">
         <v>0.05172</v>
       </c>
       <c r="Q62" s="28" t="n">
-        <v>0.013808</v>
+        <v>-0.062753</v>
       </c>
       <c r="R62" s="26" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="S62" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T62" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-margin-v2</t>
         </is>
       </c>
       <c r="U62" s="24" t="inlineStr">
@@ -19353,7 +19394,7 @@
       <c r="AD62" s="24" t="n"/>
       <c r="AE62" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.98-4.16; raw selected-side p=0.6065, calibrated p=0.5443.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.31-4.86; raw selected-side p=0.6181, calibrated p=0.5775.</t>
         </is>
       </c>
       <c r="AF62" s="31" t="inlineStr">
@@ -19394,32 +19435,32 @@
       </c>
       <c r="AP62" s="24" t="inlineStr">
         <is>
-          <t>mlb-sf</t>
+          <t>mlb-tor</t>
         </is>
       </c>
       <c r="AQ62" s="24" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Toronto Blue Jays</t>
         </is>
       </c>
       <c r="AR62" s="24" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Toronto Blue Jays</t>
         </is>
       </c>
       <c r="AS62" s="24" t="inlineStr">
         <is>
-          <t>mlb-tex</t>
+          <t>mlb-hou</t>
         </is>
       </c>
       <c r="AT62" s="24" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="AU62" s="24" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="AV62" s="24" t="n"/>
@@ -19437,7 +19478,7 @@
       </c>
       <c r="BA62" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
         </is>
       </c>
       <c r="BB62" s="24" t="inlineStr">
@@ -19447,12 +19488,12 @@
       </c>
       <c r="BC62" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-margin-v2</t>
         </is>
       </c>
       <c r="BD62" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
         </is>
       </c>
       <c r="BE62" s="24" t="inlineStr">
@@ -19472,7 +19513,7 @@
       </c>
       <c r="BH62" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI62" s="24" t="inlineStr">
@@ -19481,19 +19522,19 @@
         </is>
       </c>
       <c r="BJ62" s="25" t="n">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
       <c r="BK62" s="26" t="n">
-        <v>-113</v>
+        <v>-178</v>
       </c>
       <c r="BL62" s="27" t="n">
-        <v>1.884956</v>
+        <v>1.561798</v>
       </c>
       <c r="BM62" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.640288</v>
       </c>
       <c r="BN62" s="28" t="n">
-        <v>0.527363</v>
+        <v>0.636816</v>
       </c>
       <c r="BO62" s="28" t="n"/>
       <c r="BP62" s="25" t="n"/>
@@ -19524,21 +19565,22 @@
       <c r="CO62" s="24" t="n"/>
       <c r="CP62" s="24" t="n"/>
       <c r="CQ62" s="24" t="n"/>
-      <c r="CR62" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
+      <c r="CR62" s="24" t="n"/>
+      <c r="CS62" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="63" ht="36" customHeight="1">
       <c r="A63" s="24" t="inlineStr">
         <is>
-          <t>5f01a74edfff4cf0</t>
+          <t>d43d12ed43b34018</t>
         </is>
       </c>
       <c r="B63" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C63" s="24" t="inlineStr">
@@ -19568,16 +19610,16 @@
       </c>
       <c r="H63" s="24" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="I63" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>over</t>
         </is>
       </c>
       <c r="J63" s="25" t="n">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="K63" s="24" t="inlineStr">
         <is>
@@ -19585,32 +19627,32 @@
         </is>
       </c>
       <c r="L63" s="26" t="n">
-        <v>-178</v>
+        <v>104</v>
       </c>
       <c r="M63" s="27" t="n">
-        <v>1.561798</v>
+        <v>2.04</v>
       </c>
       <c r="N63" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.490196</v>
       </c>
       <c r="O63" s="28" t="n">
-        <v>0.577995</v>
+        <v>0.516834</v>
       </c>
       <c r="P63" s="28" t="n">
         <v>0.05172</v>
       </c>
       <c r="Q63" s="28" t="n">
-        <v>-0.062293</v>
+        <v>0.026638</v>
       </c>
       <c r="R63" s="26" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="S63" s="29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T63" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-totals-v2</t>
         </is>
       </c>
       <c r="U63" s="24" t="inlineStr">
@@ -19629,7 +19671,7 @@
       <c r="AD63" s="24" t="n"/>
       <c r="AE63" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.31-4.86; raw selected-side p=0.6188, calibrated p=0.5780.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.31-4.86; raw selected-side p=0.5260, calibrated p=0.5168.</t>
         </is>
       </c>
       <c r="AF63" s="31" t="inlineStr">
@@ -19713,7 +19755,7 @@
       </c>
       <c r="BA63" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
         </is>
       </c>
       <c r="BB63" s="24" t="inlineStr">
@@ -19723,12 +19765,12 @@
       </c>
       <c r="BC63" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-totals-v2</t>
         </is>
       </c>
       <c r="BD63" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
         </is>
       </c>
       <c r="BE63" s="24" t="inlineStr">
@@ -19748,7 +19790,7 @@
       </c>
       <c r="BH63" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI63" s="24" t="inlineStr">
@@ -19757,19 +19799,19 @@
         </is>
       </c>
       <c r="BJ63" s="25" t="n">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="BK63" s="26" t="n">
-        <v>-178</v>
+        <v>104</v>
       </c>
       <c r="BL63" s="27" t="n">
-        <v>1.561798</v>
+        <v>2.04</v>
       </c>
       <c r="BM63" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.490196</v>
       </c>
       <c r="BN63" s="28" t="n">
-        <v>0.636816</v>
+        <v>0.487562</v>
       </c>
       <c r="BO63" s="28" t="n"/>
       <c r="BP63" s="25" t="n"/>
@@ -19800,31 +19842,32 @@
       <c r="CO63" s="24" t="n"/>
       <c r="CP63" s="24" t="n"/>
       <c r="CQ63" s="24" t="n"/>
-      <c r="CR63" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
+      <c r="CR63" s="24" t="n"/>
+      <c r="CS63" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="64" ht="36" customHeight="1">
       <c r="A64" s="24" t="inlineStr">
         <is>
-          <t>11bdcee0bebc494a</t>
+          <t>9d6188233c84469f</t>
         </is>
       </c>
       <c r="B64" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C64" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T00:10Z</t>
+          <t>2026-08-05T00:40Z</t>
         </is>
       </c>
       <c r="D64" s="24" t="inlineStr">
         <is>
-          <t>401816395</t>
+          <t>401816396</t>
         </is>
       </c>
       <c r="E64" s="24" t="inlineStr">
@@ -19834,26 +19877,26 @@
       </c>
       <c r="F64" s="24" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="G64" s="24" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="H64" s="24" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="I64" s="24" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J64" s="25" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="K64" s="24" t="inlineStr">
         <is>
@@ -19861,32 +19904,32 @@
         </is>
       </c>
       <c r="L64" s="26" t="n">
-        <v>104</v>
+        <v>-104</v>
       </c>
       <c r="M64" s="27" t="n">
-        <v>2.04</v>
+        <v>1.961538</v>
       </c>
       <c r="N64" s="28" t="n">
-        <v>0.490196</v>
+        <v>0.509804</v>
       </c>
       <c r="O64" s="28" t="n">
-        <v>0.515724</v>
+        <v>0.6912700000000001</v>
       </c>
       <c r="P64" s="28" t="n">
         <v>0.05172</v>
       </c>
       <c r="Q64" s="28" t="n">
-        <v>0.025528</v>
+        <v>0.181466</v>
       </c>
       <c r="R64" s="26" t="n">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="S64" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T64" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-margin-v2</t>
         </is>
       </c>
       <c r="U64" s="24" t="inlineStr">
@@ -19905,7 +19948,7 @@
       <c r="AD64" s="24" t="n"/>
       <c r="AE64" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.31-4.86; raw selected-side p=0.5228, calibrated p=0.5157.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.49-6.29; raw selected-side p=0.7914, calibrated p=0.6913.</t>
         </is>
       </c>
       <c r="AF64" s="31" t="inlineStr">
@@ -19946,32 +19989,32 @@
       </c>
       <c r="AP64" s="24" t="inlineStr">
         <is>
-          <t>mlb-tor</t>
+          <t>mlb-tb</t>
         </is>
       </c>
       <c r="AQ64" s="24" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="AR64" s="24" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="AS64" s="24" t="inlineStr">
         <is>
-          <t>mlb-hou</t>
+          <t>mlb-col</t>
         </is>
       </c>
       <c r="AT64" s="24" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="AU64" s="24" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="AV64" s="24" t="n"/>
@@ -19989,7 +20032,7 @@
       </c>
       <c r="BA64" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
         </is>
       </c>
       <c r="BB64" s="24" t="inlineStr">
@@ -19999,12 +20042,12 @@
       </c>
       <c r="BC64" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-margin-v2</t>
         </is>
       </c>
       <c r="BD64" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
         </is>
       </c>
       <c r="BE64" s="24" t="inlineStr">
@@ -20024,7 +20067,7 @@
       </c>
       <c r="BH64" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI64" s="24" t="inlineStr">
@@ -20033,19 +20076,19 @@
         </is>
       </c>
       <c r="BJ64" s="25" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="BK64" s="26" t="n">
-        <v>104</v>
+        <v>-104</v>
       </c>
       <c r="BL64" s="27" t="n">
-        <v>2.04</v>
+        <v>1.961538</v>
       </c>
       <c r="BM64" s="28" t="n">
-        <v>0.490196</v>
+        <v>0.509804</v>
       </c>
       <c r="BN64" s="28" t="n">
-        <v>0.487562</v>
+        <v>0.507463</v>
       </c>
       <c r="BO64" s="28" t="n"/>
       <c r="BP64" s="25" t="n"/>
@@ -20076,7 +20119,8 @@
       <c r="CO64" s="24" t="n"/>
       <c r="CP64" s="24" t="n"/>
       <c r="CQ64" s="24" t="n"/>
-      <c r="CR64" s="24" t="inlineStr">
+      <c r="CR64" s="24" t="n"/>
+      <c r="CS64" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -20085,12 +20129,12 @@
     <row r="65" ht="36" customHeight="1">
       <c r="A65" s="24" t="inlineStr">
         <is>
-          <t>42347c86496a4115</t>
+          <t>b2a3b70378ef493f</t>
         </is>
       </c>
       <c r="B65" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C65" s="24" t="inlineStr">
@@ -20120,16 +20164,16 @@
       </c>
       <c r="H65" s="24" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="I65" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>under</t>
         </is>
       </c>
       <c r="J65" s="25" t="n">
-        <v>1.5</v>
+        <v>11.5</v>
       </c>
       <c r="K65" s="24" t="inlineStr">
         <is>
@@ -20137,32 +20181,32 @@
         </is>
       </c>
       <c r="L65" s="26" t="n">
-        <v>-120</v>
+        <v>-117</v>
       </c>
       <c r="M65" s="27" t="n">
-        <v>1.833333</v>
+        <v>1.854701</v>
       </c>
       <c r="N65" s="28" t="n">
-        <v>0.545455</v>
+        <v>0.539171</v>
       </c>
       <c r="O65" s="28" t="n">
-        <v>0.687662</v>
+        <v>0.544905</v>
       </c>
       <c r="P65" s="28" t="n">
         <v>0.05172</v>
       </c>
       <c r="Q65" s="28" t="n">
-        <v>0.142207</v>
+        <v>0.005734</v>
       </c>
       <c r="R65" s="26" t="n">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="S65" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T65" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-totals-v2</t>
         </is>
       </c>
       <c r="U65" s="24" t="inlineStr">
@@ -20181,7 +20225,7 @@
       <c r="AD65" s="24" t="n"/>
       <c r="AE65" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.49-6.29; raw selected-side p=0.7860, calibrated p=0.6877.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.49-6.29; raw selected-side p=0.6081, calibrated p=0.5449.</t>
         </is>
       </c>
       <c r="AF65" s="31" t="inlineStr">
@@ -20265,7 +20309,7 @@
       </c>
       <c r="BA65" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
         </is>
       </c>
       <c r="BB65" s="24" t="inlineStr">
@@ -20275,12 +20319,12 @@
       </c>
       <c r="BC65" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-totals-v2</t>
         </is>
       </c>
       <c r="BD65" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
         </is>
       </c>
       <c r="BE65" s="24" t="inlineStr">
@@ -20300,7 +20344,7 @@
       </c>
       <c r="BH65" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI65" s="24" t="inlineStr">
@@ -20309,19 +20353,19 @@
         </is>
       </c>
       <c r="BJ65" s="25" t="n">
-        <v>1.5</v>
+        <v>11.5</v>
       </c>
       <c r="BK65" s="26" t="n">
-        <v>-120</v>
+        <v>-117</v>
       </c>
       <c r="BL65" s="27" t="n">
-        <v>1.833333</v>
+        <v>1.854701</v>
       </c>
       <c r="BM65" s="28" t="n">
-        <v>0.545455</v>
+        <v>0.539171</v>
       </c>
       <c r="BN65" s="28" t="n">
-        <v>0.542289</v>
+        <v>0.537313</v>
       </c>
       <c r="BO65" s="28" t="n"/>
       <c r="BP65" s="25" t="n"/>
@@ -20352,7 +20396,8 @@
       <c r="CO65" s="24" t="n"/>
       <c r="CP65" s="24" t="n"/>
       <c r="CQ65" s="24" t="n"/>
-      <c r="CR65" s="24" t="inlineStr">
+      <c r="CR65" s="24" t="n"/>
+      <c r="CS65" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -20361,22 +20406,22 @@
     <row r="66" ht="36" customHeight="1">
       <c r="A66" s="24" t="inlineStr">
         <is>
-          <t>f3472920e7b045eb</t>
+          <t>87a3403819ca4958</t>
         </is>
       </c>
       <c r="B66" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C66" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T00:40Z</t>
+          <t>2026-08-05T01:40Z</t>
         </is>
       </c>
       <c r="D66" s="24" t="inlineStr">
         <is>
-          <t>401816396</t>
+          <t>401816398</t>
         </is>
       </c>
       <c r="E66" s="24" t="inlineStr">
@@ -20386,26 +20431,26 @@
       </c>
       <c r="F66" s="24" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="G66" s="24" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="H66" s="24" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="I66" s="24" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J66" s="25" t="n">
-        <v>11.5</v>
+        <v>1.5</v>
       </c>
       <c r="K66" s="24" t="inlineStr">
         <is>
@@ -20413,32 +20458,32 @@
         </is>
       </c>
       <c r="L66" s="26" t="n">
-        <v>-120</v>
+        <v>-178</v>
       </c>
       <c r="M66" s="27" t="n">
-        <v>1.833333</v>
+        <v>1.561798</v>
       </c>
       <c r="N66" s="28" t="n">
-        <v>0.545455</v>
+        <v>0.640288</v>
       </c>
       <c r="O66" s="28" t="n">
-        <v>0.544956</v>
+        <v>0.543418</v>
       </c>
       <c r="P66" s="28" t="n">
-        <v>0.05172</v>
+        <v>0.042131</v>
       </c>
       <c r="Q66" s="28" t="n">
-        <v>-0.000499</v>
+        <v>-0.09687</v>
       </c>
       <c r="R66" s="26" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="S66" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T66" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-margin-v2</t>
         </is>
       </c>
       <c r="U66" s="24" t="inlineStr">
@@ -20457,7 +20502,7 @@
       <c r="AD66" s="24" t="n"/>
       <c r="AE66" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.49-6.29; raw selected-side p=0.6083, calibrated p=0.5450.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.09-5.16; raw selected-side p=0.5661, calibrated p=0.5434.</t>
         </is>
       </c>
       <c r="AF66" s="31" t="inlineStr">
@@ -20498,32 +20543,32 @@
       </c>
       <c r="AP66" s="24" t="inlineStr">
         <is>
-          <t>mlb-tb</t>
+          <t>mlb-sd</t>
         </is>
       </c>
       <c r="AQ66" s="24" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="AR66" s="24" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="AS66" s="24" t="inlineStr">
         <is>
-          <t>mlb-col</t>
+          <t>mlb-ari</t>
         </is>
       </c>
       <c r="AT66" s="24" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="AU66" s="24" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="AV66" s="24" t="n"/>
@@ -20541,7 +20586,7 @@
       </c>
       <c r="BA66" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
         </is>
       </c>
       <c r="BB66" s="24" t="inlineStr">
@@ -20551,12 +20596,12 @@
       </c>
       <c r="BC66" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-margin-v2</t>
         </is>
       </c>
       <c r="BD66" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
         </is>
       </c>
       <c r="BE66" s="24" t="inlineStr">
@@ -20576,7 +20621,7 @@
       </c>
       <c r="BH66" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI66" s="24" t="inlineStr">
@@ -20585,19 +20630,19 @@
         </is>
       </c>
       <c r="BJ66" s="25" t="n">
-        <v>11.5</v>
+        <v>1.5</v>
       </c>
       <c r="BK66" s="26" t="n">
-        <v>-120</v>
+        <v>-178</v>
       </c>
       <c r="BL66" s="27" t="n">
-        <v>1.833333</v>
+        <v>1.561798</v>
       </c>
       <c r="BM66" s="28" t="n">
-        <v>0.545455</v>
+        <v>0.640288</v>
       </c>
       <c r="BN66" s="28" t="n">
-        <v>0.542289</v>
+        <v>0.636816</v>
       </c>
       <c r="BO66" s="28" t="n"/>
       <c r="BP66" s="25" t="n"/>
@@ -20628,7 +20673,8 @@
       <c r="CO66" s="24" t="n"/>
       <c r="CP66" s="24" t="n"/>
       <c r="CQ66" s="24" t="n"/>
-      <c r="CR66" s="24" t="inlineStr">
+      <c r="CR66" s="24" t="n"/>
+      <c r="CS66" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -20637,12 +20683,12 @@
     <row r="67" ht="36" customHeight="1">
       <c r="A67" s="24" t="inlineStr">
         <is>
-          <t>183c547310514240</t>
+          <t>df3742dc80134149</t>
         </is>
       </c>
       <c r="B67" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="C67" s="24" t="inlineStr">
@@ -20672,16 +20718,16 @@
       </c>
       <c r="H67" s="24" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="I67" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>over</t>
         </is>
       </c>
       <c r="J67" s="25" t="n">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="K67" s="24" t="inlineStr">
         <is>
@@ -20689,32 +20735,32 @@
         </is>
       </c>
       <c r="L67" s="26" t="n">
-        <v>-178</v>
+        <v>-125</v>
       </c>
       <c r="M67" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.8</v>
       </c>
       <c r="N67" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.555556</v>
       </c>
       <c r="O67" s="28" t="n">
-        <v>0.5404330000000001</v>
+        <v>0.520781</v>
       </c>
       <c r="P67" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q67" s="28" t="n">
-        <v>-0.099855</v>
+        <v>-0.034775</v>
       </c>
       <c r="R67" s="26" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S67" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T67" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-totals-v2</t>
         </is>
       </c>
       <c r="U67" s="24" t="inlineStr">
@@ -20733,7 +20779,7 @@
       <c r="AD67" s="24" t="n"/>
       <c r="AE67" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.09-5.16; raw selected-side p=0.5615, calibrated p=0.5404.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.09-5.16; raw selected-side p=0.5375, calibrated p=0.5208.</t>
         </is>
       </c>
       <c r="AF67" s="31" t="inlineStr">
@@ -20817,7 +20863,7 @@
       </c>
       <c r="BA67" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
         </is>
       </c>
       <c r="BB67" s="24" t="inlineStr">
@@ -20827,12 +20873,12 @@
       </c>
       <c r="BC67" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-totals-v2</t>
         </is>
       </c>
       <c r="BD67" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
         </is>
       </c>
       <c r="BE67" s="24" t="inlineStr">
@@ -20852,7 +20898,7 @@
       </c>
       <c r="BH67" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
+          <t>2026-08-04T14:25:15.642219Z</t>
         </is>
       </c>
       <c r="BI67" s="24" t="inlineStr">
@@ -20861,19 +20907,19 @@
         </is>
       </c>
       <c r="BJ67" s="25" t="n">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="BK67" s="26" t="n">
-        <v>-178</v>
+        <v>-125</v>
       </c>
       <c r="BL67" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.8</v>
       </c>
       <c r="BM67" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.555556</v>
       </c>
       <c r="BN67" s="28" t="n">
-        <v>0.636816</v>
+        <v>0.552239</v>
       </c>
       <c r="BO67" s="28" t="n"/>
       <c r="BP67" s="25" t="n"/>
@@ -20904,285 +20950,10 @@
       <c r="CO67" s="24" t="n"/>
       <c r="CP67" s="24" t="n"/>
       <c r="CQ67" s="24" t="n"/>
-      <c r="CR67" s="24" t="inlineStr">
+      <c r="CR67" s="24" t="n"/>
+      <c r="CS67" s="24" t="inlineStr">
         <is>
           <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="36" customHeight="1">
-      <c r="A68" s="24" t="inlineStr">
-        <is>
-          <t>3323c6ba254a4283</t>
-        </is>
-      </c>
-      <c r="B68" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
-        </is>
-      </c>
-      <c r="C68" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T01:40Z</t>
-        </is>
-      </c>
-      <c r="D68" s="24" t="inlineStr">
-        <is>
-          <t>401816398</t>
-        </is>
-      </c>
-      <c r="E68" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F68" s="24" t="inlineStr">
-        <is>
-          <t>San Diego Padres</t>
-        </is>
-      </c>
-      <c r="G68" s="24" t="inlineStr">
-        <is>
-          <t>Arizona Diamondbacks</t>
-        </is>
-      </c>
-      <c r="H68" s="24" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="I68" s="24" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="J68" s="25" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="K68" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L68" s="26" t="n">
-        <v>-104</v>
-      </c>
-      <c r="M68" s="27" t="n">
-        <v>1.961538</v>
-      </c>
-      <c r="N68" s="28" t="n">
-        <v>0.509804</v>
-      </c>
-      <c r="O68" s="28" t="n">
-        <v>0.520815</v>
-      </c>
-      <c r="P68" s="28" t="n">
-        <v>0.042131</v>
-      </c>
-      <c r="Q68" s="28" t="n">
-        <v>0.011011</v>
-      </c>
-      <c r="R68" s="26" t="n">
-        <v>31</v>
-      </c>
-      <c r="S68" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T68" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-totals-v2</t>
-        </is>
-      </c>
-      <c r="U68" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V68" s="24" t="n"/>
-      <c r="W68" s="26" t="n"/>
-      <c r="X68" s="26" t="n"/>
-      <c r="Y68" s="25" t="n"/>
-      <c r="Z68" s="26" t="n"/>
-      <c r="AA68" s="28" t="n"/>
-      <c r="AB68" s="28" t="n"/>
-      <c r="AC68" s="30" t="n"/>
-      <c r="AD68" s="24" t="n"/>
-      <c r="AE68" s="31" t="inlineStr">
-        <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.09-5.16; raw selected-side p=0.5376, calibrated p=0.5208.</t>
-        </is>
-      </c>
-      <c r="AF68" s="31" t="inlineStr">
-        <is>
-          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
-        </is>
-      </c>
-      <c r="AG68" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH68" s="24" t="n"/>
-      <c r="AI68" s="31" t="n"/>
-      <c r="AJ68" s="31" t="n"/>
-      <c r="AK68" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL68" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM68" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN68" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO68" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP68" s="24" t="inlineStr">
-        <is>
-          <t>mlb-sd</t>
-        </is>
-      </c>
-      <c r="AQ68" s="24" t="inlineStr">
-        <is>
-          <t>San Diego Padres</t>
-        </is>
-      </c>
-      <c r="AR68" s="24" t="inlineStr">
-        <is>
-          <t>San Diego Padres</t>
-        </is>
-      </c>
-      <c r="AS68" s="24" t="inlineStr">
-        <is>
-          <t>mlb-ari</t>
-        </is>
-      </c>
-      <c r="AT68" s="24" t="inlineStr">
-        <is>
-          <t>Arizona Diamondbacks</t>
-        </is>
-      </c>
-      <c r="AU68" s="24" t="inlineStr">
-        <is>
-          <t>Arizona Diamondbacks</t>
-        </is>
-      </c>
-      <c r="AV68" s="24" t="n"/>
-      <c r="AW68" s="24" t="n"/>
-      <c r="AX68" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY68" s="24" t="n"/>
-      <c r="AZ68" s="24" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="BA68" s="24" t="inlineStr">
-        <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
-        </is>
-      </c>
-      <c r="BB68" s="24" t="inlineStr">
-        <is>
-          <t>flat_probability_shrinkage_toward_half</t>
-        </is>
-      </c>
-      <c r="BC68" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-totals-v2</t>
-        </is>
-      </c>
-      <c r="BD68" s="24" t="inlineStr">
-        <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
-        </is>
-      </c>
-      <c r="BE68" s="24" t="inlineStr">
-        <is>
-          <t>v3</t>
-        </is>
-      </c>
-      <c r="BF68" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG68" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-paired-v1</t>
-        </is>
-      </c>
-      <c r="BH68" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-04T08:54:58.120999Z</t>
-        </is>
-      </c>
-      <c r="BI68" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ68" s="25" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="BK68" s="26" t="n">
-        <v>-104</v>
-      </c>
-      <c r="BL68" s="27" t="n">
-        <v>1.961538</v>
-      </c>
-      <c r="BM68" s="28" t="n">
-        <v>0.509804</v>
-      </c>
-      <c r="BN68" s="28" t="n">
-        <v>0.507463</v>
-      </c>
-      <c r="BO68" s="28" t="n"/>
-      <c r="BP68" s="25" t="n"/>
-      <c r="BQ68" s="27" t="n"/>
-      <c r="BR68" s="28" t="n"/>
-      <c r="BS68" s="28" t="n"/>
-      <c r="BT68" s="28" t="n"/>
-      <c r="BU68" s="25" t="n"/>
-      <c r="BV68" s="29" t="n"/>
-      <c r="BW68" s="24" t="n"/>
-      <c r="BX68" s="30" t="n"/>
-      <c r="BY68" s="27" t="n"/>
-      <c r="BZ68" s="24" t="n"/>
-      <c r="CA68" s="31" t="n"/>
-      <c r="CB68" s="24" t="n"/>
-      <c r="CC68" s="24" t="n"/>
-      <c r="CD68" s="24" t="n"/>
-      <c r="CE68" s="24" t="n"/>
-      <c r="CF68" s="24" t="n"/>
-      <c r="CG68" s="24" t="n"/>
-      <c r="CH68" s="24" t="n"/>
-      <c r="CI68" s="24" t="n"/>
-      <c r="CJ68" s="24" t="n"/>
-      <c r="CK68" s="24" t="n"/>
-      <c r="CL68" s="24" t="n"/>
-      <c r="CM68" s="24" t="n"/>
-      <c r="CN68" s="24" t="n"/>
-      <c r="CO68" s="24" t="n"/>
-      <c r="CP68" s="24" t="n"/>
-      <c r="CQ68" s="24" t="n"/>
-      <c r="CR68" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
         </is>
       </c>
     </row>

--- a/data/main/mlb.xlsx
+++ b/data/main/mlb.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS67" headerRowCount="1">
-  <autoFilter ref="A1:CS67"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS79" headerRowCount="1">
+  <autoFilter ref="A1:CS79"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$67)</f>
+        <f>COUNTA('Picks'!$A$2:$A$79)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$67,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$79,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$67,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$79,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"win")+COUNTIFS('Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$79,"settled",'Picks'!$V$2:$V$79,"win")+COUNTIFS('Picks'!$U$2:$U$79,"settled",'Picks'!$V$2:$V$79,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$67,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$79,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$67,"&gt;0",'Picks'!$V$2:$V$67,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$67,"&gt;0",'Picks'!$V$2:$V$67,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$79,"&gt;0",'Picks'!$V$2:$V$79,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$79,"&gt;0",'Picks'!$V$2:$V$79,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$67,"&gt;0",'Picks'!$V$2:$V$67,"win")/(COUNTIFS('Picks'!$BX$2:$BX$67,"&gt;0",'Picks'!$V$2:$V$67,"win")+COUNTIFS('Picks'!$BX$2:$BX$67,"&gt;0",'Picks'!$V$2:$V$67,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$79,"&gt;0",'Picks'!$V$2:$V$79,"win")/(COUNTIFS('Picks'!$BX$2:$BX$79,"&gt;0",'Picks'!$V$2:$V$79,"win")+COUNTIFS('Picks'!$BX$2:$BX$79,"&gt;0",'Picks'!$V$2:$V$79,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$67)/SUM('Picks'!$BX$2:$BX$67),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$79)/SUM('Picks'!$BX$2:$BX$79),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$67)</f>
+        <f>SUM('Picks'!$BY$2:$BY$79)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$67,"&lt;&gt;",'Picks'!$AB$2:$AB$67),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$79,"&lt;&gt;",'Picks'!$AB$2:$AB$79),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$67,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$67,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$79,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$79,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$67,'Picks'!$AM$2:$AM$67,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$79,'Picks'!$AM$2:$AM$79,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$67,$A14,'Picks'!$U$2:$U$67,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$79,$A14,'Picks'!$U$2:$U$79,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$67,$A14,'Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$79,$A14,'Picks'!$U$2:$U$79,"settled",'Picks'!$V$2:$V$79,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$67,$A14,'Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$79,$A14,'Picks'!$U$2:$U$79,"settled",'Picks'!$V$2:$V$79,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$67,'Picks'!$H$2:$H$67,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$79,'Picks'!$H$2:$H$79,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$67,'Picks'!$H$2:$H$67,$A14,'Picks'!$U$2:$U$67,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$79,'Picks'!$H$2:$H$79,$A14,'Picks'!$U$2:$U$79,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$67,$A15,'Picks'!$U$2:$U$67,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$79,$A15,'Picks'!$U$2:$U$79,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$67,$A15,'Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$79,$A15,'Picks'!$U$2:$U$79,"settled",'Picks'!$V$2:$V$79,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$67,$A15,'Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$79,$A15,'Picks'!$U$2:$U$79,"settled",'Picks'!$V$2:$V$79,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$67,'Picks'!$H$2:$H$67,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$79,'Picks'!$H$2:$H$79,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$67,'Picks'!$H$2:$H$67,$A15,'Picks'!$U$2:$U$67,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$79,'Picks'!$H$2:$H$79,$A15,'Picks'!$U$2:$U$79,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$67,$A16,'Picks'!$U$2:$U$67,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$79,$A16,'Picks'!$U$2:$U$79,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$67,$A16,'Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$79,$A16,'Picks'!$U$2:$U$79,"settled",'Picks'!$V$2:$V$79,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$67,$A16,'Picks'!$U$2:$U$67,"settled",'Picks'!$V$2:$V$67,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$79,$A16,'Picks'!$U$2:$U$79,"settled",'Picks'!$V$2:$V$79,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$67,'Picks'!$H$2:$H$67,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$79,'Picks'!$H$2:$H$79,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$67,'Picks'!$H$2:$H$67,$A16,'Picks'!$U$2:$U$67,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$79,'Picks'!$H$2:$H$79,$A16,'Picks'!$U$2:$U$79,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS67"/>
+  <dimension ref="A1:CS79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -13758,22 +13758,22 @@
     <row r="42" ht="36" customHeight="1">
       <c r="A42" s="24" t="inlineStr">
         <is>
-          <t>97896ce4943849be</t>
+          <t>bcb6241cb2b04b99</t>
         </is>
       </c>
       <c r="B42" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T01:08:02.646600Z</t>
         </is>
       </c>
       <c r="C42" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T22:40Z</t>
+          <t>2026-08-05T01:40Z</t>
         </is>
       </c>
       <c r="D42" s="24" t="inlineStr">
         <is>
-          <t>401816385</t>
+          <t>401816397</t>
         </is>
       </c>
       <c r="E42" s="24" t="inlineStr">
@@ -13783,12 +13783,12 @@
       </c>
       <c r="F42" s="24" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="G42" s="24" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="H42" s="24" t="inlineStr">
@@ -13810,51 +13810,73 @@
         </is>
       </c>
       <c r="L42" s="26" t="n">
-        <v>-163</v>
+        <v>-186</v>
       </c>
       <c r="M42" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.537634</v>
       </c>
       <c r="N42" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.65035</v>
       </c>
       <c r="O42" s="28" t="n">
-        <v>0.56005</v>
+        <v>0.657369</v>
       </c>
       <c r="P42" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q42" s="28" t="n">
-        <v>-0.059722</v>
+        <v>0.007019</v>
       </c>
       <c r="R42" s="26" t="n">
+        <v>30</v>
+      </c>
+      <c r="S42" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T42" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v3</t>
+        </is>
+      </c>
+      <c r="U42" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V42" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W42" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="X42" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="S42" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T42" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-margin-v2</t>
-        </is>
-      </c>
-      <c r="U42" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V42" s="24" t="n"/>
-      <c r="W42" s="26" t="n"/>
-      <c r="X42" s="26" t="n"/>
-      <c r="Y42" s="25" t="n"/>
-      <c r="Z42" s="26" t="n"/>
-      <c r="AA42" s="28" t="n"/>
-      <c r="AB42" s="28" t="n"/>
-      <c r="AC42" s="30" t="n"/>
-      <c r="AD42" s="24" t="n"/>
+      <c r="Y42" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z42" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="AA42" s="28" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AB42" s="28" t="n">
+        <v>-0.00035</v>
+      </c>
+      <c r="AC42" s="30" t="n">
+        <v>0.9409</v>
+      </c>
+      <c r="AD42" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:21:26.372391Z</t>
+        </is>
+      </c>
       <c r="AE42" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 3.87-4.68; raw selected-side p=0.5915, calibrated p=0.5601.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.19-3.76; raw selected-side p=0.7309, calibrated p=0.6574.</t>
         </is>
       </c>
       <c r="AF42" s="31" t="inlineStr">
@@ -13895,32 +13917,32 @@
       </c>
       <c r="AP42" s="24" t="inlineStr">
         <is>
-          <t>mlb-ath</t>
+          <t>mlb-det</t>
         </is>
       </c>
       <c r="AQ42" s="24" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="AR42" s="24" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="AS42" s="24" t="inlineStr">
         <is>
-          <t>mlb-cin</t>
+          <t>mlb-sea</t>
         </is>
       </c>
       <c r="AT42" s="24" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="AU42" s="24" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="AV42" s="24" t="n"/>
@@ -13938,7 +13960,7 @@
       </c>
       <c r="BA42" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BB42" s="24" t="inlineStr">
@@ -13948,12 +13970,12 @@
       </c>
       <c r="BC42" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="BD42" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BE42" s="24" t="inlineStr">
@@ -13973,7 +13995,7 @@
       </c>
       <c r="BH42" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T01:08:02.646600Z</t>
         </is>
       </c>
       <c r="BI42" s="24" t="inlineStr">
@@ -13985,21 +14007,25 @@
         <v>1.5</v>
       </c>
       <c r="BK42" s="26" t="n">
-        <v>-163</v>
+        <v>-186</v>
       </c>
       <c r="BL42" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.537634</v>
       </c>
       <c r="BM42" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.65035</v>
       </c>
       <c r="BN42" s="28" t="n">
-        <v>0.616915</v>
+        <v>0.646766</v>
       </c>
       <c r="BO42" s="28" t="n"/>
       <c r="BP42" s="25" t="n"/>
-      <c r="BQ42" s="27" t="n"/>
-      <c r="BR42" s="28" t="n"/>
+      <c r="BQ42" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="BR42" s="28" t="n">
+        <v>0.65</v>
+      </c>
       <c r="BS42" s="28" t="n"/>
       <c r="BT42" s="28" t="n"/>
       <c r="BU42" s="25" t="n"/>
@@ -14028,29 +14054,29 @@
       <c r="CR42" s="24" t="n"/>
       <c r="CS42" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="43" ht="36" customHeight="1">
       <c r="A43" s="24" t="inlineStr">
         <is>
-          <t>ddeb2a337c46426e</t>
+          <t>ce99df3a66214167</t>
         </is>
       </c>
       <c r="B43" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T01:08:02.646600Z</t>
         </is>
       </c>
       <c r="C43" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T22:40Z</t>
+          <t>2026-08-05T01:40Z</t>
         </is>
       </c>
       <c r="D43" s="24" t="inlineStr">
         <is>
-          <t>401816385</t>
+          <t>401816397</t>
         </is>
       </c>
       <c r="E43" s="24" t="inlineStr">
@@ -14060,12 +14086,12 @@
       </c>
       <c r="F43" s="24" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="G43" s="24" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="H43" s="24" t="inlineStr">
@@ -14079,7 +14105,7 @@
         </is>
       </c>
       <c r="J43" s="25" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="K43" s="24" t="inlineStr">
         <is>
@@ -14087,51 +14113,73 @@
         </is>
       </c>
       <c r="L43" s="26" t="n">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="M43" s="27" t="n">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="N43" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.480769</v>
       </c>
       <c r="O43" s="28" t="n">
-        <v>0.514254</v>
+        <v>0.506992</v>
       </c>
       <c r="P43" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q43" s="28" t="n">
-        <v>0.063804</v>
+        <v>0.026223</v>
       </c>
       <c r="R43" s="26" t="n">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="S43" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T43" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="U43" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V43" s="24" t="n"/>
-      <c r="W43" s="26" t="n"/>
-      <c r="X43" s="26" t="n"/>
-      <c r="Y43" s="25" t="n"/>
-      <c r="Z43" s="26" t="n"/>
-      <c r="AA43" s="28" t="n"/>
-      <c r="AB43" s="28" t="n"/>
-      <c r="AC43" s="30" t="n"/>
-      <c r="AD43" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V43" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W43" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="X43" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="25" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Z43" s="26" t="n">
+        <v>108</v>
+      </c>
+      <c r="AA43" s="28" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AB43" s="28" t="n">
+        <v>-0.000769</v>
+      </c>
+      <c r="AC43" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD43" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:21:26.662275Z</t>
+        </is>
+      </c>
       <c r="AE43" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 3.87-4.68; raw selected-side p=0.5184, calibrated p=0.5143.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.19-3.76; raw selected-side p=0.5048, calibrated p=0.5070.</t>
         </is>
       </c>
       <c r="AF43" s="31" t="inlineStr">
@@ -14141,7 +14189,7 @@
       </c>
       <c r="AG43" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH43" s="24" t="n"/>
@@ -14172,32 +14220,32 @@
       </c>
       <c r="AP43" s="24" t="inlineStr">
         <is>
-          <t>mlb-ath</t>
+          <t>mlb-det</t>
         </is>
       </c>
       <c r="AQ43" s="24" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="AR43" s="24" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="AS43" s="24" t="inlineStr">
         <is>
-          <t>mlb-cin</t>
+          <t>mlb-sea</t>
         </is>
       </c>
       <c r="AT43" s="24" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="AU43" s="24" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="AV43" s="24" t="n"/>
@@ -14215,7 +14263,7 @@
       </c>
       <c r="BA43" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BB43" s="24" t="inlineStr">
@@ -14225,12 +14273,12 @@
       </c>
       <c r="BC43" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="BD43" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BE43" s="24" t="inlineStr">
@@ -14250,7 +14298,7 @@
       </c>
       <c r="BH43" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T01:08:02.646600Z</t>
         </is>
       </c>
       <c r="BI43" s="24" t="inlineStr">
@@ -14259,24 +14307,28 @@
         </is>
       </c>
       <c r="BJ43" s="25" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="BK43" s="26" t="n">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="BL43" s="27" t="n">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="BM43" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.480769</v>
       </c>
       <c r="BN43" s="28" t="n">
-        <v>0.447761</v>
+        <v>0.477612</v>
       </c>
       <c r="BO43" s="28" t="n"/>
       <c r="BP43" s="25" t="n"/>
-      <c r="BQ43" s="27" t="n"/>
-      <c r="BR43" s="28" t="n"/>
+      <c r="BQ43" s="27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BR43" s="28" t="n">
+        <v>0.48</v>
+      </c>
       <c r="BS43" s="28" t="n"/>
       <c r="BT43" s="28" t="n"/>
       <c r="BU43" s="25" t="n"/>
@@ -14312,22 +14364,22 @@
     <row r="44" ht="36" customHeight="1">
       <c r="A44" s="24" t="inlineStr">
         <is>
-          <t>6811d5d9494c4c1f</t>
+          <t>67f54f960d2240f2</t>
         </is>
       </c>
       <c r="B44" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T01:08:02.646600Z</t>
         </is>
       </c>
       <c r="C44" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T22:40Z</t>
+          <t>2026-08-05T01:40Z</t>
         </is>
       </c>
       <c r="D44" s="24" t="inlineStr">
         <is>
-          <t>401816388</t>
+          <t>401816398</t>
         </is>
       </c>
       <c r="E44" s="24" t="inlineStr">
@@ -14337,12 +14389,12 @@
       </c>
       <c r="F44" s="24" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="G44" s="24" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="H44" s="24" t="inlineStr">
@@ -14352,7 +14404,7 @@
       </c>
       <c r="I44" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J44" s="25" t="n">
@@ -14364,51 +14416,73 @@
         </is>
       </c>
       <c r="L44" s="26" t="n">
-        <v>-163</v>
+        <v>-182</v>
       </c>
       <c r="M44" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.549451</v>
       </c>
       <c r="N44" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.64539</v>
       </c>
       <c r="O44" s="28" t="n">
-        <v>0.600007</v>
+        <v>0.655325</v>
       </c>
       <c r="P44" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q44" s="28" t="n">
-        <v>-0.019765</v>
+        <v>0.009934999999999999</v>
       </c>
       <c r="R44" s="26" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="S44" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T44" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v3</t>
+        </is>
+      </c>
+      <c r="U44" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V44" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W44" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="X44" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y44" s="25" t="n">
         <v>1.5</v>
       </c>
-      <c r="T44" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-margin-v2</t>
-        </is>
-      </c>
-      <c r="U44" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V44" s="24" t="n"/>
-      <c r="W44" s="26" t="n"/>
-      <c r="X44" s="26" t="n"/>
-      <c r="Y44" s="25" t="n"/>
-      <c r="Z44" s="26" t="n"/>
-      <c r="AA44" s="28" t="n"/>
-      <c r="AB44" s="28" t="n"/>
-      <c r="AC44" s="30" t="n"/>
-      <c r="AD44" s="24" t="n"/>
+      <c r="Z44" s="26" t="n">
+        <v>-182</v>
+      </c>
+      <c r="AA44" s="28" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="AB44" s="28" t="n">
+        <v>-0.00039</v>
+      </c>
+      <c r="AC44" s="30" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AD44" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:33:02.754328Z</t>
+        </is>
+      </c>
       <c r="AE44" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.10-4.32; raw selected-side p=0.6523, calibrated p=0.6000.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.22-4.93; raw selected-side p=0.7279, calibrated p=0.6553.</t>
         </is>
       </c>
       <c r="AF44" s="31" t="inlineStr">
@@ -14418,7 +14492,7 @@
       </c>
       <c r="AG44" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH44" s="24" t="n"/>
@@ -14449,32 +14523,32 @@
       </c>
       <c r="AP44" s="24" t="inlineStr">
         <is>
-          <t>mlb-nym</t>
+          <t>mlb-sd</t>
         </is>
       </c>
       <c r="AQ44" s="24" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="AR44" s="24" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="AS44" s="24" t="inlineStr">
         <is>
-          <t>mlb-cle</t>
+          <t>mlb-ari</t>
         </is>
       </c>
       <c r="AT44" s="24" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="AU44" s="24" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="AV44" s="24" t="n"/>
@@ -14492,7 +14566,7 @@
       </c>
       <c r="BA44" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BB44" s="24" t="inlineStr">
@@ -14502,12 +14576,12 @@
       </c>
       <c r="BC44" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="BD44" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BE44" s="24" t="inlineStr">
@@ -14527,7 +14601,7 @@
       </c>
       <c r="BH44" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T01:08:02.646600Z</t>
         </is>
       </c>
       <c r="BI44" s="24" t="inlineStr">
@@ -14539,21 +14613,25 @@
         <v>1.5</v>
       </c>
       <c r="BK44" s="26" t="n">
-        <v>-163</v>
+        <v>-182</v>
       </c>
       <c r="BL44" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.549451</v>
       </c>
       <c r="BM44" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.64539</v>
       </c>
       <c r="BN44" s="28" t="n">
-        <v>0.616915</v>
+        <v>0.641791</v>
       </c>
       <c r="BO44" s="28" t="n"/>
       <c r="BP44" s="25" t="n"/>
-      <c r="BQ44" s="27" t="n"/>
-      <c r="BR44" s="28" t="n"/>
+      <c r="BQ44" s="27" t="n">
+        <v>1.549451</v>
+      </c>
+      <c r="BR44" s="28" t="n">
+        <v>0.645</v>
+      </c>
       <c r="BS44" s="28" t="n"/>
       <c r="BT44" s="28" t="n"/>
       <c r="BU44" s="25" t="n"/>
@@ -14582,29 +14660,29 @@
       <c r="CR44" s="24" t="n"/>
       <c r="CS44" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="45" ht="36" customHeight="1">
       <c r="A45" s="24" t="inlineStr">
         <is>
-          <t>c7b77c0e4f0b4e4a</t>
+          <t>44764b238eb747c7</t>
         </is>
       </c>
       <c r="B45" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T01:08:02.646600Z</t>
         </is>
       </c>
       <c r="C45" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T22:40Z</t>
+          <t>2026-08-05T01:40Z</t>
         </is>
       </c>
       <c r="D45" s="24" t="inlineStr">
         <is>
-          <t>401816388</t>
+          <t>401816398</t>
         </is>
       </c>
       <c r="E45" s="24" t="inlineStr">
@@ -14614,12 +14692,12 @@
       </c>
       <c r="F45" s="24" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="G45" s="24" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="H45" s="24" t="inlineStr">
@@ -14633,7 +14711,7 @@
         </is>
       </c>
       <c r="J45" s="25" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="K45" s="24" t="inlineStr">
         <is>
@@ -14641,51 +14719,73 @@
         </is>
       </c>
       <c r="L45" s="26" t="n">
-        <v>-106</v>
+        <v>-117</v>
       </c>
       <c r="M45" s="27" t="n">
-        <v>1.943396</v>
+        <v>1.854701</v>
       </c>
       <c r="N45" s="28" t="n">
-        <v>0.514563</v>
+        <v>0.539171</v>
       </c>
       <c r="O45" s="28" t="n">
-        <v>0.521567</v>
+        <v>0.512594</v>
       </c>
       <c r="P45" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q45" s="28" t="n">
-        <v>0.007004</v>
+        <v>-0.026577</v>
       </c>
       <c r="R45" s="26" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="S45" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T45" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="U45" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V45" s="24" t="n"/>
-      <c r="W45" s="26" t="n"/>
-      <c r="X45" s="26" t="n"/>
-      <c r="Y45" s="25" t="n"/>
-      <c r="Z45" s="26" t="n"/>
-      <c r="AA45" s="28" t="n"/>
-      <c r="AB45" s="28" t="n"/>
-      <c r="AC45" s="30" t="n"/>
-      <c r="AD45" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V45" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W45" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="X45" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y45" s="25" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z45" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="AA45" s="28" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AB45" s="28" t="n">
+        <v>0.000829</v>
+      </c>
+      <c r="AC45" s="30" t="n">
+        <v>0.8547</v>
+      </c>
+      <c r="AD45" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:33:03.225054Z</t>
+        </is>
+      </c>
       <c r="AE45" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.10-4.32; raw selected-side p=0.5399, calibrated p=0.5216.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.22-4.93; raw selected-side p=0.5273, calibrated p=0.5126.</t>
         </is>
       </c>
       <c r="AF45" s="31" t="inlineStr">
@@ -14726,32 +14826,32 @@
       </c>
       <c r="AP45" s="24" t="inlineStr">
         <is>
-          <t>mlb-nym</t>
+          <t>mlb-sd</t>
         </is>
       </c>
       <c r="AQ45" s="24" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="AR45" s="24" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="AS45" s="24" t="inlineStr">
         <is>
-          <t>mlb-cle</t>
+          <t>mlb-ari</t>
         </is>
       </c>
       <c r="AT45" s="24" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="AU45" s="24" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="AV45" s="24" t="n"/>
@@ -14769,7 +14869,7 @@
       </c>
       <c r="BA45" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BB45" s="24" t="inlineStr">
@@ -14779,12 +14879,12 @@
       </c>
       <c r="BC45" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="BD45" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BE45" s="24" t="inlineStr">
@@ -14804,7 +14904,7 @@
       </c>
       <c r="BH45" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T01:08:02.646600Z</t>
         </is>
       </c>
       <c r="BI45" s="24" t="inlineStr">
@@ -14813,24 +14913,28 @@
         </is>
       </c>
       <c r="BJ45" s="25" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="BK45" s="26" t="n">
-        <v>-106</v>
+        <v>-117</v>
       </c>
       <c r="BL45" s="27" t="n">
-        <v>1.943396</v>
+        <v>1.854701</v>
       </c>
       <c r="BM45" s="28" t="n">
-        <v>0.514563</v>
+        <v>0.539171</v>
       </c>
       <c r="BN45" s="28" t="n">
-        <v>0.5124379999999999</v>
+        <v>0.537313</v>
       </c>
       <c r="BO45" s="28" t="n"/>
       <c r="BP45" s="25" t="n"/>
-      <c r="BQ45" s="27" t="n"/>
-      <c r="BR45" s="28" t="n"/>
+      <c r="BQ45" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BR45" s="28" t="n">
+        <v>0.54</v>
+      </c>
       <c r="BS45" s="28" t="n"/>
       <c r="BT45" s="28" t="n"/>
       <c r="BU45" s="25" t="n"/>
@@ -14859,29 +14963,29 @@
       <c r="CR45" s="24" t="n"/>
       <c r="CS45" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="46" ht="36" customHeight="1">
       <c r="A46" s="24" t="inlineStr">
         <is>
-          <t>d21c466f2c6e41c8</t>
+          <t>4e14a1299a594d08</t>
         </is>
       </c>
       <c r="B46" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T04:35:50.664769Z</t>
         </is>
       </c>
       <c r="C46" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T22:40Z</t>
+          <t>2026-08-05T15:10:00-0400</t>
         </is>
       </c>
       <c r="D46" s="24" t="inlineStr">
         <is>
-          <t>401816390</t>
+          <t>401816411</t>
         </is>
       </c>
       <c r="E46" s="24" t="inlineStr">
@@ -14891,17 +14995,17 @@
       </c>
       <c r="F46" s="24" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="G46" s="24" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="H46" s="24" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>moneyline</t>
         </is>
       </c>
       <c r="I46" s="24" t="inlineStr">
@@ -14909,41 +15013,37 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J46" s="25" t="n">
-        <v>1.5</v>
-      </c>
+      <c r="J46" s="25" t="n"/>
       <c r="K46" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L46" s="26" t="n">
-        <v>117</v>
+        <v>-147</v>
       </c>
       <c r="M46" s="27" t="n">
-        <v>2.17</v>
+        <v>1.680272</v>
       </c>
       <c r="N46" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.5951419999999999</v>
       </c>
       <c r="O46" s="28" t="n">
-        <v>0.540597</v>
-      </c>
-      <c r="P46" s="28" t="n">
-        <v>0.042131</v>
-      </c>
+        <v>0.651419</v>
+      </c>
+      <c r="P46" s="28" t="n"/>
       <c r="Q46" s="28" t="n">
-        <v>0.07976800000000001</v>
+        <v>0.056277</v>
       </c>
       <c r="R46" s="26" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="S46" s="29" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="T46" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="U46" s="24" t="inlineStr">
@@ -14962,12 +15062,12 @@
       <c r="AD46" s="24" t="n"/>
       <c r="AE46" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 3.92-5.03; raw selected-side p=0.5618, calibrated p=0.5406.</t>
+          <t>Learned LR call at threshold 0.5873; executable ask 0.5950 (aec-mlb-tb-col-2026-08-05); model edge vs ask +0.0564.</t>
         </is>
       </c>
       <c r="AF46" s="31" t="inlineStr">
         <is>
-          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+          <t>Learned model; shadow-qualified via operator override.</t>
         </is>
       </c>
       <c r="AG46" s="24" t="inlineStr">
@@ -15003,32 +15103,32 @@
       </c>
       <c r="AP46" s="24" t="inlineStr">
         <is>
-          <t>mlb-wsh</t>
+          <t>mlb-tb</t>
         </is>
       </c>
       <c r="AQ46" s="24" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="AR46" s="24" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="AS46" s="24" t="inlineStr">
         <is>
-          <t>mlb-phi</t>
+          <t>mlb-col</t>
         </is>
       </c>
       <c r="AT46" s="24" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="AU46" s="24" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="AV46" s="24" t="n"/>
@@ -15041,32 +15141,32 @@
       <c r="AY46" s="24" t="n"/>
       <c r="AZ46" s="24" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>shadow_qualified</t>
         </is>
       </c>
       <c r="BA46" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
         </is>
       </c>
       <c r="BB46" s="24" t="inlineStr">
         <is>
-          <t>flat_probability_shrinkage_toward_half</t>
+          <t>learned_lr</t>
         </is>
       </c>
       <c r="BC46" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="BD46" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
         </is>
       </c>
       <c r="BE46" s="24" t="inlineStr">
         <is>
-          <t>v3</t>
+          <t>afbdfea2d660f7f9</t>
         </is>
       </c>
       <c r="BF46" s="24" t="inlineStr">
@@ -15076,12 +15176,12 @@
       </c>
       <c r="BG46" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-paired-v1</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="BH46" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T04:33:52.558033Z</t>
         </is>
       </c>
       <c r="BI46" s="24" t="inlineStr">
@@ -15089,20 +15189,18 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ46" s="25" t="n">
-        <v>1.5</v>
-      </c>
+      <c r="BJ46" s="25" t="n"/>
       <c r="BK46" s="26" t="n">
-        <v>117</v>
+        <v>-147</v>
       </c>
       <c r="BL46" s="27" t="n">
-        <v>2.17</v>
+        <v>1.680272</v>
       </c>
       <c r="BM46" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.5951419999999999</v>
       </c>
       <c r="BN46" s="28" t="n">
-        <v>0.457711</v>
+        <v>0.59204</v>
       </c>
       <c r="BO46" s="28" t="n"/>
       <c r="BP46" s="25" t="n"/>
@@ -15118,22 +15216,54 @@
       <c r="BZ46" s="24" t="n"/>
       <c r="CA46" s="31" t="n"/>
       <c r="CB46" s="24" t="n"/>
-      <c r="CC46" s="24" t="n"/>
-      <c r="CD46" s="24" t="n"/>
-      <c r="CE46" s="24" t="n"/>
-      <c r="CF46" s="24" t="n"/>
+      <c r="CC46" s="24" t="inlineStr">
+        <is>
+          <t>0.3717088646</t>
+        </is>
+      </c>
+      <c r="CD46" s="24" t="inlineStr">
+        <is>
+          <t>1.48701</t>
+        </is>
+      </c>
+      <c r="CE46" s="24" t="inlineStr">
+        <is>
+          <t>1.193</t>
+        </is>
+      </c>
+      <c r="CF46" s="24" t="inlineStr">
+        <is>
+          <t>1.0105</t>
+        </is>
+      </c>
       <c r="CG46" s="24" t="n"/>
       <c r="CH46" s="24" t="n"/>
       <c r="CI46" s="24" t="n"/>
-      <c r="CJ46" s="24" t="n"/>
+      <c r="CJ46" s="24" t="inlineStr">
+        <is>
+          <t>0.458973</t>
+        </is>
+      </c>
       <c r="CK46" s="24" t="n"/>
-      <c r="CL46" s="24" t="n"/>
-      <c r="CM46" s="24" t="n"/>
+      <c r="CL46" s="24" t="inlineStr">
+        <is>
+          <t>0.032773</t>
+        </is>
+      </c>
+      <c r="CM46" s="24" t="inlineStr">
+        <is>
+          <t>3.3324</t>
+        </is>
+      </c>
       <c r="CN46" s="24" t="n"/>
       <c r="CO46" s="24" t="n"/>
       <c r="CP46" s="24" t="n"/>
       <c r="CQ46" s="24" t="n"/>
-      <c r="CR46" s="24" t="n"/>
+      <c r="CR46" s="24" t="inlineStr">
+        <is>
+          <t>0.651419</t>
+        </is>
+      </c>
       <c r="CS46" s="24" t="inlineStr">
         <is>
           <t>True</t>
@@ -15143,22 +15273,22 @@
     <row r="47" ht="36" customHeight="1">
       <c r="A47" s="24" t="inlineStr">
         <is>
-          <t>24ac0a3e828e402a</t>
+          <t>2a3b5ab213d44603</t>
         </is>
       </c>
       <c r="B47" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T04:35:50.664769Z</t>
         </is>
       </c>
       <c r="C47" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T22:40Z</t>
+          <t>2026-08-05T18:35:00-0400</t>
         </is>
       </c>
       <c r="D47" s="24" t="inlineStr">
         <is>
-          <t>401816390</t>
+          <t>401816399</t>
         </is>
       </c>
       <c r="E47" s="24" t="inlineStr">
@@ -15168,59 +15298,55 @@
       </c>
       <c r="F47" s="24" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="G47" s="24" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="H47" s="24" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>moneyline</t>
         </is>
       </c>
       <c r="I47" s="24" t="inlineStr">
         <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="J47" s="25" t="n">
-        <v>8.5</v>
-      </c>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J47" s="25" t="n"/>
       <c r="K47" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L47" s="26" t="n">
-        <v>-117</v>
+        <v>-130</v>
       </c>
       <c r="M47" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.769231</v>
       </c>
       <c r="N47" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.565217</v>
       </c>
       <c r="O47" s="28" t="n">
-        <v>0.511059</v>
-      </c>
-      <c r="P47" s="28" t="n">
-        <v>0.042131</v>
-      </c>
+        <v>0.620283</v>
+      </c>
+      <c r="P47" s="28" t="n"/>
       <c r="Q47" s="28" t="n">
-        <v>-0.028112</v>
+        <v>0.055066</v>
       </c>
       <c r="R47" s="26" t="n">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="S47" s="29" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="T47" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="U47" s="24" t="inlineStr">
@@ -15239,12 +15365,12 @@
       <c r="AD47" s="24" t="n"/>
       <c r="AE47" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 3.92-5.03; raw selected-side p=0.5091, calibrated p=0.5111.</t>
+          <t>Learned LR call at threshold 0.5873; executable ask 0.5650 (aec-mlb-laa-bal-2026-08-05); model edge vs ask +0.0553.</t>
         </is>
       </c>
       <c r="AF47" s="31" t="inlineStr">
         <is>
-          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+          <t>Learned model; shadow-qualified via operator override.</t>
         </is>
       </c>
       <c r="AG47" s="24" t="inlineStr">
@@ -15280,32 +15406,32 @@
       </c>
       <c r="AP47" s="24" t="inlineStr">
         <is>
-          <t>mlb-wsh</t>
+          <t>mlb-laa</t>
         </is>
       </c>
       <c r="AQ47" s="24" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="AR47" s="24" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="AS47" s="24" t="inlineStr">
         <is>
-          <t>mlb-phi</t>
+          <t>mlb-bal</t>
         </is>
       </c>
       <c r="AT47" s="24" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="AU47" s="24" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="AV47" s="24" t="n"/>
@@ -15318,32 +15444,32 @@
       <c r="AY47" s="24" t="n"/>
       <c r="AZ47" s="24" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>shadow_qualified</t>
         </is>
       </c>
       <c r="BA47" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
         </is>
       </c>
       <c r="BB47" s="24" t="inlineStr">
         <is>
-          <t>flat_probability_shrinkage_toward_half</t>
+          <t>learned_lr</t>
         </is>
       </c>
       <c r="BC47" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="BD47" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
         </is>
       </c>
       <c r="BE47" s="24" t="inlineStr">
         <is>
-          <t>v3</t>
+          <t>0c5ef877e6b12160</t>
         </is>
       </c>
       <c r="BF47" s="24" t="inlineStr">
@@ -15353,12 +15479,12 @@
       </c>
       <c r="BG47" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-paired-v1</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="BH47" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T04:33:53.451157Z</t>
         </is>
       </c>
       <c r="BI47" s="24" t="inlineStr">
@@ -15366,20 +15492,18 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ47" s="25" t="n">
-        <v>8.5</v>
-      </c>
+      <c r="BJ47" s="25" t="n"/>
       <c r="BK47" s="26" t="n">
-        <v>-117</v>
+        <v>-130</v>
       </c>
       <c r="BL47" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.769231</v>
       </c>
       <c r="BM47" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.565217</v>
       </c>
       <c r="BN47" s="28" t="n">
-        <v>0.537313</v>
+        <v>0.562189</v>
       </c>
       <c r="BO47" s="28" t="n"/>
       <c r="BP47" s="25" t="n"/>
@@ -15395,47 +15519,79 @@
       <c r="BZ47" s="24" t="n"/>
       <c r="CA47" s="31" t="n"/>
       <c r="CB47" s="24" t="n"/>
-      <c r="CC47" s="24" t="n"/>
-      <c r="CD47" s="24" t="n"/>
-      <c r="CE47" s="24" t="n"/>
-      <c r="CF47" s="24" t="n"/>
+      <c r="CC47" s="24" t="inlineStr">
+        <is>
+          <t>0.6265993564</t>
+        </is>
+      </c>
+      <c r="CD47" s="24" t="inlineStr">
+        <is>
+          <t>0.186002</t>
+        </is>
+      </c>
+      <c r="CE47" s="24" t="inlineStr">
+        <is>
+          <t>1.03</t>
+        </is>
+      </c>
+      <c r="CF47" s="24" t="inlineStr">
+        <is>
+          <t>1.0102</t>
+        </is>
+      </c>
       <c r="CG47" s="24" t="n"/>
       <c r="CH47" s="24" t="n"/>
       <c r="CI47" s="24" t="n"/>
-      <c r="CJ47" s="24" t="n"/>
+      <c r="CJ47" s="24" t="inlineStr">
+        <is>
+          <t>-1.60185</t>
+        </is>
+      </c>
       <c r="CK47" s="24" t="n"/>
-      <c r="CL47" s="24" t="n"/>
-      <c r="CM47" s="24" t="n"/>
+      <c r="CL47" s="24" t="inlineStr">
+        <is>
+          <t>0.070802</t>
+        </is>
+      </c>
+      <c r="CM47" s="24" t="inlineStr">
+        <is>
+          <t>-4.8571</t>
+        </is>
+      </c>
       <c r="CN47" s="24" t="n"/>
       <c r="CO47" s="24" t="n"/>
       <c r="CP47" s="24" t="n"/>
       <c r="CQ47" s="24" t="n"/>
-      <c r="CR47" s="24" t="n"/>
+      <c r="CR47" s="24" t="inlineStr">
+        <is>
+          <t>0.620283</t>
+        </is>
+      </c>
       <c r="CS47" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="48" ht="36" customHeight="1">
       <c r="A48" s="24" t="inlineStr">
         <is>
-          <t>4269da3d4eca4177</t>
+          <t>fd35ca527b5a46d5</t>
         </is>
       </c>
       <c r="B48" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T04:35:50.664769Z</t>
         </is>
       </c>
       <c r="C48" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T23:05Z</t>
+          <t>2026-08-05T19:15:00-0400</t>
         </is>
       </c>
       <c r="D48" s="24" t="inlineStr">
         <is>
-          <t>401816389</t>
+          <t>401816402</t>
         </is>
       </c>
       <c r="E48" s="24" t="inlineStr">
@@ -15445,27 +15601,25 @@
       </c>
       <c r="F48" s="24" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="G48" s="24" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="H48" s="24" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>moneyline</t>
         </is>
       </c>
       <c r="I48" s="24" t="inlineStr">
         <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J48" s="25" t="n">
-        <v>1.5</v>
-      </c>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J48" s="25" t="n"/>
       <c r="K48" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -15481,23 +15635,21 @@
         <v>0.545455</v>
       </c>
       <c r="O48" s="28" t="n">
-        <v>0.612998</v>
-      </c>
-      <c r="P48" s="28" t="n">
-        <v>0.05172</v>
-      </c>
+        <v>0.59089</v>
+      </c>
+      <c r="P48" s="28" t="n"/>
       <c r="Q48" s="28" t="n">
-        <v>0.06754300000000001</v>
+        <v>0.045435</v>
       </c>
       <c r="R48" s="26" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="S48" s="29" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="T48" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="U48" s="24" t="inlineStr">
@@ -15516,12 +15668,12 @@
       <c r="AD48" s="24" t="n"/>
       <c r="AE48" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.35-4.35; raw selected-side p=0.6722, calibrated p=0.6130.</t>
+          <t>Learned LR call at threshold 0.5873; executable ask 0.5450 (aec-mlb-mia-atl-2026-08-05); model edge vs ask +0.0459. NOTE: NO_CALL_STARTER_ERA_GAP_INSUFFICIENT_HISTORY unavailable for this game — defaulted to neutral, other features used normally.</t>
         </is>
       </c>
       <c r="AF48" s="31" t="inlineStr">
         <is>
-          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+          <t>Learned model; shadow-qualified via operator override.</t>
         </is>
       </c>
       <c r="AG48" s="24" t="inlineStr">
@@ -15557,32 +15709,32 @@
       </c>
       <c r="AP48" s="24" t="inlineStr">
         <is>
-          <t>mlb-stl</t>
+          <t>mlb-mia</t>
         </is>
       </c>
       <c r="AQ48" s="24" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="AR48" s="24" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="AS48" s="24" t="inlineStr">
         <is>
-          <t>mlb-nyy</t>
+          <t>mlb-atl</t>
         </is>
       </c>
       <c r="AT48" s="24" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="AU48" s="24" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="AV48" s="24" t="n"/>
@@ -15595,32 +15747,32 @@
       <c r="AY48" s="24" t="n"/>
       <c r="AZ48" s="24" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>shadow_qualified</t>
         </is>
       </c>
       <c r="BA48" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
         </is>
       </c>
       <c r="BB48" s="24" t="inlineStr">
         <is>
-          <t>flat_probability_shrinkage_toward_half</t>
+          <t>learned_lr</t>
         </is>
       </c>
       <c r="BC48" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="BD48" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
         </is>
       </c>
       <c r="BE48" s="24" t="inlineStr">
         <is>
-          <t>v3</t>
+          <t>bb6f41cb5975b5bb</t>
         </is>
       </c>
       <c r="BF48" s="24" t="inlineStr">
@@ -15630,12 +15782,12 @@
       </c>
       <c r="BG48" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-paired-v1</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="BH48" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T04:33:58.789026Z</t>
         </is>
       </c>
       <c r="BI48" s="24" t="inlineStr">
@@ -15643,9 +15795,7 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ48" s="25" t="n">
-        <v>1.5</v>
-      </c>
+      <c r="BJ48" s="25" t="n"/>
       <c r="BK48" s="26" t="n">
         <v>-120</v>
       </c>
@@ -15672,22 +15822,58 @@
       <c r="BZ48" s="24" t="n"/>
       <c r="CA48" s="31" t="n"/>
       <c r="CB48" s="24" t="n"/>
-      <c r="CC48" s="24" t="n"/>
-      <c r="CD48" s="24" t="n"/>
-      <c r="CE48" s="24" t="n"/>
-      <c r="CF48" s="24" t="n"/>
+      <c r="CC48" s="24" t="inlineStr">
+        <is>
+          <t>0.5924601602</t>
+        </is>
+      </c>
+      <c r="CD48" s="24" t="inlineStr">
+        <is>
+          <t>0.154672</t>
+        </is>
+      </c>
+      <c r="CE48" s="24" t="inlineStr">
+        <is>
+          <t>0.929</t>
+        </is>
+      </c>
+      <c r="CF48" s="24" t="inlineStr">
+        <is>
+          <t>1.0072</t>
+        </is>
+      </c>
       <c r="CG48" s="24" t="n"/>
       <c r="CH48" s="24" t="n"/>
-      <c r="CI48" s="24" t="n"/>
-      <c r="CJ48" s="24" t="n"/>
+      <c r="CI48" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_STARTER_ERA_GAP_INSUFFICIENT_HISTORY</t>
+        </is>
+      </c>
+      <c r="CJ48" s="24" t="inlineStr">
+        <is>
+          <t>0.044324</t>
+        </is>
+      </c>
       <c r="CK48" s="24" t="n"/>
-      <c r="CL48" s="24" t="n"/>
-      <c r="CM48" s="24" t="n"/>
+      <c r="CL48" s="24" t="inlineStr">
+        <is>
+          <t>-0.05834</t>
+        </is>
+      </c>
+      <c r="CM48" s="24" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="CN48" s="24" t="n"/>
       <c r="CO48" s="24" t="n"/>
       <c r="CP48" s="24" t="n"/>
       <c r="CQ48" s="24" t="n"/>
-      <c r="CR48" s="24" t="n"/>
+      <c r="CR48" s="24" t="inlineStr">
+        <is>
+          <t>0.59089</t>
+        </is>
+      </c>
       <c r="CS48" s="24" t="inlineStr">
         <is>
           <t>True</t>
@@ -15697,22 +15883,22 @@
     <row r="49" ht="36" customHeight="1">
       <c r="A49" s="24" t="inlineStr">
         <is>
-          <t>7447a7a90b074319</t>
+          <t>8cfab79e9feb48df</t>
         </is>
       </c>
       <c r="B49" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T04:35:50.664769Z</t>
         </is>
       </c>
       <c r="C49" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T23:05Z</t>
+          <t>2026-08-05T19:30:00-0400</t>
         </is>
       </c>
       <c r="D49" s="24" t="inlineStr">
         <is>
-          <t>401816389</t>
+          <t>401816408</t>
         </is>
       </c>
       <c r="E49" s="24" t="inlineStr">
@@ -15722,59 +15908,55 @@
       </c>
       <c r="F49" s="24" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="G49" s="24" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="H49" s="24" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>moneyline</t>
         </is>
       </c>
       <c r="I49" s="24" t="inlineStr">
         <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="J49" s="25" t="n">
-        <v>8.5</v>
-      </c>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J49" s="25" t="n"/>
       <c r="K49" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L49" s="26" t="n">
-        <v>-111</v>
+        <v>-122</v>
       </c>
       <c r="M49" s="27" t="n">
-        <v>1.900901</v>
+        <v>1.819672</v>
       </c>
       <c r="N49" s="28" t="n">
-        <v>0.526066</v>
+        <v>0.54955</v>
       </c>
       <c r="O49" s="28" t="n">
-        <v>0.510786</v>
-      </c>
-      <c r="P49" s="28" t="n">
-        <v>0.05172</v>
-      </c>
+        <v>0.6155080000000001</v>
+      </c>
+      <c r="P49" s="28" t="n"/>
       <c r="Q49" s="28" t="n">
-        <v>-0.01528</v>
+        <v>0.065958</v>
       </c>
       <c r="R49" s="26" t="n">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="S49" s="29" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="T49" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="U49" s="24" t="inlineStr">
@@ -15793,12 +15975,12 @@
       <c r="AD49" s="24" t="n"/>
       <c r="AE49" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.35-4.35; raw selected-side p=0.5083, calibrated p=0.5108.</t>
+          <t>Learned LR call at threshold 0.5873; executable ask 0.5500 (aec-mlb-pit-mil-2026-08-05); model edge vs ask +0.0655.</t>
         </is>
       </c>
       <c r="AF49" s="31" t="inlineStr">
         <is>
-          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+          <t>Learned model; shadow-qualified via operator override.</t>
         </is>
       </c>
       <c r="AG49" s="24" t="inlineStr">
@@ -15834,32 +16016,32 @@
       </c>
       <c r="AP49" s="24" t="inlineStr">
         <is>
-          <t>mlb-stl</t>
+          <t>mlb-pit</t>
         </is>
       </c>
       <c r="AQ49" s="24" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="AR49" s="24" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="AS49" s="24" t="inlineStr">
         <is>
-          <t>mlb-nyy</t>
+          <t>mlb-mil</t>
         </is>
       </c>
       <c r="AT49" s="24" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="AU49" s="24" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="AV49" s="24" t="n"/>
@@ -15872,32 +16054,32 @@
       <c r="AY49" s="24" t="n"/>
       <c r="AZ49" s="24" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>shadow_qualified</t>
         </is>
       </c>
       <c r="BA49" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
         </is>
       </c>
       <c r="BB49" s="24" t="inlineStr">
         <is>
-          <t>flat_probability_shrinkage_toward_half</t>
+          <t>learned_lr</t>
         </is>
       </c>
       <c r="BC49" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="BD49" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
         </is>
       </c>
       <c r="BE49" s="24" t="inlineStr">
         <is>
-          <t>v3</t>
+          <t>23aa584b6028ab97</t>
         </is>
       </c>
       <c r="BF49" s="24" t="inlineStr">
@@ -15907,12 +16089,12 @@
       </c>
       <c r="BG49" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-paired-v1</t>
+          <t>mlb-elo-trend-lr-v8</t>
         </is>
       </c>
       <c r="BH49" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T04:33:59.358107Z</t>
         </is>
       </c>
       <c r="BI49" s="24" t="inlineStr">
@@ -15920,20 +16102,18 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ49" s="25" t="n">
-        <v>8.5</v>
-      </c>
+      <c r="BJ49" s="25" t="n"/>
       <c r="BK49" s="26" t="n">
-        <v>-111</v>
+        <v>-122</v>
       </c>
       <c r="BL49" s="27" t="n">
-        <v>1.900901</v>
+        <v>1.819672</v>
       </c>
       <c r="BM49" s="28" t="n">
-        <v>0.526066</v>
+        <v>0.54955</v>
       </c>
       <c r="BN49" s="28" t="n">
-        <v>0.522388</v>
+        <v>0.547264</v>
       </c>
       <c r="BO49" s="28" t="n"/>
       <c r="BP49" s="25" t="n"/>
@@ -15949,47 +16129,79 @@
       <c r="BZ49" s="24" t="n"/>
       <c r="CA49" s="31" t="n"/>
       <c r="CB49" s="24" t="n"/>
-      <c r="CC49" s="24" t="n"/>
-      <c r="CD49" s="24" t="n"/>
-      <c r="CE49" s="24" t="n"/>
-      <c r="CF49" s="24" t="n"/>
+      <c r="CC49" s="24" t="inlineStr">
+        <is>
+          <t>0.6284314187</t>
+        </is>
+      </c>
+      <c r="CD49" s="24" t="inlineStr">
+        <is>
+          <t>0.320781</t>
+        </is>
+      </c>
+      <c r="CE49" s="24" t="inlineStr">
+        <is>
+          <t>0.997</t>
+        </is>
+      </c>
+      <c r="CF49" s="24" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
       <c r="CG49" s="24" t="n"/>
       <c r="CH49" s="24" t="n"/>
       <c r="CI49" s="24" t="n"/>
-      <c r="CJ49" s="24" t="n"/>
+      <c r="CJ49" s="24" t="inlineStr">
+        <is>
+          <t>0.061913</t>
+        </is>
+      </c>
       <c r="CK49" s="24" t="n"/>
-      <c r="CL49" s="24" t="n"/>
-      <c r="CM49" s="24" t="n"/>
+      <c r="CL49" s="24" t="inlineStr">
+        <is>
+          <t>0.125345</t>
+        </is>
+      </c>
+      <c r="CM49" s="24" t="inlineStr">
+        <is>
+          <t>-1.5183</t>
+        </is>
+      </c>
       <c r="CN49" s="24" t="n"/>
       <c r="CO49" s="24" t="n"/>
       <c r="CP49" s="24" t="n"/>
       <c r="CQ49" s="24" t="n"/>
-      <c r="CR49" s="24" t="n"/>
+      <c r="CR49" s="24" t="inlineStr">
+        <is>
+          <t>0.615508</t>
+        </is>
+      </c>
       <c r="CS49" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="50" ht="36" customHeight="1">
       <c r="A50" s="24" t="inlineStr">
         <is>
-          <t>74826e5d920a490b</t>
+          <t>c07c11cf26cf4d40</t>
         </is>
       </c>
       <c r="B50" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T04:36:16.771749Z</t>
         </is>
       </c>
       <c r="C50" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T23:10Z</t>
+          <t>2026-08-05T18:10Z</t>
         </is>
       </c>
       <c r="D50" s="24" t="inlineStr">
         <is>
-          <t>401816386</t>
+          <t>401816410</t>
         </is>
       </c>
       <c r="E50" s="24" t="inlineStr">
@@ -15999,12 +16211,12 @@
       </c>
       <c r="F50" s="24" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Toronto Blue Jays</t>
         </is>
       </c>
       <c r="G50" s="24" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="H50" s="24" t="inlineStr">
@@ -16026,32 +16238,32 @@
         </is>
       </c>
       <c r="L50" s="26" t="n">
-        <v>-174</v>
+        <v>-135</v>
       </c>
       <c r="M50" s="27" t="n">
-        <v>1.574713</v>
+        <v>1.740741</v>
       </c>
       <c r="N50" s="28" t="n">
-        <v>0.635036</v>
+        <v>0.574468</v>
       </c>
       <c r="O50" s="28" t="n">
-        <v>0.558902</v>
+        <v>0.556045</v>
       </c>
       <c r="P50" s="28" t="n">
-        <v>0.05172</v>
+        <v>0.042131</v>
       </c>
       <c r="Q50" s="28" t="n">
-        <v>-0.07613399999999999</v>
+        <v>-0.018423</v>
       </c>
       <c r="R50" s="26" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="S50" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T50" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="U50" s="24" t="inlineStr">
@@ -16070,7 +16282,7 @@
       <c r="AD50" s="24" t="n"/>
       <c r="AE50" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.37-5.16; raw selected-side p=0.5897, calibrated p=0.5589.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.45-5.29; raw selected-side p=0.5823, calibrated p=0.5560.</t>
         </is>
       </c>
       <c r="AF50" s="31" t="inlineStr">
@@ -16111,32 +16323,32 @@
       </c>
       <c r="AP50" s="24" t="inlineStr">
         <is>
-          <t>mlb-cws</t>
+          <t>mlb-tor</t>
         </is>
       </c>
       <c r="AQ50" s="24" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Toronto Blue Jays</t>
         </is>
       </c>
       <c r="AR50" s="24" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Toronto Blue Jays</t>
         </is>
       </c>
       <c r="AS50" s="24" t="inlineStr">
         <is>
-          <t>mlb-bos</t>
+          <t>mlb-hou</t>
         </is>
       </c>
       <c r="AT50" s="24" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="AU50" s="24" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="AV50" s="24" t="n"/>
@@ -16154,7 +16366,7 @@
       </c>
       <c r="BA50" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BB50" s="24" t="inlineStr">
@@ -16164,12 +16376,12 @@
       </c>
       <c r="BC50" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="BD50" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BE50" s="24" t="inlineStr">
@@ -16189,7 +16401,7 @@
       </c>
       <c r="BH50" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T04:36:16.771749Z</t>
         </is>
       </c>
       <c r="BI50" s="24" t="inlineStr">
@@ -16201,16 +16413,16 @@
         <v>1.5</v>
       </c>
       <c r="BK50" s="26" t="n">
-        <v>-174</v>
+        <v>-135</v>
       </c>
       <c r="BL50" s="27" t="n">
-        <v>1.574713</v>
+        <v>1.740741</v>
       </c>
       <c r="BM50" s="28" t="n">
-        <v>0.635036</v>
+        <v>0.574468</v>
       </c>
       <c r="BN50" s="28" t="n">
-        <v>0.631841</v>
+        <v>0.572139</v>
       </c>
       <c r="BO50" s="28" t="n"/>
       <c r="BP50" s="25" t="n"/>
@@ -16251,22 +16463,22 @@
     <row r="51" ht="36" customHeight="1">
       <c r="A51" s="24" t="inlineStr">
         <is>
-          <t>8e58043a780a4849</t>
+          <t>59dab69433aa4a48</t>
         </is>
       </c>
       <c r="B51" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T04:36:16.771749Z</t>
         </is>
       </c>
       <c r="C51" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T23:10Z</t>
+          <t>2026-08-05T18:10Z</t>
         </is>
       </c>
       <c r="D51" s="24" t="inlineStr">
         <is>
-          <t>401816386</t>
+          <t>401816410</t>
         </is>
       </c>
       <c r="E51" s="24" t="inlineStr">
@@ -16276,12 +16488,12 @@
       </c>
       <c r="F51" s="24" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Toronto Blue Jays</t>
         </is>
       </c>
       <c r="G51" s="24" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="H51" s="24" t="inlineStr">
@@ -16303,32 +16515,32 @@
         </is>
       </c>
       <c r="L51" s="26" t="n">
-        <v>-122</v>
+        <v>111</v>
       </c>
       <c r="M51" s="27" t="n">
-        <v>1.819672</v>
+        <v>2.11</v>
       </c>
       <c r="N51" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.473934</v>
       </c>
       <c r="O51" s="28" t="n">
-        <v>0.529648</v>
+        <v>0.524815</v>
       </c>
       <c r="P51" s="28" t="n">
-        <v>0.05172</v>
+        <v>0.042131</v>
       </c>
       <c r="Q51" s="28" t="n">
-        <v>-0.019902</v>
+        <v>0.050881</v>
       </c>
       <c r="R51" s="26" t="n">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="S51" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T51" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="U51" s="24" t="inlineStr">
@@ -16347,7 +16559,7 @@
       <c r="AD51" s="24" t="n"/>
       <c r="AE51" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.37-5.16; raw selected-side p=0.5635, calibrated p=0.5296.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.45-5.29; raw selected-side p=0.5766, calibrated p=0.5248.</t>
         </is>
       </c>
       <c r="AF51" s="31" t="inlineStr">
@@ -16388,32 +16600,32 @@
       </c>
       <c r="AP51" s="24" t="inlineStr">
         <is>
-          <t>mlb-cws</t>
+          <t>mlb-tor</t>
         </is>
       </c>
       <c r="AQ51" s="24" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Toronto Blue Jays</t>
         </is>
       </c>
       <c r="AR51" s="24" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Toronto Blue Jays</t>
         </is>
       </c>
       <c r="AS51" s="24" t="inlineStr">
         <is>
-          <t>mlb-bos</t>
+          <t>mlb-hou</t>
         </is>
       </c>
       <c r="AT51" s="24" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="AU51" s="24" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="AV51" s="24" t="n"/>
@@ -16431,7 +16643,7 @@
       </c>
       <c r="BA51" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BB51" s="24" t="inlineStr">
@@ -16441,12 +16653,12 @@
       </c>
       <c r="BC51" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="BD51" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BE51" s="24" t="inlineStr">
@@ -16466,7 +16678,7 @@
       </c>
       <c r="BH51" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T04:36:16.771749Z</t>
         </is>
       </c>
       <c r="BI51" s="24" t="inlineStr">
@@ -16478,16 +16690,16 @@
         <v>8.5</v>
       </c>
       <c r="BK51" s="26" t="n">
-        <v>-122</v>
+        <v>111</v>
       </c>
       <c r="BL51" s="27" t="n">
-        <v>1.819672</v>
+        <v>2.11</v>
       </c>
       <c r="BM51" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.473934</v>
       </c>
       <c r="BN51" s="28" t="n">
-        <v>0.547264</v>
+        <v>0.472637</v>
       </c>
       <c r="BO51" s="28" t="n"/>
       <c r="BP51" s="25" t="n"/>
@@ -16521,29 +16733,29 @@
       <c r="CR51" s="24" t="n"/>
       <c r="CS51" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="52" ht="36" customHeight="1">
       <c r="A52" s="24" t="inlineStr">
         <is>
-          <t>8c1d1d3f571d4025</t>
+          <t>56c8fcf5c0bf4137</t>
         </is>
       </c>
       <c r="B52" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T04:36:16.771749Z</t>
         </is>
       </c>
       <c r="C52" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T23:15Z</t>
+          <t>2026-08-05T18:20Z</t>
         </is>
       </c>
       <c r="D52" s="24" t="inlineStr">
         <is>
-          <t>401816387</t>
+          <t>401816406</t>
         </is>
       </c>
       <c r="E52" s="24" t="inlineStr">
@@ -16553,12 +16765,12 @@
       </c>
       <c r="F52" s="24" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="G52" s="24" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="H52" s="24" t="inlineStr">
@@ -16568,7 +16780,7 @@
       </c>
       <c r="I52" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J52" s="25" t="n">
@@ -16580,32 +16792,32 @@
         </is>
       </c>
       <c r="L52" s="26" t="n">
-        <v>-150</v>
+        <v>-174</v>
       </c>
       <c r="M52" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.574713</v>
       </c>
       <c r="N52" s="28" t="n">
-        <v>0.6</v>
+        <v>0.635036</v>
       </c>
       <c r="O52" s="28" t="n">
-        <v>0.567661</v>
+        <v>0.6607420000000001</v>
       </c>
       <c r="P52" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q52" s="28" t="n">
-        <v>-0.032339</v>
+        <v>0.025706</v>
       </c>
       <c r="R52" s="26" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="S52" s="29" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="T52" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="U52" s="24" t="inlineStr">
@@ -16624,7 +16836,7 @@
       <c r="AD52" s="24" t="n"/>
       <c r="AE52" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.10-4.82; raw selected-side p=0.6030, calibrated p=0.5677.</t>
+          <t>Measured Edge Margin: Trend Engine projected 3.96-4.59; raw selected-side p=0.7359, calibrated p=0.6607.</t>
         </is>
       </c>
       <c r="AF52" s="31" t="inlineStr">
@@ -16665,32 +16877,32 @@
       </c>
       <c r="AP52" s="24" t="inlineStr">
         <is>
-          <t>mlb-mia</t>
+          <t>mlb-lad</t>
         </is>
       </c>
       <c r="AQ52" s="24" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="AR52" s="24" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="AS52" s="24" t="inlineStr">
         <is>
-          <t>mlb-atl</t>
+          <t>mlb-chc</t>
         </is>
       </c>
       <c r="AT52" s="24" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="AU52" s="24" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="AV52" s="24" t="n"/>
@@ -16708,7 +16920,7 @@
       </c>
       <c r="BA52" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BB52" s="24" t="inlineStr">
@@ -16718,12 +16930,12 @@
       </c>
       <c r="BC52" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="BD52" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BE52" s="24" t="inlineStr">
@@ -16743,7 +16955,7 @@
       </c>
       <c r="BH52" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T04:36:16.771749Z</t>
         </is>
       </c>
       <c r="BI52" s="24" t="inlineStr">
@@ -16755,16 +16967,16 @@
         <v>1.5</v>
       </c>
       <c r="BK52" s="26" t="n">
-        <v>-150</v>
+        <v>-174</v>
       </c>
       <c r="BL52" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.574713</v>
       </c>
       <c r="BM52" s="28" t="n">
-        <v>0.6</v>
+        <v>0.635036</v>
       </c>
       <c r="BN52" s="28" t="n">
-        <v>0.597015</v>
+        <v>0.631841</v>
       </c>
       <c r="BO52" s="28" t="n"/>
       <c r="BP52" s="25" t="n"/>
@@ -16798,29 +17010,29 @@
       <c r="CR52" s="24" t="n"/>
       <c r="CS52" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="53" ht="36" customHeight="1">
       <c r="A53" s="24" t="inlineStr">
         <is>
-          <t>1f9fb77aaf164589</t>
+          <t>8032753e796f4fa5</t>
         </is>
       </c>
       <c r="B53" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T04:36:16.771749Z</t>
         </is>
       </c>
       <c r="C53" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T23:15Z</t>
+          <t>2026-08-05T18:20Z</t>
         </is>
       </c>
       <c r="D53" s="24" t="inlineStr">
         <is>
-          <t>401816387</t>
+          <t>401816406</t>
         </is>
       </c>
       <c r="E53" s="24" t="inlineStr">
@@ -16830,12 +17042,12 @@
       </c>
       <c r="F53" s="24" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="G53" s="24" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="H53" s="24" t="inlineStr">
@@ -16857,32 +17069,32 @@
         </is>
       </c>
       <c r="L53" s="26" t="n">
-        <v>-113</v>
+        <v>-108</v>
       </c>
       <c r="M53" s="27" t="n">
-        <v>1.884956</v>
+        <v>1.925926</v>
       </c>
       <c r="N53" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.519231</v>
       </c>
       <c r="O53" s="28" t="n">
-        <v>0.54376</v>
+        <v>0.539558</v>
       </c>
       <c r="P53" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q53" s="28" t="n">
-        <v>0.013244</v>
+        <v>0.020327</v>
       </c>
       <c r="R53" s="26" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="S53" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T53" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="U53" s="24" t="inlineStr">
@@ -16901,7 +17113,7 @@
       <c r="AD53" s="24" t="n"/>
       <c r="AE53" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.10-4.82; raw selected-side p=0.6048, calibrated p=0.5438.</t>
+          <t>Measured Edge Totals: Trend Engine projected 3.96-4.59; raw selected-side p=0.6359, calibrated p=0.5396.</t>
         </is>
       </c>
       <c r="AF53" s="31" t="inlineStr">
@@ -16942,32 +17154,32 @@
       </c>
       <c r="AP53" s="24" t="inlineStr">
         <is>
-          <t>mlb-mia</t>
+          <t>mlb-lad</t>
         </is>
       </c>
       <c r="AQ53" s="24" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="AR53" s="24" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="AS53" s="24" t="inlineStr">
         <is>
-          <t>mlb-atl</t>
+          <t>mlb-chc</t>
         </is>
       </c>
       <c r="AT53" s="24" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="AU53" s="24" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="AV53" s="24" t="n"/>
@@ -16985,7 +17197,7 @@
       </c>
       <c r="BA53" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BB53" s="24" t="inlineStr">
@@ -16995,12 +17207,12 @@
       </c>
       <c r="BC53" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="BD53" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BE53" s="24" t="inlineStr">
@@ -17020,7 +17232,7 @@
       </c>
       <c r="BH53" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T04:36:16.771749Z</t>
         </is>
       </c>
       <c r="BI53" s="24" t="inlineStr">
@@ -17032,16 +17244,16 @@
         <v>9.5</v>
       </c>
       <c r="BK53" s="26" t="n">
-        <v>-113</v>
+        <v>-108</v>
       </c>
       <c r="BL53" s="27" t="n">
-        <v>1.884956</v>
+        <v>1.925926</v>
       </c>
       <c r="BM53" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.519231</v>
       </c>
       <c r="BN53" s="28" t="n">
-        <v>0.527363</v>
+        <v>0.517413</v>
       </c>
       <c r="BO53" s="28" t="n"/>
       <c r="BP53" s="25" t="n"/>
@@ -17082,22 +17294,22 @@
     <row r="54" ht="36" customHeight="1">
       <c r="A54" s="24" t="inlineStr">
         <is>
-          <t>032ac8c42bb54932</t>
+          <t>a9b6d40e45ac4271</t>
         </is>
       </c>
       <c r="B54" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T04:36:16.771749Z</t>
         </is>
       </c>
       <c r="C54" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T23:40Z</t>
+          <t>2026-08-05T18:35Z</t>
         </is>
       </c>
       <c r="D54" s="24" t="inlineStr">
         <is>
-          <t>401816392</t>
+          <t>401816409</t>
         </is>
       </c>
       <c r="E54" s="24" t="inlineStr">
@@ -17107,12 +17319,12 @@
       </c>
       <c r="F54" s="24" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>San Francisco Giants</t>
         </is>
       </c>
       <c r="G54" s="24" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="H54" s="24" t="inlineStr">
@@ -17122,7 +17334,7 @@
       </c>
       <c r="I54" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J54" s="25" t="n">
@@ -17134,32 +17346,32 @@
         </is>
       </c>
       <c r="L54" s="26" t="n">
-        <v>-122</v>
+        <v>-130</v>
       </c>
       <c r="M54" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.769231</v>
       </c>
       <c r="N54" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.565217</v>
       </c>
       <c r="O54" s="28" t="n">
-        <v>0.700193</v>
+        <v>0.588514</v>
       </c>
       <c r="P54" s="28" t="n">
         <v>0.05172</v>
       </c>
       <c r="Q54" s="28" t="n">
-        <v>0.150643</v>
+        <v>0.023297</v>
       </c>
       <c r="R54" s="26" t="n">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="S54" s="29" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="T54" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="U54" s="24" t="inlineStr">
@@ -17178,7 +17390,7 @@
       <c r="AD54" s="24" t="n"/>
       <c r="AE54" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 3.16-4.32; raw selected-side p=0.8051, calibrated p=0.7002.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.57-4.92; raw selected-side p=0.6299, calibrated p=0.5885.</t>
         </is>
       </c>
       <c r="AF54" s="31" t="inlineStr">
@@ -17219,32 +17431,32 @@
       </c>
       <c r="AP54" s="24" t="inlineStr">
         <is>
-          <t>mlb-min</t>
+          <t>mlb-sf</t>
         </is>
       </c>
       <c r="AQ54" s="24" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>San Francisco Giants</t>
         </is>
       </c>
       <c r="AR54" s="24" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>San Francisco Giants</t>
         </is>
       </c>
       <c r="AS54" s="24" t="inlineStr">
         <is>
-          <t>mlb-kc</t>
+          <t>mlb-tex</t>
         </is>
       </c>
       <c r="AT54" s="24" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="AU54" s="24" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="AV54" s="24" t="n"/>
@@ -17262,7 +17474,7 @@
       </c>
       <c r="BA54" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BB54" s="24" t="inlineStr">
@@ -17272,12 +17484,12 @@
       </c>
       <c r="BC54" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="BD54" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BE54" s="24" t="inlineStr">
@@ -17297,7 +17509,7 @@
       </c>
       <c r="BH54" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T04:36:16.771749Z</t>
         </is>
       </c>
       <c r="BI54" s="24" t="inlineStr">
@@ -17309,16 +17521,16 @@
         <v>1.5</v>
       </c>
       <c r="BK54" s="26" t="n">
-        <v>-122</v>
+        <v>-130</v>
       </c>
       <c r="BL54" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.769231</v>
       </c>
       <c r="BM54" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.565217</v>
       </c>
       <c r="BN54" s="28" t="n">
-        <v>0.547264</v>
+        <v>0.562189</v>
       </c>
       <c r="BO54" s="28" t="n"/>
       <c r="BP54" s="25" t="n"/>
@@ -17359,22 +17571,22 @@
     <row r="55" ht="36" customHeight="1">
       <c r="A55" s="24" t="inlineStr">
         <is>
-          <t>352ff4cb49064cdb</t>
+          <t>47d5b72109194f7c</t>
         </is>
       </c>
       <c r="B55" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T04:36:16.771749Z</t>
         </is>
       </c>
       <c r="C55" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T23:40Z</t>
+          <t>2026-08-05T18:35Z</t>
         </is>
       </c>
       <c r="D55" s="24" t="inlineStr">
         <is>
-          <t>401816392</t>
+          <t>401816409</t>
         </is>
       </c>
       <c r="E55" s="24" t="inlineStr">
@@ -17384,12 +17596,12 @@
       </c>
       <c r="F55" s="24" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>San Francisco Giants</t>
         </is>
       </c>
       <c r="G55" s="24" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="H55" s="24" t="inlineStr">
@@ -17399,11 +17611,11 @@
       </c>
       <c r="I55" s="24" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="J55" s="25" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="K55" s="24" t="inlineStr">
         <is>
@@ -17411,32 +17623,32 @@
         </is>
       </c>
       <c r="L55" s="26" t="n">
-        <v>-120</v>
+        <v>108</v>
       </c>
       <c r="M55" s="27" t="n">
-        <v>1.833333</v>
+        <v>2.08</v>
       </c>
       <c r="N55" s="28" t="n">
-        <v>0.545455</v>
+        <v>0.480769</v>
       </c>
       <c r="O55" s="28" t="n">
-        <v>0.587703</v>
+        <v>0.522257</v>
       </c>
       <c r="P55" s="28" t="n">
         <v>0.05172</v>
       </c>
       <c r="Q55" s="28" t="n">
-        <v>0.042248</v>
+        <v>0.041488</v>
       </c>
       <c r="R55" s="26" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="S55" s="29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T55" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="U55" s="24" t="inlineStr">
@@ -17455,7 +17667,7 @@
       <c r="AD55" s="24" t="n"/>
       <c r="AE55" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 3.16-4.32; raw selected-side p=0.7334, calibrated p=0.5877.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.57-4.92; raw selected-side p=0.5663, calibrated p=0.5223.</t>
         </is>
       </c>
       <c r="AF55" s="31" t="inlineStr">
@@ -17496,32 +17708,32 @@
       </c>
       <c r="AP55" s="24" t="inlineStr">
         <is>
-          <t>mlb-min</t>
+          <t>mlb-sf</t>
         </is>
       </c>
       <c r="AQ55" s="24" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>San Francisco Giants</t>
         </is>
       </c>
       <c r="AR55" s="24" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>San Francisco Giants</t>
         </is>
       </c>
       <c r="AS55" s="24" t="inlineStr">
         <is>
-          <t>mlb-kc</t>
+          <t>mlb-tex</t>
         </is>
       </c>
       <c r="AT55" s="24" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="AU55" s="24" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="AV55" s="24" t="n"/>
@@ -17539,7 +17751,7 @@
       </c>
       <c r="BA55" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BB55" s="24" t="inlineStr">
@@ -17549,12 +17761,12 @@
       </c>
       <c r="BC55" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="BD55" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BE55" s="24" t="inlineStr">
@@ -17574,7 +17786,7 @@
       </c>
       <c r="BH55" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T04:36:16.771749Z</t>
         </is>
       </c>
       <c r="BI55" s="24" t="inlineStr">
@@ -17583,19 +17795,19 @@
         </is>
       </c>
       <c r="BJ55" s="25" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="BK55" s="26" t="n">
-        <v>-120</v>
+        <v>108</v>
       </c>
       <c r="BL55" s="27" t="n">
-        <v>1.833333</v>
+        <v>2.08</v>
       </c>
       <c r="BM55" s="28" t="n">
-        <v>0.545455</v>
+        <v>0.480769</v>
       </c>
       <c r="BN55" s="28" t="n">
-        <v>0.542289</v>
+        <v>0.477612</v>
       </c>
       <c r="BO55" s="28" t="n"/>
       <c r="BP55" s="25" t="n"/>
@@ -17636,22 +17848,22 @@
     <row r="56" ht="36" customHeight="1">
       <c r="A56" s="24" t="inlineStr">
         <is>
-          <t>72db7fcab77e4e00</t>
+          <t>37a73a36f6874342</t>
         </is>
       </c>
       <c r="B56" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T04:36:16.771749Z</t>
         </is>
       </c>
       <c r="C56" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T23:40Z</t>
+          <t>2026-08-05T19:10Z</t>
         </is>
       </c>
       <c r="D56" s="24" t="inlineStr">
         <is>
-          <t>401816393</t>
+          <t>401816411</t>
         </is>
       </c>
       <c r="E56" s="24" t="inlineStr">
@@ -17661,12 +17873,12 @@
       </c>
       <c r="F56" s="24" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="G56" s="24" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="H56" s="24" t="inlineStr">
@@ -17676,7 +17888,7 @@
       </c>
       <c r="I56" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J56" s="25" t="n">
@@ -17688,32 +17900,32 @@
         </is>
       </c>
       <c r="L56" s="26" t="n">
-        <v>-147</v>
+        <v>-104</v>
       </c>
       <c r="M56" s="27" t="n">
-        <v>1.680272</v>
+        <v>1.961538</v>
       </c>
       <c r="N56" s="28" t="n">
-        <v>0.5951419999999999</v>
+        <v>0.509804</v>
       </c>
       <c r="O56" s="28" t="n">
-        <v>0.597054</v>
+        <v>0.602278</v>
       </c>
       <c r="P56" s="28" t="n">
-        <v>0.05172</v>
+        <v>0.042131</v>
       </c>
       <c r="Q56" s="28" t="n">
-        <v>0.001912</v>
+        <v>0.092474</v>
       </c>
       <c r="R56" s="26" t="n">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="S56" s="29" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="T56" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="U56" s="24" t="inlineStr">
@@ -17732,7 +17944,7 @@
       <c r="AD56" s="24" t="n"/>
       <c r="AE56" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 3.58-4.00; raw selected-side p=0.6479, calibrated p=0.5971.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.81-4.67; raw selected-side p=0.6501, calibrated p=0.6023.</t>
         </is>
       </c>
       <c r="AF56" s="31" t="inlineStr">
@@ -17773,32 +17985,32 @@
       </c>
       <c r="AP56" s="24" t="inlineStr">
         <is>
-          <t>mlb-pit</t>
+          <t>mlb-tb</t>
         </is>
       </c>
       <c r="AQ56" s="24" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="AR56" s="24" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="AS56" s="24" t="inlineStr">
         <is>
-          <t>mlb-mil</t>
+          <t>mlb-col</t>
         </is>
       </c>
       <c r="AT56" s="24" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="AU56" s="24" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="AV56" s="24" t="n"/>
@@ -17816,7 +18028,7 @@
       </c>
       <c r="BA56" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BB56" s="24" t="inlineStr">
@@ -17826,12 +18038,12 @@
       </c>
       <c r="BC56" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="BD56" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BE56" s="24" t="inlineStr">
@@ -17851,7 +18063,7 @@
       </c>
       <c r="BH56" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T04:36:16.771749Z</t>
         </is>
       </c>
       <c r="BI56" s="24" t="inlineStr">
@@ -17863,16 +18075,16 @@
         <v>1.5</v>
       </c>
       <c r="BK56" s="26" t="n">
-        <v>-147</v>
+        <v>-104</v>
       </c>
       <c r="BL56" s="27" t="n">
-        <v>1.680272</v>
+        <v>1.961538</v>
       </c>
       <c r="BM56" s="28" t="n">
-        <v>0.5951419999999999</v>
+        <v>0.509804</v>
       </c>
       <c r="BN56" s="28" t="n">
-        <v>0.59204</v>
+        <v>0.507463</v>
       </c>
       <c r="BO56" s="28" t="n"/>
       <c r="BP56" s="25" t="n"/>
@@ -17913,22 +18125,22 @@
     <row r="57" ht="36" customHeight="1">
       <c r="A57" s="24" t="inlineStr">
         <is>
-          <t>3aaaf6eb6eef4eb1</t>
+          <t>d57ee209bea94133</t>
         </is>
       </c>
       <c r="B57" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T04:36:16.771749Z</t>
         </is>
       </c>
       <c r="C57" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T23:40Z</t>
+          <t>2026-08-05T19:10Z</t>
         </is>
       </c>
       <c r="D57" s="24" t="inlineStr">
         <is>
-          <t>401816393</t>
+          <t>401816411</t>
         </is>
       </c>
       <c r="E57" s="24" t="inlineStr">
@@ -17938,12 +18150,12 @@
       </c>
       <c r="F57" s="24" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="G57" s="24" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="H57" s="24" t="inlineStr">
@@ -17957,7 +18169,7 @@
         </is>
       </c>
       <c r="J57" s="25" t="n">
-        <v>7.5</v>
+        <v>11.5</v>
       </c>
       <c r="K57" s="24" t="inlineStr">
         <is>
@@ -17965,32 +18177,32 @@
         </is>
       </c>
       <c r="L57" s="26" t="n">
-        <v>-106</v>
+        <v>100</v>
       </c>
       <c r="M57" s="27" t="n">
-        <v>1.943396</v>
+        <v>2</v>
       </c>
       <c r="N57" s="28" t="n">
-        <v>0.514563</v>
+        <v>0.5</v>
       </c>
       <c r="O57" s="28" t="n">
-        <v>0.523429</v>
+        <v>0.557989</v>
       </c>
       <c r="P57" s="28" t="n">
-        <v>0.05172</v>
+        <v>0.042131</v>
       </c>
       <c r="Q57" s="28" t="n">
-        <v>0.008866000000000001</v>
+        <v>0.057989</v>
       </c>
       <c r="R57" s="26" t="n">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="S57" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T57" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="U57" s="24" t="inlineStr">
@@ -18009,7 +18221,7 @@
       <c r="AD57" s="24" t="n"/>
       <c r="AE57" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 3.58-4.00; raw selected-side p=0.5453, calibrated p=0.5234.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.81-4.67; raw selected-side p=0.7101, calibrated p=0.5580.</t>
         </is>
       </c>
       <c r="AF57" s="31" t="inlineStr">
@@ -18050,32 +18262,32 @@
       </c>
       <c r="AP57" s="24" t="inlineStr">
         <is>
-          <t>mlb-pit</t>
+          <t>mlb-tb</t>
         </is>
       </c>
       <c r="AQ57" s="24" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="AR57" s="24" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="AS57" s="24" t="inlineStr">
         <is>
-          <t>mlb-mil</t>
+          <t>mlb-col</t>
         </is>
       </c>
       <c r="AT57" s="24" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="AU57" s="24" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="AV57" s="24" t="n"/>
@@ -18093,7 +18305,7 @@
       </c>
       <c r="BA57" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BB57" s="24" t="inlineStr">
@@ -18103,12 +18315,12 @@
       </c>
       <c r="BC57" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="BD57" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BE57" s="24" t="inlineStr">
@@ -18128,7 +18340,7 @@
       </c>
       <c r="BH57" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T04:36:16.771749Z</t>
         </is>
       </c>
       <c r="BI57" s="24" t="inlineStr">
@@ -18137,19 +18349,19 @@
         </is>
       </c>
       <c r="BJ57" s="25" t="n">
-        <v>7.5</v>
+        <v>11.5</v>
       </c>
       <c r="BK57" s="26" t="n">
-        <v>-106</v>
+        <v>100</v>
       </c>
       <c r="BL57" s="27" t="n">
-        <v>1.943396</v>
+        <v>2</v>
       </c>
       <c r="BM57" s="28" t="n">
-        <v>0.514563</v>
+        <v>0.5</v>
       </c>
       <c r="BN57" s="28" t="n">
-        <v>0.509901</v>
+        <v>0.49505</v>
       </c>
       <c r="BO57" s="28" t="n"/>
       <c r="BP57" s="25" t="n"/>
@@ -18190,22 +18402,22 @@
     <row r="58" ht="36" customHeight="1">
       <c r="A58" s="24" t="inlineStr">
         <is>
-          <t>efd57fffe90f4d98</t>
+          <t>e0227c7ea7774bea</t>
         </is>
       </c>
       <c r="B58" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T04:36:16.771749Z</t>
         </is>
       </c>
       <c r="C58" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T00:05Z</t>
+          <t>2026-08-05T22:35Z</t>
         </is>
       </c>
       <c r="D58" s="24" t="inlineStr">
         <is>
-          <t>401816391</t>
+          <t>401816399</t>
         </is>
       </c>
       <c r="E58" s="24" t="inlineStr">
@@ -18215,12 +18427,12 @@
       </c>
       <c r="F58" s="24" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="G58" s="24" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="H58" s="24" t="inlineStr">
@@ -18230,7 +18442,7 @@
       </c>
       <c r="I58" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J58" s="25" t="n">
@@ -18242,32 +18454,32 @@
         </is>
       </c>
       <c r="L58" s="26" t="n">
-        <v>117</v>
+        <v>-167</v>
       </c>
       <c r="M58" s="27" t="n">
-        <v>2.17</v>
+        <v>1.598802</v>
       </c>
       <c r="N58" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.625468</v>
       </c>
       <c r="O58" s="28" t="n">
-        <v>0.62835</v>
+        <v>0.585379</v>
       </c>
       <c r="P58" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q58" s="28" t="n">
-        <v>0.167521</v>
+        <v>-0.040089</v>
       </c>
       <c r="R58" s="26" t="n">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="S58" s="29" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="T58" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="U58" s="24" t="inlineStr">
@@ -18286,7 +18498,7 @@
       <c r="AD58" s="24" t="n"/>
       <c r="AE58" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 3.82-3.91; raw selected-side p=0.6956, calibrated p=0.6284.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.25-4.70; raw selected-side p=0.6253, calibrated p=0.5854.</t>
         </is>
       </c>
       <c r="AF58" s="31" t="inlineStr">
@@ -18327,32 +18539,32 @@
       </c>
       <c r="AP58" s="24" t="inlineStr">
         <is>
-          <t>mlb-lad</t>
+          <t>mlb-laa</t>
         </is>
       </c>
       <c r="AQ58" s="24" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="AR58" s="24" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="AS58" s="24" t="inlineStr">
         <is>
-          <t>mlb-chc</t>
+          <t>mlb-bal</t>
         </is>
       </c>
       <c r="AT58" s="24" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="AU58" s="24" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="AV58" s="24" t="n"/>
@@ -18370,7 +18582,7 @@
       </c>
       <c r="BA58" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BB58" s="24" t="inlineStr">
@@ -18380,12 +18592,12 @@
       </c>
       <c r="BC58" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="BD58" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BE58" s="24" t="inlineStr">
@@ -18405,7 +18617,7 @@
       </c>
       <c r="BH58" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T04:36:16.771749Z</t>
         </is>
       </c>
       <c r="BI58" s="24" t="inlineStr">
@@ -18417,16 +18629,16 @@
         <v>1.5</v>
       </c>
       <c r="BK58" s="26" t="n">
-        <v>117</v>
+        <v>-167</v>
       </c>
       <c r="BL58" s="27" t="n">
-        <v>2.17</v>
+        <v>1.598802</v>
       </c>
       <c r="BM58" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.625468</v>
       </c>
       <c r="BN58" s="28" t="n">
-        <v>0.455446</v>
+        <v>0.621891</v>
       </c>
       <c r="BO58" s="28" t="n"/>
       <c r="BP58" s="25" t="n"/>
@@ -18460,29 +18672,29 @@
       <c r="CR58" s="24" t="n"/>
       <c r="CS58" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="59" ht="36" customHeight="1">
       <c r="A59" s="24" t="inlineStr">
         <is>
-          <t>5afdfe6a6e5342e0</t>
+          <t>cd9479291a4d4d56</t>
         </is>
       </c>
       <c r="B59" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T04:36:16.771749Z</t>
         </is>
       </c>
       <c r="C59" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T00:05Z</t>
+          <t>2026-08-05T22:35Z</t>
         </is>
       </c>
       <c r="D59" s="24" t="inlineStr">
         <is>
-          <t>401816391</t>
+          <t>401816399</t>
         </is>
       </c>
       <c r="E59" s="24" t="inlineStr">
@@ -18492,12 +18704,12 @@
       </c>
       <c r="F59" s="24" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="G59" s="24" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="H59" s="24" t="inlineStr">
@@ -18507,11 +18719,11 @@
       </c>
       <c r="I59" s="24" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="J59" s="25" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="K59" s="24" t="inlineStr">
         <is>
@@ -18519,32 +18731,32 @@
         </is>
       </c>
       <c r="L59" s="26" t="n">
-        <v>-122</v>
+        <v>111</v>
       </c>
       <c r="M59" s="27" t="n">
-        <v>1.819672</v>
+        <v>2.11</v>
       </c>
       <c r="N59" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.473934</v>
       </c>
       <c r="O59" s="28" t="n">
-        <v>0.579434</v>
+        <v>0.5089669999999999</v>
       </c>
       <c r="P59" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q59" s="28" t="n">
-        <v>0.029884</v>
+        <v>0.035033</v>
       </c>
       <c r="R59" s="26" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="S59" s="29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T59" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="U59" s="24" t="inlineStr">
@@ -18563,7 +18775,7 @@
       <c r="AD59" s="24" t="n"/>
       <c r="AE59" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 3.82-3.91; raw selected-side p=0.7092, calibrated p=0.5794.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.25-4.70; raw selected-side p=0.5128, calibrated p=0.5090.</t>
         </is>
       </c>
       <c r="AF59" s="31" t="inlineStr">
@@ -18604,32 +18816,32 @@
       </c>
       <c r="AP59" s="24" t="inlineStr">
         <is>
-          <t>mlb-lad</t>
+          <t>mlb-laa</t>
         </is>
       </c>
       <c r="AQ59" s="24" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="AR59" s="24" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="AS59" s="24" t="inlineStr">
         <is>
-          <t>mlb-chc</t>
+          <t>mlb-bal</t>
         </is>
       </c>
       <c r="AT59" s="24" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="AU59" s="24" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="AV59" s="24" t="n"/>
@@ -18647,7 +18859,7 @@
       </c>
       <c r="BA59" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BB59" s="24" t="inlineStr">
@@ -18657,12 +18869,12 @@
       </c>
       <c r="BC59" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="BD59" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BE59" s="24" t="inlineStr">
@@ -18682,7 +18894,7 @@
       </c>
       <c r="BH59" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T04:36:16.771749Z</t>
         </is>
       </c>
       <c r="BI59" s="24" t="inlineStr">
@@ -18691,19 +18903,19 @@
         </is>
       </c>
       <c r="BJ59" s="25" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="BK59" s="26" t="n">
-        <v>-122</v>
+        <v>111</v>
       </c>
       <c r="BL59" s="27" t="n">
-        <v>1.819672</v>
+        <v>2.11</v>
       </c>
       <c r="BM59" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.473934</v>
       </c>
       <c r="BN59" s="28" t="n">
-        <v>0.547264</v>
+        <v>0.472637</v>
       </c>
       <c r="BO59" s="28" t="n"/>
       <c r="BP59" s="25" t="n"/>
@@ -18744,22 +18956,22 @@
     <row r="60" ht="36" customHeight="1">
       <c r="A60" s="24" t="inlineStr">
         <is>
-          <t>19c2aae4fb7046a6</t>
+          <t>24790c1c98bc4ad9</t>
         </is>
       </c>
       <c r="B60" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T04:36:16.771749Z</t>
         </is>
       </c>
       <c r="C60" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T00:05Z</t>
+          <t>2026-08-05T22:40Z</t>
         </is>
       </c>
       <c r="D60" s="24" t="inlineStr">
         <is>
-          <t>401816394</t>
+          <t>401816400</t>
         </is>
       </c>
       <c r="E60" s="24" t="inlineStr">
@@ -18769,12 +18981,12 @@
       </c>
       <c r="F60" s="24" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="G60" s="24" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="H60" s="24" t="inlineStr">
@@ -18796,32 +19008,32 @@
         </is>
       </c>
       <c r="L60" s="26" t="n">
-        <v>-120</v>
+        <v>-153</v>
       </c>
       <c r="M60" s="27" t="n">
-        <v>1.833333</v>
+        <v>1.653595</v>
       </c>
       <c r="N60" s="28" t="n">
-        <v>0.545455</v>
+        <v>0.604743</v>
       </c>
       <c r="O60" s="28" t="n">
-        <v>0.657612</v>
+        <v>0.590797</v>
       </c>
       <c r="P60" s="28" t="n">
-        <v>0.05172</v>
+        <v>0.042131</v>
       </c>
       <c r="Q60" s="28" t="n">
-        <v>0.112157</v>
+        <v>-0.013946</v>
       </c>
       <c r="R60" s="26" t="n">
-        <v>77</v>
+        <v>19</v>
       </c>
       <c r="S60" s="29" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="T60" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="U60" s="24" t="inlineStr">
@@ -18840,7 +19052,7 @@
       <c r="AD60" s="24" t="n"/>
       <c r="AE60" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.98-4.16; raw selected-side p=0.7401, calibrated p=0.6576.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.90-5.09; raw selected-side p=0.6332, calibrated p=0.5908.</t>
         </is>
       </c>
       <c r="AF60" s="31" t="inlineStr">
@@ -18881,32 +19093,32 @@
       </c>
       <c r="AP60" s="24" t="inlineStr">
         <is>
-          <t>mlb-sf</t>
+          <t>mlb-ath</t>
         </is>
       </c>
       <c r="AQ60" s="24" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="AR60" s="24" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="AS60" s="24" t="inlineStr">
         <is>
-          <t>mlb-tex</t>
+          <t>mlb-cin</t>
         </is>
       </c>
       <c r="AT60" s="24" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="AU60" s="24" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="AV60" s="24" t="n"/>
@@ -18924,7 +19136,7 @@
       </c>
       <c r="BA60" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BB60" s="24" t="inlineStr">
@@ -18934,12 +19146,12 @@
       </c>
       <c r="BC60" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="BD60" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BE60" s="24" t="inlineStr">
@@ -18959,7 +19171,7 @@
       </c>
       <c r="BH60" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T04:36:16.771749Z</t>
         </is>
       </c>
       <c r="BI60" s="24" t="inlineStr">
@@ -18971,16 +19183,16 @@
         <v>1.5</v>
       </c>
       <c r="BK60" s="26" t="n">
-        <v>-120</v>
+        <v>-153</v>
       </c>
       <c r="BL60" s="27" t="n">
-        <v>1.833333</v>
+        <v>1.653595</v>
       </c>
       <c r="BM60" s="28" t="n">
-        <v>0.545455</v>
+        <v>0.604743</v>
       </c>
       <c r="BN60" s="28" t="n">
-        <v>0.542289</v>
+        <v>0.60199</v>
       </c>
       <c r="BO60" s="28" t="n"/>
       <c r="BP60" s="25" t="n"/>
@@ -19014,29 +19226,29 @@
       <c r="CR60" s="24" t="n"/>
       <c r="CS60" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="61" ht="36" customHeight="1">
       <c r="A61" s="24" t="inlineStr">
         <is>
-          <t>57aef3476be84083</t>
+          <t>0f33d75cea924af2</t>
         </is>
       </c>
       <c r="B61" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T04:36:16.771749Z</t>
         </is>
       </c>
       <c r="C61" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T00:05Z</t>
+          <t>2026-08-05T22:40Z</t>
         </is>
       </c>
       <c r="D61" s="24" t="inlineStr">
         <is>
-          <t>401816394</t>
+          <t>401816400</t>
         </is>
       </c>
       <c r="E61" s="24" t="inlineStr">
@@ -19046,12 +19258,12 @@
       </c>
       <c r="F61" s="24" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="G61" s="24" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="H61" s="24" t="inlineStr">
@@ -19061,11 +19273,11 @@
       </c>
       <c r="I61" s="24" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="J61" s="25" t="n">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="K61" s="24" t="inlineStr">
         <is>
@@ -19073,32 +19285,32 @@
         </is>
       </c>
       <c r="L61" s="26" t="n">
-        <v>-115</v>
+        <v>104</v>
       </c>
       <c r="M61" s="27" t="n">
-        <v>1.869565</v>
+        <v>2.04</v>
       </c>
       <c r="N61" s="28" t="n">
-        <v>0.534884</v>
+        <v>0.490196</v>
       </c>
       <c r="O61" s="28" t="n">
-        <v>0.543008</v>
+        <v>0.509116</v>
       </c>
       <c r="P61" s="28" t="n">
-        <v>0.05172</v>
+        <v>0.042131</v>
       </c>
       <c r="Q61" s="28" t="n">
-        <v>0.008123999999999999</v>
+        <v>0.01892</v>
       </c>
       <c r="R61" s="26" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="S61" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T61" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="U61" s="24" t="inlineStr">
@@ -19117,7 +19329,7 @@
       <c r="AD61" s="24" t="n"/>
       <c r="AE61" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.98-4.16; raw selected-side p=0.6026, calibrated p=0.5430.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.90-5.09; raw selected-side p=0.5133, calibrated p=0.5091.</t>
         </is>
       </c>
       <c r="AF61" s="31" t="inlineStr">
@@ -19158,32 +19370,32 @@
       </c>
       <c r="AP61" s="24" t="inlineStr">
         <is>
-          <t>mlb-sf</t>
+          <t>mlb-ath</t>
         </is>
       </c>
       <c r="AQ61" s="24" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="AR61" s="24" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="AS61" s="24" t="inlineStr">
         <is>
-          <t>mlb-tex</t>
+          <t>mlb-cin</t>
         </is>
       </c>
       <c r="AT61" s="24" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="AU61" s="24" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="AV61" s="24" t="n"/>
@@ -19201,7 +19413,7 @@
       </c>
       <c r="BA61" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BB61" s="24" t="inlineStr">
@@ -19211,12 +19423,12 @@
       </c>
       <c r="BC61" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="BD61" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BE61" s="24" t="inlineStr">
@@ -19236,7 +19448,7 @@
       </c>
       <c r="BH61" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T04:36:16.771749Z</t>
         </is>
       </c>
       <c r="BI61" s="24" t="inlineStr">
@@ -19245,19 +19457,19 @@
         </is>
       </c>
       <c r="BJ61" s="25" t="n">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="BK61" s="26" t="n">
-        <v>-115</v>
+        <v>104</v>
       </c>
       <c r="BL61" s="27" t="n">
-        <v>1.869565</v>
+        <v>2.04</v>
       </c>
       <c r="BM61" s="28" t="n">
-        <v>0.534884</v>
+        <v>0.490196</v>
       </c>
       <c r="BN61" s="28" t="n">
-        <v>0.532338</v>
+        <v>0.487562</v>
       </c>
       <c r="BO61" s="28" t="n"/>
       <c r="BP61" s="25" t="n"/>
@@ -19298,22 +19510,22 @@
     <row r="62" ht="36" customHeight="1">
       <c r="A62" s="24" t="inlineStr">
         <is>
-          <t>8bdbed487f214c46</t>
+          <t>2df7f8ae6f304847</t>
         </is>
       </c>
       <c r="B62" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T04:36:16.771749Z</t>
         </is>
       </c>
       <c r="C62" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T00:10Z</t>
+          <t>2026-08-05T22:40Z</t>
         </is>
       </c>
       <c r="D62" s="24" t="inlineStr">
         <is>
-          <t>401816395</t>
+          <t>401816403</t>
         </is>
       </c>
       <c r="E62" s="24" t="inlineStr">
@@ -19323,12 +19535,12 @@
       </c>
       <c r="F62" s="24" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="G62" s="24" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Cleveland Guardians</t>
         </is>
       </c>
       <c r="H62" s="24" t="inlineStr">
@@ -19338,7 +19550,7 @@
       </c>
       <c r="I62" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J62" s="25" t="n">
@@ -19350,32 +19562,32 @@
         </is>
       </c>
       <c r="L62" s="26" t="n">
-        <v>-178</v>
+        <v>-153</v>
       </c>
       <c r="M62" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.653595</v>
       </c>
       <c r="N62" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.604743</v>
       </c>
       <c r="O62" s="28" t="n">
-        <v>0.577535</v>
+        <v>0.60221</v>
       </c>
       <c r="P62" s="28" t="n">
-        <v>0.05172</v>
+        <v>0.042131</v>
       </c>
       <c r="Q62" s="28" t="n">
-        <v>-0.062753</v>
+        <v>-0.002533</v>
       </c>
       <c r="R62" s="26" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="S62" s="29" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="T62" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="U62" s="24" t="inlineStr">
@@ -19394,7 +19606,7 @@
       <c r="AD62" s="24" t="n"/>
       <c r="AE62" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.31-4.86; raw selected-side p=0.6181, calibrated p=0.5775.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.46-4.24; raw selected-side p=0.6500, calibrated p=0.6022.</t>
         </is>
       </c>
       <c r="AF62" s="31" t="inlineStr">
@@ -19435,32 +19647,32 @@
       </c>
       <c r="AP62" s="24" t="inlineStr">
         <is>
-          <t>mlb-tor</t>
+          <t>mlb-nym</t>
         </is>
       </c>
       <c r="AQ62" s="24" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="AR62" s="24" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="AS62" s="24" t="inlineStr">
         <is>
-          <t>mlb-hou</t>
+          <t>mlb-cle</t>
         </is>
       </c>
       <c r="AT62" s="24" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Cleveland Guardians</t>
         </is>
       </c>
       <c r="AU62" s="24" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Cleveland Guardians</t>
         </is>
       </c>
       <c r="AV62" s="24" t="n"/>
@@ -19478,7 +19690,7 @@
       </c>
       <c r="BA62" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BB62" s="24" t="inlineStr">
@@ -19488,12 +19700,12 @@
       </c>
       <c r="BC62" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="BD62" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BE62" s="24" t="inlineStr">
@@ -19513,7 +19725,7 @@
       </c>
       <c r="BH62" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T04:36:16.771749Z</t>
         </is>
       </c>
       <c r="BI62" s="24" t="inlineStr">
@@ -19525,16 +19737,16 @@
         <v>1.5</v>
       </c>
       <c r="BK62" s="26" t="n">
-        <v>-178</v>
+        <v>-153</v>
       </c>
       <c r="BL62" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.653595</v>
       </c>
       <c r="BM62" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.604743</v>
       </c>
       <c r="BN62" s="28" t="n">
-        <v>0.636816</v>
+        <v>0.60199</v>
       </c>
       <c r="BO62" s="28" t="n"/>
       <c r="BP62" s="25" t="n"/>
@@ -19575,22 +19787,22 @@
     <row r="63" ht="36" customHeight="1">
       <c r="A63" s="24" t="inlineStr">
         <is>
-          <t>d43d12ed43b34018</t>
+          <t>5eca91635a984d3d</t>
         </is>
       </c>
       <c r="B63" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T04:36:16.771749Z</t>
         </is>
       </c>
       <c r="C63" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T00:10Z</t>
+          <t>2026-08-05T22:40Z</t>
         </is>
       </c>
       <c r="D63" s="24" t="inlineStr">
         <is>
-          <t>401816395</t>
+          <t>401816403</t>
         </is>
       </c>
       <c r="E63" s="24" t="inlineStr">
@@ -19600,12 +19812,12 @@
       </c>
       <c r="F63" s="24" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="G63" s="24" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Cleveland Guardians</t>
         </is>
       </c>
       <c r="H63" s="24" t="inlineStr">
@@ -19615,7 +19827,7 @@
       </c>
       <c r="I63" s="24" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>under</t>
         </is>
       </c>
       <c r="J63" s="25" t="n">
@@ -19627,32 +19839,32 @@
         </is>
       </c>
       <c r="L63" s="26" t="n">
-        <v>104</v>
+        <v>-102</v>
       </c>
       <c r="M63" s="27" t="n">
-        <v>2.04</v>
+        <v>1.980392</v>
       </c>
       <c r="N63" s="28" t="n">
-        <v>0.490196</v>
+        <v>0.50495</v>
       </c>
       <c r="O63" s="28" t="n">
-        <v>0.516834</v>
+        <v>0.50934</v>
       </c>
       <c r="P63" s="28" t="n">
-        <v>0.05172</v>
+        <v>0.042131</v>
       </c>
       <c r="Q63" s="28" t="n">
-        <v>0.026638</v>
+        <v>0.00439</v>
       </c>
       <c r="R63" s="26" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="S63" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T63" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="U63" s="24" t="inlineStr">
@@ -19671,7 +19883,7 @@
       <c r="AD63" s="24" t="n"/>
       <c r="AE63" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.31-4.86; raw selected-side p=0.5260, calibrated p=0.5168.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.46-4.24; raw selected-side p=0.5142, calibrated p=0.5093.</t>
         </is>
       </c>
       <c r="AF63" s="31" t="inlineStr">
@@ -19712,32 +19924,32 @@
       </c>
       <c r="AP63" s="24" t="inlineStr">
         <is>
-          <t>mlb-tor</t>
+          <t>mlb-nym</t>
         </is>
       </c>
       <c r="AQ63" s="24" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="AR63" s="24" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="AS63" s="24" t="inlineStr">
         <is>
-          <t>mlb-hou</t>
+          <t>mlb-cle</t>
         </is>
       </c>
       <c r="AT63" s="24" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Cleveland Guardians</t>
         </is>
       </c>
       <c r="AU63" s="24" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Cleveland Guardians</t>
         </is>
       </c>
       <c r="AV63" s="24" t="n"/>
@@ -19755,7 +19967,7 @@
       </c>
       <c r="BA63" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BB63" s="24" t="inlineStr">
@@ -19765,12 +19977,12 @@
       </c>
       <c r="BC63" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="BD63" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BE63" s="24" t="inlineStr">
@@ -19790,7 +20002,7 @@
       </c>
       <c r="BH63" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T04:36:16.771749Z</t>
         </is>
       </c>
       <c r="BI63" s="24" t="inlineStr">
@@ -19802,16 +20014,16 @@
         <v>8.5</v>
       </c>
       <c r="BK63" s="26" t="n">
-        <v>104</v>
+        <v>-102</v>
       </c>
       <c r="BL63" s="27" t="n">
-        <v>2.04</v>
+        <v>1.980392</v>
       </c>
       <c r="BM63" s="28" t="n">
-        <v>0.490196</v>
+        <v>0.50495</v>
       </c>
       <c r="BN63" s="28" t="n">
-        <v>0.487562</v>
+        <v>0.502488</v>
       </c>
       <c r="BO63" s="28" t="n"/>
       <c r="BP63" s="25" t="n"/>
@@ -19852,22 +20064,22 @@
     <row r="64" ht="36" customHeight="1">
       <c r="A64" s="24" t="inlineStr">
         <is>
-          <t>9d6188233c84469f</t>
+          <t>f32645579d0644b7</t>
         </is>
       </c>
       <c r="B64" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T04:36:16.771749Z</t>
         </is>
       </c>
       <c r="C64" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T00:40Z</t>
+          <t>2026-08-05T22:40Z</t>
         </is>
       </c>
       <c r="D64" s="24" t="inlineStr">
         <is>
-          <t>401816396</t>
+          <t>401816405</t>
         </is>
       </c>
       <c r="E64" s="24" t="inlineStr">
@@ -19877,12 +20089,12 @@
       </c>
       <c r="F64" s="24" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="G64" s="24" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="H64" s="24" t="inlineStr">
@@ -19892,7 +20104,7 @@
       </c>
       <c r="I64" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J64" s="25" t="n">
@@ -19904,32 +20116,32 @@
         </is>
       </c>
       <c r="L64" s="26" t="n">
-        <v>-104</v>
+        <v>-127</v>
       </c>
       <c r="M64" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.787402</v>
       </c>
       <c r="N64" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="O64" s="28" t="n">
-        <v>0.6912700000000001</v>
+        <v>0.60238</v>
       </c>
       <c r="P64" s="28" t="n">
-        <v>0.05172</v>
+        <v>0.042131</v>
       </c>
       <c r="Q64" s="28" t="n">
-        <v>0.181466</v>
+        <v>0.042909</v>
       </c>
       <c r="R64" s="26" t="n">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="S64" s="29" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="T64" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="U64" s="24" t="inlineStr">
@@ -19948,7 +20160,7 @@
       <c r="AD64" s="24" t="n"/>
       <c r="AE64" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.49-6.29; raw selected-side p=0.7914, calibrated p=0.6913.</t>
+          <t>Measured Edge Margin: Trend Engine projected 5.21-5.30; raw selected-side p=0.6502, calibrated p=0.6024.</t>
         </is>
       </c>
       <c r="AF64" s="31" t="inlineStr">
@@ -19989,32 +20201,32 @@
       </c>
       <c r="AP64" s="24" t="inlineStr">
         <is>
-          <t>mlb-tb</t>
+          <t>mlb-wsh</t>
         </is>
       </c>
       <c r="AQ64" s="24" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="AR64" s="24" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="AS64" s="24" t="inlineStr">
         <is>
-          <t>mlb-col</t>
+          <t>mlb-phi</t>
         </is>
       </c>
       <c r="AT64" s="24" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="AU64" s="24" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="AV64" s="24" t="n"/>
@@ -20032,7 +20244,7 @@
       </c>
       <c r="BA64" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BB64" s="24" t="inlineStr">
@@ -20042,12 +20254,12 @@
       </c>
       <c r="BC64" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="BD64" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BE64" s="24" t="inlineStr">
@@ -20067,7 +20279,7 @@
       </c>
       <c r="BH64" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T04:36:16.771749Z</t>
         </is>
       </c>
       <c r="BI64" s="24" t="inlineStr">
@@ -20079,16 +20291,16 @@
         <v>1.5</v>
       </c>
       <c r="BK64" s="26" t="n">
-        <v>-104</v>
+        <v>-127</v>
       </c>
       <c r="BL64" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.787402</v>
       </c>
       <c r="BM64" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="BN64" s="28" t="n">
-        <v>0.507463</v>
+        <v>0.554455</v>
       </c>
       <c r="BO64" s="28" t="n"/>
       <c r="BP64" s="25" t="n"/>
@@ -20129,22 +20341,22 @@
     <row r="65" ht="36" customHeight="1">
       <c r="A65" s="24" t="inlineStr">
         <is>
-          <t>b2a3b70378ef493f</t>
+          <t>6dc05d99bf2b4f62</t>
         </is>
       </c>
       <c r="B65" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T04:36:16.771749Z</t>
         </is>
       </c>
       <c r="C65" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T00:40Z</t>
+          <t>2026-08-05T22:40Z</t>
         </is>
       </c>
       <c r="D65" s="24" t="inlineStr">
         <is>
-          <t>401816396</t>
+          <t>401816405</t>
         </is>
       </c>
       <c r="E65" s="24" t="inlineStr">
@@ -20154,12 +20366,12 @@
       </c>
       <c r="F65" s="24" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="G65" s="24" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="H65" s="24" t="inlineStr">
@@ -20169,11 +20381,11 @@
       </c>
       <c r="I65" s="24" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="J65" s="25" t="n">
-        <v>11.5</v>
+        <v>9.5</v>
       </c>
       <c r="K65" s="24" t="inlineStr">
         <is>
@@ -20181,32 +20393,32 @@
         </is>
       </c>
       <c r="L65" s="26" t="n">
-        <v>-117</v>
+        <v>-104</v>
       </c>
       <c r="M65" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.961538</v>
       </c>
       <c r="N65" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.509804</v>
       </c>
       <c r="O65" s="28" t="n">
-        <v>0.544905</v>
+        <v>0.5154879999999999</v>
       </c>
       <c r="P65" s="28" t="n">
-        <v>0.05172</v>
+        <v>0.042131</v>
       </c>
       <c r="Q65" s="28" t="n">
-        <v>0.005734</v>
+        <v>0.005684</v>
       </c>
       <c r="R65" s="26" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="S65" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T65" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="U65" s="24" t="inlineStr">
@@ -20225,7 +20437,7 @@
       <c r="AD65" s="24" t="n"/>
       <c r="AE65" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.49-6.29; raw selected-side p=0.6081, calibrated p=0.5449.</t>
+          <t>Measured Edge Totals: Trend Engine projected 5.21-5.30; raw selected-side p=0.5390, calibrated p=0.5155.</t>
         </is>
       </c>
       <c r="AF65" s="31" t="inlineStr">
@@ -20266,32 +20478,32 @@
       </c>
       <c r="AP65" s="24" t="inlineStr">
         <is>
-          <t>mlb-tb</t>
+          <t>mlb-wsh</t>
         </is>
       </c>
       <c r="AQ65" s="24" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="AR65" s="24" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="AS65" s="24" t="inlineStr">
         <is>
-          <t>mlb-col</t>
+          <t>mlb-phi</t>
         </is>
       </c>
       <c r="AT65" s="24" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="AU65" s="24" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="AV65" s="24" t="n"/>
@@ -20309,7 +20521,7 @@
       </c>
       <c r="BA65" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BB65" s="24" t="inlineStr">
@@ -20319,12 +20531,12 @@
       </c>
       <c r="BC65" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="BD65" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BE65" s="24" t="inlineStr">
@@ -20344,7 +20556,7 @@
       </c>
       <c r="BH65" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T04:36:16.771749Z</t>
         </is>
       </c>
       <c r="BI65" s="24" t="inlineStr">
@@ -20353,19 +20565,19 @@
         </is>
       </c>
       <c r="BJ65" s="25" t="n">
-        <v>11.5</v>
+        <v>9.5</v>
       </c>
       <c r="BK65" s="26" t="n">
-        <v>-117</v>
+        <v>-104</v>
       </c>
       <c r="BL65" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.961538</v>
       </c>
       <c r="BM65" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.509804</v>
       </c>
       <c r="BN65" s="28" t="n">
-        <v>0.537313</v>
+        <v>0.507463</v>
       </c>
       <c r="BO65" s="28" t="n"/>
       <c r="BP65" s="25" t="n"/>
@@ -20406,22 +20618,22 @@
     <row r="66" ht="36" customHeight="1">
       <c r="A66" s="24" t="inlineStr">
         <is>
-          <t>87a3403819ca4958</t>
+          <t>b310c5b5775a4b30</t>
         </is>
       </c>
       <c r="B66" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T04:36:16.771749Z</t>
         </is>
       </c>
       <c r="C66" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T01:40Z</t>
+          <t>2026-08-05T23:05Z</t>
         </is>
       </c>
       <c r="D66" s="24" t="inlineStr">
         <is>
-          <t>401816398</t>
+          <t>401816404</t>
         </is>
       </c>
       <c r="E66" s="24" t="inlineStr">
@@ -20431,12 +20643,12 @@
       </c>
       <c r="F66" s="24" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="G66" s="24" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="H66" s="24" t="inlineStr">
@@ -20458,32 +20670,32 @@
         </is>
       </c>
       <c r="L66" s="26" t="n">
-        <v>-178</v>
+        <v>-150</v>
       </c>
       <c r="M66" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.666667</v>
       </c>
       <c r="N66" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.6</v>
       </c>
       <c r="O66" s="28" t="n">
-        <v>0.543418</v>
+        <v>0.6248320000000001</v>
       </c>
       <c r="P66" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q66" s="28" t="n">
-        <v>-0.09687</v>
+        <v>0.024832</v>
       </c>
       <c r="R66" s="26" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="S66" s="29" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="T66" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="U66" s="24" t="inlineStr">
@@ -20502,7 +20714,7 @@
       <c r="AD66" s="24" t="n"/>
       <c r="AE66" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.09-5.16; raw selected-side p=0.5661, calibrated p=0.5434.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.74-4.57; raw selected-side p=0.6832, calibrated p=0.6248.</t>
         </is>
       </c>
       <c r="AF66" s="31" t="inlineStr">
@@ -20543,32 +20755,32 @@
       </c>
       <c r="AP66" s="24" t="inlineStr">
         <is>
-          <t>mlb-sd</t>
+          <t>mlb-stl</t>
         </is>
       </c>
       <c r="AQ66" s="24" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="AR66" s="24" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="AS66" s="24" t="inlineStr">
         <is>
-          <t>mlb-ari</t>
+          <t>mlb-nyy</t>
         </is>
       </c>
       <c r="AT66" s="24" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="AU66" s="24" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="AV66" s="24" t="n"/>
@@ -20586,7 +20798,7 @@
       </c>
       <c r="BA66" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BB66" s="24" t="inlineStr">
@@ -20596,12 +20808,12 @@
       </c>
       <c r="BC66" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v2</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="BD66" s="24" t="inlineStr">
         <is>
-          <t>8360b122264b796b0fb193095cfe4506c7e064e5f3f8c0a659aec41efd08dd25</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BE66" s="24" t="inlineStr">
@@ -20621,7 +20833,7 @@
       </c>
       <c r="BH66" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T04:36:16.771749Z</t>
         </is>
       </c>
       <c r="BI66" s="24" t="inlineStr">
@@ -20633,16 +20845,16 @@
         <v>1.5</v>
       </c>
       <c r="BK66" s="26" t="n">
-        <v>-178</v>
+        <v>-150</v>
       </c>
       <c r="BL66" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.666667</v>
       </c>
       <c r="BM66" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.6</v>
       </c>
       <c r="BN66" s="28" t="n">
-        <v>0.636816</v>
+        <v>0.597015</v>
       </c>
       <c r="BO66" s="28" t="n"/>
       <c r="BP66" s="25" t="n"/>
@@ -20676,29 +20888,29 @@
       <c r="CR66" s="24" t="n"/>
       <c r="CS66" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="67" ht="36" customHeight="1">
       <c r="A67" s="24" t="inlineStr">
         <is>
-          <t>df3742dc80134149</t>
+          <t>18af2b518b674034</t>
         </is>
       </c>
       <c r="B67" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T04:36:16.771749Z</t>
         </is>
       </c>
       <c r="C67" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T01:40Z</t>
+          <t>2026-08-05T23:05Z</t>
         </is>
       </c>
       <c r="D67" s="24" t="inlineStr">
         <is>
-          <t>401816398</t>
+          <t>401816404</t>
         </is>
       </c>
       <c r="E67" s="24" t="inlineStr">
@@ -20708,12 +20920,12 @@
       </c>
       <c r="F67" s="24" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="G67" s="24" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="H67" s="24" t="inlineStr">
@@ -20735,32 +20947,32 @@
         </is>
       </c>
       <c r="L67" s="26" t="n">
-        <v>-125</v>
+        <v>-111</v>
       </c>
       <c r="M67" s="27" t="n">
-        <v>1.8</v>
+        <v>1.900901</v>
       </c>
       <c r="N67" s="28" t="n">
-        <v>0.555556</v>
+        <v>0.526066</v>
       </c>
       <c r="O67" s="28" t="n">
-        <v>0.520781</v>
+        <v>0.516866</v>
       </c>
       <c r="P67" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q67" s="28" t="n">
-        <v>-0.034775</v>
+        <v>-0.0092</v>
       </c>
       <c r="R67" s="26" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="S67" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T67" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="U67" s="24" t="inlineStr">
@@ -20779,7 +20991,7 @@
       <c r="AD67" s="24" t="n"/>
       <c r="AE67" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.09-5.16; raw selected-side p=0.5375, calibrated p=0.5208.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.74-4.57; raw selected-side p=0.5445, calibrated p=0.5169.</t>
         </is>
       </c>
       <c r="AF67" s="31" t="inlineStr">
@@ -20820,32 +21032,32 @@
       </c>
       <c r="AP67" s="24" t="inlineStr">
         <is>
-          <t>mlb-sd</t>
+          <t>mlb-stl</t>
         </is>
       </c>
       <c r="AQ67" s="24" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="AR67" s="24" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="AS67" s="24" t="inlineStr">
         <is>
-          <t>mlb-ari</t>
+          <t>mlb-nyy</t>
         </is>
       </c>
       <c r="AT67" s="24" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="AU67" s="24" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="AV67" s="24" t="n"/>
@@ -20863,7 +21075,7 @@
       </c>
       <c r="BA67" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BB67" s="24" t="inlineStr">
@@ -20873,12 +21085,12 @@
       </c>
       <c r="BC67" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v2</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="BD67" s="24" t="inlineStr">
         <is>
-          <t>433578016242b27f9c1c7132cc6b5a2bcc7dd1b0234590c12a944455a88e71bd</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BE67" s="24" t="inlineStr">
@@ -20898,7 +21110,7 @@
       </c>
       <c r="BH67" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:25:15.642219Z</t>
+          <t>2026-08-05T04:36:16.771749Z</t>
         </is>
       </c>
       <c r="BI67" s="24" t="inlineStr">
@@ -20910,16 +21122,16 @@
         <v>8.5</v>
       </c>
       <c r="BK67" s="26" t="n">
-        <v>-125</v>
+        <v>-111</v>
       </c>
       <c r="BL67" s="27" t="n">
-        <v>1.8</v>
+        <v>1.900901</v>
       </c>
       <c r="BM67" s="28" t="n">
-        <v>0.555556</v>
+        <v>0.526066</v>
       </c>
       <c r="BN67" s="28" t="n">
-        <v>0.552239</v>
+        <v>0.522388</v>
       </c>
       <c r="BO67" s="28" t="n"/>
       <c r="BP67" s="25" t="n"/>
@@ -20957,6 +21169,3330 @@
         </is>
       </c>
     </row>
+    <row r="68" ht="36" customHeight="1">
+      <c r="A68" s="24" t="inlineStr">
+        <is>
+          <t>3b3e8899e7544707</t>
+        </is>
+      </c>
+      <c r="B68" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:16.771749Z</t>
+        </is>
+      </c>
+      <c r="C68" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T23:10Z</t>
+        </is>
+      </c>
+      <c r="D68" s="24" t="inlineStr">
+        <is>
+          <t>401816401</t>
+        </is>
+      </c>
+      <c r="E68" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F68" s="24" t="inlineStr">
+        <is>
+          <t>Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="G68" s="24" t="inlineStr">
+        <is>
+          <t>Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="H68" s="24" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="I68" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J68" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K68" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L68" s="26" t="n">
+        <v>-182</v>
+      </c>
+      <c r="M68" s="27" t="n">
+        <v>1.549451</v>
+      </c>
+      <c r="N68" s="28" t="n">
+        <v>0.64539</v>
+      </c>
+      <c r="O68" s="28" t="n">
+        <v>0.6332140000000001</v>
+      </c>
+      <c r="P68" s="28" t="n">
+        <v>0.042131</v>
+      </c>
+      <c r="Q68" s="28" t="n">
+        <v>-0.012176</v>
+      </c>
+      <c r="R68" s="26" t="n">
+        <v>20</v>
+      </c>
+      <c r="S68" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T68" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v3</t>
+        </is>
+      </c>
+      <c r="U68" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V68" s="24" t="n"/>
+      <c r="W68" s="26" t="n"/>
+      <c r="X68" s="26" t="n"/>
+      <c r="Y68" s="25" t="n"/>
+      <c r="Z68" s="26" t="n"/>
+      <c r="AA68" s="28" t="n"/>
+      <c r="AB68" s="28" t="n"/>
+      <c r="AC68" s="30" t="n"/>
+      <c r="AD68" s="24" t="n"/>
+      <c r="AE68" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Margin: Trend Engine projected 4.13-3.98; raw selected-side p=0.6955, calibrated p=0.6332.</t>
+        </is>
+      </c>
+      <c r="AF68" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG68" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH68" s="24" t="n"/>
+      <c r="AI68" s="31" t="n"/>
+      <c r="AJ68" s="31" t="n"/>
+      <c r="AK68" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL68" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM68" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN68" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO68" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP68" s="24" t="inlineStr">
+        <is>
+          <t>mlb-cws</t>
+        </is>
+      </c>
+      <c r="AQ68" s="24" t="inlineStr">
+        <is>
+          <t>Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="AR68" s="24" t="inlineStr">
+        <is>
+          <t>Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="AS68" s="24" t="inlineStr">
+        <is>
+          <t>mlb-bos</t>
+        </is>
+      </c>
+      <c r="AT68" s="24" t="inlineStr">
+        <is>
+          <t>Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="AU68" s="24" t="inlineStr">
+        <is>
+          <t>Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="AV68" s="24" t="n"/>
+      <c r="AW68" s="24" t="n"/>
+      <c r="AX68" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY68" s="24" t="n"/>
+      <c r="AZ68" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA68" s="24" t="inlineStr">
+        <is>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
+        </is>
+      </c>
+      <c r="BB68" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC68" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v3</t>
+        </is>
+      </c>
+      <c r="BD68" s="24" t="inlineStr">
+        <is>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
+        </is>
+      </c>
+      <c r="BE68" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF68" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG68" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH68" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:16.771749Z</t>
+        </is>
+      </c>
+      <c r="BI68" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ68" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK68" s="26" t="n">
+        <v>-182</v>
+      </c>
+      <c r="BL68" s="27" t="n">
+        <v>1.549451</v>
+      </c>
+      <c r="BM68" s="28" t="n">
+        <v>0.64539</v>
+      </c>
+      <c r="BN68" s="28" t="n">
+        <v>0.641791</v>
+      </c>
+      <c r="BO68" s="28" t="n"/>
+      <c r="BP68" s="25" t="n"/>
+      <c r="BQ68" s="27" t="n"/>
+      <c r="BR68" s="28" t="n"/>
+      <c r="BS68" s="28" t="n"/>
+      <c r="BT68" s="28" t="n"/>
+      <c r="BU68" s="25" t="n"/>
+      <c r="BV68" s="29" t="n"/>
+      <c r="BW68" s="24" t="n"/>
+      <c r="BX68" s="30" t="n"/>
+      <c r="BY68" s="27" t="n"/>
+      <c r="BZ68" s="24" t="n"/>
+      <c r="CA68" s="31" t="n"/>
+      <c r="CB68" s="24" t="n"/>
+      <c r="CC68" s="24" t="n"/>
+      <c r="CD68" s="24" t="n"/>
+      <c r="CE68" s="24" t="n"/>
+      <c r="CF68" s="24" t="n"/>
+      <c r="CG68" s="24" t="n"/>
+      <c r="CH68" s="24" t="n"/>
+      <c r="CI68" s="24" t="n"/>
+      <c r="CJ68" s="24" t="n"/>
+      <c r="CK68" s="24" t="n"/>
+      <c r="CL68" s="24" t="n"/>
+      <c r="CM68" s="24" t="n"/>
+      <c r="CN68" s="24" t="n"/>
+      <c r="CO68" s="24" t="n"/>
+      <c r="CP68" s="24" t="n"/>
+      <c r="CQ68" s="24" t="n"/>
+      <c r="CR68" s="24" t="n"/>
+      <c r="CS68" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="36" customHeight="1">
+      <c r="A69" s="24" t="inlineStr">
+        <is>
+          <t>ceed6ea7167640c4</t>
+        </is>
+      </c>
+      <c r="B69" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:16.771749Z</t>
+        </is>
+      </c>
+      <c r="C69" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T23:10Z</t>
+        </is>
+      </c>
+      <c r="D69" s="24" t="inlineStr">
+        <is>
+          <t>401816401</t>
+        </is>
+      </c>
+      <c r="E69" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F69" s="24" t="inlineStr">
+        <is>
+          <t>Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="G69" s="24" t="inlineStr">
+        <is>
+          <t>Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="H69" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I69" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J69" s="25" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K69" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L69" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="M69" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N69" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O69" s="28" t="n">
+        <v>0.52325</v>
+      </c>
+      <c r="P69" s="28" t="n">
+        <v>0.042131</v>
+      </c>
+      <c r="Q69" s="28" t="n">
+        <v>0.02325</v>
+      </c>
+      <c r="R69" s="26" t="n">
+        <v>38</v>
+      </c>
+      <c r="S69" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T69" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v3</t>
+        </is>
+      </c>
+      <c r="U69" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V69" s="24" t="n"/>
+      <c r="W69" s="26" t="n"/>
+      <c r="X69" s="26" t="n"/>
+      <c r="Y69" s="25" t="n"/>
+      <c r="Z69" s="26" t="n"/>
+      <c r="AA69" s="28" t="n"/>
+      <c r="AB69" s="28" t="n"/>
+      <c r="AC69" s="30" t="n"/>
+      <c r="AD69" s="24" t="n"/>
+      <c r="AE69" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Totals: Trend Engine projected 4.13-3.98; raw selected-side p=0.5703, calibrated p=0.5233.</t>
+        </is>
+      </c>
+      <c r="AF69" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG69" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH69" s="24" t="n"/>
+      <c r="AI69" s="31" t="n"/>
+      <c r="AJ69" s="31" t="n"/>
+      <c r="AK69" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL69" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM69" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN69" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO69" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP69" s="24" t="inlineStr">
+        <is>
+          <t>mlb-cws</t>
+        </is>
+      </c>
+      <c r="AQ69" s="24" t="inlineStr">
+        <is>
+          <t>Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="AR69" s="24" t="inlineStr">
+        <is>
+          <t>Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="AS69" s="24" t="inlineStr">
+        <is>
+          <t>mlb-bos</t>
+        </is>
+      </c>
+      <c r="AT69" s="24" t="inlineStr">
+        <is>
+          <t>Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="AU69" s="24" t="inlineStr">
+        <is>
+          <t>Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="AV69" s="24" t="n"/>
+      <c r="AW69" s="24" t="n"/>
+      <c r="AX69" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY69" s="24" t="n"/>
+      <c r="AZ69" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA69" s="24" t="inlineStr">
+        <is>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
+        </is>
+      </c>
+      <c r="BB69" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC69" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v3</t>
+        </is>
+      </c>
+      <c r="BD69" s="24" t="inlineStr">
+        <is>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
+        </is>
+      </c>
+      <c r="BE69" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF69" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG69" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH69" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:16.771749Z</t>
+        </is>
+      </c>
+      <c r="BI69" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ69" s="25" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BK69" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="BL69" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM69" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN69" s="28" t="n">
+        <v>0.497512</v>
+      </c>
+      <c r="BO69" s="28" t="n"/>
+      <c r="BP69" s="25" t="n"/>
+      <c r="BQ69" s="27" t="n"/>
+      <c r="BR69" s="28" t="n"/>
+      <c r="BS69" s="28" t="n"/>
+      <c r="BT69" s="28" t="n"/>
+      <c r="BU69" s="25" t="n"/>
+      <c r="BV69" s="29" t="n"/>
+      <c r="BW69" s="24" t="n"/>
+      <c r="BX69" s="30" t="n"/>
+      <c r="BY69" s="27" t="n"/>
+      <c r="BZ69" s="24" t="n"/>
+      <c r="CA69" s="31" t="n"/>
+      <c r="CB69" s="24" t="n"/>
+      <c r="CC69" s="24" t="n"/>
+      <c r="CD69" s="24" t="n"/>
+      <c r="CE69" s="24" t="n"/>
+      <c r="CF69" s="24" t="n"/>
+      <c r="CG69" s="24" t="n"/>
+      <c r="CH69" s="24" t="n"/>
+      <c r="CI69" s="24" t="n"/>
+      <c r="CJ69" s="24" t="n"/>
+      <c r="CK69" s="24" t="n"/>
+      <c r="CL69" s="24" t="n"/>
+      <c r="CM69" s="24" t="n"/>
+      <c r="CN69" s="24" t="n"/>
+      <c r="CO69" s="24" t="n"/>
+      <c r="CP69" s="24" t="n"/>
+      <c r="CQ69" s="24" t="n"/>
+      <c r="CR69" s="24" t="n"/>
+      <c r="CS69" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="36" customHeight="1">
+      <c r="A70" s="24" t="inlineStr">
+        <is>
+          <t>f9a5065e12f94a1e</t>
+        </is>
+      </c>
+      <c r="B70" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:16.771749Z</t>
+        </is>
+      </c>
+      <c r="C70" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T23:15Z</t>
+        </is>
+      </c>
+      <c r="D70" s="24" t="inlineStr">
+        <is>
+          <t>401816402</t>
+        </is>
+      </c>
+      <c r="E70" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F70" s="24" t="inlineStr">
+        <is>
+          <t>Miami Marlins</t>
+        </is>
+      </c>
+      <c r="G70" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Braves</t>
+        </is>
+      </c>
+      <c r="H70" s="24" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="I70" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J70" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K70" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L70" s="26" t="n">
+        <v>-174</v>
+      </c>
+      <c r="M70" s="27" t="n">
+        <v>1.574713</v>
+      </c>
+      <c r="N70" s="28" t="n">
+        <v>0.635036</v>
+      </c>
+      <c r="O70" s="28" t="n">
+        <v>0.639346</v>
+      </c>
+      <c r="P70" s="28" t="n">
+        <v>0.042131</v>
+      </c>
+      <c r="Q70" s="28" t="n">
+        <v>0.00431</v>
+      </c>
+      <c r="R70" s="26" t="n">
+        <v>28</v>
+      </c>
+      <c r="S70" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T70" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v3</t>
+        </is>
+      </c>
+      <c r="U70" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V70" s="24" t="n"/>
+      <c r="W70" s="26" t="n"/>
+      <c r="X70" s="26" t="n"/>
+      <c r="Y70" s="25" t="n"/>
+      <c r="Z70" s="26" t="n"/>
+      <c r="AA70" s="28" t="n"/>
+      <c r="AB70" s="28" t="n"/>
+      <c r="AC70" s="30" t="n"/>
+      <c r="AD70" s="24" t="n"/>
+      <c r="AE70" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Margin: Trend Engine projected 4.38-4.11; raw selected-side p=0.7045, calibrated p=0.6393.</t>
+        </is>
+      </c>
+      <c r="AF70" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG70" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH70" s="24" t="n"/>
+      <c r="AI70" s="31" t="n"/>
+      <c r="AJ70" s="31" t="n"/>
+      <c r="AK70" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL70" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM70" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN70" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO70" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP70" s="24" t="inlineStr">
+        <is>
+          <t>mlb-mia</t>
+        </is>
+      </c>
+      <c r="AQ70" s="24" t="inlineStr">
+        <is>
+          <t>Miami Marlins</t>
+        </is>
+      </c>
+      <c r="AR70" s="24" t="inlineStr">
+        <is>
+          <t>Miami Marlins</t>
+        </is>
+      </c>
+      <c r="AS70" s="24" t="inlineStr">
+        <is>
+          <t>mlb-atl</t>
+        </is>
+      </c>
+      <c r="AT70" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Braves</t>
+        </is>
+      </c>
+      <c r="AU70" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Braves</t>
+        </is>
+      </c>
+      <c r="AV70" s="24" t="n"/>
+      <c r="AW70" s="24" t="n"/>
+      <c r="AX70" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY70" s="24" t="n"/>
+      <c r="AZ70" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA70" s="24" t="inlineStr">
+        <is>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
+        </is>
+      </c>
+      <c r="BB70" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC70" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v3</t>
+        </is>
+      </c>
+      <c r="BD70" s="24" t="inlineStr">
+        <is>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
+        </is>
+      </c>
+      <c r="BE70" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF70" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG70" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH70" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:16.771749Z</t>
+        </is>
+      </c>
+      <c r="BI70" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ70" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK70" s="26" t="n">
+        <v>-174</v>
+      </c>
+      <c r="BL70" s="27" t="n">
+        <v>1.574713</v>
+      </c>
+      <c r="BM70" s="28" t="n">
+        <v>0.635036</v>
+      </c>
+      <c r="BN70" s="28" t="n">
+        <v>0.631841</v>
+      </c>
+      <c r="BO70" s="28" t="n"/>
+      <c r="BP70" s="25" t="n"/>
+      <c r="BQ70" s="27" t="n"/>
+      <c r="BR70" s="28" t="n"/>
+      <c r="BS70" s="28" t="n"/>
+      <c r="BT70" s="28" t="n"/>
+      <c r="BU70" s="25" t="n"/>
+      <c r="BV70" s="29" t="n"/>
+      <c r="BW70" s="24" t="n"/>
+      <c r="BX70" s="30" t="n"/>
+      <c r="BY70" s="27" t="n"/>
+      <c r="BZ70" s="24" t="n"/>
+      <c r="CA70" s="31" t="n"/>
+      <c r="CB70" s="24" t="n"/>
+      <c r="CC70" s="24" t="n"/>
+      <c r="CD70" s="24" t="n"/>
+      <c r="CE70" s="24" t="n"/>
+      <c r="CF70" s="24" t="n"/>
+      <c r="CG70" s="24" t="n"/>
+      <c r="CH70" s="24" t="n"/>
+      <c r="CI70" s="24" t="n"/>
+      <c r="CJ70" s="24" t="n"/>
+      <c r="CK70" s="24" t="n"/>
+      <c r="CL70" s="24" t="n"/>
+      <c r="CM70" s="24" t="n"/>
+      <c r="CN70" s="24" t="n"/>
+      <c r="CO70" s="24" t="n"/>
+      <c r="CP70" s="24" t="n"/>
+      <c r="CQ70" s="24" t="n"/>
+      <c r="CR70" s="24" t="n"/>
+      <c r="CS70" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="36" customHeight="1">
+      <c r="A71" s="24" t="inlineStr">
+        <is>
+          <t>9351fff5823b49cd</t>
+        </is>
+      </c>
+      <c r="B71" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:16.771749Z</t>
+        </is>
+      </c>
+      <c r="C71" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T23:15Z</t>
+        </is>
+      </c>
+      <c r="D71" s="24" t="inlineStr">
+        <is>
+          <t>401816402</t>
+        </is>
+      </c>
+      <c r="E71" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F71" s="24" t="inlineStr">
+        <is>
+          <t>Miami Marlins</t>
+        </is>
+      </c>
+      <c r="G71" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Braves</t>
+        </is>
+      </c>
+      <c r="H71" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I71" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J71" s="25" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K71" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L71" s="26" t="n">
+        <v>111</v>
+      </c>
+      <c r="M71" s="27" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="N71" s="28" t="n">
+        <v>0.473934</v>
+      </c>
+      <c r="O71" s="28" t="n">
+        <v>0.51201</v>
+      </c>
+      <c r="P71" s="28" t="n">
+        <v>0.042131</v>
+      </c>
+      <c r="Q71" s="28" t="n">
+        <v>0.038076</v>
+      </c>
+      <c r="R71" s="26" t="n">
+        <v>44</v>
+      </c>
+      <c r="S71" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T71" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v3</t>
+        </is>
+      </c>
+      <c r="U71" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V71" s="24" t="n"/>
+      <c r="W71" s="26" t="n"/>
+      <c r="X71" s="26" t="n"/>
+      <c r="Y71" s="25" t="n"/>
+      <c r="Z71" s="26" t="n"/>
+      <c r="AA71" s="28" t="n"/>
+      <c r="AB71" s="28" t="n"/>
+      <c r="AC71" s="30" t="n"/>
+      <c r="AD71" s="24" t="n"/>
+      <c r="AE71" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Totals: Trend Engine projected 4.38-4.11; raw selected-side p=0.5250, calibrated p=0.5120.</t>
+        </is>
+      </c>
+      <c r="AF71" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG71" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH71" s="24" t="n"/>
+      <c r="AI71" s="31" t="n"/>
+      <c r="AJ71" s="31" t="n"/>
+      <c r="AK71" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL71" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM71" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN71" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO71" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP71" s="24" t="inlineStr">
+        <is>
+          <t>mlb-mia</t>
+        </is>
+      </c>
+      <c r="AQ71" s="24" t="inlineStr">
+        <is>
+          <t>Miami Marlins</t>
+        </is>
+      </c>
+      <c r="AR71" s="24" t="inlineStr">
+        <is>
+          <t>Miami Marlins</t>
+        </is>
+      </c>
+      <c r="AS71" s="24" t="inlineStr">
+        <is>
+          <t>mlb-atl</t>
+        </is>
+      </c>
+      <c r="AT71" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Braves</t>
+        </is>
+      </c>
+      <c r="AU71" s="24" t="inlineStr">
+        <is>
+          <t>Atlanta Braves</t>
+        </is>
+      </c>
+      <c r="AV71" s="24" t="n"/>
+      <c r="AW71" s="24" t="n"/>
+      <c r="AX71" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY71" s="24" t="n"/>
+      <c r="AZ71" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA71" s="24" t="inlineStr">
+        <is>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
+        </is>
+      </c>
+      <c r="BB71" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC71" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v3</t>
+        </is>
+      </c>
+      <c r="BD71" s="24" t="inlineStr">
+        <is>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
+        </is>
+      </c>
+      <c r="BE71" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF71" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG71" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH71" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:16.771749Z</t>
+        </is>
+      </c>
+      <c r="BI71" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ71" s="25" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BK71" s="26" t="n">
+        <v>111</v>
+      </c>
+      <c r="BL71" s="27" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BM71" s="28" t="n">
+        <v>0.473934</v>
+      </c>
+      <c r="BN71" s="28" t="n">
+        <v>0.472637</v>
+      </c>
+      <c r="BO71" s="28" t="n"/>
+      <c r="BP71" s="25" t="n"/>
+      <c r="BQ71" s="27" t="n"/>
+      <c r="BR71" s="28" t="n"/>
+      <c r="BS71" s="28" t="n"/>
+      <c r="BT71" s="28" t="n"/>
+      <c r="BU71" s="25" t="n"/>
+      <c r="BV71" s="29" t="n"/>
+      <c r="BW71" s="24" t="n"/>
+      <c r="BX71" s="30" t="n"/>
+      <c r="BY71" s="27" t="n"/>
+      <c r="BZ71" s="24" t="n"/>
+      <c r="CA71" s="31" t="n"/>
+      <c r="CB71" s="24" t="n"/>
+      <c r="CC71" s="24" t="n"/>
+      <c r="CD71" s="24" t="n"/>
+      <c r="CE71" s="24" t="n"/>
+      <c r="CF71" s="24" t="n"/>
+      <c r="CG71" s="24" t="n"/>
+      <c r="CH71" s="24" t="n"/>
+      <c r="CI71" s="24" t="n"/>
+      <c r="CJ71" s="24" t="n"/>
+      <c r="CK71" s="24" t="n"/>
+      <c r="CL71" s="24" t="n"/>
+      <c r="CM71" s="24" t="n"/>
+      <c r="CN71" s="24" t="n"/>
+      <c r="CO71" s="24" t="n"/>
+      <c r="CP71" s="24" t="n"/>
+      <c r="CQ71" s="24" t="n"/>
+      <c r="CR71" s="24" t="n"/>
+      <c r="CS71" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="36" customHeight="1">
+      <c r="A72" s="24" t="inlineStr">
+        <is>
+          <t>113b6926d0154d9c</t>
+        </is>
+      </c>
+      <c r="B72" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:16.771749Z</t>
+        </is>
+      </c>
+      <c r="C72" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T23:30Z</t>
+        </is>
+      </c>
+      <c r="D72" s="24" t="inlineStr">
+        <is>
+          <t>401816408</t>
+        </is>
+      </c>
+      <c r="E72" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F72" s="24" t="inlineStr">
+        <is>
+          <t>Pittsburgh Pirates</t>
+        </is>
+      </c>
+      <c r="G72" s="24" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="H72" s="24" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="I72" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J72" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K72" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L72" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="M72" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="N72" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="O72" s="28" t="n">
+        <v>0.590354</v>
+      </c>
+      <c r="P72" s="28" t="n">
+        <v>0.042131</v>
+      </c>
+      <c r="Q72" s="28" t="n">
+        <v>-0.049934</v>
+      </c>
+      <c r="R72" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="S72" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T72" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v3</t>
+        </is>
+      </c>
+      <c r="U72" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V72" s="24" t="n"/>
+      <c r="W72" s="26" t="n"/>
+      <c r="X72" s="26" t="n"/>
+      <c r="Y72" s="25" t="n"/>
+      <c r="Z72" s="26" t="n"/>
+      <c r="AA72" s="28" t="n"/>
+      <c r="AB72" s="28" t="n"/>
+      <c r="AC72" s="30" t="n"/>
+      <c r="AD72" s="24" t="n"/>
+      <c r="AE72" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Margin: Trend Engine projected 4.27-4.68; raw selected-side p=0.6326, calibrated p=0.5904.</t>
+        </is>
+      </c>
+      <c r="AF72" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG72" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH72" s="24" t="n"/>
+      <c r="AI72" s="31" t="n"/>
+      <c r="AJ72" s="31" t="n"/>
+      <c r="AK72" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL72" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM72" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN72" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO72" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP72" s="24" t="inlineStr">
+        <is>
+          <t>mlb-pit</t>
+        </is>
+      </c>
+      <c r="AQ72" s="24" t="inlineStr">
+        <is>
+          <t>Pittsburgh Pirates</t>
+        </is>
+      </c>
+      <c r="AR72" s="24" t="inlineStr">
+        <is>
+          <t>Pittsburgh Pirates</t>
+        </is>
+      </c>
+      <c r="AS72" s="24" t="inlineStr">
+        <is>
+          <t>mlb-mil</t>
+        </is>
+      </c>
+      <c r="AT72" s="24" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="AU72" s="24" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="AV72" s="24" t="n"/>
+      <c r="AW72" s="24" t="n"/>
+      <c r="AX72" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY72" s="24" t="n"/>
+      <c r="AZ72" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA72" s="24" t="inlineStr">
+        <is>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
+        </is>
+      </c>
+      <c r="BB72" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC72" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v3</t>
+        </is>
+      </c>
+      <c r="BD72" s="24" t="inlineStr">
+        <is>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
+        </is>
+      </c>
+      <c r="BE72" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF72" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG72" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH72" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:16.771749Z</t>
+        </is>
+      </c>
+      <c r="BI72" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ72" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK72" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="BL72" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="BM72" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="BN72" s="28" t="n">
+        <v>0.636816</v>
+      </c>
+      <c r="BO72" s="28" t="n"/>
+      <c r="BP72" s="25" t="n"/>
+      <c r="BQ72" s="27" t="n"/>
+      <c r="BR72" s="28" t="n"/>
+      <c r="BS72" s="28" t="n"/>
+      <c r="BT72" s="28" t="n"/>
+      <c r="BU72" s="25" t="n"/>
+      <c r="BV72" s="29" t="n"/>
+      <c r="BW72" s="24" t="n"/>
+      <c r="BX72" s="30" t="n"/>
+      <c r="BY72" s="27" t="n"/>
+      <c r="BZ72" s="24" t="n"/>
+      <c r="CA72" s="31" t="n"/>
+      <c r="CB72" s="24" t="n"/>
+      <c r="CC72" s="24" t="n"/>
+      <c r="CD72" s="24" t="n"/>
+      <c r="CE72" s="24" t="n"/>
+      <c r="CF72" s="24" t="n"/>
+      <c r="CG72" s="24" t="n"/>
+      <c r="CH72" s="24" t="n"/>
+      <c r="CI72" s="24" t="n"/>
+      <c r="CJ72" s="24" t="n"/>
+      <c r="CK72" s="24" t="n"/>
+      <c r="CL72" s="24" t="n"/>
+      <c r="CM72" s="24" t="n"/>
+      <c r="CN72" s="24" t="n"/>
+      <c r="CO72" s="24" t="n"/>
+      <c r="CP72" s="24" t="n"/>
+      <c r="CQ72" s="24" t="n"/>
+      <c r="CR72" s="24" t="n"/>
+      <c r="CS72" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="36" customHeight="1">
+      <c r="A73" s="24" t="inlineStr">
+        <is>
+          <t>f39275040c124d2d</t>
+        </is>
+      </c>
+      <c r="B73" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:16.771749Z</t>
+        </is>
+      </c>
+      <c r="C73" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T23:30Z</t>
+        </is>
+      </c>
+      <c r="D73" s="24" t="inlineStr">
+        <is>
+          <t>401816408</t>
+        </is>
+      </c>
+      <c r="E73" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F73" s="24" t="inlineStr">
+        <is>
+          <t>Pittsburgh Pirates</t>
+        </is>
+      </c>
+      <c r="G73" s="24" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="H73" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I73" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J73" s="25" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="K73" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L73" s="26" t="n">
+        <v>111</v>
+      </c>
+      <c r="M73" s="27" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="N73" s="28" t="n">
+        <v>0.473934</v>
+      </c>
+      <c r="O73" s="28" t="n">
+        <v>0.527448</v>
+      </c>
+      <c r="P73" s="28" t="n">
+        <v>0.042131</v>
+      </c>
+      <c r="Q73" s="28" t="n">
+        <v>0.053514</v>
+      </c>
+      <c r="R73" s="26" t="n">
+        <v>52</v>
+      </c>
+      <c r="S73" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T73" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v3</t>
+        </is>
+      </c>
+      <c r="U73" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V73" s="24" t="n"/>
+      <c r="W73" s="26" t="n"/>
+      <c r="X73" s="26" t="n"/>
+      <c r="Y73" s="25" t="n"/>
+      <c r="Z73" s="26" t="n"/>
+      <c r="AA73" s="28" t="n"/>
+      <c r="AB73" s="28" t="n"/>
+      <c r="AC73" s="30" t="n"/>
+      <c r="AD73" s="24" t="n"/>
+      <c r="AE73" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Totals: Trend Engine projected 4.27-4.68; raw selected-side p=0.5871, calibrated p=0.5274.</t>
+        </is>
+      </c>
+      <c r="AF73" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG73" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH73" s="24" t="n"/>
+      <c r="AI73" s="31" t="n"/>
+      <c r="AJ73" s="31" t="n"/>
+      <c r="AK73" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL73" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM73" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN73" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO73" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP73" s="24" t="inlineStr">
+        <is>
+          <t>mlb-pit</t>
+        </is>
+      </c>
+      <c r="AQ73" s="24" t="inlineStr">
+        <is>
+          <t>Pittsburgh Pirates</t>
+        </is>
+      </c>
+      <c r="AR73" s="24" t="inlineStr">
+        <is>
+          <t>Pittsburgh Pirates</t>
+        </is>
+      </c>
+      <c r="AS73" s="24" t="inlineStr">
+        <is>
+          <t>mlb-mil</t>
+        </is>
+      </c>
+      <c r="AT73" s="24" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="AU73" s="24" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="AV73" s="24" t="n"/>
+      <c r="AW73" s="24" t="n"/>
+      <c r="AX73" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY73" s="24" t="n"/>
+      <c r="AZ73" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA73" s="24" t="inlineStr">
+        <is>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
+        </is>
+      </c>
+      <c r="BB73" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC73" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v3</t>
+        </is>
+      </c>
+      <c r="BD73" s="24" t="inlineStr">
+        <is>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
+        </is>
+      </c>
+      <c r="BE73" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF73" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG73" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH73" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:16.771749Z</t>
+        </is>
+      </c>
+      <c r="BI73" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ73" s="25" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BK73" s="26" t="n">
+        <v>111</v>
+      </c>
+      <c r="BL73" s="27" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BM73" s="28" t="n">
+        <v>0.473934</v>
+      </c>
+      <c r="BN73" s="28" t="n">
+        <v>0.472637</v>
+      </c>
+      <c r="BO73" s="28" t="n"/>
+      <c r="BP73" s="25" t="n"/>
+      <c r="BQ73" s="27" t="n"/>
+      <c r="BR73" s="28" t="n"/>
+      <c r="BS73" s="28" t="n"/>
+      <c r="BT73" s="28" t="n"/>
+      <c r="BU73" s="25" t="n"/>
+      <c r="BV73" s="29" t="n"/>
+      <c r="BW73" s="24" t="n"/>
+      <c r="BX73" s="30" t="n"/>
+      <c r="BY73" s="27" t="n"/>
+      <c r="BZ73" s="24" t="n"/>
+      <c r="CA73" s="31" t="n"/>
+      <c r="CB73" s="24" t="n"/>
+      <c r="CC73" s="24" t="n"/>
+      <c r="CD73" s="24" t="n"/>
+      <c r="CE73" s="24" t="n"/>
+      <c r="CF73" s="24" t="n"/>
+      <c r="CG73" s="24" t="n"/>
+      <c r="CH73" s="24" t="n"/>
+      <c r="CI73" s="24" t="n"/>
+      <c r="CJ73" s="24" t="n"/>
+      <c r="CK73" s="24" t="n"/>
+      <c r="CL73" s="24" t="n"/>
+      <c r="CM73" s="24" t="n"/>
+      <c r="CN73" s="24" t="n"/>
+      <c r="CO73" s="24" t="n"/>
+      <c r="CP73" s="24" t="n"/>
+      <c r="CQ73" s="24" t="n"/>
+      <c r="CR73" s="24" t="n"/>
+      <c r="CS73" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="36" customHeight="1">
+      <c r="A74" s="24" t="inlineStr">
+        <is>
+          <t>06679cc9303c40f3</t>
+        </is>
+      </c>
+      <c r="B74" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:16.771749Z</t>
+        </is>
+      </c>
+      <c r="C74" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T23:40Z</t>
+        </is>
+      </c>
+      <c r="D74" s="24" t="inlineStr">
+        <is>
+          <t>401816407</t>
+        </is>
+      </c>
+      <c r="E74" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F74" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="G74" s="24" t="inlineStr">
+        <is>
+          <t>Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="H74" s="24" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="I74" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J74" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K74" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L74" s="26" t="n">
+        <v>-174</v>
+      </c>
+      <c r="M74" s="27" t="n">
+        <v>1.574713</v>
+      </c>
+      <c r="N74" s="28" t="n">
+        <v>0.635036</v>
+      </c>
+      <c r="O74" s="28" t="n">
+        <v>0.647353</v>
+      </c>
+      <c r="P74" s="28" t="n">
+        <v>0.05172</v>
+      </c>
+      <c r="Q74" s="28" t="n">
+        <v>0.012317</v>
+      </c>
+      <c r="R74" s="26" t="n">
+        <v>27</v>
+      </c>
+      <c r="S74" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T74" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v3</t>
+        </is>
+      </c>
+      <c r="U74" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V74" s="24" t="n"/>
+      <c r="W74" s="26" t="n"/>
+      <c r="X74" s="26" t="n"/>
+      <c r="Y74" s="25" t="n"/>
+      <c r="Z74" s="26" t="n"/>
+      <c r="AA74" s="28" t="n"/>
+      <c r="AB74" s="28" t="n"/>
+      <c r="AC74" s="30" t="n"/>
+      <c r="AD74" s="24" t="n"/>
+      <c r="AE74" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Margin: Trend Engine projected 4.58-5.19; raw selected-side p=0.7163, calibrated p=0.6474.</t>
+        </is>
+      </c>
+      <c r="AF74" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG74" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH74" s="24" t="n"/>
+      <c r="AI74" s="31" t="n"/>
+      <c r="AJ74" s="31" t="n"/>
+      <c r="AK74" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL74" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM74" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN74" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO74" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP74" s="24" t="inlineStr">
+        <is>
+          <t>mlb-min</t>
+        </is>
+      </c>
+      <c r="AQ74" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="AR74" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="AS74" s="24" t="inlineStr">
+        <is>
+          <t>mlb-kc</t>
+        </is>
+      </c>
+      <c r="AT74" s="24" t="inlineStr">
+        <is>
+          <t>Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="AU74" s="24" t="inlineStr">
+        <is>
+          <t>Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="AV74" s="24" t="n"/>
+      <c r="AW74" s="24" t="n"/>
+      <c r="AX74" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY74" s="24" t="n"/>
+      <c r="AZ74" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA74" s="24" t="inlineStr">
+        <is>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
+        </is>
+      </c>
+      <c r="BB74" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC74" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v3</t>
+        </is>
+      </c>
+      <c r="BD74" s="24" t="inlineStr">
+        <is>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
+        </is>
+      </c>
+      <c r="BE74" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF74" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG74" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH74" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:16.771749Z</t>
+        </is>
+      </c>
+      <c r="BI74" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ74" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK74" s="26" t="n">
+        <v>-174</v>
+      </c>
+      <c r="BL74" s="27" t="n">
+        <v>1.574713</v>
+      </c>
+      <c r="BM74" s="28" t="n">
+        <v>0.635036</v>
+      </c>
+      <c r="BN74" s="28" t="n">
+        <v>0.631841</v>
+      </c>
+      <c r="BO74" s="28" t="n"/>
+      <c r="BP74" s="25" t="n"/>
+      <c r="BQ74" s="27" t="n"/>
+      <c r="BR74" s="28" t="n"/>
+      <c r="BS74" s="28" t="n"/>
+      <c r="BT74" s="28" t="n"/>
+      <c r="BU74" s="25" t="n"/>
+      <c r="BV74" s="29" t="n"/>
+      <c r="BW74" s="24" t="n"/>
+      <c r="BX74" s="30" t="n"/>
+      <c r="BY74" s="27" t="n"/>
+      <c r="BZ74" s="24" t="n"/>
+      <c r="CA74" s="31" t="n"/>
+      <c r="CB74" s="24" t="n"/>
+      <c r="CC74" s="24" t="n"/>
+      <c r="CD74" s="24" t="n"/>
+      <c r="CE74" s="24" t="n"/>
+      <c r="CF74" s="24" t="n"/>
+      <c r="CG74" s="24" t="n"/>
+      <c r="CH74" s="24" t="n"/>
+      <c r="CI74" s="24" t="n"/>
+      <c r="CJ74" s="24" t="n"/>
+      <c r="CK74" s="24" t="n"/>
+      <c r="CL74" s="24" t="n"/>
+      <c r="CM74" s="24" t="n"/>
+      <c r="CN74" s="24" t="n"/>
+      <c r="CO74" s="24" t="n"/>
+      <c r="CP74" s="24" t="n"/>
+      <c r="CQ74" s="24" t="n"/>
+      <c r="CR74" s="24" t="n"/>
+      <c r="CS74" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="36" customHeight="1">
+      <c r="A75" s="24" t="inlineStr">
+        <is>
+          <t>c3bbd2f2ca3142dd</t>
+        </is>
+      </c>
+      <c r="B75" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:16.771749Z</t>
+        </is>
+      </c>
+      <c r="C75" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T23:40Z</t>
+        </is>
+      </c>
+      <c r="D75" s="24" t="inlineStr">
+        <is>
+          <t>401816407</t>
+        </is>
+      </c>
+      <c r="E75" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F75" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="G75" s="24" t="inlineStr">
+        <is>
+          <t>Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="H75" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I75" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J75" s="25" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K75" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L75" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="M75" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="N75" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="O75" s="28" t="n">
+        <v>0.51355</v>
+      </c>
+      <c r="P75" s="28" t="n">
+        <v>0.05172</v>
+      </c>
+      <c r="Q75" s="28" t="n">
+        <v>-0.036</v>
+      </c>
+      <c r="R75" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="S75" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v3</t>
+        </is>
+      </c>
+      <c r="U75" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V75" s="24" t="n"/>
+      <c r="W75" s="26" t="n"/>
+      <c r="X75" s="26" t="n"/>
+      <c r="Y75" s="25" t="n"/>
+      <c r="Z75" s="26" t="n"/>
+      <c r="AA75" s="28" t="n"/>
+      <c r="AB75" s="28" t="n"/>
+      <c r="AC75" s="30" t="n"/>
+      <c r="AD75" s="24" t="n"/>
+      <c r="AE75" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Totals: Trend Engine projected 4.58-5.19; raw selected-side p=0.5312, calibrated p=0.5136.</t>
+        </is>
+      </c>
+      <c r="AF75" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG75" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH75" s="24" t="n"/>
+      <c r="AI75" s="31" t="n"/>
+      <c r="AJ75" s="31" t="n"/>
+      <c r="AK75" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL75" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM75" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN75" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO75" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP75" s="24" t="inlineStr">
+        <is>
+          <t>mlb-min</t>
+        </is>
+      </c>
+      <c r="AQ75" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="AR75" s="24" t="inlineStr">
+        <is>
+          <t>Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="AS75" s="24" t="inlineStr">
+        <is>
+          <t>mlb-kc</t>
+        </is>
+      </c>
+      <c r="AT75" s="24" t="inlineStr">
+        <is>
+          <t>Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="AU75" s="24" t="inlineStr">
+        <is>
+          <t>Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="AV75" s="24" t="n"/>
+      <c r="AW75" s="24" t="n"/>
+      <c r="AX75" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY75" s="24" t="n"/>
+      <c r="AZ75" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA75" s="24" t="inlineStr">
+        <is>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
+        </is>
+      </c>
+      <c r="BB75" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC75" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v3</t>
+        </is>
+      </c>
+      <c r="BD75" s="24" t="inlineStr">
+        <is>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
+        </is>
+      </c>
+      <c r="BE75" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF75" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG75" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH75" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:16.771749Z</t>
+        </is>
+      </c>
+      <c r="BI75" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ75" s="25" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BK75" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="BL75" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="BM75" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="BN75" s="28" t="n">
+        <v>0.547264</v>
+      </c>
+      <c r="BO75" s="28" t="n"/>
+      <c r="BP75" s="25" t="n"/>
+      <c r="BQ75" s="27" t="n"/>
+      <c r="BR75" s="28" t="n"/>
+      <c r="BS75" s="28" t="n"/>
+      <c r="BT75" s="28" t="n"/>
+      <c r="BU75" s="25" t="n"/>
+      <c r="BV75" s="29" t="n"/>
+      <c r="BW75" s="24" t="n"/>
+      <c r="BX75" s="30" t="n"/>
+      <c r="BY75" s="27" t="n"/>
+      <c r="BZ75" s="24" t="n"/>
+      <c r="CA75" s="31" t="n"/>
+      <c r="CB75" s="24" t="n"/>
+      <c r="CC75" s="24" t="n"/>
+      <c r="CD75" s="24" t="n"/>
+      <c r="CE75" s="24" t="n"/>
+      <c r="CF75" s="24" t="n"/>
+      <c r="CG75" s="24" t="n"/>
+      <c r="CH75" s="24" t="n"/>
+      <c r="CI75" s="24" t="n"/>
+      <c r="CJ75" s="24" t="n"/>
+      <c r="CK75" s="24" t="n"/>
+      <c r="CL75" s="24" t="n"/>
+      <c r="CM75" s="24" t="n"/>
+      <c r="CN75" s="24" t="n"/>
+      <c r="CO75" s="24" t="n"/>
+      <c r="CP75" s="24" t="n"/>
+      <c r="CQ75" s="24" t="n"/>
+      <c r="CR75" s="24" t="n"/>
+      <c r="CS75" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="36" customHeight="1">
+      <c r="A76" s="24" t="inlineStr">
+        <is>
+          <t>95193532269c4ab2</t>
+        </is>
+      </c>
+      <c r="B76" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:16.771749Z</t>
+        </is>
+      </c>
+      <c r="C76" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T01:40Z</t>
+        </is>
+      </c>
+      <c r="D76" s="24" t="inlineStr">
+        <is>
+          <t>401816412</t>
+        </is>
+      </c>
+      <c r="E76" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F76" s="24" t="inlineStr">
+        <is>
+          <t>Detroit Tigers</t>
+        </is>
+      </c>
+      <c r="G76" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="H76" s="24" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="I76" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J76" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K76" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L76" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="M76" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="N76" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="O76" s="28" t="n">
+        <v>0.631715</v>
+      </c>
+      <c r="P76" s="28" t="n">
+        <v>0.042131</v>
+      </c>
+      <c r="Q76" s="28" t="n">
+        <v>0.02234</v>
+      </c>
+      <c r="R76" s="26" t="n">
+        <v>37</v>
+      </c>
+      <c r="S76" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T76" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v3</t>
+        </is>
+      </c>
+      <c r="U76" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V76" s="24" t="n"/>
+      <c r="W76" s="26" t="n"/>
+      <c r="X76" s="26" t="n"/>
+      <c r="Y76" s="25" t="n"/>
+      <c r="Z76" s="26" t="n"/>
+      <c r="AA76" s="28" t="n"/>
+      <c r="AB76" s="28" t="n"/>
+      <c r="AC76" s="30" t="n"/>
+      <c r="AD76" s="24" t="n"/>
+      <c r="AE76" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Margin: Trend Engine projected 4.87-4.56; raw selected-side p=0.6933, calibrated p=0.6317.</t>
+        </is>
+      </c>
+      <c r="AF76" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG76" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH76" s="24" t="n"/>
+      <c r="AI76" s="31" t="n"/>
+      <c r="AJ76" s="31" t="n"/>
+      <c r="AK76" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL76" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM76" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN76" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO76" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP76" s="24" t="inlineStr">
+        <is>
+          <t>mlb-det</t>
+        </is>
+      </c>
+      <c r="AQ76" s="24" t="inlineStr">
+        <is>
+          <t>Detroit Tigers</t>
+        </is>
+      </c>
+      <c r="AR76" s="24" t="inlineStr">
+        <is>
+          <t>Detroit Tigers</t>
+        </is>
+      </c>
+      <c r="AS76" s="24" t="inlineStr">
+        <is>
+          <t>mlb-sea</t>
+        </is>
+      </c>
+      <c r="AT76" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="AU76" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="AV76" s="24" t="n"/>
+      <c r="AW76" s="24" t="n"/>
+      <c r="AX76" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY76" s="24" t="n"/>
+      <c r="AZ76" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA76" s="24" t="inlineStr">
+        <is>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
+        </is>
+      </c>
+      <c r="BB76" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC76" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v3</t>
+        </is>
+      </c>
+      <c r="BD76" s="24" t="inlineStr">
+        <is>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
+        </is>
+      </c>
+      <c r="BE76" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF76" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG76" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH76" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:16.771749Z</t>
+        </is>
+      </c>
+      <c r="BI76" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ76" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK76" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="BL76" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BM76" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="BN76" s="28" t="n">
+        <v>0.606965</v>
+      </c>
+      <c r="BO76" s="28" t="n"/>
+      <c r="BP76" s="25" t="n"/>
+      <c r="BQ76" s="27" t="n"/>
+      <c r="BR76" s="28" t="n"/>
+      <c r="BS76" s="28" t="n"/>
+      <c r="BT76" s="28" t="n"/>
+      <c r="BU76" s="25" t="n"/>
+      <c r="BV76" s="29" t="n"/>
+      <c r="BW76" s="24" t="n"/>
+      <c r="BX76" s="30" t="n"/>
+      <c r="BY76" s="27" t="n"/>
+      <c r="BZ76" s="24" t="n"/>
+      <c r="CA76" s="31" t="n"/>
+      <c r="CB76" s="24" t="n"/>
+      <c r="CC76" s="24" t="n"/>
+      <c r="CD76" s="24" t="n"/>
+      <c r="CE76" s="24" t="n"/>
+      <c r="CF76" s="24" t="n"/>
+      <c r="CG76" s="24" t="n"/>
+      <c r="CH76" s="24" t="n"/>
+      <c r="CI76" s="24" t="n"/>
+      <c r="CJ76" s="24" t="n"/>
+      <c r="CK76" s="24" t="n"/>
+      <c r="CL76" s="24" t="n"/>
+      <c r="CM76" s="24" t="n"/>
+      <c r="CN76" s="24" t="n"/>
+      <c r="CO76" s="24" t="n"/>
+      <c r="CP76" s="24" t="n"/>
+      <c r="CQ76" s="24" t="n"/>
+      <c r="CR76" s="24" t="n"/>
+      <c r="CS76" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="36" customHeight="1">
+      <c r="A77" s="24" t="inlineStr">
+        <is>
+          <t>ac951448e4bf45d9</t>
+        </is>
+      </c>
+      <c r="B77" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:16.771749Z</t>
+        </is>
+      </c>
+      <c r="C77" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T01:40Z</t>
+        </is>
+      </c>
+      <c r="D77" s="24" t="inlineStr">
+        <is>
+          <t>401816412</t>
+        </is>
+      </c>
+      <c r="E77" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F77" s="24" t="inlineStr">
+        <is>
+          <t>Detroit Tigers</t>
+        </is>
+      </c>
+      <c r="G77" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="H77" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I77" s="24" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J77" s="25" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="K77" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L77" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="M77" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="N77" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="O77" s="28" t="n">
+        <v>0.537198</v>
+      </c>
+      <c r="P77" s="28" t="n">
+        <v>0.042131</v>
+      </c>
+      <c r="Q77" s="28" t="n">
+        <v>0.006682</v>
+      </c>
+      <c r="R77" s="26" t="n">
+        <v>30</v>
+      </c>
+      <c r="S77" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T77" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v3</t>
+        </is>
+      </c>
+      <c r="U77" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V77" s="24" t="n"/>
+      <c r="W77" s="26" t="n"/>
+      <c r="X77" s="26" t="n"/>
+      <c r="Y77" s="25" t="n"/>
+      <c r="Z77" s="26" t="n"/>
+      <c r="AA77" s="28" t="n"/>
+      <c r="AB77" s="28" t="n"/>
+      <c r="AC77" s="30" t="n"/>
+      <c r="AD77" s="24" t="n"/>
+      <c r="AE77" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Totals: Trend Engine projected 4.87-4.56; raw selected-side p=0.6264, calibrated p=0.5372.</t>
+        </is>
+      </c>
+      <c r="AF77" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG77" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH77" s="24" t="n"/>
+      <c r="AI77" s="31" t="n"/>
+      <c r="AJ77" s="31" t="n"/>
+      <c r="AK77" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL77" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM77" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN77" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO77" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP77" s="24" t="inlineStr">
+        <is>
+          <t>mlb-det</t>
+        </is>
+      </c>
+      <c r="AQ77" s="24" t="inlineStr">
+        <is>
+          <t>Detroit Tigers</t>
+        </is>
+      </c>
+      <c r="AR77" s="24" t="inlineStr">
+        <is>
+          <t>Detroit Tigers</t>
+        </is>
+      </c>
+      <c r="AS77" s="24" t="inlineStr">
+        <is>
+          <t>mlb-sea</t>
+        </is>
+      </c>
+      <c r="AT77" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="AU77" s="24" t="inlineStr">
+        <is>
+          <t>Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="AV77" s="24" t="n"/>
+      <c r="AW77" s="24" t="n"/>
+      <c r="AX77" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY77" s="24" t="n"/>
+      <c r="AZ77" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA77" s="24" t="inlineStr">
+        <is>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
+        </is>
+      </c>
+      <c r="BB77" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC77" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v3</t>
+        </is>
+      </c>
+      <c r="BD77" s="24" t="inlineStr">
+        <is>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
+        </is>
+      </c>
+      <c r="BE77" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF77" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG77" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH77" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:16.771749Z</t>
+        </is>
+      </c>
+      <c r="BI77" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ77" s="25" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BK77" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="BL77" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BM77" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="BN77" s="28" t="n">
+        <v>0.527363</v>
+      </c>
+      <c r="BO77" s="28" t="n"/>
+      <c r="BP77" s="25" t="n"/>
+      <c r="BQ77" s="27" t="n"/>
+      <c r="BR77" s="28" t="n"/>
+      <c r="BS77" s="28" t="n"/>
+      <c r="BT77" s="28" t="n"/>
+      <c r="BU77" s="25" t="n"/>
+      <c r="BV77" s="29" t="n"/>
+      <c r="BW77" s="24" t="n"/>
+      <c r="BX77" s="30" t="n"/>
+      <c r="BY77" s="27" t="n"/>
+      <c r="BZ77" s="24" t="n"/>
+      <c r="CA77" s="31" t="n"/>
+      <c r="CB77" s="24" t="n"/>
+      <c r="CC77" s="24" t="n"/>
+      <c r="CD77" s="24" t="n"/>
+      <c r="CE77" s="24" t="n"/>
+      <c r="CF77" s="24" t="n"/>
+      <c r="CG77" s="24" t="n"/>
+      <c r="CH77" s="24" t="n"/>
+      <c r="CI77" s="24" t="n"/>
+      <c r="CJ77" s="24" t="n"/>
+      <c r="CK77" s="24" t="n"/>
+      <c r="CL77" s="24" t="n"/>
+      <c r="CM77" s="24" t="n"/>
+      <c r="CN77" s="24" t="n"/>
+      <c r="CO77" s="24" t="n"/>
+      <c r="CP77" s="24" t="n"/>
+      <c r="CQ77" s="24" t="n"/>
+      <c r="CR77" s="24" t="n"/>
+      <c r="CS77" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="36" customHeight="1">
+      <c r="A78" s="24" t="inlineStr">
+        <is>
+          <t>c3cc751440f24f77</t>
+        </is>
+      </c>
+      <c r="B78" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:16.771749Z</t>
+        </is>
+      </c>
+      <c r="C78" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T01:40Z</t>
+        </is>
+      </c>
+      <c r="D78" s="24" t="inlineStr">
+        <is>
+          <t>401816413</t>
+        </is>
+      </c>
+      <c r="E78" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F78" s="24" t="inlineStr">
+        <is>
+          <t>San Diego Padres</t>
+        </is>
+      </c>
+      <c r="G78" s="24" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="H78" s="24" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="I78" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J78" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K78" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L78" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M78" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="N78" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O78" s="28" t="n">
+        <v>0.580303</v>
+      </c>
+      <c r="P78" s="28" t="n">
+        <v>0.05172</v>
+      </c>
+      <c r="Q78" s="28" t="n">
+        <v>-0.019697</v>
+      </c>
+      <c r="R78" s="26" t="n">
+        <v>11</v>
+      </c>
+      <c r="S78" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T78" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v3</t>
+        </is>
+      </c>
+      <c r="U78" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V78" s="24" t="n"/>
+      <c r="W78" s="26" t="n"/>
+      <c r="X78" s="26" t="n"/>
+      <c r="Y78" s="25" t="n"/>
+      <c r="Z78" s="26" t="n"/>
+      <c r="AA78" s="28" t="n"/>
+      <c r="AB78" s="28" t="n"/>
+      <c r="AC78" s="30" t="n"/>
+      <c r="AD78" s="24" t="n"/>
+      <c r="AE78" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Margin: Trend Engine projected 4.83-4.33; raw selected-side p=0.6179, calibrated p=0.5803.</t>
+        </is>
+      </c>
+      <c r="AF78" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG78" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH78" s="24" t="n"/>
+      <c r="AI78" s="31" t="n"/>
+      <c r="AJ78" s="31" t="n"/>
+      <c r="AK78" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL78" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM78" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN78" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO78" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP78" s="24" t="inlineStr">
+        <is>
+          <t>mlb-sd</t>
+        </is>
+      </c>
+      <c r="AQ78" s="24" t="inlineStr">
+        <is>
+          <t>San Diego Padres</t>
+        </is>
+      </c>
+      <c r="AR78" s="24" t="inlineStr">
+        <is>
+          <t>San Diego Padres</t>
+        </is>
+      </c>
+      <c r="AS78" s="24" t="inlineStr">
+        <is>
+          <t>mlb-ari</t>
+        </is>
+      </c>
+      <c r="AT78" s="24" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="AU78" s="24" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="AV78" s="24" t="n"/>
+      <c r="AW78" s="24" t="n"/>
+      <c r="AX78" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY78" s="24" t="n"/>
+      <c r="AZ78" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA78" s="24" t="inlineStr">
+        <is>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
+        </is>
+      </c>
+      <c r="BB78" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC78" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v3</t>
+        </is>
+      </c>
+      <c r="BD78" s="24" t="inlineStr">
+        <is>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
+        </is>
+      </c>
+      <c r="BE78" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF78" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG78" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH78" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:16.771749Z</t>
+        </is>
+      </c>
+      <c r="BI78" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ78" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK78" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BL78" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BM78" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN78" s="28" t="n">
+        <v>0.597015</v>
+      </c>
+      <c r="BO78" s="28" t="n"/>
+      <c r="BP78" s="25" t="n"/>
+      <c r="BQ78" s="27" t="n"/>
+      <c r="BR78" s="28" t="n"/>
+      <c r="BS78" s="28" t="n"/>
+      <c r="BT78" s="28" t="n"/>
+      <c r="BU78" s="25" t="n"/>
+      <c r="BV78" s="29" t="n"/>
+      <c r="BW78" s="24" t="n"/>
+      <c r="BX78" s="30" t="n"/>
+      <c r="BY78" s="27" t="n"/>
+      <c r="BZ78" s="24" t="n"/>
+      <c r="CA78" s="31" t="n"/>
+      <c r="CB78" s="24" t="n"/>
+      <c r="CC78" s="24" t="n"/>
+      <c r="CD78" s="24" t="n"/>
+      <c r="CE78" s="24" t="n"/>
+      <c r="CF78" s="24" t="n"/>
+      <c r="CG78" s="24" t="n"/>
+      <c r="CH78" s="24" t="n"/>
+      <c r="CI78" s="24" t="n"/>
+      <c r="CJ78" s="24" t="n"/>
+      <c r="CK78" s="24" t="n"/>
+      <c r="CL78" s="24" t="n"/>
+      <c r="CM78" s="24" t="n"/>
+      <c r="CN78" s="24" t="n"/>
+      <c r="CO78" s="24" t="n"/>
+      <c r="CP78" s="24" t="n"/>
+      <c r="CQ78" s="24" t="n"/>
+      <c r="CR78" s="24" t="n"/>
+      <c r="CS78" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="36" customHeight="1">
+      <c r="A79" s="24" t="inlineStr">
+        <is>
+          <t>ca3b482530ef4461</t>
+        </is>
+      </c>
+      <c r="B79" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:16.771749Z</t>
+        </is>
+      </c>
+      <c r="C79" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T01:40Z</t>
+        </is>
+      </c>
+      <c r="D79" s="24" t="inlineStr">
+        <is>
+          <t>401816413</t>
+        </is>
+      </c>
+      <c r="E79" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F79" s="24" t="inlineStr">
+        <is>
+          <t>San Diego Padres</t>
+        </is>
+      </c>
+      <c r="G79" s="24" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="H79" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I79" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J79" s="25" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K79" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L79" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="M79" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="N79" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="O79" s="28" t="n">
+        <v>0.527374</v>
+      </c>
+      <c r="P79" s="28" t="n">
+        <v>0.05172</v>
+      </c>
+      <c r="Q79" s="28" t="n">
+        <v>-0.003142</v>
+      </c>
+      <c r="R79" s="26" t="n">
+        <v>19</v>
+      </c>
+      <c r="S79" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T79" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v3</t>
+        </is>
+      </c>
+      <c r="U79" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V79" s="24" t="n"/>
+      <c r="W79" s="26" t="n"/>
+      <c r="X79" s="26" t="n"/>
+      <c r="Y79" s="25" t="n"/>
+      <c r="Z79" s="26" t="n"/>
+      <c r="AA79" s="28" t="n"/>
+      <c r="AB79" s="28" t="n"/>
+      <c r="AC79" s="30" t="n"/>
+      <c r="AD79" s="24" t="n"/>
+      <c r="AE79" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Totals: Trend Engine projected 4.83-4.33; raw selected-side p=0.5868, calibrated p=0.5274.</t>
+        </is>
+      </c>
+      <c r="AF79" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG79" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH79" s="24" t="n"/>
+      <c r="AI79" s="31" t="n"/>
+      <c r="AJ79" s="31" t="n"/>
+      <c r="AK79" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL79" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM79" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN79" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO79" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP79" s="24" t="inlineStr">
+        <is>
+          <t>mlb-sd</t>
+        </is>
+      </c>
+      <c r="AQ79" s="24" t="inlineStr">
+        <is>
+          <t>San Diego Padres</t>
+        </is>
+      </c>
+      <c r="AR79" s="24" t="inlineStr">
+        <is>
+          <t>San Diego Padres</t>
+        </is>
+      </c>
+      <c r="AS79" s="24" t="inlineStr">
+        <is>
+          <t>mlb-ari</t>
+        </is>
+      </c>
+      <c r="AT79" s="24" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="AU79" s="24" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="AV79" s="24" t="n"/>
+      <c r="AW79" s="24" t="n"/>
+      <c r="AX79" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY79" s="24" t="n"/>
+      <c r="AZ79" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA79" s="24" t="inlineStr">
+        <is>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
+        </is>
+      </c>
+      <c r="BB79" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC79" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v3</t>
+        </is>
+      </c>
+      <c r="BD79" s="24" t="inlineStr">
+        <is>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
+        </is>
+      </c>
+      <c r="BE79" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF79" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG79" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH79" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:16.771749Z</t>
+        </is>
+      </c>
+      <c r="BI79" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ79" s="25" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BK79" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="BL79" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BM79" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="BN79" s="28" t="n">
+        <v>0.527363</v>
+      </c>
+      <c r="BO79" s="28" t="n"/>
+      <c r="BP79" s="25" t="n"/>
+      <c r="BQ79" s="27" t="n"/>
+      <c r="BR79" s="28" t="n"/>
+      <c r="BS79" s="28" t="n"/>
+      <c r="BT79" s="28" t="n"/>
+      <c r="BU79" s="25" t="n"/>
+      <c r="BV79" s="29" t="n"/>
+      <c r="BW79" s="24" t="n"/>
+      <c r="BX79" s="30" t="n"/>
+      <c r="BY79" s="27" t="n"/>
+      <c r="BZ79" s="24" t="n"/>
+      <c r="CA79" s="31" t="n"/>
+      <c r="CB79" s="24" t="n"/>
+      <c r="CC79" s="24" t="n"/>
+      <c r="CD79" s="24" t="n"/>
+      <c r="CE79" s="24" t="n"/>
+      <c r="CF79" s="24" t="n"/>
+      <c r="CG79" s="24" t="n"/>
+      <c r="CH79" s="24" t="n"/>
+      <c r="CI79" s="24" t="n"/>
+      <c r="CJ79" s="24" t="n"/>
+      <c r="CK79" s="24" t="n"/>
+      <c r="CL79" s="24" t="n"/>
+      <c r="CM79" s="24" t="n"/>
+      <c r="CN79" s="24" t="n"/>
+      <c r="CO79" s="24" t="n"/>
+      <c r="CP79" s="24" t="n"/>
+      <c r="CQ79" s="24" t="n"/>
+      <c r="CR79" s="24" t="n"/>
+      <c r="CS79" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/main/mlb.xlsx
+++ b/data/main/mlb.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Picks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Picks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
@@ -14970,12 +14970,12 @@
     <row r="46" ht="36" customHeight="1">
       <c r="A46" s="24" t="inlineStr">
         <is>
-          <t>4e14a1299a594d08</t>
+          <t>19abf39469cc4d0c</t>
         </is>
       </c>
       <c r="B46" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:35:50.664769Z</t>
+          <t>2026-08-05T13:54:09.180176Z</t>
         </is>
       </c>
       <c r="C46" s="24" t="inlineStr">
@@ -15020,23 +15020,23 @@
         </is>
       </c>
       <c r="L46" s="26" t="n">
-        <v>-147</v>
+        <v>-153</v>
       </c>
       <c r="M46" s="27" t="n">
-        <v>1.680272</v>
+        <v>1.653595</v>
       </c>
       <c r="N46" s="28" t="n">
-        <v>0.5951419999999999</v>
+        <v>0.604743</v>
       </c>
       <c r="O46" s="28" t="n">
-        <v>0.651419</v>
+        <v>0.651358</v>
       </c>
       <c r="P46" s="28" t="n"/>
       <c r="Q46" s="28" t="n">
-        <v>0.056277</v>
+        <v>0.046615</v>
       </c>
       <c r="R46" s="26" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="S46" s="29" t="n">
         <v>1.75</v>
@@ -15062,7 +15062,7 @@
       <c r="AD46" s="24" t="n"/>
       <c r="AE46" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5873; executable ask 0.5950 (aec-mlb-tb-col-2026-08-05); model edge vs ask +0.0564.</t>
+          <t>Learned LR call at threshold 0.5873; executable ask 0.6050 (aec-mlb-tb-col-2026-08-05); model edge vs ask +0.0464.</t>
         </is>
       </c>
       <c r="AF46" s="31" t="inlineStr">
@@ -15166,7 +15166,7 @@
       </c>
       <c r="BE46" s="24" t="inlineStr">
         <is>
-          <t>afbdfea2d660f7f9</t>
+          <t>133a0f8d2d67fce5</t>
         </is>
       </c>
       <c r="BF46" s="24" t="inlineStr">
@@ -15181,7 +15181,7 @@
       </c>
       <c r="BH46" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:33:52.558033Z</t>
+          <t>2026-08-05T13:52:26.086277Z</t>
         </is>
       </c>
       <c r="BI46" s="24" t="inlineStr">
@@ -15191,16 +15191,16 @@
       </c>
       <c r="BJ46" s="25" t="n"/>
       <c r="BK46" s="26" t="n">
-        <v>-147</v>
+        <v>-153</v>
       </c>
       <c r="BL46" s="27" t="n">
-        <v>1.680272</v>
+        <v>1.653595</v>
       </c>
       <c r="BM46" s="28" t="n">
-        <v>0.5951419999999999</v>
+        <v>0.604743</v>
       </c>
       <c r="BN46" s="28" t="n">
-        <v>0.59204</v>
+        <v>0.60199</v>
       </c>
       <c r="BO46" s="28" t="n"/>
       <c r="BP46" s="25" t="n"/>
@@ -15233,7 +15233,7 @@
       </c>
       <c r="CF46" s="24" t="inlineStr">
         <is>
-          <t>1.0105</t>
+          <t>1.0096</t>
         </is>
       </c>
       <c r="CG46" s="24" t="n"/>
@@ -15261,7 +15261,7 @@
       <c r="CQ46" s="24" t="n"/>
       <c r="CR46" s="24" t="inlineStr">
         <is>
-          <t>0.651419</t>
+          <t>0.651358</t>
         </is>
       </c>
       <c r="CS46" s="24" t="inlineStr">
@@ -15273,12 +15273,12 @@
     <row r="47" ht="36" customHeight="1">
       <c r="A47" s="24" t="inlineStr">
         <is>
-          <t>2a3b5ab213d44603</t>
+          <t>3f8c04156c7845ce</t>
         </is>
       </c>
       <c r="B47" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:35:50.664769Z</t>
+          <t>2026-08-05T13:54:09.180176Z</t>
         </is>
       </c>
       <c r="C47" s="24" t="inlineStr">
@@ -15323,23 +15323,23 @@
         </is>
       </c>
       <c r="L47" s="26" t="n">
-        <v>-130</v>
+        <v>-117</v>
       </c>
       <c r="M47" s="27" t="n">
-        <v>1.769231</v>
+        <v>1.854701</v>
       </c>
       <c r="N47" s="28" t="n">
-        <v>0.565217</v>
+        <v>0.539171</v>
       </c>
       <c r="O47" s="28" t="n">
-        <v>0.620283</v>
+        <v>0.620156</v>
       </c>
       <c r="P47" s="28" t="n"/>
       <c r="Q47" s="28" t="n">
-        <v>0.055066</v>
+        <v>0.080985</v>
       </c>
       <c r="R47" s="26" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="S47" s="29" t="n">
         <v>1.5</v>
@@ -15365,7 +15365,7 @@
       <c r="AD47" s="24" t="n"/>
       <c r="AE47" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5873; executable ask 0.5650 (aec-mlb-laa-bal-2026-08-05); model edge vs ask +0.0553.</t>
+          <t>Learned LR call at threshold 0.5873; executable ask 0.5400 (aec-mlb-laa-bal-2026-08-05); model edge vs ask +0.0802.</t>
         </is>
       </c>
       <c r="AF47" s="31" t="inlineStr">
@@ -15469,7 +15469,7 @@
       </c>
       <c r="BE47" s="24" t="inlineStr">
         <is>
-          <t>0c5ef877e6b12160</t>
+          <t>90250452b4135146</t>
         </is>
       </c>
       <c r="BF47" s="24" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="BH47" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:33:53.451157Z</t>
+          <t>2026-08-05T13:52:26.546603Z</t>
         </is>
       </c>
       <c r="BI47" s="24" t="inlineStr">
@@ -15494,16 +15494,16 @@
       </c>
       <c r="BJ47" s="25" t="n"/>
       <c r="BK47" s="26" t="n">
-        <v>-130</v>
+        <v>-117</v>
       </c>
       <c r="BL47" s="27" t="n">
-        <v>1.769231</v>
+        <v>1.854701</v>
       </c>
       <c r="BM47" s="28" t="n">
-        <v>0.565217</v>
+        <v>0.539171</v>
       </c>
       <c r="BN47" s="28" t="n">
-        <v>0.562189</v>
+        <v>0.537313</v>
       </c>
       <c r="BO47" s="28" t="n"/>
       <c r="BP47" s="25" t="n"/>
@@ -15536,7 +15536,7 @@
       </c>
       <c r="CF47" s="24" t="inlineStr">
         <is>
-          <t>1.0102</t>
+          <t>1.012</t>
         </is>
       </c>
       <c r="CG47" s="24" t="n"/>
@@ -15564,7 +15564,7 @@
       <c r="CQ47" s="24" t="n"/>
       <c r="CR47" s="24" t="inlineStr">
         <is>
-          <t>0.620283</t>
+          <t>0.620156</t>
         </is>
       </c>
       <c r="CS47" s="24" t="inlineStr">
@@ -15576,12 +15576,12 @@
     <row r="48" ht="36" customHeight="1">
       <c r="A48" s="24" t="inlineStr">
         <is>
-          <t>fd35ca527b5a46d5</t>
+          <t>130e866c4e914279</t>
         </is>
       </c>
       <c r="B48" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:35:50.664769Z</t>
+          <t>2026-08-05T13:54:09.180176Z</t>
         </is>
       </c>
       <c r="C48" s="24" t="inlineStr">
@@ -15635,11 +15635,11 @@
         <v>0.545455</v>
       </c>
       <c r="O48" s="28" t="n">
-        <v>0.59089</v>
+        <v>0.590933</v>
       </c>
       <c r="P48" s="28" t="n"/>
       <c r="Q48" s="28" t="n">
-        <v>0.045435</v>
+        <v>0.045478</v>
       </c>
       <c r="R48" s="26" t="n">
         <v>44</v>
@@ -15772,7 +15772,7 @@
       </c>
       <c r="BE48" s="24" t="inlineStr">
         <is>
-          <t>bb6f41cb5975b5bb</t>
+          <t>06a32b1aa50e018d</t>
         </is>
       </c>
       <c r="BF48" s="24" t="inlineStr">
@@ -15787,7 +15787,7 @@
       </c>
       <c r="BH48" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:33:58.789026Z</t>
+          <t>2026-08-05T13:52:29.624655Z</t>
         </is>
       </c>
       <c r="BI48" s="24" t="inlineStr">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="CF48" s="24" t="inlineStr">
         <is>
-          <t>1.0072</t>
+          <t>1.0066</t>
         </is>
       </c>
       <c r="CG48" s="24" t="n"/>
@@ -15871,7 +15871,7 @@
       <c r="CQ48" s="24" t="n"/>
       <c r="CR48" s="24" t="inlineStr">
         <is>
-          <t>0.59089</t>
+          <t>0.590933</t>
         </is>
       </c>
       <c r="CS48" s="24" t="inlineStr">
@@ -15883,12 +15883,12 @@
     <row r="49" ht="36" customHeight="1">
       <c r="A49" s="24" t="inlineStr">
         <is>
-          <t>8cfab79e9feb48df</t>
+          <t>2440471e155946a7</t>
         </is>
       </c>
       <c r="B49" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:35:50.664769Z</t>
+          <t>2026-08-05T13:54:09.180176Z</t>
         </is>
       </c>
       <c r="C49" s="24" t="inlineStr">
@@ -15933,23 +15933,23 @@
         </is>
       </c>
       <c r="L49" s="26" t="n">
-        <v>-122</v>
+        <v>-125</v>
       </c>
       <c r="M49" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.8</v>
       </c>
       <c r="N49" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.555556</v>
       </c>
       <c r="O49" s="28" t="n">
         <v>0.6155080000000001</v>
       </c>
       <c r="P49" s="28" t="n"/>
       <c r="Q49" s="28" t="n">
-        <v>0.065958</v>
+        <v>0.059952</v>
       </c>
       <c r="R49" s="26" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="S49" s="29" t="n">
         <v>1.5</v>
@@ -15975,7 +15975,7 @@
       <c r="AD49" s="24" t="n"/>
       <c r="AE49" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5873; executable ask 0.5500 (aec-mlb-pit-mil-2026-08-05); model edge vs ask +0.0655.</t>
+          <t>Learned LR call at threshold 0.5873; executable ask 0.5550 (aec-mlb-pit-mil-2026-08-05); model edge vs ask +0.0605.</t>
         </is>
       </c>
       <c r="AF49" s="31" t="inlineStr">
@@ -16094,7 +16094,7 @@
       </c>
       <c r="BH49" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:33:59.358107Z</t>
+          <t>2026-08-05T13:52:30.079092Z</t>
         </is>
       </c>
       <c r="BI49" s="24" t="inlineStr">
@@ -16104,16 +16104,16 @@
       </c>
       <c r="BJ49" s="25" t="n"/>
       <c r="BK49" s="26" t="n">
-        <v>-122</v>
+        <v>-125</v>
       </c>
       <c r="BL49" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.8</v>
       </c>
       <c r="BM49" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.555556</v>
       </c>
       <c r="BN49" s="28" t="n">
-        <v>0.547264</v>
+        <v>0.552239</v>
       </c>
       <c r="BO49" s="28" t="n"/>
       <c r="BP49" s="25" t="n"/>
@@ -16186,12 +16186,12 @@
     <row r="50" ht="36" customHeight="1">
       <c r="A50" s="24" t="inlineStr">
         <is>
-          <t>c07c11cf26cf4d40</t>
+          <t>7d9c71814d1948ec</t>
         </is>
       </c>
       <c r="B50" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C50" s="24" t="inlineStr">
@@ -16238,25 +16238,25 @@
         </is>
       </c>
       <c r="L50" s="26" t="n">
-        <v>-135</v>
+        <v>-122</v>
       </c>
       <c r="M50" s="27" t="n">
-        <v>1.740741</v>
+        <v>1.819672</v>
       </c>
       <c r="N50" s="28" t="n">
-        <v>0.574468</v>
+        <v>0.54955</v>
       </c>
       <c r="O50" s="28" t="n">
-        <v>0.556045</v>
+        <v>0.554069</v>
       </c>
       <c r="P50" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q50" s="28" t="n">
-        <v>-0.018423</v>
+        <v>0.004519</v>
       </c>
       <c r="R50" s="26" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="S50" s="29" t="n">
         <v>1</v>
@@ -16282,7 +16282,7 @@
       <c r="AD50" s="24" t="n"/>
       <c r="AE50" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.45-5.29; raw selected-side p=0.5823, calibrated p=0.5560.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.45-5.29; raw selected-side p=0.5794, calibrated p=0.5541.</t>
         </is>
       </c>
       <c r="AF50" s="31" t="inlineStr">
@@ -16401,7 +16401,7 @@
       </c>
       <c r="BH50" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI50" s="24" t="inlineStr">
@@ -16413,16 +16413,16 @@
         <v>1.5</v>
       </c>
       <c r="BK50" s="26" t="n">
-        <v>-135</v>
+        <v>-122</v>
       </c>
       <c r="BL50" s="27" t="n">
-        <v>1.740741</v>
+        <v>1.819672</v>
       </c>
       <c r="BM50" s="28" t="n">
-        <v>0.574468</v>
+        <v>0.54955</v>
       </c>
       <c r="BN50" s="28" t="n">
-        <v>0.572139</v>
+        <v>0.547264</v>
       </c>
       <c r="BO50" s="28" t="n"/>
       <c r="BP50" s="25" t="n"/>
@@ -16456,19 +16456,19 @@
       <c r="CR50" s="24" t="n"/>
       <c r="CS50" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="51" ht="36" customHeight="1">
       <c r="A51" s="24" t="inlineStr">
         <is>
-          <t>59dab69433aa4a48</t>
+          <t>967334ce4e8e44dc</t>
         </is>
       </c>
       <c r="B51" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C51" s="24" t="inlineStr">
@@ -16524,13 +16524,13 @@
         <v>0.473934</v>
       </c>
       <c r="O51" s="28" t="n">
-        <v>0.524815</v>
+        <v>0.525275</v>
       </c>
       <c r="P51" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q51" s="28" t="n">
-        <v>0.050881</v>
+        <v>0.051341</v>
       </c>
       <c r="R51" s="26" t="n">
         <v>51</v>
@@ -16559,7 +16559,7 @@
       <c r="AD51" s="24" t="n"/>
       <c r="AE51" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.45-5.29; raw selected-side p=0.5766, calibrated p=0.5248.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.45-5.29; raw selected-side p=0.5784, calibrated p=0.5253.</t>
         </is>
       </c>
       <c r="AF51" s="31" t="inlineStr">
@@ -16678,7 +16678,7 @@
       </c>
       <c r="BH51" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI51" s="24" t="inlineStr">
@@ -16740,12 +16740,12 @@
     <row r="52" ht="36" customHeight="1">
       <c r="A52" s="24" t="inlineStr">
         <is>
-          <t>56c8fcf5c0bf4137</t>
+          <t>7249e78e60894244</t>
         </is>
       </c>
       <c r="B52" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C52" s="24" t="inlineStr">
@@ -16780,7 +16780,7 @@
       </c>
       <c r="I52" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J52" s="25" t="n">
@@ -16801,19 +16801,19 @@
         <v>0.635036</v>
       </c>
       <c r="O52" s="28" t="n">
-        <v>0.6607420000000001</v>
+        <v>0.576862</v>
       </c>
       <c r="P52" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q52" s="28" t="n">
-        <v>0.025706</v>
+        <v>-0.058174</v>
       </c>
       <c r="R52" s="26" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="S52" s="29" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="T52" s="24" t="inlineStr">
         <is>
@@ -16836,7 +16836,7 @@
       <c r="AD52" s="24" t="n"/>
       <c r="AE52" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 3.96-4.59; raw selected-side p=0.7359, calibrated p=0.6607.</t>
+          <t>Measured Edge Margin: Trend Engine projected 3.96-4.59; raw selected-side p=0.6128, calibrated p=0.5769.</t>
         </is>
       </c>
       <c r="AF52" s="31" t="inlineStr">
@@ -16955,7 +16955,7 @@
       </c>
       <c r="BH52" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI52" s="24" t="inlineStr">
@@ -17010,19 +17010,19 @@
       <c r="CR52" s="24" t="n"/>
       <c r="CS52" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="53" ht="36" customHeight="1">
       <c r="A53" s="24" t="inlineStr">
         <is>
-          <t>8032753e796f4fa5</t>
+          <t>44b24f7ab36a46a8</t>
         </is>
       </c>
       <c r="B53" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C53" s="24" t="inlineStr">
@@ -17069,25 +17069,25 @@
         </is>
       </c>
       <c r="L53" s="26" t="n">
-        <v>-108</v>
+        <v>-104</v>
       </c>
       <c r="M53" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.961538</v>
       </c>
       <c r="N53" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.509804</v>
       </c>
       <c r="O53" s="28" t="n">
-        <v>0.539558</v>
+        <v>0.540166</v>
       </c>
       <c r="P53" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q53" s="28" t="n">
-        <v>0.020327</v>
+        <v>0.030362</v>
       </c>
       <c r="R53" s="26" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="S53" s="29" t="n">
         <v>1</v>
@@ -17113,7 +17113,7 @@
       <c r="AD53" s="24" t="n"/>
       <c r="AE53" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 3.96-4.59; raw selected-side p=0.6359, calibrated p=0.5396.</t>
+          <t>Measured Edge Totals: Trend Engine projected 3.96-4.59; raw selected-side p=0.6383, calibrated p=0.5402.</t>
         </is>
       </c>
       <c r="AF53" s="31" t="inlineStr">
@@ -17232,7 +17232,7 @@
       </c>
       <c r="BH53" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI53" s="24" t="inlineStr">
@@ -17244,16 +17244,16 @@
         <v>9.5</v>
       </c>
       <c r="BK53" s="26" t="n">
-        <v>-108</v>
+        <v>-104</v>
       </c>
       <c r="BL53" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.961538</v>
       </c>
       <c r="BM53" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.509804</v>
       </c>
       <c r="BN53" s="28" t="n">
-        <v>0.517413</v>
+        <v>0.507463</v>
       </c>
       <c r="BO53" s="28" t="n"/>
       <c r="BP53" s="25" t="n"/>
@@ -17294,12 +17294,12 @@
     <row r="54" ht="36" customHeight="1">
       <c r="A54" s="24" t="inlineStr">
         <is>
-          <t>a9b6d40e45ac4271</t>
+          <t>b2af3889bd544a83</t>
         </is>
       </c>
       <c r="B54" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C54" s="24" t="inlineStr">
@@ -17355,13 +17355,13 @@
         <v>0.565217</v>
       </c>
       <c r="O54" s="28" t="n">
-        <v>0.588514</v>
+        <v>0.587935</v>
       </c>
       <c r="P54" s="28" t="n">
         <v>0.05172</v>
       </c>
       <c r="Q54" s="28" t="n">
-        <v>0.023297</v>
+        <v>0.022718</v>
       </c>
       <c r="R54" s="26" t="n">
         <v>32</v>
@@ -17390,7 +17390,7 @@
       <c r="AD54" s="24" t="n"/>
       <c r="AE54" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.57-4.92; raw selected-side p=0.6299, calibrated p=0.5885.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.57-4.92; raw selected-side p=0.6290, calibrated p=0.5879.</t>
         </is>
       </c>
       <c r="AF54" s="31" t="inlineStr">
@@ -17509,7 +17509,7 @@
       </c>
       <c r="BH54" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI54" s="24" t="inlineStr">
@@ -17571,12 +17571,12 @@
     <row r="55" ht="36" customHeight="1">
       <c r="A55" s="24" t="inlineStr">
         <is>
-          <t>47d5b72109194f7c</t>
+          <t>5aac644a67c749c0</t>
         </is>
       </c>
       <c r="B55" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C55" s="24" t="inlineStr">
@@ -17632,16 +17632,16 @@
         <v>0.480769</v>
       </c>
       <c r="O55" s="28" t="n">
-        <v>0.522257</v>
+        <v>0.519176</v>
       </c>
       <c r="P55" s="28" t="n">
         <v>0.05172</v>
       </c>
       <c r="Q55" s="28" t="n">
-        <v>0.041488</v>
+        <v>0.038407</v>
       </c>
       <c r="R55" s="26" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="S55" s="29" t="n">
         <v>1</v>
@@ -17667,7 +17667,7 @@
       <c r="AD55" s="24" t="n"/>
       <c r="AE55" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.57-4.92; raw selected-side p=0.5663, calibrated p=0.5223.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.57-4.92; raw selected-side p=0.5538, calibrated p=0.5192.</t>
         </is>
       </c>
       <c r="AF55" s="31" t="inlineStr">
@@ -17786,7 +17786,7 @@
       </c>
       <c r="BH55" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI55" s="24" t="inlineStr">
@@ -17848,12 +17848,12 @@
     <row r="56" ht="36" customHeight="1">
       <c r="A56" s="24" t="inlineStr">
         <is>
-          <t>37a73a36f6874342</t>
+          <t>708d653b7b5343f2</t>
         </is>
       </c>
       <c r="B56" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C56" s="24" t="inlineStr">
@@ -17900,25 +17900,25 @@
         </is>
       </c>
       <c r="L56" s="26" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="M56" s="27" t="n">
-        <v>1.961538</v>
+        <v>2</v>
       </c>
       <c r="N56" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.5</v>
       </c>
       <c r="O56" s="28" t="n">
-        <v>0.602278</v>
+        <v>0.600915</v>
       </c>
       <c r="P56" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q56" s="28" t="n">
-        <v>0.092474</v>
+        <v>0.100915</v>
       </c>
       <c r="R56" s="26" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="S56" s="29" t="n">
         <v>1.5</v>
@@ -17944,7 +17944,7 @@
       <c r="AD56" s="24" t="n"/>
       <c r="AE56" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.81-4.67; raw selected-side p=0.6501, calibrated p=0.6023.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.81-4.66; raw selected-side p=0.6481, calibrated p=0.6009.</t>
         </is>
       </c>
       <c r="AF56" s="31" t="inlineStr">
@@ -18063,7 +18063,7 @@
       </c>
       <c r="BH56" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI56" s="24" t="inlineStr">
@@ -18075,16 +18075,16 @@
         <v>1.5</v>
       </c>
       <c r="BK56" s="26" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="BL56" s="27" t="n">
-        <v>1.961538</v>
+        <v>2</v>
       </c>
       <c r="BM56" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.5</v>
       </c>
       <c r="BN56" s="28" t="n">
-        <v>0.507463</v>
+        <v>0.497512</v>
       </c>
       <c r="BO56" s="28" t="n"/>
       <c r="BP56" s="25" t="n"/>
@@ -18125,12 +18125,12 @@
     <row r="57" ht="36" customHeight="1">
       <c r="A57" s="24" t="inlineStr">
         <is>
-          <t>d57ee209bea94133</t>
+          <t>cdd7b779863c4990</t>
         </is>
       </c>
       <c r="B57" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C57" s="24" t="inlineStr">
@@ -18177,25 +18177,25 @@
         </is>
       </c>
       <c r="L57" s="26" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M57" s="27" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="N57" s="28" t="n">
-        <v>0.5</v>
+        <v>0.49505</v>
       </c>
       <c r="O57" s="28" t="n">
-        <v>0.557989</v>
+        <v>0.558548</v>
       </c>
       <c r="P57" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q57" s="28" t="n">
-        <v>0.057989</v>
+        <v>0.063498</v>
       </c>
       <c r="R57" s="26" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="S57" s="29" t="n">
         <v>1</v>
@@ -18221,7 +18221,7 @@
       <c r="AD57" s="24" t="n"/>
       <c r="AE57" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.81-4.67; raw selected-side p=0.7101, calibrated p=0.5580.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.81-4.66; raw selected-side p=0.7124, calibrated p=0.5585.</t>
         </is>
       </c>
       <c r="AF57" s="31" t="inlineStr">
@@ -18340,7 +18340,7 @@
       </c>
       <c r="BH57" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI57" s="24" t="inlineStr">
@@ -18352,16 +18352,16 @@
         <v>11.5</v>
       </c>
       <c r="BK57" s="26" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="BL57" s="27" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="BM57" s="28" t="n">
-        <v>0.5</v>
+        <v>0.49505</v>
       </c>
       <c r="BN57" s="28" t="n">
-        <v>0.49505</v>
+        <v>0.492537</v>
       </c>
       <c r="BO57" s="28" t="n"/>
       <c r="BP57" s="25" t="n"/>
@@ -18402,12 +18402,12 @@
     <row r="58" ht="36" customHeight="1">
       <c r="A58" s="24" t="inlineStr">
         <is>
-          <t>e0227c7ea7774bea</t>
+          <t>d61245e964ba4945</t>
         </is>
       </c>
       <c r="B58" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C58" s="24" t="inlineStr">
@@ -18454,25 +18454,25 @@
         </is>
       </c>
       <c r="L58" s="26" t="n">
-        <v>-167</v>
+        <v>-174</v>
       </c>
       <c r="M58" s="27" t="n">
-        <v>1.598802</v>
+        <v>1.574713</v>
       </c>
       <c r="N58" s="28" t="n">
-        <v>0.625468</v>
+        <v>0.635036</v>
       </c>
       <c r="O58" s="28" t="n">
-        <v>0.585379</v>
+        <v>0.590183</v>
       </c>
       <c r="P58" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q58" s="28" t="n">
-        <v>-0.040089</v>
+        <v>-0.044853</v>
       </c>
       <c r="R58" s="26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S58" s="29" t="n">
         <v>1.25</v>
@@ -18498,7 +18498,7 @@
       <c r="AD58" s="24" t="n"/>
       <c r="AE58" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.25-4.70; raw selected-side p=0.6253, calibrated p=0.5854.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.25-4.70; raw selected-side p=0.6323, calibrated p=0.5902.</t>
         </is>
       </c>
       <c r="AF58" s="31" t="inlineStr">
@@ -18617,7 +18617,7 @@
       </c>
       <c r="BH58" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI58" s="24" t="inlineStr">
@@ -18629,16 +18629,16 @@
         <v>1.5</v>
       </c>
       <c r="BK58" s="26" t="n">
-        <v>-167</v>
+        <v>-174</v>
       </c>
       <c r="BL58" s="27" t="n">
-        <v>1.598802</v>
+        <v>1.574713</v>
       </c>
       <c r="BM58" s="28" t="n">
-        <v>0.625468</v>
+        <v>0.635036</v>
       </c>
       <c r="BN58" s="28" t="n">
-        <v>0.621891</v>
+        <v>0.631841</v>
       </c>
       <c r="BO58" s="28" t="n"/>
       <c r="BP58" s="25" t="n"/>
@@ -18679,12 +18679,12 @@
     <row r="59" ht="36" customHeight="1">
       <c r="A59" s="24" t="inlineStr">
         <is>
-          <t>cd9479291a4d4d56</t>
+          <t>d33140fbe9924bde</t>
         </is>
       </c>
       <c r="B59" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C59" s="24" t="inlineStr">
@@ -18723,7 +18723,7 @@
         </is>
       </c>
       <c r="J59" s="25" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="K59" s="24" t="inlineStr">
         <is>
@@ -18731,25 +18731,25 @@
         </is>
       </c>
       <c r="L59" s="26" t="n">
-        <v>111</v>
+        <v>-115</v>
       </c>
       <c r="M59" s="27" t="n">
-        <v>2.11</v>
+        <v>1.869565</v>
       </c>
       <c r="N59" s="28" t="n">
-        <v>0.473934</v>
+        <v>0.534884</v>
       </c>
       <c r="O59" s="28" t="n">
-        <v>0.5089669999999999</v>
+        <v>0.527597</v>
       </c>
       <c r="P59" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q59" s="28" t="n">
-        <v>0.035033</v>
+        <v>-0.007287</v>
       </c>
       <c r="R59" s="26" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="S59" s="29" t="n">
         <v>1</v>
@@ -18775,7 +18775,7 @@
       <c r="AD59" s="24" t="n"/>
       <c r="AE59" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.25-4.70; raw selected-side p=0.5128, calibrated p=0.5090.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.25-4.70; raw selected-side p=0.5877, calibrated p=0.5276.</t>
         </is>
       </c>
       <c r="AF59" s="31" t="inlineStr">
@@ -18894,7 +18894,7 @@
       </c>
       <c r="BH59" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI59" s="24" t="inlineStr">
@@ -18903,19 +18903,19 @@
         </is>
       </c>
       <c r="BJ59" s="25" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="BK59" s="26" t="n">
-        <v>111</v>
+        <v>-115</v>
       </c>
       <c r="BL59" s="27" t="n">
-        <v>2.11</v>
+        <v>1.869565</v>
       </c>
       <c r="BM59" s="28" t="n">
-        <v>0.473934</v>
+        <v>0.534884</v>
       </c>
       <c r="BN59" s="28" t="n">
-        <v>0.472637</v>
+        <v>0.532338</v>
       </c>
       <c r="BO59" s="28" t="n"/>
       <c r="BP59" s="25" t="n"/>
@@ -18949,19 +18949,19 @@
       <c r="CR59" s="24" t="n"/>
       <c r="CS59" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="60" ht="36" customHeight="1">
       <c r="A60" s="24" t="inlineStr">
         <is>
-          <t>24790c1c98bc4ad9</t>
+          <t>553a1c4913444d4c</t>
         </is>
       </c>
       <c r="B60" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C60" s="24" t="inlineStr">
@@ -19017,16 +19017,16 @@
         <v>0.604743</v>
       </c>
       <c r="O60" s="28" t="n">
-        <v>0.590797</v>
+        <v>0.594067</v>
       </c>
       <c r="P60" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q60" s="28" t="n">
-        <v>-0.013946</v>
+        <v>-0.010676</v>
       </c>
       <c r="R60" s="26" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="S60" s="29" t="n">
         <v>1.25</v>
@@ -19052,7 +19052,7 @@
       <c r="AD60" s="24" t="n"/>
       <c r="AE60" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.90-5.09; raw selected-side p=0.6332, calibrated p=0.5908.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.90-5.09; raw selected-side p=0.6381, calibrated p=0.5941.</t>
         </is>
       </c>
       <c r="AF60" s="31" t="inlineStr">
@@ -19171,7 +19171,7 @@
       </c>
       <c r="BH60" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI60" s="24" t="inlineStr">
@@ -19233,12 +19233,12 @@
     <row r="61" ht="36" customHeight="1">
       <c r="A61" s="24" t="inlineStr">
         <is>
-          <t>0f33d75cea924af2</t>
+          <t>6fd03525015e4b7e</t>
         </is>
       </c>
       <c r="B61" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C61" s="24" t="inlineStr">
@@ -19294,16 +19294,16 @@
         <v>0.490196</v>
       </c>
       <c r="O61" s="28" t="n">
-        <v>0.509116</v>
+        <v>0.509961</v>
       </c>
       <c r="P61" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q61" s="28" t="n">
-        <v>0.01892</v>
+        <v>0.019765</v>
       </c>
       <c r="R61" s="26" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S61" s="29" t="n">
         <v>1</v>
@@ -19329,7 +19329,7 @@
       <c r="AD61" s="24" t="n"/>
       <c r="AE61" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.90-5.09; raw selected-side p=0.5133, calibrated p=0.5091.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.90-5.09; raw selected-side p=0.5168, calibrated p=0.5100.</t>
         </is>
       </c>
       <c r="AF61" s="31" t="inlineStr">
@@ -19448,7 +19448,7 @@
       </c>
       <c r="BH61" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI61" s="24" t="inlineStr">
@@ -19510,12 +19510,12 @@
     <row r="62" ht="36" customHeight="1">
       <c r="A62" s="24" t="inlineStr">
         <is>
-          <t>2df7f8ae6f304847</t>
+          <t>450a30c6e80245ad</t>
         </is>
       </c>
       <c r="B62" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C62" s="24" t="inlineStr">
@@ -19562,25 +19562,25 @@
         </is>
       </c>
       <c r="L62" s="26" t="n">
-        <v>-153</v>
+        <v>-170</v>
       </c>
       <c r="M62" s="27" t="n">
-        <v>1.653595</v>
+        <v>1.588235</v>
       </c>
       <c r="N62" s="28" t="n">
-        <v>0.604743</v>
+        <v>0.62963</v>
       </c>
       <c r="O62" s="28" t="n">
-        <v>0.60221</v>
+        <v>0.611375</v>
       </c>
       <c r="P62" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q62" s="28" t="n">
-        <v>-0.002533</v>
+        <v>-0.018255</v>
       </c>
       <c r="R62" s="26" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="S62" s="29" t="n">
         <v>1.5</v>
@@ -19606,7 +19606,7 @@
       <c r="AD62" s="24" t="n"/>
       <c r="AE62" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.46-4.24; raw selected-side p=0.6500, calibrated p=0.6022.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.46-4.24; raw selected-side p=0.6634, calibrated p=0.6114.</t>
         </is>
       </c>
       <c r="AF62" s="31" t="inlineStr">
@@ -19725,7 +19725,7 @@
       </c>
       <c r="BH62" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI62" s="24" t="inlineStr">
@@ -19737,16 +19737,16 @@
         <v>1.5</v>
       </c>
       <c r="BK62" s="26" t="n">
-        <v>-153</v>
+        <v>-170</v>
       </c>
       <c r="BL62" s="27" t="n">
-        <v>1.653595</v>
+        <v>1.588235</v>
       </c>
       <c r="BM62" s="28" t="n">
-        <v>0.604743</v>
+        <v>0.62963</v>
       </c>
       <c r="BN62" s="28" t="n">
-        <v>0.60199</v>
+        <v>0.626866</v>
       </c>
       <c r="BO62" s="28" t="n"/>
       <c r="BP62" s="25" t="n"/>
@@ -19787,12 +19787,12 @@
     <row r="63" ht="36" customHeight="1">
       <c r="A63" s="24" t="inlineStr">
         <is>
-          <t>5eca91635a984d3d</t>
+          <t>746b27f47bc140dd</t>
         </is>
       </c>
       <c r="B63" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C63" s="24" t="inlineStr">
@@ -19827,11 +19827,11 @@
       </c>
       <c r="I63" s="24" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="J63" s="25" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="K63" s="24" t="inlineStr">
         <is>
@@ -19839,25 +19839,25 @@
         </is>
       </c>
       <c r="L63" s="26" t="n">
-        <v>-102</v>
+        <v>-111</v>
       </c>
       <c r="M63" s="27" t="n">
-        <v>1.980392</v>
+        <v>1.900901</v>
       </c>
       <c r="N63" s="28" t="n">
-        <v>0.50495</v>
+        <v>0.526066</v>
       </c>
       <c r="O63" s="28" t="n">
-        <v>0.50934</v>
+        <v>0.522244</v>
       </c>
       <c r="P63" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q63" s="28" t="n">
-        <v>0.00439</v>
+        <v>-0.003822</v>
       </c>
       <c r="R63" s="26" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="S63" s="29" t="n">
         <v>1</v>
@@ -19883,7 +19883,7 @@
       <c r="AD63" s="24" t="n"/>
       <c r="AE63" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.46-4.24; raw selected-side p=0.5142, calibrated p=0.5093.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.46-4.24; raw selected-side p=0.5662, calibrated p=0.5222.</t>
         </is>
       </c>
       <c r="AF63" s="31" t="inlineStr">
@@ -20002,7 +20002,7 @@
       </c>
       <c r="BH63" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI63" s="24" t="inlineStr">
@@ -20011,19 +20011,19 @@
         </is>
       </c>
       <c r="BJ63" s="25" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="BK63" s="26" t="n">
-        <v>-102</v>
+        <v>-111</v>
       </c>
       <c r="BL63" s="27" t="n">
-        <v>1.980392</v>
+        <v>1.900901</v>
       </c>
       <c r="BM63" s="28" t="n">
-        <v>0.50495</v>
+        <v>0.526066</v>
       </c>
       <c r="BN63" s="28" t="n">
-        <v>0.502488</v>
+        <v>0.522388</v>
       </c>
       <c r="BO63" s="28" t="n"/>
       <c r="BP63" s="25" t="n"/>
@@ -20057,19 +20057,19 @@
       <c r="CR63" s="24" t="n"/>
       <c r="CS63" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="64" ht="36" customHeight="1">
       <c r="A64" s="24" t="inlineStr">
         <is>
-          <t>f32645579d0644b7</t>
+          <t>bd7535aa372b4bce</t>
         </is>
       </c>
       <c r="B64" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C64" s="24" t="inlineStr">
@@ -20116,25 +20116,25 @@
         </is>
       </c>
       <c r="L64" s="26" t="n">
-        <v>-127</v>
+        <v>-122</v>
       </c>
       <c r="M64" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.819672</v>
       </c>
       <c r="N64" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.54955</v>
       </c>
       <c r="O64" s="28" t="n">
-        <v>0.60238</v>
+        <v>0.603096</v>
       </c>
       <c r="P64" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q64" s="28" t="n">
-        <v>0.042909</v>
+        <v>0.053546</v>
       </c>
       <c r="R64" s="26" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="S64" s="29" t="n">
         <v>1.5</v>
@@ -20160,7 +20160,7 @@
       <c r="AD64" s="24" t="n"/>
       <c r="AE64" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 5.21-5.30; raw selected-side p=0.6502, calibrated p=0.6024.</t>
+          <t>Measured Edge Margin: Trend Engine projected 5.21-5.30; raw selected-side p=0.6513, calibrated p=0.6031.</t>
         </is>
       </c>
       <c r="AF64" s="31" t="inlineStr">
@@ -20279,7 +20279,7 @@
       </c>
       <c r="BH64" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI64" s="24" t="inlineStr">
@@ -20291,16 +20291,16 @@
         <v>1.5</v>
       </c>
       <c r="BK64" s="26" t="n">
-        <v>-127</v>
+        <v>-122</v>
       </c>
       <c r="BL64" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.819672</v>
       </c>
       <c r="BM64" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.54955</v>
       </c>
       <c r="BN64" s="28" t="n">
-        <v>0.554455</v>
+        <v>0.547264</v>
       </c>
       <c r="BO64" s="28" t="n"/>
       <c r="BP64" s="25" t="n"/>
@@ -20341,12 +20341,12 @@
     <row r="65" ht="36" customHeight="1">
       <c r="A65" s="24" t="inlineStr">
         <is>
-          <t>6dc05d99bf2b4f62</t>
+          <t>353ff6ee090247b2</t>
         </is>
       </c>
       <c r="B65" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C65" s="24" t="inlineStr">
@@ -20393,22 +20393,22 @@
         </is>
       </c>
       <c r="L65" s="26" t="n">
-        <v>-104</v>
+        <v>-102</v>
       </c>
       <c r="M65" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.980392</v>
       </c>
       <c r="N65" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.50495</v>
       </c>
       <c r="O65" s="28" t="n">
-        <v>0.5154879999999999</v>
+        <v>0.511737</v>
       </c>
       <c r="P65" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q65" s="28" t="n">
-        <v>0.005684</v>
+        <v>0.006787</v>
       </c>
       <c r="R65" s="26" t="n">
         <v>29</v>
@@ -20437,7 +20437,7 @@
       <c r="AD65" s="24" t="n"/>
       <c r="AE65" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 5.21-5.30; raw selected-side p=0.5390, calibrated p=0.5155.</t>
+          <t>Measured Edge Totals: Trend Engine projected 5.21-5.30; raw selected-side p=0.5239, calibrated p=0.5117.</t>
         </is>
       </c>
       <c r="AF65" s="31" t="inlineStr">
@@ -20556,7 +20556,7 @@
       </c>
       <c r="BH65" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI65" s="24" t="inlineStr">
@@ -20568,16 +20568,16 @@
         <v>9.5</v>
       </c>
       <c r="BK65" s="26" t="n">
-        <v>-104</v>
+        <v>-102</v>
       </c>
       <c r="BL65" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.980392</v>
       </c>
       <c r="BM65" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.50495</v>
       </c>
       <c r="BN65" s="28" t="n">
-        <v>0.507463</v>
+        <v>0.502488</v>
       </c>
       <c r="BO65" s="28" t="n"/>
       <c r="BP65" s="25" t="n"/>
@@ -20618,12 +20618,12 @@
     <row r="66" ht="36" customHeight="1">
       <c r="A66" s="24" t="inlineStr">
         <is>
-          <t>b310c5b5775a4b30</t>
+          <t>548336d41e204260</t>
         </is>
       </c>
       <c r="B66" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C66" s="24" t="inlineStr">
@@ -20670,25 +20670,25 @@
         </is>
       </c>
       <c r="L66" s="26" t="n">
-        <v>-150</v>
+        <v>-144</v>
       </c>
       <c r="M66" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.694444</v>
       </c>
       <c r="N66" s="28" t="n">
-        <v>0.6</v>
+        <v>0.590164</v>
       </c>
       <c r="O66" s="28" t="n">
-        <v>0.6248320000000001</v>
+        <v>0.624219</v>
       </c>
       <c r="P66" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q66" s="28" t="n">
-        <v>0.024832</v>
+        <v>0.034055</v>
       </c>
       <c r="R66" s="26" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="S66" s="29" t="n">
         <v>1.5</v>
@@ -20714,7 +20714,7 @@
       <c r="AD66" s="24" t="n"/>
       <c r="AE66" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.74-4.57; raw selected-side p=0.6832, calibrated p=0.6248.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.74-4.57; raw selected-side p=0.6823, calibrated p=0.6242.</t>
         </is>
       </c>
       <c r="AF66" s="31" t="inlineStr">
@@ -20833,7 +20833,7 @@
       </c>
       <c r="BH66" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI66" s="24" t="inlineStr">
@@ -20845,16 +20845,16 @@
         <v>1.5</v>
       </c>
       <c r="BK66" s="26" t="n">
-        <v>-150</v>
+        <v>-144</v>
       </c>
       <c r="BL66" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.694444</v>
       </c>
       <c r="BM66" s="28" t="n">
-        <v>0.6</v>
+        <v>0.590164</v>
       </c>
       <c r="BN66" s="28" t="n">
-        <v>0.597015</v>
+        <v>0.5870649999999999</v>
       </c>
       <c r="BO66" s="28" t="n"/>
       <c r="BP66" s="25" t="n"/>
@@ -20895,12 +20895,12 @@
     <row r="67" ht="36" customHeight="1">
       <c r="A67" s="24" t="inlineStr">
         <is>
-          <t>18af2b518b674034</t>
+          <t>0e446d444bfd48fa</t>
         </is>
       </c>
       <c r="B67" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C67" s="24" t="inlineStr">
@@ -20947,25 +20947,25 @@
         </is>
       </c>
       <c r="L67" s="26" t="n">
-        <v>-111</v>
+        <v>-108</v>
       </c>
       <c r="M67" s="27" t="n">
-        <v>1.900901</v>
+        <v>1.925926</v>
       </c>
       <c r="N67" s="28" t="n">
-        <v>0.526066</v>
+        <v>0.519231</v>
       </c>
       <c r="O67" s="28" t="n">
-        <v>0.516866</v>
+        <v>0.515997</v>
       </c>
       <c r="P67" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q67" s="28" t="n">
-        <v>-0.0092</v>
+        <v>-0.003234</v>
       </c>
       <c r="R67" s="26" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="S67" s="29" t="n">
         <v>1</v>
@@ -20991,7 +20991,7 @@
       <c r="AD67" s="24" t="n"/>
       <c r="AE67" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.74-4.57; raw selected-side p=0.5445, calibrated p=0.5169.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.74-4.57; raw selected-side p=0.5411, calibrated p=0.5160.</t>
         </is>
       </c>
       <c r="AF67" s="31" t="inlineStr">
@@ -21110,7 +21110,7 @@
       </c>
       <c r="BH67" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI67" s="24" t="inlineStr">
@@ -21122,16 +21122,16 @@
         <v>8.5</v>
       </c>
       <c r="BK67" s="26" t="n">
-        <v>-111</v>
+        <v>-108</v>
       </c>
       <c r="BL67" s="27" t="n">
-        <v>1.900901</v>
+        <v>1.925926</v>
       </c>
       <c r="BM67" s="28" t="n">
-        <v>0.526066</v>
+        <v>0.519231</v>
       </c>
       <c r="BN67" s="28" t="n">
-        <v>0.522388</v>
+        <v>0.517413</v>
       </c>
       <c r="BO67" s="28" t="n"/>
       <c r="BP67" s="25" t="n"/>
@@ -21172,12 +21172,12 @@
     <row r="68" ht="36" customHeight="1">
       <c r="A68" s="24" t="inlineStr">
         <is>
-          <t>3b3e8899e7544707</t>
+          <t>121480e59be84c61</t>
         </is>
       </c>
       <c r="B68" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C68" s="24" t="inlineStr">
@@ -21224,25 +21224,25 @@
         </is>
       </c>
       <c r="L68" s="26" t="n">
-        <v>-182</v>
+        <v>-167</v>
       </c>
       <c r="M68" s="27" t="n">
-        <v>1.549451</v>
+        <v>1.598802</v>
       </c>
       <c r="N68" s="28" t="n">
-        <v>0.64539</v>
+        <v>0.625468</v>
       </c>
       <c r="O68" s="28" t="n">
-        <v>0.6332140000000001</v>
+        <v>0.633248</v>
       </c>
       <c r="P68" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q68" s="28" t="n">
-        <v>-0.012176</v>
+        <v>0.00778</v>
       </c>
       <c r="R68" s="26" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="S68" s="29" t="n">
         <v>1.5</v>
@@ -21268,7 +21268,7 @@
       <c r="AD68" s="24" t="n"/>
       <c r="AE68" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.13-3.98; raw selected-side p=0.6955, calibrated p=0.6332.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.13-3.98; raw selected-side p=0.6956, calibrated p=0.6332.</t>
         </is>
       </c>
       <c r="AF68" s="31" t="inlineStr">
@@ -21387,7 +21387,7 @@
       </c>
       <c r="BH68" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI68" s="24" t="inlineStr">
@@ -21399,16 +21399,16 @@
         <v>1.5</v>
       </c>
       <c r="BK68" s="26" t="n">
-        <v>-182</v>
+        <v>-167</v>
       </c>
       <c r="BL68" s="27" t="n">
-        <v>1.549451</v>
+        <v>1.598802</v>
       </c>
       <c r="BM68" s="28" t="n">
-        <v>0.64539</v>
+        <v>0.625468</v>
       </c>
       <c r="BN68" s="28" t="n">
-        <v>0.641791</v>
+        <v>0.621891</v>
       </c>
       <c r="BO68" s="28" t="n"/>
       <c r="BP68" s="25" t="n"/>
@@ -21442,19 +21442,19 @@
       <c r="CR68" s="24" t="n"/>
       <c r="CS68" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="69" ht="36" customHeight="1">
       <c r="A69" s="24" t="inlineStr">
         <is>
-          <t>ceed6ea7167640c4</t>
+          <t>357bc9b9aa6f487b</t>
         </is>
       </c>
       <c r="B69" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C69" s="24" t="inlineStr">
@@ -21501,25 +21501,25 @@
         </is>
       </c>
       <c r="L69" s="26" t="n">
-        <v>100</v>
+        <v>-111</v>
       </c>
       <c r="M69" s="27" t="n">
-        <v>2</v>
+        <v>1.900901</v>
       </c>
       <c r="N69" s="28" t="n">
-        <v>0.5</v>
+        <v>0.526066</v>
       </c>
       <c r="O69" s="28" t="n">
-        <v>0.52325</v>
+        <v>0.522381</v>
       </c>
       <c r="P69" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q69" s="28" t="n">
-        <v>0.02325</v>
+        <v>-0.003685</v>
       </c>
       <c r="R69" s="26" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="S69" s="29" t="n">
         <v>1</v>
@@ -21545,7 +21545,7 @@
       <c r="AD69" s="24" t="n"/>
       <c r="AE69" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.13-3.98; raw selected-side p=0.5703, calibrated p=0.5233.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.13-3.98; raw selected-side p=0.5667, calibrated p=0.5224.</t>
         </is>
       </c>
       <c r="AF69" s="31" t="inlineStr">
@@ -21664,7 +21664,7 @@
       </c>
       <c r="BH69" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI69" s="24" t="inlineStr">
@@ -21676,16 +21676,16 @@
         <v>8.5</v>
       </c>
       <c r="BK69" s="26" t="n">
-        <v>100</v>
+        <v>-111</v>
       </c>
       <c r="BL69" s="27" t="n">
-        <v>2</v>
+        <v>1.900901</v>
       </c>
       <c r="BM69" s="28" t="n">
-        <v>0.5</v>
+        <v>0.526066</v>
       </c>
       <c r="BN69" s="28" t="n">
-        <v>0.497512</v>
+        <v>0.522388</v>
       </c>
       <c r="BO69" s="28" t="n"/>
       <c r="BP69" s="25" t="n"/>
@@ -21719,19 +21719,19 @@
       <c r="CR69" s="24" t="n"/>
       <c r="CS69" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="70" ht="36" customHeight="1">
       <c r="A70" s="24" t="inlineStr">
         <is>
-          <t>f9a5065e12f94a1e</t>
+          <t>eaf4c819130f4347</t>
         </is>
       </c>
       <c r="B70" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C70" s="24" t="inlineStr">
@@ -21787,16 +21787,16 @@
         <v>0.635036</v>
       </c>
       <c r="O70" s="28" t="n">
-        <v>0.639346</v>
+        <v>0.639551</v>
       </c>
       <c r="P70" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q70" s="28" t="n">
-        <v>0.00431</v>
+        <v>0.004515</v>
       </c>
       <c r="R70" s="26" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S70" s="29" t="n">
         <v>1.75</v>
@@ -21822,7 +21822,7 @@
       <c r="AD70" s="24" t="n"/>
       <c r="AE70" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.38-4.11; raw selected-side p=0.7045, calibrated p=0.6393.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.38-4.11; raw selected-side p=0.7048, calibrated p=0.6396.</t>
         </is>
       </c>
       <c r="AF70" s="31" t="inlineStr">
@@ -21941,7 +21941,7 @@
       </c>
       <c r="BH70" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI70" s="24" t="inlineStr">
@@ -22003,12 +22003,12 @@
     <row r="71" ht="36" customHeight="1">
       <c r="A71" s="24" t="inlineStr">
         <is>
-          <t>9351fff5823b49cd</t>
+          <t>b4aa3184686a4646</t>
         </is>
       </c>
       <c r="B71" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C71" s="24" t="inlineStr">
@@ -22055,25 +22055,25 @@
         </is>
       </c>
       <c r="L71" s="26" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="M71" s="27" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="N71" s="28" t="n">
-        <v>0.473934</v>
+        <v>0.480769</v>
       </c>
       <c r="O71" s="28" t="n">
-        <v>0.51201</v>
+        <v>0.513637</v>
       </c>
       <c r="P71" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q71" s="28" t="n">
-        <v>0.038076</v>
+        <v>0.032868</v>
       </c>
       <c r="R71" s="26" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="S71" s="29" t="n">
         <v>1</v>
@@ -22099,7 +22099,7 @@
       <c r="AD71" s="24" t="n"/>
       <c r="AE71" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.38-4.11; raw selected-side p=0.5250, calibrated p=0.5120.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.38-4.11; raw selected-side p=0.5315, calibrated p=0.5136.</t>
         </is>
       </c>
       <c r="AF71" s="31" t="inlineStr">
@@ -22218,7 +22218,7 @@
       </c>
       <c r="BH71" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI71" s="24" t="inlineStr">
@@ -22230,16 +22230,16 @@
         <v>8.5</v>
       </c>
       <c r="BK71" s="26" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="BL71" s="27" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="BM71" s="28" t="n">
-        <v>0.473934</v>
+        <v>0.480769</v>
       </c>
       <c r="BN71" s="28" t="n">
-        <v>0.472637</v>
+        <v>0.477612</v>
       </c>
       <c r="BO71" s="28" t="n"/>
       <c r="BP71" s="25" t="n"/>
@@ -22280,12 +22280,12 @@
     <row r="72" ht="36" customHeight="1">
       <c r="A72" s="24" t="inlineStr">
         <is>
-          <t>113b6926d0154d9c</t>
+          <t>6a8f0f1cb0614a33</t>
         </is>
       </c>
       <c r="B72" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C72" s="24" t="inlineStr">
@@ -22341,16 +22341,16 @@
         <v>0.640288</v>
       </c>
       <c r="O72" s="28" t="n">
-        <v>0.590354</v>
+        <v>0.586402</v>
       </c>
       <c r="P72" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q72" s="28" t="n">
-        <v>-0.049934</v>
+        <v>-0.053886</v>
       </c>
       <c r="R72" s="26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S72" s="29" t="n">
         <v>1.25</v>
@@ -22376,7 +22376,7 @@
       <c r="AD72" s="24" t="n"/>
       <c r="AE72" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.27-4.68; raw selected-side p=0.6326, calibrated p=0.5904.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.27-4.68; raw selected-side p=0.6268, calibrated p=0.5864.</t>
         </is>
       </c>
       <c r="AF72" s="31" t="inlineStr">
@@ -22495,7 +22495,7 @@
       </c>
       <c r="BH72" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI72" s="24" t="inlineStr">
@@ -22557,12 +22557,12 @@
     <row r="73" ht="36" customHeight="1">
       <c r="A73" s="24" t="inlineStr">
         <is>
-          <t>f39275040c124d2d</t>
+          <t>12d42c3262224698</t>
         </is>
       </c>
       <c r="B73" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C73" s="24" t="inlineStr">
@@ -22609,25 +22609,25 @@
         </is>
       </c>
       <c r="L73" s="26" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="M73" s="27" t="n">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="N73" s="28" t="n">
-        <v>0.473934</v>
+        <v>0.460829</v>
       </c>
       <c r="O73" s="28" t="n">
-        <v>0.527448</v>
+        <v>0.527398</v>
       </c>
       <c r="P73" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q73" s="28" t="n">
-        <v>0.053514</v>
+        <v>0.066569</v>
       </c>
       <c r="R73" s="26" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="S73" s="29" t="n">
         <v>1</v>
@@ -22653,7 +22653,7 @@
       <c r="AD73" s="24" t="n"/>
       <c r="AE73" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.27-4.68; raw selected-side p=0.5871, calibrated p=0.5274.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.27-4.68; raw selected-side p=0.5869, calibrated p=0.5274.</t>
         </is>
       </c>
       <c r="AF73" s="31" t="inlineStr">
@@ -22772,7 +22772,7 @@
       </c>
       <c r="BH73" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI73" s="24" t="inlineStr">
@@ -22784,16 +22784,16 @@
         <v>7.5</v>
       </c>
       <c r="BK73" s="26" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="BL73" s="27" t="n">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="BM73" s="28" t="n">
-        <v>0.473934</v>
+        <v>0.460829</v>
       </c>
       <c r="BN73" s="28" t="n">
-        <v>0.472637</v>
+        <v>0.457711</v>
       </c>
       <c r="BO73" s="28" t="n"/>
       <c r="BP73" s="25" t="n"/>
@@ -22834,12 +22834,12 @@
     <row r="74" ht="36" customHeight="1">
       <c r="A74" s="24" t="inlineStr">
         <is>
-          <t>06679cc9303c40f3</t>
+          <t>a440f9bcad354056</t>
         </is>
       </c>
       <c r="B74" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C74" s="24" t="inlineStr">
@@ -22886,25 +22886,25 @@
         </is>
       </c>
       <c r="L74" s="26" t="n">
-        <v>-174</v>
+        <v>-178</v>
       </c>
       <c r="M74" s="27" t="n">
-        <v>1.574713</v>
+        <v>1.561798</v>
       </c>
       <c r="N74" s="28" t="n">
-        <v>0.635036</v>
+        <v>0.640288</v>
       </c>
       <c r="O74" s="28" t="n">
-        <v>0.647353</v>
+        <v>0.648545</v>
       </c>
       <c r="P74" s="28" t="n">
         <v>0.05172</v>
       </c>
       <c r="Q74" s="28" t="n">
-        <v>0.012317</v>
+        <v>0.008257</v>
       </c>
       <c r="R74" s="26" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S74" s="29" t="n">
         <v>1.75</v>
@@ -22930,7 +22930,7 @@
       <c r="AD74" s="24" t="n"/>
       <c r="AE74" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.58-5.19; raw selected-side p=0.7163, calibrated p=0.6474.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.58-5.19; raw selected-side p=0.7180, calibrated p=0.6485.</t>
         </is>
       </c>
       <c r="AF74" s="31" t="inlineStr">
@@ -23049,7 +23049,7 @@
       </c>
       <c r="BH74" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI74" s="24" t="inlineStr">
@@ -23061,16 +23061,16 @@
         <v>1.5</v>
       </c>
       <c r="BK74" s="26" t="n">
-        <v>-174</v>
+        <v>-178</v>
       </c>
       <c r="BL74" s="27" t="n">
-        <v>1.574713</v>
+        <v>1.561798</v>
       </c>
       <c r="BM74" s="28" t="n">
-        <v>0.635036</v>
+        <v>0.640288</v>
       </c>
       <c r="BN74" s="28" t="n">
-        <v>0.631841</v>
+        <v>0.636816</v>
       </c>
       <c r="BO74" s="28" t="n"/>
       <c r="BP74" s="25" t="n"/>
@@ -23111,12 +23111,12 @@
     <row r="75" ht="36" customHeight="1">
       <c r="A75" s="24" t="inlineStr">
         <is>
-          <t>c3bbd2f2ca3142dd</t>
+          <t>2e8ee2437c3349dc</t>
         </is>
       </c>
       <c r="B75" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C75" s="24" t="inlineStr">
@@ -23151,11 +23151,11 @@
       </c>
       <c r="I75" s="24" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>over</t>
         </is>
       </c>
       <c r="J75" s="25" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="K75" s="24" t="inlineStr">
         <is>
@@ -23163,25 +23163,25 @@
         </is>
       </c>
       <c r="L75" s="26" t="n">
-        <v>-122</v>
+        <v>-111</v>
       </c>
       <c r="M75" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.900901</v>
       </c>
       <c r="N75" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.526066</v>
       </c>
       <c r="O75" s="28" t="n">
-        <v>0.51355</v>
+        <v>0.524778</v>
       </c>
       <c r="P75" s="28" t="n">
         <v>0.05172</v>
       </c>
       <c r="Q75" s="28" t="n">
-        <v>-0.036</v>
+        <v>-0.001288</v>
       </c>
       <c r="R75" s="26" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="S75" s="29" t="n">
         <v>1</v>
@@ -23207,7 +23207,7 @@
       <c r="AD75" s="24" t="n"/>
       <c r="AE75" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.58-5.19; raw selected-side p=0.5312, calibrated p=0.5136.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.58-5.19; raw selected-side p=0.5764, calibrated p=0.5248.</t>
         </is>
       </c>
       <c r="AF75" s="31" t="inlineStr">
@@ -23326,7 +23326,7 @@
       </c>
       <c r="BH75" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI75" s="24" t="inlineStr">
@@ -23335,19 +23335,19 @@
         </is>
       </c>
       <c r="BJ75" s="25" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="BK75" s="26" t="n">
-        <v>-122</v>
+        <v>-111</v>
       </c>
       <c r="BL75" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.900901</v>
       </c>
       <c r="BM75" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.526066</v>
       </c>
       <c r="BN75" s="28" t="n">
-        <v>0.547264</v>
+        <v>0.522388</v>
       </c>
       <c r="BO75" s="28" t="n"/>
       <c r="BP75" s="25" t="n"/>
@@ -23388,12 +23388,12 @@
     <row r="76" ht="36" customHeight="1">
       <c r="A76" s="24" t="inlineStr">
         <is>
-          <t>95193532269c4ab2</t>
+          <t>782aabd620da42b0</t>
         </is>
       </c>
       <c r="B76" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C76" s="24" t="inlineStr">
@@ -23440,25 +23440,25 @@
         </is>
       </c>
       <c r="L76" s="26" t="n">
-        <v>-156</v>
+        <v>-153</v>
       </c>
       <c r="M76" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.653595</v>
       </c>
       <c r="N76" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.604743</v>
       </c>
       <c r="O76" s="28" t="n">
-        <v>0.631715</v>
+        <v>0.633554</v>
       </c>
       <c r="P76" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q76" s="28" t="n">
-        <v>0.02234</v>
+        <v>0.028811</v>
       </c>
       <c r="R76" s="26" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="S76" s="29" t="n">
         <v>1.5</v>
@@ -23484,7 +23484,7 @@
       <c r="AD76" s="24" t="n"/>
       <c r="AE76" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.87-4.56; raw selected-side p=0.6933, calibrated p=0.6317.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.87-4.56; raw selected-side p=0.6960, calibrated p=0.6336.</t>
         </is>
       </c>
       <c r="AF76" s="31" t="inlineStr">
@@ -23603,7 +23603,7 @@
       </c>
       <c r="BH76" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI76" s="24" t="inlineStr">
@@ -23615,16 +23615,16 @@
         <v>1.5</v>
       </c>
       <c r="BK76" s="26" t="n">
-        <v>-156</v>
+        <v>-153</v>
       </c>
       <c r="BL76" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.653595</v>
       </c>
       <c r="BM76" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.604743</v>
       </c>
       <c r="BN76" s="28" t="n">
-        <v>0.606965</v>
+        <v>0.60199</v>
       </c>
       <c r="BO76" s="28" t="n"/>
       <c r="BP76" s="25" t="n"/>
@@ -23665,12 +23665,12 @@
     <row r="77" ht="36" customHeight="1">
       <c r="A77" s="24" t="inlineStr">
         <is>
-          <t>ac951448e4bf45d9</t>
+          <t>53ea51af68e84e54</t>
         </is>
       </c>
       <c r="B77" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C77" s="24" t="inlineStr">
@@ -23717,25 +23717,25 @@
         </is>
       </c>
       <c r="L77" s="26" t="n">
-        <v>-113</v>
+        <v>-102</v>
       </c>
       <c r="M77" s="27" t="n">
-        <v>1.884956</v>
+        <v>1.980392</v>
       </c>
       <c r="N77" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.50495</v>
       </c>
       <c r="O77" s="28" t="n">
-        <v>0.537198</v>
+        <v>0.537173</v>
       </c>
       <c r="P77" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q77" s="28" t="n">
-        <v>0.006682</v>
+        <v>0.032223</v>
       </c>
       <c r="R77" s="26" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="S77" s="29" t="n">
         <v>1</v>
@@ -23761,7 +23761,7 @@
       <c r="AD77" s="24" t="n"/>
       <c r="AE77" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.87-4.56; raw selected-side p=0.6264, calibrated p=0.5372.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.87-4.56; raw selected-side p=0.6263, calibrated p=0.5372.</t>
         </is>
       </c>
       <c r="AF77" s="31" t="inlineStr">
@@ -23880,7 +23880,7 @@
       </c>
       <c r="BH77" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI77" s="24" t="inlineStr">
@@ -23892,16 +23892,16 @@
         <v>7.5</v>
       </c>
       <c r="BK77" s="26" t="n">
-        <v>-113</v>
+        <v>-102</v>
       </c>
       <c r="BL77" s="27" t="n">
-        <v>1.884956</v>
+        <v>1.980392</v>
       </c>
       <c r="BM77" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.50495</v>
       </c>
       <c r="BN77" s="28" t="n">
-        <v>0.527363</v>
+        <v>0.502488</v>
       </c>
       <c r="BO77" s="28" t="n"/>
       <c r="BP77" s="25" t="n"/>
@@ -23942,12 +23942,12 @@
     <row r="78" ht="36" customHeight="1">
       <c r="A78" s="24" t="inlineStr">
         <is>
-          <t>c3cc751440f24f77</t>
+          <t>ccd69ef788fa45c5</t>
         </is>
       </c>
       <c r="B78" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C78" s="24" t="inlineStr">
@@ -23994,25 +23994,25 @@
         </is>
       </c>
       <c r="L78" s="26" t="n">
-        <v>-150</v>
+        <v>-141</v>
       </c>
       <c r="M78" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.70922</v>
       </c>
       <c r="N78" s="28" t="n">
-        <v>0.6</v>
+        <v>0.585062</v>
       </c>
       <c r="O78" s="28" t="n">
-        <v>0.580303</v>
+        <v>0.5781230000000001</v>
       </c>
       <c r="P78" s="28" t="n">
         <v>0.05172</v>
       </c>
       <c r="Q78" s="28" t="n">
-        <v>-0.019697</v>
+        <v>-0.006939</v>
       </c>
       <c r="R78" s="26" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="S78" s="29" t="n">
         <v>1.25</v>
@@ -24038,7 +24038,7 @@
       <c r="AD78" s="24" t="n"/>
       <c r="AE78" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.83-4.33; raw selected-side p=0.6179, calibrated p=0.5803.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.83-4.33; raw selected-side p=0.6147, calibrated p=0.5781.</t>
         </is>
       </c>
       <c r="AF78" s="31" t="inlineStr">
@@ -24157,7 +24157,7 @@
       </c>
       <c r="BH78" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI78" s="24" t="inlineStr">
@@ -24169,16 +24169,16 @@
         <v>1.5</v>
       </c>
       <c r="BK78" s="26" t="n">
-        <v>-150</v>
+        <v>-141</v>
       </c>
       <c r="BL78" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.70922</v>
       </c>
       <c r="BM78" s="28" t="n">
-        <v>0.6</v>
+        <v>0.585062</v>
       </c>
       <c r="BN78" s="28" t="n">
-        <v>0.597015</v>
+        <v>0.58209</v>
       </c>
       <c r="BO78" s="28" t="n"/>
       <c r="BP78" s="25" t="n"/>
@@ -24219,12 +24219,12 @@
     <row r="79" ht="36" customHeight="1">
       <c r="A79" s="24" t="inlineStr">
         <is>
-          <t>ca3b482530ef4461</t>
+          <t>002f58116035474e</t>
         </is>
       </c>
       <c r="B79" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="C79" s="24" t="inlineStr">
@@ -24271,25 +24271,25 @@
         </is>
       </c>
       <c r="L79" s="26" t="n">
-        <v>-113</v>
+        <v>-120</v>
       </c>
       <c r="M79" s="27" t="n">
-        <v>1.884956</v>
+        <v>1.833333</v>
       </c>
       <c r="N79" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.545455</v>
       </c>
       <c r="O79" s="28" t="n">
-        <v>0.527374</v>
+        <v>0.526914</v>
       </c>
       <c r="P79" s="28" t="n">
         <v>0.05172</v>
       </c>
       <c r="Q79" s="28" t="n">
-        <v>-0.003142</v>
+        <v>-0.018541</v>
       </c>
       <c r="R79" s="26" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="S79" s="29" t="n">
         <v>1</v>
@@ -24315,7 +24315,7 @@
       <c r="AD79" s="24" t="n"/>
       <c r="AE79" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.83-4.33; raw selected-side p=0.5868, calibrated p=0.5274.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.83-4.33; raw selected-side p=0.5850, calibrated p=0.5269.</t>
         </is>
       </c>
       <c r="AF79" s="31" t="inlineStr">
@@ -24434,7 +24434,7 @@
       </c>
       <c r="BH79" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:36:16.771749Z</t>
+          <t>2026-08-05T13:54:46.877508Z</t>
         </is>
       </c>
       <c r="BI79" s="24" t="inlineStr">
@@ -24446,16 +24446,16 @@
         <v>9.5</v>
       </c>
       <c r="BK79" s="26" t="n">
-        <v>-113</v>
+        <v>-120</v>
       </c>
       <c r="BL79" s="27" t="n">
-        <v>1.884956</v>
+        <v>1.833333</v>
       </c>
       <c r="BM79" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.545455</v>
       </c>
       <c r="BN79" s="28" t="n">
-        <v>0.527363</v>
+        <v>0.542289</v>
       </c>
       <c r="BO79" s="28" t="n"/>
       <c r="BP79" s="25" t="n"/>

--- a/data/main/mlb.xlsx
+++ b/data/main/mlb.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS79" headerRowCount="1">
-  <autoFilter ref="A1:CS79"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS48" headerRowCount="1">
+  <autoFilter ref="A1:CS48"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$79)</f>
+        <f>COUNTA('Picks'!$A$2:$A$48)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$79,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$48,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$79,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$48,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$79,"settled",'Picks'!$V$2:$V$79,"win")+COUNTIFS('Picks'!$U$2:$U$79,"settled",'Picks'!$V$2:$V$79,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"win")+COUNTIFS('Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$79,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$48,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$79,"&gt;0",'Picks'!$V$2:$V$79,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$79,"&gt;0",'Picks'!$V$2:$V$79,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$48,"&gt;0",'Picks'!$V$2:$V$48,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$48,"&gt;0",'Picks'!$V$2:$V$48,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$79,"&gt;0",'Picks'!$V$2:$V$79,"win")/(COUNTIFS('Picks'!$BX$2:$BX$79,"&gt;0",'Picks'!$V$2:$V$79,"win")+COUNTIFS('Picks'!$BX$2:$BX$79,"&gt;0",'Picks'!$V$2:$V$79,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$48,"&gt;0",'Picks'!$V$2:$V$48,"win")/(COUNTIFS('Picks'!$BX$2:$BX$48,"&gt;0",'Picks'!$V$2:$V$48,"win")+COUNTIFS('Picks'!$BX$2:$BX$48,"&gt;0",'Picks'!$V$2:$V$48,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$79)/SUM('Picks'!$BX$2:$BX$79),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$48)/SUM('Picks'!$BX$2:$BX$48),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$79)</f>
+        <f>SUM('Picks'!$BY$2:$BY$48)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$79,"&lt;&gt;",'Picks'!$AB$2:$AB$79),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$48,"&lt;&gt;",'Picks'!$AB$2:$AB$48),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$79,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$79,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$48,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$48,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$79,'Picks'!$AM$2:$AM$79,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$48,'Picks'!$AM$2:$AM$48,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$79,$A14,'Picks'!$U$2:$U$79,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$48,$A14,'Picks'!$U$2:$U$48,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$79,$A14,'Picks'!$U$2:$U$79,"settled",'Picks'!$V$2:$V$79,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$48,$A14,'Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$79,$A14,'Picks'!$U$2:$U$79,"settled",'Picks'!$V$2:$V$79,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$48,$A14,'Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$79,'Picks'!$H$2:$H$79,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$48,'Picks'!$H$2:$H$48,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$79,'Picks'!$H$2:$H$79,$A14,'Picks'!$U$2:$U$79,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$48,'Picks'!$H$2:$H$48,$A14,'Picks'!$U$2:$U$48,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$79,$A15,'Picks'!$U$2:$U$79,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$48,$A15,'Picks'!$U$2:$U$48,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$79,$A15,'Picks'!$U$2:$U$79,"settled",'Picks'!$V$2:$V$79,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$48,$A15,'Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$79,$A15,'Picks'!$U$2:$U$79,"settled",'Picks'!$V$2:$V$79,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$48,$A15,'Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$79,'Picks'!$H$2:$H$79,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$48,'Picks'!$H$2:$H$48,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$79,'Picks'!$H$2:$H$79,$A15,'Picks'!$U$2:$U$79,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$48,'Picks'!$H$2:$H$48,$A15,'Picks'!$U$2:$U$48,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$79,$A16,'Picks'!$U$2:$U$79,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$48,$A16,'Picks'!$U$2:$U$48,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$79,$A16,'Picks'!$U$2:$U$79,"settled",'Picks'!$V$2:$V$79,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$48,$A16,'Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$79,$A16,'Picks'!$U$2:$U$79,"settled",'Picks'!$V$2:$V$79,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$48,$A16,'Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$79,'Picks'!$H$2:$H$79,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$48,'Picks'!$H$2:$H$48,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$79,'Picks'!$H$2:$H$79,$A16,'Picks'!$U$2:$U$79,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$48,'Picks'!$H$2:$H$48,$A16,'Picks'!$U$2:$U$48,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS79"/>
+  <dimension ref="A1:CS48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14970,22 +14970,22 @@
     <row r="46" ht="36" customHeight="1">
       <c r="A46" s="24" t="inlineStr">
         <is>
-          <t>19abf39469cc4d0c</t>
+          <t>2a3c60fe55c84636</t>
         </is>
       </c>
       <c r="B46" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:54:09.180176Z</t>
+          <t>2026-08-05T21:01:36.734850Z</t>
         </is>
       </c>
       <c r="C46" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T15:10:00-0400</t>
+          <t>2026-08-05T23:30Z</t>
         </is>
       </c>
       <c r="D46" s="24" t="inlineStr">
         <is>
-          <t>401816411</t>
+          <t>401816408</t>
         </is>
       </c>
       <c r="E46" s="24" t="inlineStr">
@@ -14995,84 +14995,110 @@
       </c>
       <c r="F46" s="24" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="G46" s="24" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="H46" s="24" t="inlineStr">
         <is>
-          <t>moneyline</t>
+          <t>total</t>
         </is>
       </c>
       <c r="I46" s="24" t="inlineStr">
         <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J46" s="25" t="n"/>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J46" s="25" t="n">
+        <v>7.5</v>
+      </c>
       <c r="K46" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L46" s="26" t="n">
-        <v>-153</v>
+        <v>127</v>
       </c>
       <c r="M46" s="27" t="n">
-        <v>1.653595</v>
+        <v>2.27</v>
       </c>
       <c r="N46" s="28" t="n">
-        <v>0.604743</v>
+        <v>0.440529</v>
       </c>
       <c r="O46" s="28" t="n">
-        <v>0.651358</v>
-      </c>
-      <c r="P46" s="28" t="n"/>
+        <v>0.527212</v>
+      </c>
+      <c r="P46" s="28" t="n">
+        <v>0.042131</v>
+      </c>
       <c r="Q46" s="28" t="n">
-        <v>0.046615</v>
+        <v>0.086683</v>
       </c>
       <c r="R46" s="26" t="n">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="S46" s="29" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="T46" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v8</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="U46" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V46" s="24" t="n"/>
-      <c r="W46" s="26" t="n"/>
-      <c r="X46" s="26" t="n"/>
-      <c r="Y46" s="25" t="n"/>
-      <c r="Z46" s="26" t="n"/>
-      <c r="AA46" s="28" t="n"/>
-      <c r="AB46" s="28" t="n"/>
-      <c r="AC46" s="30" t="n"/>
-      <c r="AD46" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V46" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W46" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="X46" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y46" s="25" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Z46" s="26" t="n">
+        <v>127</v>
+      </c>
+      <c r="AA46" s="28" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AB46" s="28" t="n">
+        <v>-0.000529</v>
+      </c>
+      <c r="AC46" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD46" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T03:25:25.925315Z</t>
+        </is>
+      </c>
       <c r="AE46" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5873; executable ask 0.6050 (aec-mlb-tb-col-2026-08-05); model edge vs ask +0.0464.</t>
+          <t>Measured Edge Totals: Trend Engine projected 4.27-4.68; raw selected-side p=0.5862, calibrated p=0.5272.</t>
         </is>
       </c>
       <c r="AF46" s="31" t="inlineStr">
         <is>
-          <t>Learned model; shadow-qualified via operator override.</t>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
         </is>
       </c>
       <c r="AG46" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH46" s="24" t="n"/>
@@ -15103,32 +15129,32 @@
       </c>
       <c r="AP46" s="24" t="inlineStr">
         <is>
-          <t>mlb-tb</t>
+          <t>mlb-pit</t>
         </is>
       </c>
       <c r="AQ46" s="24" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="AR46" s="24" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="AS46" s="24" t="inlineStr">
         <is>
-          <t>mlb-col</t>
+          <t>mlb-mil</t>
         </is>
       </c>
       <c r="AT46" s="24" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="AU46" s="24" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="AV46" s="24" t="n"/>
@@ -15141,32 +15167,32 @@
       <c r="AY46" s="24" t="n"/>
       <c r="AZ46" s="24" t="inlineStr">
         <is>
-          <t>shadow_qualified</t>
+          <t>research</t>
         </is>
       </c>
       <c r="BA46" s="24" t="inlineStr">
         <is>
-          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BB46" s="24" t="inlineStr">
         <is>
-          <t>learned_lr</t>
+          <t>flat_probability_shrinkage_toward_half</t>
         </is>
       </c>
       <c r="BC46" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v8</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="BD46" s="24" t="inlineStr">
         <is>
-          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BE46" s="24" t="inlineStr">
         <is>
-          <t>133a0f8d2d67fce5</t>
+          <t>v3</t>
         </is>
       </c>
       <c r="BF46" s="24" t="inlineStr">
@@ -15176,12 +15202,12 @@
       </c>
       <c r="BG46" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v8</t>
+          <t>measured-edge-paired-v1</t>
         </is>
       </c>
       <c r="BH46" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:52:26.086277Z</t>
+          <t>2026-08-05T21:01:36.734850Z</t>
         </is>
       </c>
       <c r="BI46" s="24" t="inlineStr">
@@ -15189,23 +15215,29 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ46" s="25" t="n"/>
+      <c r="BJ46" s="25" t="n">
+        <v>7.5</v>
+      </c>
       <c r="BK46" s="26" t="n">
-        <v>-153</v>
+        <v>127</v>
       </c>
       <c r="BL46" s="27" t="n">
-        <v>1.653595</v>
+        <v>2.27</v>
       </c>
       <c r="BM46" s="28" t="n">
-        <v>0.604743</v>
+        <v>0.440529</v>
       </c>
       <c r="BN46" s="28" t="n">
-        <v>0.60199</v>
+        <v>0.437811</v>
       </c>
       <c r="BO46" s="28" t="n"/>
       <c r="BP46" s="25" t="n"/>
-      <c r="BQ46" s="27" t="n"/>
-      <c r="BR46" s="28" t="n"/>
+      <c r="BQ46" s="27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BR46" s="28" t="n">
+        <v>0.44</v>
+      </c>
       <c r="BS46" s="28" t="n"/>
       <c r="BT46" s="28" t="n"/>
       <c r="BU46" s="25" t="n"/>
@@ -15216,54 +15248,22 @@
       <c r="BZ46" s="24" t="n"/>
       <c r="CA46" s="31" t="n"/>
       <c r="CB46" s="24" t="n"/>
-      <c r="CC46" s="24" t="inlineStr">
-        <is>
-          <t>0.3717088646</t>
-        </is>
-      </c>
-      <c r="CD46" s="24" t="inlineStr">
-        <is>
-          <t>1.48701</t>
-        </is>
-      </c>
-      <c r="CE46" s="24" t="inlineStr">
-        <is>
-          <t>1.193</t>
-        </is>
-      </c>
-      <c r="CF46" s="24" t="inlineStr">
-        <is>
-          <t>1.0096</t>
-        </is>
-      </c>
+      <c r="CC46" s="24" t="n"/>
+      <c r="CD46" s="24" t="n"/>
+      <c r="CE46" s="24" t="n"/>
+      <c r="CF46" s="24" t="n"/>
       <c r="CG46" s="24" t="n"/>
       <c r="CH46" s="24" t="n"/>
       <c r="CI46" s="24" t="n"/>
-      <c r="CJ46" s="24" t="inlineStr">
-        <is>
-          <t>0.458973</t>
-        </is>
-      </c>
+      <c r="CJ46" s="24" t="n"/>
       <c r="CK46" s="24" t="n"/>
-      <c r="CL46" s="24" t="inlineStr">
-        <is>
-          <t>0.032773</t>
-        </is>
-      </c>
-      <c r="CM46" s="24" t="inlineStr">
-        <is>
-          <t>3.3324</t>
-        </is>
-      </c>
+      <c r="CL46" s="24" t="n"/>
+      <c r="CM46" s="24" t="n"/>
       <c r="CN46" s="24" t="n"/>
       <c r="CO46" s="24" t="n"/>
       <c r="CP46" s="24" t="n"/>
       <c r="CQ46" s="24" t="n"/>
-      <c r="CR46" s="24" t="inlineStr">
-        <is>
-          <t>0.651358</t>
-        </is>
-      </c>
+      <c r="CR46" s="24" t="n"/>
       <c r="CS46" s="24" t="inlineStr">
         <is>
           <t>True</t>
@@ -15273,22 +15273,22 @@
     <row r="47" ht="36" customHeight="1">
       <c r="A47" s="24" t="inlineStr">
         <is>
-          <t>3f8c04156c7845ce</t>
+          <t>9581ac3086d84147</t>
         </is>
       </c>
       <c r="B47" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:54:09.180176Z</t>
+          <t>2026-08-07T15:22:19.501521Z</t>
         </is>
       </c>
       <c r="C47" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T18:35:00-0400</t>
+          <t>2026-08-08T00:10Z</t>
         </is>
       </c>
       <c r="D47" s="24" t="inlineStr">
         <is>
-          <t>401816399</t>
+          <t>401816431</t>
         </is>
       </c>
       <c r="E47" s="24" t="inlineStr">
@@ -15298,17 +15298,17 @@
       </c>
       <c r="F47" s="24" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="G47" s="24" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="H47" s="24" t="inlineStr">
         <is>
-          <t>moneyline</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="I47" s="24" t="inlineStr">
@@ -15316,37 +15316,41 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J47" s="25" t="n"/>
+      <c r="J47" s="25" t="n">
+        <v>1.5</v>
+      </c>
       <c r="K47" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L47" s="26" t="n">
-        <v>-117</v>
+        <v>-104</v>
       </c>
       <c r="M47" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.961538</v>
       </c>
       <c r="N47" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.509804</v>
       </c>
       <c r="O47" s="28" t="n">
-        <v>0.620156</v>
-      </c>
-      <c r="P47" s="28" t="n"/>
+        <v>0.655325</v>
+      </c>
+      <c r="P47" s="28" t="n">
+        <v>0.042131</v>
+      </c>
       <c r="Q47" s="28" t="n">
-        <v>0.080985</v>
+        <v>0.145521</v>
       </c>
       <c r="R47" s="26" t="n">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="S47" s="29" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="T47" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v8</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="U47" s="24" t="inlineStr">
@@ -15365,12 +15369,12 @@
       <c r="AD47" s="24" t="n"/>
       <c r="AE47" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5873; executable ask 0.5400 (aec-mlb-laa-bal-2026-08-05); model edge vs ask +0.0802.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.08-4.72; raw selected-side p=0.7279, calibrated p=0.6553.</t>
         </is>
       </c>
       <c r="AF47" s="31" t="inlineStr">
         <is>
-          <t>Learned model; shadow-qualified via operator override.</t>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
         </is>
       </c>
       <c r="AG47" s="24" t="inlineStr">
@@ -15406,32 +15410,32 @@
       </c>
       <c r="AP47" s="24" t="inlineStr">
         <is>
-          <t>mlb-laa</t>
+          <t>mlb-chc</t>
         </is>
       </c>
       <c r="AQ47" s="24" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="AR47" s="24" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="AS47" s="24" t="inlineStr">
         <is>
-          <t>mlb-bal</t>
+          <t>mlb-kc</t>
         </is>
       </c>
       <c r="AT47" s="24" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="AU47" s="24" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="AV47" s="24" t="n"/>
@@ -15444,32 +15448,32 @@
       <c r="AY47" s="24" t="n"/>
       <c r="AZ47" s="24" t="inlineStr">
         <is>
-          <t>shadow_qualified</t>
+          <t>research</t>
         </is>
       </c>
       <c r="BA47" s="24" t="inlineStr">
         <is>
-          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BB47" s="24" t="inlineStr">
         <is>
-          <t>learned_lr</t>
+          <t>flat_probability_shrinkage_toward_half</t>
         </is>
       </c>
       <c r="BC47" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v8</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="BD47" s="24" t="inlineStr">
         <is>
-          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BE47" s="24" t="inlineStr">
         <is>
-          <t>90250452b4135146</t>
+          <t>v3</t>
         </is>
       </c>
       <c r="BF47" s="24" t="inlineStr">
@@ -15479,12 +15483,12 @@
       </c>
       <c r="BG47" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v8</t>
+          <t>measured-edge-paired-v1</t>
         </is>
       </c>
       <c r="BH47" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:52:26.546603Z</t>
+          <t>2026-08-07T15:22:19.501521Z</t>
         </is>
       </c>
       <c r="BI47" s="24" t="inlineStr">
@@ -15492,18 +15496,20 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ47" s="25" t="n"/>
+      <c r="BJ47" s="25" t="n">
+        <v>1.5</v>
+      </c>
       <c r="BK47" s="26" t="n">
-        <v>-117</v>
+        <v>-104</v>
       </c>
       <c r="BL47" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.961538</v>
       </c>
       <c r="BM47" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.509804</v>
       </c>
       <c r="BN47" s="28" t="n">
-        <v>0.537313</v>
+        <v>0.507463</v>
       </c>
       <c r="BO47" s="28" t="n"/>
       <c r="BP47" s="25" t="n"/>
@@ -15519,54 +15525,22 @@
       <c r="BZ47" s="24" t="n"/>
       <c r="CA47" s="31" t="n"/>
       <c r="CB47" s="24" t="n"/>
-      <c r="CC47" s="24" t="inlineStr">
-        <is>
-          <t>0.6265993564</t>
-        </is>
-      </c>
-      <c r="CD47" s="24" t="inlineStr">
-        <is>
-          <t>0.186002</t>
-        </is>
-      </c>
-      <c r="CE47" s="24" t="inlineStr">
-        <is>
-          <t>1.03</t>
-        </is>
-      </c>
-      <c r="CF47" s="24" t="inlineStr">
-        <is>
-          <t>1.012</t>
-        </is>
-      </c>
+      <c r="CC47" s="24" t="n"/>
+      <c r="CD47" s="24" t="n"/>
+      <c r="CE47" s="24" t="n"/>
+      <c r="CF47" s="24" t="n"/>
       <c r="CG47" s="24" t="n"/>
       <c r="CH47" s="24" t="n"/>
       <c r="CI47" s="24" t="n"/>
-      <c r="CJ47" s="24" t="inlineStr">
-        <is>
-          <t>-1.60185</t>
-        </is>
-      </c>
+      <c r="CJ47" s="24" t="n"/>
       <c r="CK47" s="24" t="n"/>
-      <c r="CL47" s="24" t="inlineStr">
-        <is>
-          <t>0.070802</t>
-        </is>
-      </c>
-      <c r="CM47" s="24" t="inlineStr">
-        <is>
-          <t>-4.8571</t>
-        </is>
-      </c>
+      <c r="CL47" s="24" t="n"/>
+      <c r="CM47" s="24" t="n"/>
       <c r="CN47" s="24" t="n"/>
       <c r="CO47" s="24" t="n"/>
       <c r="CP47" s="24" t="n"/>
       <c r="CQ47" s="24" t="n"/>
-      <c r="CR47" s="24" t="inlineStr">
-        <is>
-          <t>0.620156</t>
-        </is>
-      </c>
+      <c r="CR47" s="24" t="n"/>
       <c r="CS47" s="24" t="inlineStr">
         <is>
           <t>True</t>
@@ -15576,22 +15550,22 @@
     <row r="48" ht="36" customHeight="1">
       <c r="A48" s="24" t="inlineStr">
         <is>
-          <t>130e866c4e914279</t>
+          <t>3b3245b6b87e40d5</t>
         </is>
       </c>
       <c r="B48" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:54:09.180176Z</t>
+          <t>2026-08-07T15:22:19.501521Z</t>
         </is>
       </c>
       <c r="C48" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T19:15:00-0400</t>
+          <t>2026-08-08T01:40Z</t>
         </is>
       </c>
       <c r="D48" s="24" t="inlineStr">
         <is>
-          <t>401816402</t>
+          <t>401816437</t>
         </is>
       </c>
       <c r="E48" s="24" t="inlineStr">
@@ -15601,17 +15575,17 @@
       </c>
       <c r="F48" s="24" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="G48" s="24" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="H48" s="24" t="inlineStr">
         <is>
-          <t>moneyline</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="I48" s="24" t="inlineStr">
@@ -15619,37 +15593,41 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J48" s="25" t="n"/>
+      <c r="J48" s="25" t="n">
+        <v>1.5</v>
+      </c>
       <c r="K48" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L48" s="26" t="n">
-        <v>-120</v>
+        <v>100</v>
       </c>
       <c r="M48" s="27" t="n">
-        <v>1.833333</v>
+        <v>2</v>
       </c>
       <c r="N48" s="28" t="n">
-        <v>0.545455</v>
+        <v>0.5</v>
       </c>
       <c r="O48" s="28" t="n">
-        <v>0.590933</v>
-      </c>
-      <c r="P48" s="28" t="n"/>
+        <v>0.627047</v>
+      </c>
+      <c r="P48" s="28" t="n">
+        <v>0.042131</v>
+      </c>
       <c r="Q48" s="28" t="n">
-        <v>0.045478</v>
+        <v>0.127047</v>
       </c>
       <c r="R48" s="26" t="n">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="S48" s="29" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="T48" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v8</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="U48" s="24" t="inlineStr">
@@ -15668,12 +15646,12 @@
       <c r="AD48" s="24" t="n"/>
       <c r="AE48" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.5873; executable ask 0.5450 (aec-mlb-mia-atl-2026-08-05); model edge vs ask +0.0459. NOTE: NO_CALL_STARTER_ERA_GAP_INSUFFICIENT_HISTORY unavailable for this game — defaulted to neutral, other features used normally.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.62-4.87; raw selected-side p=0.6865, calibrated p=0.6270.</t>
         </is>
       </c>
       <c r="AF48" s="31" t="inlineStr">
         <is>
-          <t>Learned model; shadow-qualified via operator override.</t>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
         </is>
       </c>
       <c r="AG48" s="24" t="inlineStr">
@@ -15709,32 +15687,32 @@
       </c>
       <c r="AP48" s="24" t="inlineStr">
         <is>
-          <t>mlb-mia</t>
+          <t>mlb-lad</t>
         </is>
       </c>
       <c r="AQ48" s="24" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="AR48" s="24" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="AS48" s="24" t="inlineStr">
         <is>
-          <t>mlb-atl</t>
+          <t>mlb-ari</t>
         </is>
       </c>
       <c r="AT48" s="24" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="AU48" s="24" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="AV48" s="24" t="n"/>
@@ -15747,32 +15725,32 @@
       <c r="AY48" s="24" t="n"/>
       <c r="AZ48" s="24" t="inlineStr">
         <is>
-          <t>shadow_qualified</t>
+          <t>research</t>
         </is>
       </c>
       <c r="BA48" s="24" t="inlineStr">
         <is>
-          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BB48" s="24" t="inlineStr">
         <is>
-          <t>learned_lr</t>
+          <t>flat_probability_shrinkage_toward_half</t>
         </is>
       </c>
       <c r="BC48" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v8</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="BD48" s="24" t="inlineStr">
         <is>
-          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BE48" s="24" t="inlineStr">
         <is>
-          <t>06a32b1aa50e018d</t>
+          <t>v3</t>
         </is>
       </c>
       <c r="BF48" s="24" t="inlineStr">
@@ -15782,12 +15760,12 @@
       </c>
       <c r="BG48" s="24" t="inlineStr">
         <is>
-          <t>mlb-elo-trend-lr-v8</t>
+          <t>measured-edge-paired-v1</t>
         </is>
       </c>
       <c r="BH48" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:52:29.624655Z</t>
+          <t>2026-08-07T15:22:19.501521Z</t>
         </is>
       </c>
       <c r="BI48" s="24" t="inlineStr">
@@ -15795,18 +15773,20 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ48" s="25" t="n"/>
+      <c r="BJ48" s="25" t="n">
+        <v>1.5</v>
+      </c>
       <c r="BK48" s="26" t="n">
-        <v>-120</v>
+        <v>100</v>
       </c>
       <c r="BL48" s="27" t="n">
-        <v>1.833333</v>
+        <v>2</v>
       </c>
       <c r="BM48" s="28" t="n">
-        <v>0.545455</v>
+        <v>0.5</v>
       </c>
       <c r="BN48" s="28" t="n">
-        <v>0.542289</v>
+        <v>0.497512</v>
       </c>
       <c r="BO48" s="28" t="n"/>
       <c r="BP48" s="25" t="n"/>
@@ -15822,8674 +15802,25 @@
       <c r="BZ48" s="24" t="n"/>
       <c r="CA48" s="31" t="n"/>
       <c r="CB48" s="24" t="n"/>
-      <c r="CC48" s="24" t="inlineStr">
-        <is>
-          <t>0.5924601602</t>
-        </is>
-      </c>
-      <c r="CD48" s="24" t="inlineStr">
-        <is>
-          <t>0.154672</t>
-        </is>
-      </c>
-      <c r="CE48" s="24" t="inlineStr">
-        <is>
-          <t>0.929</t>
-        </is>
-      </c>
-      <c r="CF48" s="24" t="inlineStr">
-        <is>
-          <t>1.0066</t>
-        </is>
-      </c>
+      <c r="CC48" s="24" t="n"/>
+      <c r="CD48" s="24" t="n"/>
+      <c r="CE48" s="24" t="n"/>
+      <c r="CF48" s="24" t="n"/>
       <c r="CG48" s="24" t="n"/>
       <c r="CH48" s="24" t="n"/>
-      <c r="CI48" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_STARTER_ERA_GAP_INSUFFICIENT_HISTORY</t>
-        </is>
-      </c>
-      <c r="CJ48" s="24" t="inlineStr">
-        <is>
-          <t>0.044324</t>
-        </is>
-      </c>
+      <c r="CI48" s="24" t="n"/>
+      <c r="CJ48" s="24" t="n"/>
       <c r="CK48" s="24" t="n"/>
-      <c r="CL48" s="24" t="inlineStr">
-        <is>
-          <t>-0.05834</t>
-        </is>
-      </c>
-      <c r="CM48" s="24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="CL48" s="24" t="n"/>
+      <c r="CM48" s="24" t="n"/>
       <c r="CN48" s="24" t="n"/>
       <c r="CO48" s="24" t="n"/>
       <c r="CP48" s="24" t="n"/>
       <c r="CQ48" s="24" t="n"/>
-      <c r="CR48" s="24" t="inlineStr">
-        <is>
-          <t>0.590933</t>
-        </is>
-      </c>
+      <c r="CR48" s="24" t="n"/>
       <c r="CS48" s="24" t="inlineStr">
         <is>
           <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="36" customHeight="1">
-      <c r="A49" s="24" t="inlineStr">
-        <is>
-          <t>2440471e155946a7</t>
-        </is>
-      </c>
-      <c r="B49" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:09.180176Z</t>
-        </is>
-      </c>
-      <c r="C49" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T19:30:00-0400</t>
-        </is>
-      </c>
-      <c r="D49" s="24" t="inlineStr">
-        <is>
-          <t>401816408</t>
-        </is>
-      </c>
-      <c r="E49" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F49" s="24" t="inlineStr">
-        <is>
-          <t>Pittsburgh Pirates</t>
-        </is>
-      </c>
-      <c r="G49" s="24" t="inlineStr">
-        <is>
-          <t>Milwaukee Brewers</t>
-        </is>
-      </c>
-      <c r="H49" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I49" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J49" s="25" t="n"/>
-      <c r="K49" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L49" s="26" t="n">
-        <v>-125</v>
-      </c>
-      <c r="M49" s="27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="N49" s="28" t="n">
-        <v>0.555556</v>
-      </c>
-      <c r="O49" s="28" t="n">
-        <v>0.6155080000000001</v>
-      </c>
-      <c r="P49" s="28" t="n"/>
-      <c r="Q49" s="28" t="n">
-        <v>0.059952</v>
-      </c>
-      <c r="R49" s="26" t="n">
-        <v>52</v>
-      </c>
-      <c r="S49" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T49" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v8</t>
-        </is>
-      </c>
-      <c r="U49" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V49" s="24" t="n"/>
-      <c r="W49" s="26" t="n"/>
-      <c r="X49" s="26" t="n"/>
-      <c r="Y49" s="25" t="n"/>
-      <c r="Z49" s="26" t="n"/>
-      <c r="AA49" s="28" t="n"/>
-      <c r="AB49" s="28" t="n"/>
-      <c r="AC49" s="30" t="n"/>
-      <c r="AD49" s="24" t="n"/>
-      <c r="AE49" s="31" t="inlineStr">
-        <is>
-          <t>Learned LR call at threshold 0.5873; executable ask 0.5550 (aec-mlb-pit-mil-2026-08-05); model edge vs ask +0.0605.</t>
-        </is>
-      </c>
-      <c r="AF49" s="31" t="inlineStr">
-        <is>
-          <t>Learned model; shadow-qualified via operator override.</t>
-        </is>
-      </c>
-      <c r="AG49" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH49" s="24" t="n"/>
-      <c r="AI49" s="31" t="n"/>
-      <c r="AJ49" s="31" t="n"/>
-      <c r="AK49" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL49" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM49" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN49" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO49" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP49" s="24" t="inlineStr">
-        <is>
-          <t>mlb-pit</t>
-        </is>
-      </c>
-      <c r="AQ49" s="24" t="inlineStr">
-        <is>
-          <t>Pittsburgh Pirates</t>
-        </is>
-      </c>
-      <c r="AR49" s="24" t="inlineStr">
-        <is>
-          <t>Pittsburgh Pirates</t>
-        </is>
-      </c>
-      <c r="AS49" s="24" t="inlineStr">
-        <is>
-          <t>mlb-mil</t>
-        </is>
-      </c>
-      <c r="AT49" s="24" t="inlineStr">
-        <is>
-          <t>Milwaukee Brewers</t>
-        </is>
-      </c>
-      <c r="AU49" s="24" t="inlineStr">
-        <is>
-          <t>Milwaukee Brewers</t>
-        </is>
-      </c>
-      <c r="AV49" s="24" t="n"/>
-      <c r="AW49" s="24" t="n"/>
-      <c r="AX49" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY49" s="24" t="n"/>
-      <c r="AZ49" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA49" s="24" t="inlineStr">
-        <is>
-          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
-        </is>
-      </c>
-      <c r="BB49" s="24" t="inlineStr">
-        <is>
-          <t>learned_lr</t>
-        </is>
-      </c>
-      <c r="BC49" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v8</t>
-        </is>
-      </c>
-      <c r="BD49" s="24" t="inlineStr">
-        <is>
-          <t>6a5c79541b0e50cb9f7318270e63d5ccc65cbd7bc53a019748ff772d49de5075</t>
-        </is>
-      </c>
-      <c r="BE49" s="24" t="inlineStr">
-        <is>
-          <t>23aa584b6028ab97</t>
-        </is>
-      </c>
-      <c r="BF49" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG49" s="24" t="inlineStr">
-        <is>
-          <t>mlb-elo-trend-lr-v8</t>
-        </is>
-      </c>
-      <c r="BH49" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:52:30.079092Z</t>
-        </is>
-      </c>
-      <c r="BI49" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ49" s="25" t="n"/>
-      <c r="BK49" s="26" t="n">
-        <v>-125</v>
-      </c>
-      <c r="BL49" s="27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BM49" s="28" t="n">
-        <v>0.555556</v>
-      </c>
-      <c r="BN49" s="28" t="n">
-        <v>0.552239</v>
-      </c>
-      <c r="BO49" s="28" t="n"/>
-      <c r="BP49" s="25" t="n"/>
-      <c r="BQ49" s="27" t="n"/>
-      <c r="BR49" s="28" t="n"/>
-      <c r="BS49" s="28" t="n"/>
-      <c r="BT49" s="28" t="n"/>
-      <c r="BU49" s="25" t="n"/>
-      <c r="BV49" s="29" t="n"/>
-      <c r="BW49" s="24" t="n"/>
-      <c r="BX49" s="30" t="n"/>
-      <c r="BY49" s="27" t="n"/>
-      <c r="BZ49" s="24" t="n"/>
-      <c r="CA49" s="31" t="n"/>
-      <c r="CB49" s="24" t="n"/>
-      <c r="CC49" s="24" t="inlineStr">
-        <is>
-          <t>0.6284314187</t>
-        </is>
-      </c>
-      <c r="CD49" s="24" t="inlineStr">
-        <is>
-          <t>0.320781</t>
-        </is>
-      </c>
-      <c r="CE49" s="24" t="inlineStr">
-        <is>
-          <t>0.997</t>
-        </is>
-      </c>
-      <c r="CF49" s="24" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="CG49" s="24" t="n"/>
-      <c r="CH49" s="24" t="n"/>
-      <c r="CI49" s="24" t="n"/>
-      <c r="CJ49" s="24" t="inlineStr">
-        <is>
-          <t>0.061913</t>
-        </is>
-      </c>
-      <c r="CK49" s="24" t="n"/>
-      <c r="CL49" s="24" t="inlineStr">
-        <is>
-          <t>0.125345</t>
-        </is>
-      </c>
-      <c r="CM49" s="24" t="inlineStr">
-        <is>
-          <t>-1.5183</t>
-        </is>
-      </c>
-      <c r="CN49" s="24" t="n"/>
-      <c r="CO49" s="24" t="n"/>
-      <c r="CP49" s="24" t="n"/>
-      <c r="CQ49" s="24" t="n"/>
-      <c r="CR49" s="24" t="inlineStr">
-        <is>
-          <t>0.615508</t>
-        </is>
-      </c>
-      <c r="CS49" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="36" customHeight="1">
-      <c r="A50" s="24" t="inlineStr">
-        <is>
-          <t>7d9c71814d1948ec</t>
-        </is>
-      </c>
-      <c r="B50" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="C50" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T18:10Z</t>
-        </is>
-      </c>
-      <c r="D50" s="24" t="inlineStr">
-        <is>
-          <t>401816410</t>
-        </is>
-      </c>
-      <c r="E50" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F50" s="24" t="inlineStr">
-        <is>
-          <t>Toronto Blue Jays</t>
-        </is>
-      </c>
-      <c r="G50" s="24" t="inlineStr">
-        <is>
-          <t>Houston Astros</t>
-        </is>
-      </c>
-      <c r="H50" s="24" t="inlineStr">
-        <is>
-          <t>spread</t>
-        </is>
-      </c>
-      <c r="I50" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J50" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K50" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L50" s="26" t="n">
-        <v>-122</v>
-      </c>
-      <c r="M50" s="27" t="n">
-        <v>1.819672</v>
-      </c>
-      <c r="N50" s="28" t="n">
-        <v>0.54955</v>
-      </c>
-      <c r="O50" s="28" t="n">
-        <v>0.554069</v>
-      </c>
-      <c r="P50" s="28" t="n">
-        <v>0.042131</v>
-      </c>
-      <c r="Q50" s="28" t="n">
-        <v>0.004519</v>
-      </c>
-      <c r="R50" s="26" t="n">
-        <v>28</v>
-      </c>
-      <c r="S50" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T50" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-margin-v3</t>
-        </is>
-      </c>
-      <c r="U50" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V50" s="24" t="n"/>
-      <c r="W50" s="26" t="n"/>
-      <c r="X50" s="26" t="n"/>
-      <c r="Y50" s="25" t="n"/>
-      <c r="Z50" s="26" t="n"/>
-      <c r="AA50" s="28" t="n"/>
-      <c r="AB50" s="28" t="n"/>
-      <c r="AC50" s="30" t="n"/>
-      <c r="AD50" s="24" t="n"/>
-      <c r="AE50" s="31" t="inlineStr">
-        <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.45-5.29; raw selected-side p=0.5794, calibrated p=0.5541.</t>
-        </is>
-      </c>
-      <c r="AF50" s="31" t="inlineStr">
-        <is>
-          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
-        </is>
-      </c>
-      <c r="AG50" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH50" s="24" t="n"/>
-      <c r="AI50" s="31" t="n"/>
-      <c r="AJ50" s="31" t="n"/>
-      <c r="AK50" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL50" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM50" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN50" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO50" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP50" s="24" t="inlineStr">
-        <is>
-          <t>mlb-tor</t>
-        </is>
-      </c>
-      <c r="AQ50" s="24" t="inlineStr">
-        <is>
-          <t>Toronto Blue Jays</t>
-        </is>
-      </c>
-      <c r="AR50" s="24" t="inlineStr">
-        <is>
-          <t>Toronto Blue Jays</t>
-        </is>
-      </c>
-      <c r="AS50" s="24" t="inlineStr">
-        <is>
-          <t>mlb-hou</t>
-        </is>
-      </c>
-      <c r="AT50" s="24" t="inlineStr">
-        <is>
-          <t>Houston Astros</t>
-        </is>
-      </c>
-      <c r="AU50" s="24" t="inlineStr">
-        <is>
-          <t>Houston Astros</t>
-        </is>
-      </c>
-      <c r="AV50" s="24" t="n"/>
-      <c r="AW50" s="24" t="n"/>
-      <c r="AX50" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY50" s="24" t="n"/>
-      <c r="AZ50" s="24" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="BA50" s="24" t="inlineStr">
-        <is>
-          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
-        </is>
-      </c>
-      <c r="BB50" s="24" t="inlineStr">
-        <is>
-          <t>flat_probability_shrinkage_toward_half</t>
-        </is>
-      </c>
-      <c r="BC50" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-margin-v3</t>
-        </is>
-      </c>
-      <c r="BD50" s="24" t="inlineStr">
-        <is>
-          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
-        </is>
-      </c>
-      <c r="BE50" s="24" t="inlineStr">
-        <is>
-          <t>v3</t>
-        </is>
-      </c>
-      <c r="BF50" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG50" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-paired-v1</t>
-        </is>
-      </c>
-      <c r="BH50" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="BI50" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ50" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BK50" s="26" t="n">
-        <v>-122</v>
-      </c>
-      <c r="BL50" s="27" t="n">
-        <v>1.819672</v>
-      </c>
-      <c r="BM50" s="28" t="n">
-        <v>0.54955</v>
-      </c>
-      <c r="BN50" s="28" t="n">
-        <v>0.547264</v>
-      </c>
-      <c r="BO50" s="28" t="n"/>
-      <c r="BP50" s="25" t="n"/>
-      <c r="BQ50" s="27" t="n"/>
-      <c r="BR50" s="28" t="n"/>
-      <c r="BS50" s="28" t="n"/>
-      <c r="BT50" s="28" t="n"/>
-      <c r="BU50" s="25" t="n"/>
-      <c r="BV50" s="29" t="n"/>
-      <c r="BW50" s="24" t="n"/>
-      <c r="BX50" s="30" t="n"/>
-      <c r="BY50" s="27" t="n"/>
-      <c r="BZ50" s="24" t="n"/>
-      <c r="CA50" s="31" t="n"/>
-      <c r="CB50" s="24" t="n"/>
-      <c r="CC50" s="24" t="n"/>
-      <c r="CD50" s="24" t="n"/>
-      <c r="CE50" s="24" t="n"/>
-      <c r="CF50" s="24" t="n"/>
-      <c r="CG50" s="24" t="n"/>
-      <c r="CH50" s="24" t="n"/>
-      <c r="CI50" s="24" t="n"/>
-      <c r="CJ50" s="24" t="n"/>
-      <c r="CK50" s="24" t="n"/>
-      <c r="CL50" s="24" t="n"/>
-      <c r="CM50" s="24" t="n"/>
-      <c r="CN50" s="24" t="n"/>
-      <c r="CO50" s="24" t="n"/>
-      <c r="CP50" s="24" t="n"/>
-      <c r="CQ50" s="24" t="n"/>
-      <c r="CR50" s="24" t="n"/>
-      <c r="CS50" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="36" customHeight="1">
-      <c r="A51" s="24" t="inlineStr">
-        <is>
-          <t>967334ce4e8e44dc</t>
-        </is>
-      </c>
-      <c r="B51" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="C51" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T18:10Z</t>
-        </is>
-      </c>
-      <c r="D51" s="24" t="inlineStr">
-        <is>
-          <t>401816410</t>
-        </is>
-      </c>
-      <c r="E51" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F51" s="24" t="inlineStr">
-        <is>
-          <t>Toronto Blue Jays</t>
-        </is>
-      </c>
-      <c r="G51" s="24" t="inlineStr">
-        <is>
-          <t>Houston Astros</t>
-        </is>
-      </c>
-      <c r="H51" s="24" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="I51" s="24" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="J51" s="25" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="K51" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L51" s="26" t="n">
-        <v>111</v>
-      </c>
-      <c r="M51" s="27" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="N51" s="28" t="n">
-        <v>0.473934</v>
-      </c>
-      <c r="O51" s="28" t="n">
-        <v>0.525275</v>
-      </c>
-      <c r="P51" s="28" t="n">
-        <v>0.042131</v>
-      </c>
-      <c r="Q51" s="28" t="n">
-        <v>0.051341</v>
-      </c>
-      <c r="R51" s="26" t="n">
-        <v>51</v>
-      </c>
-      <c r="S51" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T51" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-totals-v3</t>
-        </is>
-      </c>
-      <c r="U51" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V51" s="24" t="n"/>
-      <c r="W51" s="26" t="n"/>
-      <c r="X51" s="26" t="n"/>
-      <c r="Y51" s="25" t="n"/>
-      <c r="Z51" s="26" t="n"/>
-      <c r="AA51" s="28" t="n"/>
-      <c r="AB51" s="28" t="n"/>
-      <c r="AC51" s="30" t="n"/>
-      <c r="AD51" s="24" t="n"/>
-      <c r="AE51" s="31" t="inlineStr">
-        <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.45-5.29; raw selected-side p=0.5784, calibrated p=0.5253.</t>
-        </is>
-      </c>
-      <c r="AF51" s="31" t="inlineStr">
-        <is>
-          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
-        </is>
-      </c>
-      <c r="AG51" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH51" s="24" t="n"/>
-      <c r="AI51" s="31" t="n"/>
-      <c r="AJ51" s="31" t="n"/>
-      <c r="AK51" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL51" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM51" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN51" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO51" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP51" s="24" t="inlineStr">
-        <is>
-          <t>mlb-tor</t>
-        </is>
-      </c>
-      <c r="AQ51" s="24" t="inlineStr">
-        <is>
-          <t>Toronto Blue Jays</t>
-        </is>
-      </c>
-      <c r="AR51" s="24" t="inlineStr">
-        <is>
-          <t>Toronto Blue Jays</t>
-        </is>
-      </c>
-      <c r="AS51" s="24" t="inlineStr">
-        <is>
-          <t>mlb-hou</t>
-        </is>
-      </c>
-      <c r="AT51" s="24" t="inlineStr">
-        <is>
-          <t>Houston Astros</t>
-        </is>
-      </c>
-      <c r="AU51" s="24" t="inlineStr">
-        <is>
-          <t>Houston Astros</t>
-        </is>
-      </c>
-      <c r="AV51" s="24" t="n"/>
-      <c r="AW51" s="24" t="n"/>
-      <c r="AX51" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY51" s="24" t="n"/>
-      <c r="AZ51" s="24" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="BA51" s="24" t="inlineStr">
-        <is>
-          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
-        </is>
-      </c>
-      <c r="BB51" s="24" t="inlineStr">
-        <is>
-          <t>flat_probability_shrinkage_toward_half</t>
-        </is>
-      </c>
-      <c r="BC51" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-totals-v3</t>
-        </is>
-      </c>
-      <c r="BD51" s="24" t="inlineStr">
-        <is>
-          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
-        </is>
-      </c>
-      <c r="BE51" s="24" t="inlineStr">
-        <is>
-          <t>v3</t>
-        </is>
-      </c>
-      <c r="BF51" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG51" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-paired-v1</t>
-        </is>
-      </c>
-      <c r="BH51" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="BI51" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ51" s="25" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="BK51" s="26" t="n">
-        <v>111</v>
-      </c>
-      <c r="BL51" s="27" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="BM51" s="28" t="n">
-        <v>0.473934</v>
-      </c>
-      <c r="BN51" s="28" t="n">
-        <v>0.472637</v>
-      </c>
-      <c r="BO51" s="28" t="n"/>
-      <c r="BP51" s="25" t="n"/>
-      <c r="BQ51" s="27" t="n"/>
-      <c r="BR51" s="28" t="n"/>
-      <c r="BS51" s="28" t="n"/>
-      <c r="BT51" s="28" t="n"/>
-      <c r="BU51" s="25" t="n"/>
-      <c r="BV51" s="29" t="n"/>
-      <c r="BW51" s="24" t="n"/>
-      <c r="BX51" s="30" t="n"/>
-      <c r="BY51" s="27" t="n"/>
-      <c r="BZ51" s="24" t="n"/>
-      <c r="CA51" s="31" t="n"/>
-      <c r="CB51" s="24" t="n"/>
-      <c r="CC51" s="24" t="n"/>
-      <c r="CD51" s="24" t="n"/>
-      <c r="CE51" s="24" t="n"/>
-      <c r="CF51" s="24" t="n"/>
-      <c r="CG51" s="24" t="n"/>
-      <c r="CH51" s="24" t="n"/>
-      <c r="CI51" s="24" t="n"/>
-      <c r="CJ51" s="24" t="n"/>
-      <c r="CK51" s="24" t="n"/>
-      <c r="CL51" s="24" t="n"/>
-      <c r="CM51" s="24" t="n"/>
-      <c r="CN51" s="24" t="n"/>
-      <c r="CO51" s="24" t="n"/>
-      <c r="CP51" s="24" t="n"/>
-      <c r="CQ51" s="24" t="n"/>
-      <c r="CR51" s="24" t="n"/>
-      <c r="CS51" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="36" customHeight="1">
-      <c r="A52" s="24" t="inlineStr">
-        <is>
-          <t>7249e78e60894244</t>
-        </is>
-      </c>
-      <c r="B52" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="C52" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T18:20Z</t>
-        </is>
-      </c>
-      <c r="D52" s="24" t="inlineStr">
-        <is>
-          <t>401816406</t>
-        </is>
-      </c>
-      <c r="E52" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F52" s="24" t="inlineStr">
-        <is>
-          <t>Los Angeles Dodgers</t>
-        </is>
-      </c>
-      <c r="G52" s="24" t="inlineStr">
-        <is>
-          <t>Chicago Cubs</t>
-        </is>
-      </c>
-      <c r="H52" s="24" t="inlineStr">
-        <is>
-          <t>spread</t>
-        </is>
-      </c>
-      <c r="I52" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J52" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K52" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L52" s="26" t="n">
-        <v>-174</v>
-      </c>
-      <c r="M52" s="27" t="n">
-        <v>1.574713</v>
-      </c>
-      <c r="N52" s="28" t="n">
-        <v>0.635036</v>
-      </c>
-      <c r="O52" s="28" t="n">
-        <v>0.576862</v>
-      </c>
-      <c r="P52" s="28" t="n">
-        <v>0.042131</v>
-      </c>
-      <c r="Q52" s="28" t="n">
-        <v>-0.058174</v>
-      </c>
-      <c r="R52" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" s="29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T52" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-margin-v3</t>
-        </is>
-      </c>
-      <c r="U52" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V52" s="24" t="n"/>
-      <c r="W52" s="26" t="n"/>
-      <c r="X52" s="26" t="n"/>
-      <c r="Y52" s="25" t="n"/>
-      <c r="Z52" s="26" t="n"/>
-      <c r="AA52" s="28" t="n"/>
-      <c r="AB52" s="28" t="n"/>
-      <c r="AC52" s="30" t="n"/>
-      <c r="AD52" s="24" t="n"/>
-      <c r="AE52" s="31" t="inlineStr">
-        <is>
-          <t>Measured Edge Margin: Trend Engine projected 3.96-4.59; raw selected-side p=0.6128, calibrated p=0.5769.</t>
-        </is>
-      </c>
-      <c r="AF52" s="31" t="inlineStr">
-        <is>
-          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
-        </is>
-      </c>
-      <c r="AG52" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH52" s="24" t="n"/>
-      <c r="AI52" s="31" t="n"/>
-      <c r="AJ52" s="31" t="n"/>
-      <c r="AK52" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL52" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM52" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN52" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO52" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP52" s="24" t="inlineStr">
-        <is>
-          <t>mlb-lad</t>
-        </is>
-      </c>
-      <c r="AQ52" s="24" t="inlineStr">
-        <is>
-          <t>Los Angeles Dodgers</t>
-        </is>
-      </c>
-      <c r="AR52" s="24" t="inlineStr">
-        <is>
-          <t>Los Angeles Dodgers</t>
-        </is>
-      </c>
-      <c r="AS52" s="24" t="inlineStr">
-        <is>
-          <t>mlb-chc</t>
-        </is>
-      </c>
-      <c r="AT52" s="24" t="inlineStr">
-        <is>
-          <t>Chicago Cubs</t>
-        </is>
-      </c>
-      <c r="AU52" s="24" t="inlineStr">
-        <is>
-          <t>Chicago Cubs</t>
-        </is>
-      </c>
-      <c r="AV52" s="24" t="n"/>
-      <c r="AW52" s="24" t="n"/>
-      <c r="AX52" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY52" s="24" t="n"/>
-      <c r="AZ52" s="24" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="BA52" s="24" t="inlineStr">
-        <is>
-          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
-        </is>
-      </c>
-      <c r="BB52" s="24" t="inlineStr">
-        <is>
-          <t>flat_probability_shrinkage_toward_half</t>
-        </is>
-      </c>
-      <c r="BC52" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-margin-v3</t>
-        </is>
-      </c>
-      <c r="BD52" s="24" t="inlineStr">
-        <is>
-          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
-        </is>
-      </c>
-      <c r="BE52" s="24" t="inlineStr">
-        <is>
-          <t>v3</t>
-        </is>
-      </c>
-      <c r="BF52" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG52" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-paired-v1</t>
-        </is>
-      </c>
-      <c r="BH52" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="BI52" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ52" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BK52" s="26" t="n">
-        <v>-174</v>
-      </c>
-      <c r="BL52" s="27" t="n">
-        <v>1.574713</v>
-      </c>
-      <c r="BM52" s="28" t="n">
-        <v>0.635036</v>
-      </c>
-      <c r="BN52" s="28" t="n">
-        <v>0.631841</v>
-      </c>
-      <c r="BO52" s="28" t="n"/>
-      <c r="BP52" s="25" t="n"/>
-      <c r="BQ52" s="27" t="n"/>
-      <c r="BR52" s="28" t="n"/>
-      <c r="BS52" s="28" t="n"/>
-      <c r="BT52" s="28" t="n"/>
-      <c r="BU52" s="25" t="n"/>
-      <c r="BV52" s="29" t="n"/>
-      <c r="BW52" s="24" t="n"/>
-      <c r="BX52" s="30" t="n"/>
-      <c r="BY52" s="27" t="n"/>
-      <c r="BZ52" s="24" t="n"/>
-      <c r="CA52" s="31" t="n"/>
-      <c r="CB52" s="24" t="n"/>
-      <c r="CC52" s="24" t="n"/>
-      <c r="CD52" s="24" t="n"/>
-      <c r="CE52" s="24" t="n"/>
-      <c r="CF52" s="24" t="n"/>
-      <c r="CG52" s="24" t="n"/>
-      <c r="CH52" s="24" t="n"/>
-      <c r="CI52" s="24" t="n"/>
-      <c r="CJ52" s="24" t="n"/>
-      <c r="CK52" s="24" t="n"/>
-      <c r="CL52" s="24" t="n"/>
-      <c r="CM52" s="24" t="n"/>
-      <c r="CN52" s="24" t="n"/>
-      <c r="CO52" s="24" t="n"/>
-      <c r="CP52" s="24" t="n"/>
-      <c r="CQ52" s="24" t="n"/>
-      <c r="CR52" s="24" t="n"/>
-      <c r="CS52" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="36" customHeight="1">
-      <c r="A53" s="24" t="inlineStr">
-        <is>
-          <t>44b24f7ab36a46a8</t>
-        </is>
-      </c>
-      <c r="B53" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="C53" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T18:20Z</t>
-        </is>
-      </c>
-      <c r="D53" s="24" t="inlineStr">
-        <is>
-          <t>401816406</t>
-        </is>
-      </c>
-      <c r="E53" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F53" s="24" t="inlineStr">
-        <is>
-          <t>Los Angeles Dodgers</t>
-        </is>
-      </c>
-      <c r="G53" s="24" t="inlineStr">
-        <is>
-          <t>Chicago Cubs</t>
-        </is>
-      </c>
-      <c r="H53" s="24" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="I53" s="24" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="J53" s="25" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="K53" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L53" s="26" t="n">
-        <v>-104</v>
-      </c>
-      <c r="M53" s="27" t="n">
-        <v>1.961538</v>
-      </c>
-      <c r="N53" s="28" t="n">
-        <v>0.509804</v>
-      </c>
-      <c r="O53" s="28" t="n">
-        <v>0.540166</v>
-      </c>
-      <c r="P53" s="28" t="n">
-        <v>0.042131</v>
-      </c>
-      <c r="Q53" s="28" t="n">
-        <v>0.030362</v>
-      </c>
-      <c r="R53" s="26" t="n">
-        <v>41</v>
-      </c>
-      <c r="S53" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T53" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-totals-v3</t>
-        </is>
-      </c>
-      <c r="U53" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V53" s="24" t="n"/>
-      <c r="W53" s="26" t="n"/>
-      <c r="X53" s="26" t="n"/>
-      <c r="Y53" s="25" t="n"/>
-      <c r="Z53" s="26" t="n"/>
-      <c r="AA53" s="28" t="n"/>
-      <c r="AB53" s="28" t="n"/>
-      <c r="AC53" s="30" t="n"/>
-      <c r="AD53" s="24" t="n"/>
-      <c r="AE53" s="31" t="inlineStr">
-        <is>
-          <t>Measured Edge Totals: Trend Engine projected 3.96-4.59; raw selected-side p=0.6383, calibrated p=0.5402.</t>
-        </is>
-      </c>
-      <c r="AF53" s="31" t="inlineStr">
-        <is>
-          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
-        </is>
-      </c>
-      <c r="AG53" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH53" s="24" t="n"/>
-      <c r="AI53" s="31" t="n"/>
-      <c r="AJ53" s="31" t="n"/>
-      <c r="AK53" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL53" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM53" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN53" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO53" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP53" s="24" t="inlineStr">
-        <is>
-          <t>mlb-lad</t>
-        </is>
-      </c>
-      <c r="AQ53" s="24" t="inlineStr">
-        <is>
-          <t>Los Angeles Dodgers</t>
-        </is>
-      </c>
-      <c r="AR53" s="24" t="inlineStr">
-        <is>
-          <t>Los Angeles Dodgers</t>
-        </is>
-      </c>
-      <c r="AS53" s="24" t="inlineStr">
-        <is>
-          <t>mlb-chc</t>
-        </is>
-      </c>
-      <c r="AT53" s="24" t="inlineStr">
-        <is>
-          <t>Chicago Cubs</t>
-        </is>
-      </c>
-      <c r="AU53" s="24" t="inlineStr">
-        <is>
-          <t>Chicago Cubs</t>
-        </is>
-      </c>
-      <c r="AV53" s="24" t="n"/>
-      <c r="AW53" s="24" t="n"/>
-      <c r="AX53" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY53" s="24" t="n"/>
-      <c r="AZ53" s="24" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="BA53" s="24" t="inlineStr">
-        <is>
-          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
-        </is>
-      </c>
-      <c r="BB53" s="24" t="inlineStr">
-        <is>
-          <t>flat_probability_shrinkage_toward_half</t>
-        </is>
-      </c>
-      <c r="BC53" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-totals-v3</t>
-        </is>
-      </c>
-      <c r="BD53" s="24" t="inlineStr">
-        <is>
-          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
-        </is>
-      </c>
-      <c r="BE53" s="24" t="inlineStr">
-        <is>
-          <t>v3</t>
-        </is>
-      </c>
-      <c r="BF53" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG53" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-paired-v1</t>
-        </is>
-      </c>
-      <c r="BH53" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="BI53" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ53" s="25" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="BK53" s="26" t="n">
-        <v>-104</v>
-      </c>
-      <c r="BL53" s="27" t="n">
-        <v>1.961538</v>
-      </c>
-      <c r="BM53" s="28" t="n">
-        <v>0.509804</v>
-      </c>
-      <c r="BN53" s="28" t="n">
-        <v>0.507463</v>
-      </c>
-      <c r="BO53" s="28" t="n"/>
-      <c r="BP53" s="25" t="n"/>
-      <c r="BQ53" s="27" t="n"/>
-      <c r="BR53" s="28" t="n"/>
-      <c r="BS53" s="28" t="n"/>
-      <c r="BT53" s="28" t="n"/>
-      <c r="BU53" s="25" t="n"/>
-      <c r="BV53" s="29" t="n"/>
-      <c r="BW53" s="24" t="n"/>
-      <c r="BX53" s="30" t="n"/>
-      <c r="BY53" s="27" t="n"/>
-      <c r="BZ53" s="24" t="n"/>
-      <c r="CA53" s="31" t="n"/>
-      <c r="CB53" s="24" t="n"/>
-      <c r="CC53" s="24" t="n"/>
-      <c r="CD53" s="24" t="n"/>
-      <c r="CE53" s="24" t="n"/>
-      <c r="CF53" s="24" t="n"/>
-      <c r="CG53" s="24" t="n"/>
-      <c r="CH53" s="24" t="n"/>
-      <c r="CI53" s="24" t="n"/>
-      <c r="CJ53" s="24" t="n"/>
-      <c r="CK53" s="24" t="n"/>
-      <c r="CL53" s="24" t="n"/>
-      <c r="CM53" s="24" t="n"/>
-      <c r="CN53" s="24" t="n"/>
-      <c r="CO53" s="24" t="n"/>
-      <c r="CP53" s="24" t="n"/>
-      <c r="CQ53" s="24" t="n"/>
-      <c r="CR53" s="24" t="n"/>
-      <c r="CS53" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="36" customHeight="1">
-      <c r="A54" s="24" t="inlineStr">
-        <is>
-          <t>b2af3889bd544a83</t>
-        </is>
-      </c>
-      <c r="B54" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="C54" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T18:35Z</t>
-        </is>
-      </c>
-      <c r="D54" s="24" t="inlineStr">
-        <is>
-          <t>401816409</t>
-        </is>
-      </c>
-      <c r="E54" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F54" s="24" t="inlineStr">
-        <is>
-          <t>San Francisco Giants</t>
-        </is>
-      </c>
-      <c r="G54" s="24" t="inlineStr">
-        <is>
-          <t>Texas Rangers</t>
-        </is>
-      </c>
-      <c r="H54" s="24" t="inlineStr">
-        <is>
-          <t>spread</t>
-        </is>
-      </c>
-      <c r="I54" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J54" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K54" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L54" s="26" t="n">
-        <v>-130</v>
-      </c>
-      <c r="M54" s="27" t="n">
-        <v>1.769231</v>
-      </c>
-      <c r="N54" s="28" t="n">
-        <v>0.565217</v>
-      </c>
-      <c r="O54" s="28" t="n">
-        <v>0.587935</v>
-      </c>
-      <c r="P54" s="28" t="n">
-        <v>0.05172</v>
-      </c>
-      <c r="Q54" s="28" t="n">
-        <v>0.022718</v>
-      </c>
-      <c r="R54" s="26" t="n">
-        <v>32</v>
-      </c>
-      <c r="S54" s="29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T54" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-margin-v3</t>
-        </is>
-      </c>
-      <c r="U54" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V54" s="24" t="n"/>
-      <c r="W54" s="26" t="n"/>
-      <c r="X54" s="26" t="n"/>
-      <c r="Y54" s="25" t="n"/>
-      <c r="Z54" s="26" t="n"/>
-      <c r="AA54" s="28" t="n"/>
-      <c r="AB54" s="28" t="n"/>
-      <c r="AC54" s="30" t="n"/>
-      <c r="AD54" s="24" t="n"/>
-      <c r="AE54" s="31" t="inlineStr">
-        <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.57-4.92; raw selected-side p=0.6290, calibrated p=0.5879.</t>
-        </is>
-      </c>
-      <c r="AF54" s="31" t="inlineStr">
-        <is>
-          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
-        </is>
-      </c>
-      <c r="AG54" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH54" s="24" t="n"/>
-      <c r="AI54" s="31" t="n"/>
-      <c r="AJ54" s="31" t="n"/>
-      <c r="AK54" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL54" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM54" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN54" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO54" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP54" s="24" t="inlineStr">
-        <is>
-          <t>mlb-sf</t>
-        </is>
-      </c>
-      <c r="AQ54" s="24" t="inlineStr">
-        <is>
-          <t>San Francisco Giants</t>
-        </is>
-      </c>
-      <c r="AR54" s="24" t="inlineStr">
-        <is>
-          <t>San Francisco Giants</t>
-        </is>
-      </c>
-      <c r="AS54" s="24" t="inlineStr">
-        <is>
-          <t>mlb-tex</t>
-        </is>
-      </c>
-      <c r="AT54" s="24" t="inlineStr">
-        <is>
-          <t>Texas Rangers</t>
-        </is>
-      </c>
-      <c r="AU54" s="24" t="inlineStr">
-        <is>
-          <t>Texas Rangers</t>
-        </is>
-      </c>
-      <c r="AV54" s="24" t="n"/>
-      <c r="AW54" s="24" t="n"/>
-      <c r="AX54" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY54" s="24" t="n"/>
-      <c r="AZ54" s="24" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="BA54" s="24" t="inlineStr">
-        <is>
-          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
-        </is>
-      </c>
-      <c r="BB54" s="24" t="inlineStr">
-        <is>
-          <t>flat_probability_shrinkage_toward_half</t>
-        </is>
-      </c>
-      <c r="BC54" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-margin-v3</t>
-        </is>
-      </c>
-      <c r="BD54" s="24" t="inlineStr">
-        <is>
-          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
-        </is>
-      </c>
-      <c r="BE54" s="24" t="inlineStr">
-        <is>
-          <t>v3</t>
-        </is>
-      </c>
-      <c r="BF54" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG54" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-paired-v1</t>
-        </is>
-      </c>
-      <c r="BH54" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="BI54" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ54" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BK54" s="26" t="n">
-        <v>-130</v>
-      </c>
-      <c r="BL54" s="27" t="n">
-        <v>1.769231</v>
-      </c>
-      <c r="BM54" s="28" t="n">
-        <v>0.565217</v>
-      </c>
-      <c r="BN54" s="28" t="n">
-        <v>0.562189</v>
-      </c>
-      <c r="BO54" s="28" t="n"/>
-      <c r="BP54" s="25" t="n"/>
-      <c r="BQ54" s="27" t="n"/>
-      <c r="BR54" s="28" t="n"/>
-      <c r="BS54" s="28" t="n"/>
-      <c r="BT54" s="28" t="n"/>
-      <c r="BU54" s="25" t="n"/>
-      <c r="BV54" s="29" t="n"/>
-      <c r="BW54" s="24" t="n"/>
-      <c r="BX54" s="30" t="n"/>
-      <c r="BY54" s="27" t="n"/>
-      <c r="BZ54" s="24" t="n"/>
-      <c r="CA54" s="31" t="n"/>
-      <c r="CB54" s="24" t="n"/>
-      <c r="CC54" s="24" t="n"/>
-      <c r="CD54" s="24" t="n"/>
-      <c r="CE54" s="24" t="n"/>
-      <c r="CF54" s="24" t="n"/>
-      <c r="CG54" s="24" t="n"/>
-      <c r="CH54" s="24" t="n"/>
-      <c r="CI54" s="24" t="n"/>
-      <c r="CJ54" s="24" t="n"/>
-      <c r="CK54" s="24" t="n"/>
-      <c r="CL54" s="24" t="n"/>
-      <c r="CM54" s="24" t="n"/>
-      <c r="CN54" s="24" t="n"/>
-      <c r="CO54" s="24" t="n"/>
-      <c r="CP54" s="24" t="n"/>
-      <c r="CQ54" s="24" t="n"/>
-      <c r="CR54" s="24" t="n"/>
-      <c r="CS54" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="36" customHeight="1">
-      <c r="A55" s="24" t="inlineStr">
-        <is>
-          <t>5aac644a67c749c0</t>
-        </is>
-      </c>
-      <c r="B55" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="C55" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T18:35Z</t>
-        </is>
-      </c>
-      <c r="D55" s="24" t="inlineStr">
-        <is>
-          <t>401816409</t>
-        </is>
-      </c>
-      <c r="E55" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F55" s="24" t="inlineStr">
-        <is>
-          <t>San Francisco Giants</t>
-        </is>
-      </c>
-      <c r="G55" s="24" t="inlineStr">
-        <is>
-          <t>Texas Rangers</t>
-        </is>
-      </c>
-      <c r="H55" s="24" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="I55" s="24" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="J55" s="25" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="K55" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L55" s="26" t="n">
-        <v>108</v>
-      </c>
-      <c r="M55" s="27" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="N55" s="28" t="n">
-        <v>0.480769</v>
-      </c>
-      <c r="O55" s="28" t="n">
-        <v>0.519176</v>
-      </c>
-      <c r="P55" s="28" t="n">
-        <v>0.05172</v>
-      </c>
-      <c r="Q55" s="28" t="n">
-        <v>0.038407</v>
-      </c>
-      <c r="R55" s="26" t="n">
-        <v>40</v>
-      </c>
-      <c r="S55" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T55" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-totals-v3</t>
-        </is>
-      </c>
-      <c r="U55" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V55" s="24" t="n"/>
-      <c r="W55" s="26" t="n"/>
-      <c r="X55" s="26" t="n"/>
-      <c r="Y55" s="25" t="n"/>
-      <c r="Z55" s="26" t="n"/>
-      <c r="AA55" s="28" t="n"/>
-      <c r="AB55" s="28" t="n"/>
-      <c r="AC55" s="30" t="n"/>
-      <c r="AD55" s="24" t="n"/>
-      <c r="AE55" s="31" t="inlineStr">
-        <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.57-4.92; raw selected-side p=0.5538, calibrated p=0.5192.</t>
-        </is>
-      </c>
-      <c r="AF55" s="31" t="inlineStr">
-        <is>
-          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
-        </is>
-      </c>
-      <c r="AG55" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH55" s="24" t="n"/>
-      <c r="AI55" s="31" t="n"/>
-      <c r="AJ55" s="31" t="n"/>
-      <c r="AK55" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL55" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM55" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN55" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO55" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP55" s="24" t="inlineStr">
-        <is>
-          <t>mlb-sf</t>
-        </is>
-      </c>
-      <c r="AQ55" s="24" t="inlineStr">
-        <is>
-          <t>San Francisco Giants</t>
-        </is>
-      </c>
-      <c r="AR55" s="24" t="inlineStr">
-        <is>
-          <t>San Francisco Giants</t>
-        </is>
-      </c>
-      <c r="AS55" s="24" t="inlineStr">
-        <is>
-          <t>mlb-tex</t>
-        </is>
-      </c>
-      <c r="AT55" s="24" t="inlineStr">
-        <is>
-          <t>Texas Rangers</t>
-        </is>
-      </c>
-      <c r="AU55" s="24" t="inlineStr">
-        <is>
-          <t>Texas Rangers</t>
-        </is>
-      </c>
-      <c r="AV55" s="24" t="n"/>
-      <c r="AW55" s="24" t="n"/>
-      <c r="AX55" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY55" s="24" t="n"/>
-      <c r="AZ55" s="24" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="BA55" s="24" t="inlineStr">
-        <is>
-          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
-        </is>
-      </c>
-      <c r="BB55" s="24" t="inlineStr">
-        <is>
-          <t>flat_probability_shrinkage_toward_half</t>
-        </is>
-      </c>
-      <c r="BC55" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-totals-v3</t>
-        </is>
-      </c>
-      <c r="BD55" s="24" t="inlineStr">
-        <is>
-          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
-        </is>
-      </c>
-      <c r="BE55" s="24" t="inlineStr">
-        <is>
-          <t>v3</t>
-        </is>
-      </c>
-      <c r="BF55" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG55" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-paired-v1</t>
-        </is>
-      </c>
-      <c r="BH55" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="BI55" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ55" s="25" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="BK55" s="26" t="n">
-        <v>108</v>
-      </c>
-      <c r="BL55" s="27" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BM55" s="28" t="n">
-        <v>0.480769</v>
-      </c>
-      <c r="BN55" s="28" t="n">
-        <v>0.477612</v>
-      </c>
-      <c r="BO55" s="28" t="n"/>
-      <c r="BP55" s="25" t="n"/>
-      <c r="BQ55" s="27" t="n"/>
-      <c r="BR55" s="28" t="n"/>
-      <c r="BS55" s="28" t="n"/>
-      <c r="BT55" s="28" t="n"/>
-      <c r="BU55" s="25" t="n"/>
-      <c r="BV55" s="29" t="n"/>
-      <c r="BW55" s="24" t="n"/>
-      <c r="BX55" s="30" t="n"/>
-      <c r="BY55" s="27" t="n"/>
-      <c r="BZ55" s="24" t="n"/>
-      <c r="CA55" s="31" t="n"/>
-      <c r="CB55" s="24" t="n"/>
-      <c r="CC55" s="24" t="n"/>
-      <c r="CD55" s="24" t="n"/>
-      <c r="CE55" s="24" t="n"/>
-      <c r="CF55" s="24" t="n"/>
-      <c r="CG55" s="24" t="n"/>
-      <c r="CH55" s="24" t="n"/>
-      <c r="CI55" s="24" t="n"/>
-      <c r="CJ55" s="24" t="n"/>
-      <c r="CK55" s="24" t="n"/>
-      <c r="CL55" s="24" t="n"/>
-      <c r="CM55" s="24" t="n"/>
-      <c r="CN55" s="24" t="n"/>
-      <c r="CO55" s="24" t="n"/>
-      <c r="CP55" s="24" t="n"/>
-      <c r="CQ55" s="24" t="n"/>
-      <c r="CR55" s="24" t="n"/>
-      <c r="CS55" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="36" customHeight="1">
-      <c r="A56" s="24" t="inlineStr">
-        <is>
-          <t>708d653b7b5343f2</t>
-        </is>
-      </c>
-      <c r="B56" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="C56" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T19:10Z</t>
-        </is>
-      </c>
-      <c r="D56" s="24" t="inlineStr">
-        <is>
-          <t>401816411</t>
-        </is>
-      </c>
-      <c r="E56" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F56" s="24" t="inlineStr">
-        <is>
-          <t>Tampa Bay Rays</t>
-        </is>
-      </c>
-      <c r="G56" s="24" t="inlineStr">
-        <is>
-          <t>Colorado Rockies</t>
-        </is>
-      </c>
-      <c r="H56" s="24" t="inlineStr">
-        <is>
-          <t>spread</t>
-        </is>
-      </c>
-      <c r="I56" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J56" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K56" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L56" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="M56" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="N56" s="28" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O56" s="28" t="n">
-        <v>0.600915</v>
-      </c>
-      <c r="P56" s="28" t="n">
-        <v>0.042131</v>
-      </c>
-      <c r="Q56" s="28" t="n">
-        <v>0.100915</v>
-      </c>
-      <c r="R56" s="26" t="n">
-        <v>76</v>
-      </c>
-      <c r="S56" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T56" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-margin-v3</t>
-        </is>
-      </c>
-      <c r="U56" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V56" s="24" t="n"/>
-      <c r="W56" s="26" t="n"/>
-      <c r="X56" s="26" t="n"/>
-      <c r="Y56" s="25" t="n"/>
-      <c r="Z56" s="26" t="n"/>
-      <c r="AA56" s="28" t="n"/>
-      <c r="AB56" s="28" t="n"/>
-      <c r="AC56" s="30" t="n"/>
-      <c r="AD56" s="24" t="n"/>
-      <c r="AE56" s="31" t="inlineStr">
-        <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.81-4.66; raw selected-side p=0.6481, calibrated p=0.6009.</t>
-        </is>
-      </c>
-      <c r="AF56" s="31" t="inlineStr">
-        <is>
-          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
-        </is>
-      </c>
-      <c r="AG56" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH56" s="24" t="n"/>
-      <c r="AI56" s="31" t="n"/>
-      <c r="AJ56" s="31" t="n"/>
-      <c r="AK56" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL56" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM56" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN56" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO56" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP56" s="24" t="inlineStr">
-        <is>
-          <t>mlb-tb</t>
-        </is>
-      </c>
-      <c r="AQ56" s="24" t="inlineStr">
-        <is>
-          <t>Tampa Bay Rays</t>
-        </is>
-      </c>
-      <c r="AR56" s="24" t="inlineStr">
-        <is>
-          <t>Tampa Bay Rays</t>
-        </is>
-      </c>
-      <c r="AS56" s="24" t="inlineStr">
-        <is>
-          <t>mlb-col</t>
-        </is>
-      </c>
-      <c r="AT56" s="24" t="inlineStr">
-        <is>
-          <t>Colorado Rockies</t>
-        </is>
-      </c>
-      <c r="AU56" s="24" t="inlineStr">
-        <is>
-          <t>Colorado Rockies</t>
-        </is>
-      </c>
-      <c r="AV56" s="24" t="n"/>
-      <c r="AW56" s="24" t="n"/>
-      <c r="AX56" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY56" s="24" t="n"/>
-      <c r="AZ56" s="24" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="BA56" s="24" t="inlineStr">
-        <is>
-          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
-        </is>
-      </c>
-      <c r="BB56" s="24" t="inlineStr">
-        <is>
-          <t>flat_probability_shrinkage_toward_half</t>
-        </is>
-      </c>
-      <c r="BC56" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-margin-v3</t>
-        </is>
-      </c>
-      <c r="BD56" s="24" t="inlineStr">
-        <is>
-          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
-        </is>
-      </c>
-      <c r="BE56" s="24" t="inlineStr">
-        <is>
-          <t>v3</t>
-        </is>
-      </c>
-      <c r="BF56" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG56" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-paired-v1</t>
-        </is>
-      </c>
-      <c r="BH56" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="BI56" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ56" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BK56" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="BL56" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM56" s="28" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BN56" s="28" t="n">
-        <v>0.497512</v>
-      </c>
-      <c r="BO56" s="28" t="n"/>
-      <c r="BP56" s="25" t="n"/>
-      <c r="BQ56" s="27" t="n"/>
-      <c r="BR56" s="28" t="n"/>
-      <c r="BS56" s="28" t="n"/>
-      <c r="BT56" s="28" t="n"/>
-      <c r="BU56" s="25" t="n"/>
-      <c r="BV56" s="29" t="n"/>
-      <c r="BW56" s="24" t="n"/>
-      <c r="BX56" s="30" t="n"/>
-      <c r="BY56" s="27" t="n"/>
-      <c r="BZ56" s="24" t="n"/>
-      <c r="CA56" s="31" t="n"/>
-      <c r="CB56" s="24" t="n"/>
-      <c r="CC56" s="24" t="n"/>
-      <c r="CD56" s="24" t="n"/>
-      <c r="CE56" s="24" t="n"/>
-      <c r="CF56" s="24" t="n"/>
-      <c r="CG56" s="24" t="n"/>
-      <c r="CH56" s="24" t="n"/>
-      <c r="CI56" s="24" t="n"/>
-      <c r="CJ56" s="24" t="n"/>
-      <c r="CK56" s="24" t="n"/>
-      <c r="CL56" s="24" t="n"/>
-      <c r="CM56" s="24" t="n"/>
-      <c r="CN56" s="24" t="n"/>
-      <c r="CO56" s="24" t="n"/>
-      <c r="CP56" s="24" t="n"/>
-      <c r="CQ56" s="24" t="n"/>
-      <c r="CR56" s="24" t="n"/>
-      <c r="CS56" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="36" customHeight="1">
-      <c r="A57" s="24" t="inlineStr">
-        <is>
-          <t>cdd7b779863c4990</t>
-        </is>
-      </c>
-      <c r="B57" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="C57" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T19:10Z</t>
-        </is>
-      </c>
-      <c r="D57" s="24" t="inlineStr">
-        <is>
-          <t>401816411</t>
-        </is>
-      </c>
-      <c r="E57" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F57" s="24" t="inlineStr">
-        <is>
-          <t>Tampa Bay Rays</t>
-        </is>
-      </c>
-      <c r="G57" s="24" t="inlineStr">
-        <is>
-          <t>Colorado Rockies</t>
-        </is>
-      </c>
-      <c r="H57" s="24" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="I57" s="24" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="J57" s="25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="K57" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L57" s="26" t="n">
-        <v>102</v>
-      </c>
-      <c r="M57" s="27" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="N57" s="28" t="n">
-        <v>0.49505</v>
-      </c>
-      <c r="O57" s="28" t="n">
-        <v>0.558548</v>
-      </c>
-      <c r="P57" s="28" t="n">
-        <v>0.042131</v>
-      </c>
-      <c r="Q57" s="28" t="n">
-        <v>0.063498</v>
-      </c>
-      <c r="R57" s="26" t="n">
-        <v>58</v>
-      </c>
-      <c r="S57" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T57" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-totals-v3</t>
-        </is>
-      </c>
-      <c r="U57" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V57" s="24" t="n"/>
-      <c r="W57" s="26" t="n"/>
-      <c r="X57" s="26" t="n"/>
-      <c r="Y57" s="25" t="n"/>
-      <c r="Z57" s="26" t="n"/>
-      <c r="AA57" s="28" t="n"/>
-      <c r="AB57" s="28" t="n"/>
-      <c r="AC57" s="30" t="n"/>
-      <c r="AD57" s="24" t="n"/>
-      <c r="AE57" s="31" t="inlineStr">
-        <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.81-4.66; raw selected-side p=0.7124, calibrated p=0.5585.</t>
-        </is>
-      </c>
-      <c r="AF57" s="31" t="inlineStr">
-        <is>
-          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
-        </is>
-      </c>
-      <c r="AG57" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH57" s="24" t="n"/>
-      <c r="AI57" s="31" t="n"/>
-      <c r="AJ57" s="31" t="n"/>
-      <c r="AK57" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL57" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM57" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN57" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO57" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP57" s="24" t="inlineStr">
-        <is>
-          <t>mlb-tb</t>
-        </is>
-      </c>
-      <c r="AQ57" s="24" t="inlineStr">
-        <is>
-          <t>Tampa Bay Rays</t>
-        </is>
-      </c>
-      <c r="AR57" s="24" t="inlineStr">
-        <is>
-          <t>Tampa Bay Rays</t>
-        </is>
-      </c>
-      <c r="AS57" s="24" t="inlineStr">
-        <is>
-          <t>mlb-col</t>
-        </is>
-      </c>
-      <c r="AT57" s="24" t="inlineStr">
-        <is>
-          <t>Colorado Rockies</t>
-        </is>
-      </c>
-      <c r="AU57" s="24" t="inlineStr">
-        <is>
-          <t>Colorado Rockies</t>
-        </is>
-      </c>
-      <c r="AV57" s="24" t="n"/>
-      <c r="AW57" s="24" t="n"/>
-      <c r="AX57" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY57" s="24" t="n"/>
-      <c r="AZ57" s="24" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="BA57" s="24" t="inlineStr">
-        <is>
-          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
-        </is>
-      </c>
-      <c r="BB57" s="24" t="inlineStr">
-        <is>
-          <t>flat_probability_shrinkage_toward_half</t>
-        </is>
-      </c>
-      <c r="BC57" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-totals-v3</t>
-        </is>
-      </c>
-      <c r="BD57" s="24" t="inlineStr">
-        <is>
-          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
-        </is>
-      </c>
-      <c r="BE57" s="24" t="inlineStr">
-        <is>
-          <t>v3</t>
-        </is>
-      </c>
-      <c r="BF57" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG57" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-paired-v1</t>
-        </is>
-      </c>
-      <c r="BH57" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="BI57" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ57" s="25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK57" s="26" t="n">
-        <v>102</v>
-      </c>
-      <c r="BL57" s="27" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BM57" s="28" t="n">
-        <v>0.49505</v>
-      </c>
-      <c r="BN57" s="28" t="n">
-        <v>0.492537</v>
-      </c>
-      <c r="BO57" s="28" t="n"/>
-      <c r="BP57" s="25" t="n"/>
-      <c r="BQ57" s="27" t="n"/>
-      <c r="BR57" s="28" t="n"/>
-      <c r="BS57" s="28" t="n"/>
-      <c r="BT57" s="28" t="n"/>
-      <c r="BU57" s="25" t="n"/>
-      <c r="BV57" s="29" t="n"/>
-      <c r="BW57" s="24" t="n"/>
-      <c r="BX57" s="30" t="n"/>
-      <c r="BY57" s="27" t="n"/>
-      <c r="BZ57" s="24" t="n"/>
-      <c r="CA57" s="31" t="n"/>
-      <c r="CB57" s="24" t="n"/>
-      <c r="CC57" s="24" t="n"/>
-      <c r="CD57" s="24" t="n"/>
-      <c r="CE57" s="24" t="n"/>
-      <c r="CF57" s="24" t="n"/>
-      <c r="CG57" s="24" t="n"/>
-      <c r="CH57" s="24" t="n"/>
-      <c r="CI57" s="24" t="n"/>
-      <c r="CJ57" s="24" t="n"/>
-      <c r="CK57" s="24" t="n"/>
-      <c r="CL57" s="24" t="n"/>
-      <c r="CM57" s="24" t="n"/>
-      <c r="CN57" s="24" t="n"/>
-      <c r="CO57" s="24" t="n"/>
-      <c r="CP57" s="24" t="n"/>
-      <c r="CQ57" s="24" t="n"/>
-      <c r="CR57" s="24" t="n"/>
-      <c r="CS57" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="36" customHeight="1">
-      <c r="A58" s="24" t="inlineStr">
-        <is>
-          <t>d61245e964ba4945</t>
-        </is>
-      </c>
-      <c r="B58" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="C58" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T22:35Z</t>
-        </is>
-      </c>
-      <c r="D58" s="24" t="inlineStr">
-        <is>
-          <t>401816399</t>
-        </is>
-      </c>
-      <c r="E58" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F58" s="24" t="inlineStr">
-        <is>
-          <t>Los Angeles Angels</t>
-        </is>
-      </c>
-      <c r="G58" s="24" t="inlineStr">
-        <is>
-          <t>Baltimore Orioles</t>
-        </is>
-      </c>
-      <c r="H58" s="24" t="inlineStr">
-        <is>
-          <t>spread</t>
-        </is>
-      </c>
-      <c r="I58" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J58" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K58" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L58" s="26" t="n">
-        <v>-174</v>
-      </c>
-      <c r="M58" s="27" t="n">
-        <v>1.574713</v>
-      </c>
-      <c r="N58" s="28" t="n">
-        <v>0.635036</v>
-      </c>
-      <c r="O58" s="28" t="n">
-        <v>0.590183</v>
-      </c>
-      <c r="P58" s="28" t="n">
-        <v>0.042131</v>
-      </c>
-      <c r="Q58" s="28" t="n">
-        <v>-0.044853</v>
-      </c>
-      <c r="R58" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="S58" s="29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T58" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-margin-v3</t>
-        </is>
-      </c>
-      <c r="U58" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V58" s="24" t="n"/>
-      <c r="W58" s="26" t="n"/>
-      <c r="X58" s="26" t="n"/>
-      <c r="Y58" s="25" t="n"/>
-      <c r="Z58" s="26" t="n"/>
-      <c r="AA58" s="28" t="n"/>
-      <c r="AB58" s="28" t="n"/>
-      <c r="AC58" s="30" t="n"/>
-      <c r="AD58" s="24" t="n"/>
-      <c r="AE58" s="31" t="inlineStr">
-        <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.25-4.70; raw selected-side p=0.6323, calibrated p=0.5902.</t>
-        </is>
-      </c>
-      <c r="AF58" s="31" t="inlineStr">
-        <is>
-          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
-        </is>
-      </c>
-      <c r="AG58" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH58" s="24" t="n"/>
-      <c r="AI58" s="31" t="n"/>
-      <c r="AJ58" s="31" t="n"/>
-      <c r="AK58" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL58" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM58" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN58" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO58" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP58" s="24" t="inlineStr">
-        <is>
-          <t>mlb-laa</t>
-        </is>
-      </c>
-      <c r="AQ58" s="24" t="inlineStr">
-        <is>
-          <t>Los Angeles Angels</t>
-        </is>
-      </c>
-      <c r="AR58" s="24" t="inlineStr">
-        <is>
-          <t>Los Angeles Angels</t>
-        </is>
-      </c>
-      <c r="AS58" s="24" t="inlineStr">
-        <is>
-          <t>mlb-bal</t>
-        </is>
-      </c>
-      <c r="AT58" s="24" t="inlineStr">
-        <is>
-          <t>Baltimore Orioles</t>
-        </is>
-      </c>
-      <c r="AU58" s="24" t="inlineStr">
-        <is>
-          <t>Baltimore Orioles</t>
-        </is>
-      </c>
-      <c r="AV58" s="24" t="n"/>
-      <c r="AW58" s="24" t="n"/>
-      <c r="AX58" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY58" s="24" t="n"/>
-      <c r="AZ58" s="24" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="BA58" s="24" t="inlineStr">
-        <is>
-          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
-        </is>
-      </c>
-      <c r="BB58" s="24" t="inlineStr">
-        <is>
-          <t>flat_probability_shrinkage_toward_half</t>
-        </is>
-      </c>
-      <c r="BC58" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-margin-v3</t>
-        </is>
-      </c>
-      <c r="BD58" s="24" t="inlineStr">
-        <is>
-          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
-        </is>
-      </c>
-      <c r="BE58" s="24" t="inlineStr">
-        <is>
-          <t>v3</t>
-        </is>
-      </c>
-      <c r="BF58" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG58" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-paired-v1</t>
-        </is>
-      </c>
-      <c r="BH58" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="BI58" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ58" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BK58" s="26" t="n">
-        <v>-174</v>
-      </c>
-      <c r="BL58" s="27" t="n">
-        <v>1.574713</v>
-      </c>
-      <c r="BM58" s="28" t="n">
-        <v>0.635036</v>
-      </c>
-      <c r="BN58" s="28" t="n">
-        <v>0.631841</v>
-      </c>
-      <c r="BO58" s="28" t="n"/>
-      <c r="BP58" s="25" t="n"/>
-      <c r="BQ58" s="27" t="n"/>
-      <c r="BR58" s="28" t="n"/>
-      <c r="BS58" s="28" t="n"/>
-      <c r="BT58" s="28" t="n"/>
-      <c r="BU58" s="25" t="n"/>
-      <c r="BV58" s="29" t="n"/>
-      <c r="BW58" s="24" t="n"/>
-      <c r="BX58" s="30" t="n"/>
-      <c r="BY58" s="27" t="n"/>
-      <c r="BZ58" s="24" t="n"/>
-      <c r="CA58" s="31" t="n"/>
-      <c r="CB58" s="24" t="n"/>
-      <c r="CC58" s="24" t="n"/>
-      <c r="CD58" s="24" t="n"/>
-      <c r="CE58" s="24" t="n"/>
-      <c r="CF58" s="24" t="n"/>
-      <c r="CG58" s="24" t="n"/>
-      <c r="CH58" s="24" t="n"/>
-      <c r="CI58" s="24" t="n"/>
-      <c r="CJ58" s="24" t="n"/>
-      <c r="CK58" s="24" t="n"/>
-      <c r="CL58" s="24" t="n"/>
-      <c r="CM58" s="24" t="n"/>
-      <c r="CN58" s="24" t="n"/>
-      <c r="CO58" s="24" t="n"/>
-      <c r="CP58" s="24" t="n"/>
-      <c r="CQ58" s="24" t="n"/>
-      <c r="CR58" s="24" t="n"/>
-      <c r="CS58" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="36" customHeight="1">
-      <c r="A59" s="24" t="inlineStr">
-        <is>
-          <t>d33140fbe9924bde</t>
-        </is>
-      </c>
-      <c r="B59" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="C59" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T22:35Z</t>
-        </is>
-      </c>
-      <c r="D59" s="24" t="inlineStr">
-        <is>
-          <t>401816399</t>
-        </is>
-      </c>
-      <c r="E59" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F59" s="24" t="inlineStr">
-        <is>
-          <t>Los Angeles Angels</t>
-        </is>
-      </c>
-      <c r="G59" s="24" t="inlineStr">
-        <is>
-          <t>Baltimore Orioles</t>
-        </is>
-      </c>
-      <c r="H59" s="24" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="I59" s="24" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="J59" s="25" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="K59" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L59" s="26" t="n">
-        <v>-115</v>
-      </c>
-      <c r="M59" s="27" t="n">
-        <v>1.869565</v>
-      </c>
-      <c r="N59" s="28" t="n">
-        <v>0.534884</v>
-      </c>
-      <c r="O59" s="28" t="n">
-        <v>0.527597</v>
-      </c>
-      <c r="P59" s="28" t="n">
-        <v>0.042131</v>
-      </c>
-      <c r="Q59" s="28" t="n">
-        <v>-0.007287</v>
-      </c>
-      <c r="R59" s="26" t="n">
-        <v>22</v>
-      </c>
-      <c r="S59" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T59" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-totals-v3</t>
-        </is>
-      </c>
-      <c r="U59" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V59" s="24" t="n"/>
-      <c r="W59" s="26" t="n"/>
-      <c r="X59" s="26" t="n"/>
-      <c r="Y59" s="25" t="n"/>
-      <c r="Z59" s="26" t="n"/>
-      <c r="AA59" s="28" t="n"/>
-      <c r="AB59" s="28" t="n"/>
-      <c r="AC59" s="30" t="n"/>
-      <c r="AD59" s="24" t="n"/>
-      <c r="AE59" s="31" t="inlineStr">
-        <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.25-4.70; raw selected-side p=0.5877, calibrated p=0.5276.</t>
-        </is>
-      </c>
-      <c r="AF59" s="31" t="inlineStr">
-        <is>
-          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
-        </is>
-      </c>
-      <c r="AG59" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH59" s="24" t="n"/>
-      <c r="AI59" s="31" t="n"/>
-      <c r="AJ59" s="31" t="n"/>
-      <c r="AK59" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL59" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM59" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN59" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO59" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP59" s="24" t="inlineStr">
-        <is>
-          <t>mlb-laa</t>
-        </is>
-      </c>
-      <c r="AQ59" s="24" t="inlineStr">
-        <is>
-          <t>Los Angeles Angels</t>
-        </is>
-      </c>
-      <c r="AR59" s="24" t="inlineStr">
-        <is>
-          <t>Los Angeles Angels</t>
-        </is>
-      </c>
-      <c r="AS59" s="24" t="inlineStr">
-        <is>
-          <t>mlb-bal</t>
-        </is>
-      </c>
-      <c r="AT59" s="24" t="inlineStr">
-        <is>
-          <t>Baltimore Orioles</t>
-        </is>
-      </c>
-      <c r="AU59" s="24" t="inlineStr">
-        <is>
-          <t>Baltimore Orioles</t>
-        </is>
-      </c>
-      <c r="AV59" s="24" t="n"/>
-      <c r="AW59" s="24" t="n"/>
-      <c r="AX59" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY59" s="24" t="n"/>
-      <c r="AZ59" s="24" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="BA59" s="24" t="inlineStr">
-        <is>
-          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
-        </is>
-      </c>
-      <c r="BB59" s="24" t="inlineStr">
-        <is>
-          <t>flat_probability_shrinkage_toward_half</t>
-        </is>
-      </c>
-      <c r="BC59" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-totals-v3</t>
-        </is>
-      </c>
-      <c r="BD59" s="24" t="inlineStr">
-        <is>
-          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
-        </is>
-      </c>
-      <c r="BE59" s="24" t="inlineStr">
-        <is>
-          <t>v3</t>
-        </is>
-      </c>
-      <c r="BF59" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG59" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-paired-v1</t>
-        </is>
-      </c>
-      <c r="BH59" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="BI59" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ59" s="25" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="BK59" s="26" t="n">
-        <v>-115</v>
-      </c>
-      <c r="BL59" s="27" t="n">
-        <v>1.869565</v>
-      </c>
-      <c r="BM59" s="28" t="n">
-        <v>0.534884</v>
-      </c>
-      <c r="BN59" s="28" t="n">
-        <v>0.532338</v>
-      </c>
-      <c r="BO59" s="28" t="n"/>
-      <c r="BP59" s="25" t="n"/>
-      <c r="BQ59" s="27" t="n"/>
-      <c r="BR59" s="28" t="n"/>
-      <c r="BS59" s="28" t="n"/>
-      <c r="BT59" s="28" t="n"/>
-      <c r="BU59" s="25" t="n"/>
-      <c r="BV59" s="29" t="n"/>
-      <c r="BW59" s="24" t="n"/>
-      <c r="BX59" s="30" t="n"/>
-      <c r="BY59" s="27" t="n"/>
-      <c r="BZ59" s="24" t="n"/>
-      <c r="CA59" s="31" t="n"/>
-      <c r="CB59" s="24" t="n"/>
-      <c r="CC59" s="24" t="n"/>
-      <c r="CD59" s="24" t="n"/>
-      <c r="CE59" s="24" t="n"/>
-      <c r="CF59" s="24" t="n"/>
-      <c r="CG59" s="24" t="n"/>
-      <c r="CH59" s="24" t="n"/>
-      <c r="CI59" s="24" t="n"/>
-      <c r="CJ59" s="24" t="n"/>
-      <c r="CK59" s="24" t="n"/>
-      <c r="CL59" s="24" t="n"/>
-      <c r="CM59" s="24" t="n"/>
-      <c r="CN59" s="24" t="n"/>
-      <c r="CO59" s="24" t="n"/>
-      <c r="CP59" s="24" t="n"/>
-      <c r="CQ59" s="24" t="n"/>
-      <c r="CR59" s="24" t="n"/>
-      <c r="CS59" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="36" customHeight="1">
-      <c r="A60" s="24" t="inlineStr">
-        <is>
-          <t>553a1c4913444d4c</t>
-        </is>
-      </c>
-      <c r="B60" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="C60" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T22:40Z</t>
-        </is>
-      </c>
-      <c r="D60" s="24" t="inlineStr">
-        <is>
-          <t>401816400</t>
-        </is>
-      </c>
-      <c r="E60" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F60" s="24" t="inlineStr">
-        <is>
-          <t>Athletics</t>
-        </is>
-      </c>
-      <c r="G60" s="24" t="inlineStr">
-        <is>
-          <t>Cincinnati Reds</t>
-        </is>
-      </c>
-      <c r="H60" s="24" t="inlineStr">
-        <is>
-          <t>spread</t>
-        </is>
-      </c>
-      <c r="I60" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J60" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K60" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L60" s="26" t="n">
-        <v>-153</v>
-      </c>
-      <c r="M60" s="27" t="n">
-        <v>1.653595</v>
-      </c>
-      <c r="N60" s="28" t="n">
-        <v>0.604743</v>
-      </c>
-      <c r="O60" s="28" t="n">
-        <v>0.594067</v>
-      </c>
-      <c r="P60" s="28" t="n">
-        <v>0.042131</v>
-      </c>
-      <c r="Q60" s="28" t="n">
-        <v>-0.010676</v>
-      </c>
-      <c r="R60" s="26" t="n">
-        <v>21</v>
-      </c>
-      <c r="S60" s="29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T60" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-margin-v3</t>
-        </is>
-      </c>
-      <c r="U60" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V60" s="24" t="n"/>
-      <c r="W60" s="26" t="n"/>
-      <c r="X60" s="26" t="n"/>
-      <c r="Y60" s="25" t="n"/>
-      <c r="Z60" s="26" t="n"/>
-      <c r="AA60" s="28" t="n"/>
-      <c r="AB60" s="28" t="n"/>
-      <c r="AC60" s="30" t="n"/>
-      <c r="AD60" s="24" t="n"/>
-      <c r="AE60" s="31" t="inlineStr">
-        <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.90-5.09; raw selected-side p=0.6381, calibrated p=0.5941.</t>
-        </is>
-      </c>
-      <c r="AF60" s="31" t="inlineStr">
-        <is>
-          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
-        </is>
-      </c>
-      <c r="AG60" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH60" s="24" t="n"/>
-      <c r="AI60" s="31" t="n"/>
-      <c r="AJ60" s="31" t="n"/>
-      <c r="AK60" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL60" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM60" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN60" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO60" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP60" s="24" t="inlineStr">
-        <is>
-          <t>mlb-ath</t>
-        </is>
-      </c>
-      <c r="AQ60" s="24" t="inlineStr">
-        <is>
-          <t>Athletics</t>
-        </is>
-      </c>
-      <c r="AR60" s="24" t="inlineStr">
-        <is>
-          <t>Athletics</t>
-        </is>
-      </c>
-      <c r="AS60" s="24" t="inlineStr">
-        <is>
-          <t>mlb-cin</t>
-        </is>
-      </c>
-      <c r="AT60" s="24" t="inlineStr">
-        <is>
-          <t>Cincinnati Reds</t>
-        </is>
-      </c>
-      <c r="AU60" s="24" t="inlineStr">
-        <is>
-          <t>Cincinnati Reds</t>
-        </is>
-      </c>
-      <c r="AV60" s="24" t="n"/>
-      <c r="AW60" s="24" t="n"/>
-      <c r="AX60" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY60" s="24" t="n"/>
-      <c r="AZ60" s="24" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="BA60" s="24" t="inlineStr">
-        <is>
-          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
-        </is>
-      </c>
-      <c r="BB60" s="24" t="inlineStr">
-        <is>
-          <t>flat_probability_shrinkage_toward_half</t>
-        </is>
-      </c>
-      <c r="BC60" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-margin-v3</t>
-        </is>
-      </c>
-      <c r="BD60" s="24" t="inlineStr">
-        <is>
-          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
-        </is>
-      </c>
-      <c r="BE60" s="24" t="inlineStr">
-        <is>
-          <t>v3</t>
-        </is>
-      </c>
-      <c r="BF60" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG60" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-paired-v1</t>
-        </is>
-      </c>
-      <c r="BH60" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="BI60" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ60" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BK60" s="26" t="n">
-        <v>-153</v>
-      </c>
-      <c r="BL60" s="27" t="n">
-        <v>1.653595</v>
-      </c>
-      <c r="BM60" s="28" t="n">
-        <v>0.604743</v>
-      </c>
-      <c r="BN60" s="28" t="n">
-        <v>0.60199</v>
-      </c>
-      <c r="BO60" s="28" t="n"/>
-      <c r="BP60" s="25" t="n"/>
-      <c r="BQ60" s="27" t="n"/>
-      <c r="BR60" s="28" t="n"/>
-      <c r="BS60" s="28" t="n"/>
-      <c r="BT60" s="28" t="n"/>
-      <c r="BU60" s="25" t="n"/>
-      <c r="BV60" s="29" t="n"/>
-      <c r="BW60" s="24" t="n"/>
-      <c r="BX60" s="30" t="n"/>
-      <c r="BY60" s="27" t="n"/>
-      <c r="BZ60" s="24" t="n"/>
-      <c r="CA60" s="31" t="n"/>
-      <c r="CB60" s="24" t="n"/>
-      <c r="CC60" s="24" t="n"/>
-      <c r="CD60" s="24" t="n"/>
-      <c r="CE60" s="24" t="n"/>
-      <c r="CF60" s="24" t="n"/>
-      <c r="CG60" s="24" t="n"/>
-      <c r="CH60" s="24" t="n"/>
-      <c r="CI60" s="24" t="n"/>
-      <c r="CJ60" s="24" t="n"/>
-      <c r="CK60" s="24" t="n"/>
-      <c r="CL60" s="24" t="n"/>
-      <c r="CM60" s="24" t="n"/>
-      <c r="CN60" s="24" t="n"/>
-      <c r="CO60" s="24" t="n"/>
-      <c r="CP60" s="24" t="n"/>
-      <c r="CQ60" s="24" t="n"/>
-      <c r="CR60" s="24" t="n"/>
-      <c r="CS60" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="36" customHeight="1">
-      <c r="A61" s="24" t="inlineStr">
-        <is>
-          <t>6fd03525015e4b7e</t>
-        </is>
-      </c>
-      <c r="B61" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="C61" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T22:40Z</t>
-        </is>
-      </c>
-      <c r="D61" s="24" t="inlineStr">
-        <is>
-          <t>401816400</t>
-        </is>
-      </c>
-      <c r="E61" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F61" s="24" t="inlineStr">
-        <is>
-          <t>Athletics</t>
-        </is>
-      </c>
-      <c r="G61" s="24" t="inlineStr">
-        <is>
-          <t>Cincinnati Reds</t>
-        </is>
-      </c>
-      <c r="H61" s="24" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="I61" s="24" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="J61" s="25" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="K61" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L61" s="26" t="n">
-        <v>104</v>
-      </c>
-      <c r="M61" s="27" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="N61" s="28" t="n">
-        <v>0.490196</v>
-      </c>
-      <c r="O61" s="28" t="n">
-        <v>0.509961</v>
-      </c>
-      <c r="P61" s="28" t="n">
-        <v>0.042131</v>
-      </c>
-      <c r="Q61" s="28" t="n">
-        <v>0.019765</v>
-      </c>
-      <c r="R61" s="26" t="n">
-        <v>36</v>
-      </c>
-      <c r="S61" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T61" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-totals-v3</t>
-        </is>
-      </c>
-      <c r="U61" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V61" s="24" t="n"/>
-      <c r="W61" s="26" t="n"/>
-      <c r="X61" s="26" t="n"/>
-      <c r="Y61" s="25" t="n"/>
-      <c r="Z61" s="26" t="n"/>
-      <c r="AA61" s="28" t="n"/>
-      <c r="AB61" s="28" t="n"/>
-      <c r="AC61" s="30" t="n"/>
-      <c r="AD61" s="24" t="n"/>
-      <c r="AE61" s="31" t="inlineStr">
-        <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.90-5.09; raw selected-side p=0.5168, calibrated p=0.5100.</t>
-        </is>
-      </c>
-      <c r="AF61" s="31" t="inlineStr">
-        <is>
-          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
-        </is>
-      </c>
-      <c r="AG61" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH61" s="24" t="n"/>
-      <c r="AI61" s="31" t="n"/>
-      <c r="AJ61" s="31" t="n"/>
-      <c r="AK61" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL61" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM61" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN61" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO61" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP61" s="24" t="inlineStr">
-        <is>
-          <t>mlb-ath</t>
-        </is>
-      </c>
-      <c r="AQ61" s="24" t="inlineStr">
-        <is>
-          <t>Athletics</t>
-        </is>
-      </c>
-      <c r="AR61" s="24" t="inlineStr">
-        <is>
-          <t>Athletics</t>
-        </is>
-      </c>
-      <c r="AS61" s="24" t="inlineStr">
-        <is>
-          <t>mlb-cin</t>
-        </is>
-      </c>
-      <c r="AT61" s="24" t="inlineStr">
-        <is>
-          <t>Cincinnati Reds</t>
-        </is>
-      </c>
-      <c r="AU61" s="24" t="inlineStr">
-        <is>
-          <t>Cincinnati Reds</t>
-        </is>
-      </c>
-      <c r="AV61" s="24" t="n"/>
-      <c r="AW61" s="24" t="n"/>
-      <c r="AX61" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY61" s="24" t="n"/>
-      <c r="AZ61" s="24" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="BA61" s="24" t="inlineStr">
-        <is>
-          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
-        </is>
-      </c>
-      <c r="BB61" s="24" t="inlineStr">
-        <is>
-          <t>flat_probability_shrinkage_toward_half</t>
-        </is>
-      </c>
-      <c r="BC61" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-totals-v3</t>
-        </is>
-      </c>
-      <c r="BD61" s="24" t="inlineStr">
-        <is>
-          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
-        </is>
-      </c>
-      <c r="BE61" s="24" t="inlineStr">
-        <is>
-          <t>v3</t>
-        </is>
-      </c>
-      <c r="BF61" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG61" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-paired-v1</t>
-        </is>
-      </c>
-      <c r="BH61" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="BI61" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ61" s="25" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="BK61" s="26" t="n">
-        <v>104</v>
-      </c>
-      <c r="BL61" s="27" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BM61" s="28" t="n">
-        <v>0.490196</v>
-      </c>
-      <c r="BN61" s="28" t="n">
-        <v>0.487562</v>
-      </c>
-      <c r="BO61" s="28" t="n"/>
-      <c r="BP61" s="25" t="n"/>
-      <c r="BQ61" s="27" t="n"/>
-      <c r="BR61" s="28" t="n"/>
-      <c r="BS61" s="28" t="n"/>
-      <c r="BT61" s="28" t="n"/>
-      <c r="BU61" s="25" t="n"/>
-      <c r="BV61" s="29" t="n"/>
-      <c r="BW61" s="24" t="n"/>
-      <c r="BX61" s="30" t="n"/>
-      <c r="BY61" s="27" t="n"/>
-      <c r="BZ61" s="24" t="n"/>
-      <c r="CA61" s="31" t="n"/>
-      <c r="CB61" s="24" t="n"/>
-      <c r="CC61" s="24" t="n"/>
-      <c r="CD61" s="24" t="n"/>
-      <c r="CE61" s="24" t="n"/>
-      <c r="CF61" s="24" t="n"/>
-      <c r="CG61" s="24" t="n"/>
-      <c r="CH61" s="24" t="n"/>
-      <c r="CI61" s="24" t="n"/>
-      <c r="CJ61" s="24" t="n"/>
-      <c r="CK61" s="24" t="n"/>
-      <c r="CL61" s="24" t="n"/>
-      <c r="CM61" s="24" t="n"/>
-      <c r="CN61" s="24" t="n"/>
-      <c r="CO61" s="24" t="n"/>
-      <c r="CP61" s="24" t="n"/>
-      <c r="CQ61" s="24" t="n"/>
-      <c r="CR61" s="24" t="n"/>
-      <c r="CS61" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="36" customHeight="1">
-      <c r="A62" s="24" t="inlineStr">
-        <is>
-          <t>450a30c6e80245ad</t>
-        </is>
-      </c>
-      <c r="B62" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="C62" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T22:40Z</t>
-        </is>
-      </c>
-      <c r="D62" s="24" t="inlineStr">
-        <is>
-          <t>401816403</t>
-        </is>
-      </c>
-      <c r="E62" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F62" s="24" t="inlineStr">
-        <is>
-          <t>New York Mets</t>
-        </is>
-      </c>
-      <c r="G62" s="24" t="inlineStr">
-        <is>
-          <t>Cleveland Guardians</t>
-        </is>
-      </c>
-      <c r="H62" s="24" t="inlineStr">
-        <is>
-          <t>spread</t>
-        </is>
-      </c>
-      <c r="I62" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J62" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K62" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L62" s="26" t="n">
-        <v>-170</v>
-      </c>
-      <c r="M62" s="27" t="n">
-        <v>1.588235</v>
-      </c>
-      <c r="N62" s="28" t="n">
-        <v>0.62963</v>
-      </c>
-      <c r="O62" s="28" t="n">
-        <v>0.611375</v>
-      </c>
-      <c r="P62" s="28" t="n">
-        <v>0.042131</v>
-      </c>
-      <c r="Q62" s="28" t="n">
-        <v>-0.018255</v>
-      </c>
-      <c r="R62" s="26" t="n">
-        <v>17</v>
-      </c>
-      <c r="S62" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T62" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-margin-v3</t>
-        </is>
-      </c>
-      <c r="U62" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V62" s="24" t="n"/>
-      <c r="W62" s="26" t="n"/>
-      <c r="X62" s="26" t="n"/>
-      <c r="Y62" s="25" t="n"/>
-      <c r="Z62" s="26" t="n"/>
-      <c r="AA62" s="28" t="n"/>
-      <c r="AB62" s="28" t="n"/>
-      <c r="AC62" s="30" t="n"/>
-      <c r="AD62" s="24" t="n"/>
-      <c r="AE62" s="31" t="inlineStr">
-        <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.46-4.24; raw selected-side p=0.6634, calibrated p=0.6114.</t>
-        </is>
-      </c>
-      <c r="AF62" s="31" t="inlineStr">
-        <is>
-          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
-        </is>
-      </c>
-      <c r="AG62" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH62" s="24" t="n"/>
-      <c r="AI62" s="31" t="n"/>
-      <c r="AJ62" s="31" t="n"/>
-      <c r="AK62" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL62" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM62" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN62" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO62" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP62" s="24" t="inlineStr">
-        <is>
-          <t>mlb-nym</t>
-        </is>
-      </c>
-      <c r="AQ62" s="24" t="inlineStr">
-        <is>
-          <t>New York Mets</t>
-        </is>
-      </c>
-      <c r="AR62" s="24" t="inlineStr">
-        <is>
-          <t>New York Mets</t>
-        </is>
-      </c>
-      <c r="AS62" s="24" t="inlineStr">
-        <is>
-          <t>mlb-cle</t>
-        </is>
-      </c>
-      <c r="AT62" s="24" t="inlineStr">
-        <is>
-          <t>Cleveland Guardians</t>
-        </is>
-      </c>
-      <c r="AU62" s="24" t="inlineStr">
-        <is>
-          <t>Cleveland Guardians</t>
-        </is>
-      </c>
-      <c r="AV62" s="24" t="n"/>
-      <c r="AW62" s="24" t="n"/>
-      <c r="AX62" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY62" s="24" t="n"/>
-      <c r="AZ62" s="24" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="BA62" s="24" t="inlineStr">
-        <is>
-          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
-        </is>
-      </c>
-      <c r="BB62" s="24" t="inlineStr">
-        <is>
-          <t>flat_probability_shrinkage_toward_half</t>
-        </is>
-      </c>
-      <c r="BC62" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-margin-v3</t>
-        </is>
-      </c>
-      <c r="BD62" s="24" t="inlineStr">
-        <is>
-          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
-        </is>
-      </c>
-      <c r="BE62" s="24" t="inlineStr">
-        <is>
-          <t>v3</t>
-        </is>
-      </c>
-      <c r="BF62" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG62" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-paired-v1</t>
-        </is>
-      </c>
-      <c r="BH62" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="BI62" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ62" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BK62" s="26" t="n">
-        <v>-170</v>
-      </c>
-      <c r="BL62" s="27" t="n">
-        <v>1.588235</v>
-      </c>
-      <c r="BM62" s="28" t="n">
-        <v>0.62963</v>
-      </c>
-      <c r="BN62" s="28" t="n">
-        <v>0.626866</v>
-      </c>
-      <c r="BO62" s="28" t="n"/>
-      <c r="BP62" s="25" t="n"/>
-      <c r="BQ62" s="27" t="n"/>
-      <c r="BR62" s="28" t="n"/>
-      <c r="BS62" s="28" t="n"/>
-      <c r="BT62" s="28" t="n"/>
-      <c r="BU62" s="25" t="n"/>
-      <c r="BV62" s="29" t="n"/>
-      <c r="BW62" s="24" t="n"/>
-      <c r="BX62" s="30" t="n"/>
-      <c r="BY62" s="27" t="n"/>
-      <c r="BZ62" s="24" t="n"/>
-      <c r="CA62" s="31" t="n"/>
-      <c r="CB62" s="24" t="n"/>
-      <c r="CC62" s="24" t="n"/>
-      <c r="CD62" s="24" t="n"/>
-      <c r="CE62" s="24" t="n"/>
-      <c r="CF62" s="24" t="n"/>
-      <c r="CG62" s="24" t="n"/>
-      <c r="CH62" s="24" t="n"/>
-      <c r="CI62" s="24" t="n"/>
-      <c r="CJ62" s="24" t="n"/>
-      <c r="CK62" s="24" t="n"/>
-      <c r="CL62" s="24" t="n"/>
-      <c r="CM62" s="24" t="n"/>
-      <c r="CN62" s="24" t="n"/>
-      <c r="CO62" s="24" t="n"/>
-      <c r="CP62" s="24" t="n"/>
-      <c r="CQ62" s="24" t="n"/>
-      <c r="CR62" s="24" t="n"/>
-      <c r="CS62" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="36" customHeight="1">
-      <c r="A63" s="24" t="inlineStr">
-        <is>
-          <t>746b27f47bc140dd</t>
-        </is>
-      </c>
-      <c r="B63" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="C63" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T22:40Z</t>
-        </is>
-      </c>
-      <c r="D63" s="24" t="inlineStr">
-        <is>
-          <t>401816403</t>
-        </is>
-      </c>
-      <c r="E63" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F63" s="24" t="inlineStr">
-        <is>
-          <t>New York Mets</t>
-        </is>
-      </c>
-      <c r="G63" s="24" t="inlineStr">
-        <is>
-          <t>Cleveland Guardians</t>
-        </is>
-      </c>
-      <c r="H63" s="24" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="I63" s="24" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="J63" s="25" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="K63" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L63" s="26" t="n">
-        <v>-111</v>
-      </c>
-      <c r="M63" s="27" t="n">
-        <v>1.900901</v>
-      </c>
-      <c r="N63" s="28" t="n">
-        <v>0.526066</v>
-      </c>
-      <c r="O63" s="28" t="n">
-        <v>0.522244</v>
-      </c>
-      <c r="P63" s="28" t="n">
-        <v>0.042131</v>
-      </c>
-      <c r="Q63" s="28" t="n">
-        <v>-0.003822</v>
-      </c>
-      <c r="R63" s="26" t="n">
-        <v>25</v>
-      </c>
-      <c r="S63" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T63" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-totals-v3</t>
-        </is>
-      </c>
-      <c r="U63" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V63" s="24" t="n"/>
-      <c r="W63" s="26" t="n"/>
-      <c r="X63" s="26" t="n"/>
-      <c r="Y63" s="25" t="n"/>
-      <c r="Z63" s="26" t="n"/>
-      <c r="AA63" s="28" t="n"/>
-      <c r="AB63" s="28" t="n"/>
-      <c r="AC63" s="30" t="n"/>
-      <c r="AD63" s="24" t="n"/>
-      <c r="AE63" s="31" t="inlineStr">
-        <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.46-4.24; raw selected-side p=0.5662, calibrated p=0.5222.</t>
-        </is>
-      </c>
-      <c r="AF63" s="31" t="inlineStr">
-        <is>
-          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
-        </is>
-      </c>
-      <c r="AG63" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH63" s="24" t="n"/>
-      <c r="AI63" s="31" t="n"/>
-      <c r="AJ63" s="31" t="n"/>
-      <c r="AK63" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL63" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM63" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN63" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO63" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP63" s="24" t="inlineStr">
-        <is>
-          <t>mlb-nym</t>
-        </is>
-      </c>
-      <c r="AQ63" s="24" t="inlineStr">
-        <is>
-          <t>New York Mets</t>
-        </is>
-      </c>
-      <c r="AR63" s="24" t="inlineStr">
-        <is>
-          <t>New York Mets</t>
-        </is>
-      </c>
-      <c r="AS63" s="24" t="inlineStr">
-        <is>
-          <t>mlb-cle</t>
-        </is>
-      </c>
-      <c r="AT63" s="24" t="inlineStr">
-        <is>
-          <t>Cleveland Guardians</t>
-        </is>
-      </c>
-      <c r="AU63" s="24" t="inlineStr">
-        <is>
-          <t>Cleveland Guardians</t>
-        </is>
-      </c>
-      <c r="AV63" s="24" t="n"/>
-      <c r="AW63" s="24" t="n"/>
-      <c r="AX63" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY63" s="24" t="n"/>
-      <c r="AZ63" s="24" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="BA63" s="24" t="inlineStr">
-        <is>
-          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
-        </is>
-      </c>
-      <c r="BB63" s="24" t="inlineStr">
-        <is>
-          <t>flat_probability_shrinkage_toward_half</t>
-        </is>
-      </c>
-      <c r="BC63" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-totals-v3</t>
-        </is>
-      </c>
-      <c r="BD63" s="24" t="inlineStr">
-        <is>
-          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
-        </is>
-      </c>
-      <c r="BE63" s="24" t="inlineStr">
-        <is>
-          <t>v3</t>
-        </is>
-      </c>
-      <c r="BF63" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG63" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-paired-v1</t>
-        </is>
-      </c>
-      <c r="BH63" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="BI63" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ63" s="25" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="BK63" s="26" t="n">
-        <v>-111</v>
-      </c>
-      <c r="BL63" s="27" t="n">
-        <v>1.900901</v>
-      </c>
-      <c r="BM63" s="28" t="n">
-        <v>0.526066</v>
-      </c>
-      <c r="BN63" s="28" t="n">
-        <v>0.522388</v>
-      </c>
-      <c r="BO63" s="28" t="n"/>
-      <c r="BP63" s="25" t="n"/>
-      <c r="BQ63" s="27" t="n"/>
-      <c r="BR63" s="28" t="n"/>
-      <c r="BS63" s="28" t="n"/>
-      <c r="BT63" s="28" t="n"/>
-      <c r="BU63" s="25" t="n"/>
-      <c r="BV63" s="29" t="n"/>
-      <c r="BW63" s="24" t="n"/>
-      <c r="BX63" s="30" t="n"/>
-      <c r="BY63" s="27" t="n"/>
-      <c r="BZ63" s="24" t="n"/>
-      <c r="CA63" s="31" t="n"/>
-      <c r="CB63" s="24" t="n"/>
-      <c r="CC63" s="24" t="n"/>
-      <c r="CD63" s="24" t="n"/>
-      <c r="CE63" s="24" t="n"/>
-      <c r="CF63" s="24" t="n"/>
-      <c r="CG63" s="24" t="n"/>
-      <c r="CH63" s="24" t="n"/>
-      <c r="CI63" s="24" t="n"/>
-      <c r="CJ63" s="24" t="n"/>
-      <c r="CK63" s="24" t="n"/>
-      <c r="CL63" s="24" t="n"/>
-      <c r="CM63" s="24" t="n"/>
-      <c r="CN63" s="24" t="n"/>
-      <c r="CO63" s="24" t="n"/>
-      <c r="CP63" s="24" t="n"/>
-      <c r="CQ63" s="24" t="n"/>
-      <c r="CR63" s="24" t="n"/>
-      <c r="CS63" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="36" customHeight="1">
-      <c r="A64" s="24" t="inlineStr">
-        <is>
-          <t>bd7535aa372b4bce</t>
-        </is>
-      </c>
-      <c r="B64" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="C64" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T22:40Z</t>
-        </is>
-      </c>
-      <c r="D64" s="24" t="inlineStr">
-        <is>
-          <t>401816405</t>
-        </is>
-      </c>
-      <c r="E64" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F64" s="24" t="inlineStr">
-        <is>
-          <t>Washington Nationals</t>
-        </is>
-      </c>
-      <c r="G64" s="24" t="inlineStr">
-        <is>
-          <t>Philadelphia Phillies</t>
-        </is>
-      </c>
-      <c r="H64" s="24" t="inlineStr">
-        <is>
-          <t>spread</t>
-        </is>
-      </c>
-      <c r="I64" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J64" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K64" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L64" s="26" t="n">
-        <v>-122</v>
-      </c>
-      <c r="M64" s="27" t="n">
-        <v>1.819672</v>
-      </c>
-      <c r="N64" s="28" t="n">
-        <v>0.54955</v>
-      </c>
-      <c r="O64" s="28" t="n">
-        <v>0.603096</v>
-      </c>
-      <c r="P64" s="28" t="n">
-        <v>0.042131</v>
-      </c>
-      <c r="Q64" s="28" t="n">
-        <v>0.053546</v>
-      </c>
-      <c r="R64" s="26" t="n">
-        <v>53</v>
-      </c>
-      <c r="S64" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T64" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-margin-v3</t>
-        </is>
-      </c>
-      <c r="U64" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V64" s="24" t="n"/>
-      <c r="W64" s="26" t="n"/>
-      <c r="X64" s="26" t="n"/>
-      <c r="Y64" s="25" t="n"/>
-      <c r="Z64" s="26" t="n"/>
-      <c r="AA64" s="28" t="n"/>
-      <c r="AB64" s="28" t="n"/>
-      <c r="AC64" s="30" t="n"/>
-      <c r="AD64" s="24" t="n"/>
-      <c r="AE64" s="31" t="inlineStr">
-        <is>
-          <t>Measured Edge Margin: Trend Engine projected 5.21-5.30; raw selected-side p=0.6513, calibrated p=0.6031.</t>
-        </is>
-      </c>
-      <c r="AF64" s="31" t="inlineStr">
-        <is>
-          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
-        </is>
-      </c>
-      <c r="AG64" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH64" s="24" t="n"/>
-      <c r="AI64" s="31" t="n"/>
-      <c r="AJ64" s="31" t="n"/>
-      <c r="AK64" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL64" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM64" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN64" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO64" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP64" s="24" t="inlineStr">
-        <is>
-          <t>mlb-wsh</t>
-        </is>
-      </c>
-      <c r="AQ64" s="24" t="inlineStr">
-        <is>
-          <t>Washington Nationals</t>
-        </is>
-      </c>
-      <c r="AR64" s="24" t="inlineStr">
-        <is>
-          <t>Washington Nationals</t>
-        </is>
-      </c>
-      <c r="AS64" s="24" t="inlineStr">
-        <is>
-          <t>mlb-phi</t>
-        </is>
-      </c>
-      <c r="AT64" s="24" t="inlineStr">
-        <is>
-          <t>Philadelphia Phillies</t>
-        </is>
-      </c>
-      <c r="AU64" s="24" t="inlineStr">
-        <is>
-          <t>Philadelphia Phillies</t>
-        </is>
-      </c>
-      <c r="AV64" s="24" t="n"/>
-      <c r="AW64" s="24" t="n"/>
-      <c r="AX64" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY64" s="24" t="n"/>
-      <c r="AZ64" s="24" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="BA64" s="24" t="inlineStr">
-        <is>
-          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
-        </is>
-      </c>
-      <c r="BB64" s="24" t="inlineStr">
-        <is>
-          <t>flat_probability_shrinkage_toward_half</t>
-        </is>
-      </c>
-      <c r="BC64" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-margin-v3</t>
-        </is>
-      </c>
-      <c r="BD64" s="24" t="inlineStr">
-        <is>
-          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
-        </is>
-      </c>
-      <c r="BE64" s="24" t="inlineStr">
-        <is>
-          <t>v3</t>
-        </is>
-      </c>
-      <c r="BF64" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG64" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-paired-v1</t>
-        </is>
-      </c>
-      <c r="BH64" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="BI64" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ64" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BK64" s="26" t="n">
-        <v>-122</v>
-      </c>
-      <c r="BL64" s="27" t="n">
-        <v>1.819672</v>
-      </c>
-      <c r="BM64" s="28" t="n">
-        <v>0.54955</v>
-      </c>
-      <c r="BN64" s="28" t="n">
-        <v>0.547264</v>
-      </c>
-      <c r="BO64" s="28" t="n"/>
-      <c r="BP64" s="25" t="n"/>
-      <c r="BQ64" s="27" t="n"/>
-      <c r="BR64" s="28" t="n"/>
-      <c r="BS64" s="28" t="n"/>
-      <c r="BT64" s="28" t="n"/>
-      <c r="BU64" s="25" t="n"/>
-      <c r="BV64" s="29" t="n"/>
-      <c r="BW64" s="24" t="n"/>
-      <c r="BX64" s="30" t="n"/>
-      <c r="BY64" s="27" t="n"/>
-      <c r="BZ64" s="24" t="n"/>
-      <c r="CA64" s="31" t="n"/>
-      <c r="CB64" s="24" t="n"/>
-      <c r="CC64" s="24" t="n"/>
-      <c r="CD64" s="24" t="n"/>
-      <c r="CE64" s="24" t="n"/>
-      <c r="CF64" s="24" t="n"/>
-      <c r="CG64" s="24" t="n"/>
-      <c r="CH64" s="24" t="n"/>
-      <c r="CI64" s="24" t="n"/>
-      <c r="CJ64" s="24" t="n"/>
-      <c r="CK64" s="24" t="n"/>
-      <c r="CL64" s="24" t="n"/>
-      <c r="CM64" s="24" t="n"/>
-      <c r="CN64" s="24" t="n"/>
-      <c r="CO64" s="24" t="n"/>
-      <c r="CP64" s="24" t="n"/>
-      <c r="CQ64" s="24" t="n"/>
-      <c r="CR64" s="24" t="n"/>
-      <c r="CS64" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="36" customHeight="1">
-      <c r="A65" s="24" t="inlineStr">
-        <is>
-          <t>353ff6ee090247b2</t>
-        </is>
-      </c>
-      <c r="B65" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="C65" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T22:40Z</t>
-        </is>
-      </c>
-      <c r="D65" s="24" t="inlineStr">
-        <is>
-          <t>401816405</t>
-        </is>
-      </c>
-      <c r="E65" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F65" s="24" t="inlineStr">
-        <is>
-          <t>Washington Nationals</t>
-        </is>
-      </c>
-      <c r="G65" s="24" t="inlineStr">
-        <is>
-          <t>Philadelphia Phillies</t>
-        </is>
-      </c>
-      <c r="H65" s="24" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="I65" s="24" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="J65" s="25" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="K65" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L65" s="26" t="n">
-        <v>-102</v>
-      </c>
-      <c r="M65" s="27" t="n">
-        <v>1.980392</v>
-      </c>
-      <c r="N65" s="28" t="n">
-        <v>0.50495</v>
-      </c>
-      <c r="O65" s="28" t="n">
-        <v>0.511737</v>
-      </c>
-      <c r="P65" s="28" t="n">
-        <v>0.042131</v>
-      </c>
-      <c r="Q65" s="28" t="n">
-        <v>0.006787</v>
-      </c>
-      <c r="R65" s="26" t="n">
-        <v>29</v>
-      </c>
-      <c r="S65" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T65" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-totals-v3</t>
-        </is>
-      </c>
-      <c r="U65" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V65" s="24" t="n"/>
-      <c r="W65" s="26" t="n"/>
-      <c r="X65" s="26" t="n"/>
-      <c r="Y65" s="25" t="n"/>
-      <c r="Z65" s="26" t="n"/>
-      <c r="AA65" s="28" t="n"/>
-      <c r="AB65" s="28" t="n"/>
-      <c r="AC65" s="30" t="n"/>
-      <c r="AD65" s="24" t="n"/>
-      <c r="AE65" s="31" t="inlineStr">
-        <is>
-          <t>Measured Edge Totals: Trend Engine projected 5.21-5.30; raw selected-side p=0.5239, calibrated p=0.5117.</t>
-        </is>
-      </c>
-      <c r="AF65" s="31" t="inlineStr">
-        <is>
-          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
-        </is>
-      </c>
-      <c r="AG65" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH65" s="24" t="n"/>
-      <c r="AI65" s="31" t="n"/>
-      <c r="AJ65" s="31" t="n"/>
-      <c r="AK65" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL65" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM65" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN65" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO65" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP65" s="24" t="inlineStr">
-        <is>
-          <t>mlb-wsh</t>
-        </is>
-      </c>
-      <c r="AQ65" s="24" t="inlineStr">
-        <is>
-          <t>Washington Nationals</t>
-        </is>
-      </c>
-      <c r="AR65" s="24" t="inlineStr">
-        <is>
-          <t>Washington Nationals</t>
-        </is>
-      </c>
-      <c r="AS65" s="24" t="inlineStr">
-        <is>
-          <t>mlb-phi</t>
-        </is>
-      </c>
-      <c r="AT65" s="24" t="inlineStr">
-        <is>
-          <t>Philadelphia Phillies</t>
-        </is>
-      </c>
-      <c r="AU65" s="24" t="inlineStr">
-        <is>
-          <t>Philadelphia Phillies</t>
-        </is>
-      </c>
-      <c r="AV65" s="24" t="n"/>
-      <c r="AW65" s="24" t="n"/>
-      <c r="AX65" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY65" s="24" t="n"/>
-      <c r="AZ65" s="24" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="BA65" s="24" t="inlineStr">
-        <is>
-          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
-        </is>
-      </c>
-      <c r="BB65" s="24" t="inlineStr">
-        <is>
-          <t>flat_probability_shrinkage_toward_half</t>
-        </is>
-      </c>
-      <c r="BC65" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-totals-v3</t>
-        </is>
-      </c>
-      <c r="BD65" s="24" t="inlineStr">
-        <is>
-          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
-        </is>
-      </c>
-      <c r="BE65" s="24" t="inlineStr">
-        <is>
-          <t>v3</t>
-        </is>
-      </c>
-      <c r="BF65" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG65" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-paired-v1</t>
-        </is>
-      </c>
-      <c r="BH65" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="BI65" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ65" s="25" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="BK65" s="26" t="n">
-        <v>-102</v>
-      </c>
-      <c r="BL65" s="27" t="n">
-        <v>1.980392</v>
-      </c>
-      <c r="BM65" s="28" t="n">
-        <v>0.50495</v>
-      </c>
-      <c r="BN65" s="28" t="n">
-        <v>0.502488</v>
-      </c>
-      <c r="BO65" s="28" t="n"/>
-      <c r="BP65" s="25" t="n"/>
-      <c r="BQ65" s="27" t="n"/>
-      <c r="BR65" s="28" t="n"/>
-      <c r="BS65" s="28" t="n"/>
-      <c r="BT65" s="28" t="n"/>
-      <c r="BU65" s="25" t="n"/>
-      <c r="BV65" s="29" t="n"/>
-      <c r="BW65" s="24" t="n"/>
-      <c r="BX65" s="30" t="n"/>
-      <c r="BY65" s="27" t="n"/>
-      <c r="BZ65" s="24" t="n"/>
-      <c r="CA65" s="31" t="n"/>
-      <c r="CB65" s="24" t="n"/>
-      <c r="CC65" s="24" t="n"/>
-      <c r="CD65" s="24" t="n"/>
-      <c r="CE65" s="24" t="n"/>
-      <c r="CF65" s="24" t="n"/>
-      <c r="CG65" s="24" t="n"/>
-      <c r="CH65" s="24" t="n"/>
-      <c r="CI65" s="24" t="n"/>
-      <c r="CJ65" s="24" t="n"/>
-      <c r="CK65" s="24" t="n"/>
-      <c r="CL65" s="24" t="n"/>
-      <c r="CM65" s="24" t="n"/>
-      <c r="CN65" s="24" t="n"/>
-      <c r="CO65" s="24" t="n"/>
-      <c r="CP65" s="24" t="n"/>
-      <c r="CQ65" s="24" t="n"/>
-      <c r="CR65" s="24" t="n"/>
-      <c r="CS65" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="36" customHeight="1">
-      <c r="A66" s="24" t="inlineStr">
-        <is>
-          <t>548336d41e204260</t>
-        </is>
-      </c>
-      <c r="B66" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="C66" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T23:05Z</t>
-        </is>
-      </c>
-      <c r="D66" s="24" t="inlineStr">
-        <is>
-          <t>401816404</t>
-        </is>
-      </c>
-      <c r="E66" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F66" s="24" t="inlineStr">
-        <is>
-          <t>St. Louis Cardinals</t>
-        </is>
-      </c>
-      <c r="G66" s="24" t="inlineStr">
-        <is>
-          <t>New York Yankees</t>
-        </is>
-      </c>
-      <c r="H66" s="24" t="inlineStr">
-        <is>
-          <t>spread</t>
-        </is>
-      </c>
-      <c r="I66" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J66" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K66" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L66" s="26" t="n">
-        <v>-144</v>
-      </c>
-      <c r="M66" s="27" t="n">
-        <v>1.694444</v>
-      </c>
-      <c r="N66" s="28" t="n">
-        <v>0.590164</v>
-      </c>
-      <c r="O66" s="28" t="n">
-        <v>0.624219</v>
-      </c>
-      <c r="P66" s="28" t="n">
-        <v>0.042131</v>
-      </c>
-      <c r="Q66" s="28" t="n">
-        <v>0.034055</v>
-      </c>
-      <c r="R66" s="26" t="n">
-        <v>43</v>
-      </c>
-      <c r="S66" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T66" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-margin-v3</t>
-        </is>
-      </c>
-      <c r="U66" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V66" s="24" t="n"/>
-      <c r="W66" s="26" t="n"/>
-      <c r="X66" s="26" t="n"/>
-      <c r="Y66" s="25" t="n"/>
-      <c r="Z66" s="26" t="n"/>
-      <c r="AA66" s="28" t="n"/>
-      <c r="AB66" s="28" t="n"/>
-      <c r="AC66" s="30" t="n"/>
-      <c r="AD66" s="24" t="n"/>
-      <c r="AE66" s="31" t="inlineStr">
-        <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.74-4.57; raw selected-side p=0.6823, calibrated p=0.6242.</t>
-        </is>
-      </c>
-      <c r="AF66" s="31" t="inlineStr">
-        <is>
-          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
-        </is>
-      </c>
-      <c r="AG66" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH66" s="24" t="n"/>
-      <c r="AI66" s="31" t="n"/>
-      <c r="AJ66" s="31" t="n"/>
-      <c r="AK66" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL66" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM66" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN66" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO66" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP66" s="24" t="inlineStr">
-        <is>
-          <t>mlb-stl</t>
-        </is>
-      </c>
-      <c r="AQ66" s="24" t="inlineStr">
-        <is>
-          <t>St. Louis Cardinals</t>
-        </is>
-      </c>
-      <c r="AR66" s="24" t="inlineStr">
-        <is>
-          <t>St. Louis Cardinals</t>
-        </is>
-      </c>
-      <c r="AS66" s="24" t="inlineStr">
-        <is>
-          <t>mlb-nyy</t>
-        </is>
-      </c>
-      <c r="AT66" s="24" t="inlineStr">
-        <is>
-          <t>New York Yankees</t>
-        </is>
-      </c>
-      <c r="AU66" s="24" t="inlineStr">
-        <is>
-          <t>New York Yankees</t>
-        </is>
-      </c>
-      <c r="AV66" s="24" t="n"/>
-      <c r="AW66" s="24" t="n"/>
-      <c r="AX66" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY66" s="24" t="n"/>
-      <c r="AZ66" s="24" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="BA66" s="24" t="inlineStr">
-        <is>
-          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
-        </is>
-      </c>
-      <c r="BB66" s="24" t="inlineStr">
-        <is>
-          <t>flat_probability_shrinkage_toward_half</t>
-        </is>
-      </c>
-      <c r="BC66" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-margin-v3</t>
-        </is>
-      </c>
-      <c r="BD66" s="24" t="inlineStr">
-        <is>
-          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
-        </is>
-      </c>
-      <c r="BE66" s="24" t="inlineStr">
-        <is>
-          <t>v3</t>
-        </is>
-      </c>
-      <c r="BF66" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG66" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-paired-v1</t>
-        </is>
-      </c>
-      <c r="BH66" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="BI66" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ66" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BK66" s="26" t="n">
-        <v>-144</v>
-      </c>
-      <c r="BL66" s="27" t="n">
-        <v>1.694444</v>
-      </c>
-      <c r="BM66" s="28" t="n">
-        <v>0.590164</v>
-      </c>
-      <c r="BN66" s="28" t="n">
-        <v>0.5870649999999999</v>
-      </c>
-      <c r="BO66" s="28" t="n"/>
-      <c r="BP66" s="25" t="n"/>
-      <c r="BQ66" s="27" t="n"/>
-      <c r="BR66" s="28" t="n"/>
-      <c r="BS66" s="28" t="n"/>
-      <c r="BT66" s="28" t="n"/>
-      <c r="BU66" s="25" t="n"/>
-      <c r="BV66" s="29" t="n"/>
-      <c r="BW66" s="24" t="n"/>
-      <c r="BX66" s="30" t="n"/>
-      <c r="BY66" s="27" t="n"/>
-      <c r="BZ66" s="24" t="n"/>
-      <c r="CA66" s="31" t="n"/>
-      <c r="CB66" s="24" t="n"/>
-      <c r="CC66" s="24" t="n"/>
-      <c r="CD66" s="24" t="n"/>
-      <c r="CE66" s="24" t="n"/>
-      <c r="CF66" s="24" t="n"/>
-      <c r="CG66" s="24" t="n"/>
-      <c r="CH66" s="24" t="n"/>
-      <c r="CI66" s="24" t="n"/>
-      <c r="CJ66" s="24" t="n"/>
-      <c r="CK66" s="24" t="n"/>
-      <c r="CL66" s="24" t="n"/>
-      <c r="CM66" s="24" t="n"/>
-      <c r="CN66" s="24" t="n"/>
-      <c r="CO66" s="24" t="n"/>
-      <c r="CP66" s="24" t="n"/>
-      <c r="CQ66" s="24" t="n"/>
-      <c r="CR66" s="24" t="n"/>
-      <c r="CS66" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="36" customHeight="1">
-      <c r="A67" s="24" t="inlineStr">
-        <is>
-          <t>0e446d444bfd48fa</t>
-        </is>
-      </c>
-      <c r="B67" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="C67" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T23:05Z</t>
-        </is>
-      </c>
-      <c r="D67" s="24" t="inlineStr">
-        <is>
-          <t>401816404</t>
-        </is>
-      </c>
-      <c r="E67" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F67" s="24" t="inlineStr">
-        <is>
-          <t>St. Louis Cardinals</t>
-        </is>
-      </c>
-      <c r="G67" s="24" t="inlineStr">
-        <is>
-          <t>New York Yankees</t>
-        </is>
-      </c>
-      <c r="H67" s="24" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="I67" s="24" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="J67" s="25" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="K67" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L67" s="26" t="n">
-        <v>-108</v>
-      </c>
-      <c r="M67" s="27" t="n">
-        <v>1.925926</v>
-      </c>
-      <c r="N67" s="28" t="n">
-        <v>0.519231</v>
-      </c>
-      <c r="O67" s="28" t="n">
-        <v>0.515997</v>
-      </c>
-      <c r="P67" s="28" t="n">
-        <v>0.042131</v>
-      </c>
-      <c r="Q67" s="28" t="n">
-        <v>-0.003234</v>
-      </c>
-      <c r="R67" s="26" t="n">
-        <v>24</v>
-      </c>
-      <c r="S67" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T67" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-totals-v3</t>
-        </is>
-      </c>
-      <c r="U67" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V67" s="24" t="n"/>
-      <c r="W67" s="26" t="n"/>
-      <c r="X67" s="26" t="n"/>
-      <c r="Y67" s="25" t="n"/>
-      <c r="Z67" s="26" t="n"/>
-      <c r="AA67" s="28" t="n"/>
-      <c r="AB67" s="28" t="n"/>
-      <c r="AC67" s="30" t="n"/>
-      <c r="AD67" s="24" t="n"/>
-      <c r="AE67" s="31" t="inlineStr">
-        <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.74-4.57; raw selected-side p=0.5411, calibrated p=0.5160.</t>
-        </is>
-      </c>
-      <c r="AF67" s="31" t="inlineStr">
-        <is>
-          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
-        </is>
-      </c>
-      <c r="AG67" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH67" s="24" t="n"/>
-      <c r="AI67" s="31" t="n"/>
-      <c r="AJ67" s="31" t="n"/>
-      <c r="AK67" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL67" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM67" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN67" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO67" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP67" s="24" t="inlineStr">
-        <is>
-          <t>mlb-stl</t>
-        </is>
-      </c>
-      <c r="AQ67" s="24" t="inlineStr">
-        <is>
-          <t>St. Louis Cardinals</t>
-        </is>
-      </c>
-      <c r="AR67" s="24" t="inlineStr">
-        <is>
-          <t>St. Louis Cardinals</t>
-        </is>
-      </c>
-      <c r="AS67" s="24" t="inlineStr">
-        <is>
-          <t>mlb-nyy</t>
-        </is>
-      </c>
-      <c r="AT67" s="24" t="inlineStr">
-        <is>
-          <t>New York Yankees</t>
-        </is>
-      </c>
-      <c r="AU67" s="24" t="inlineStr">
-        <is>
-          <t>New York Yankees</t>
-        </is>
-      </c>
-      <c r="AV67" s="24" t="n"/>
-      <c r="AW67" s="24" t="n"/>
-      <c r="AX67" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY67" s="24" t="n"/>
-      <c r="AZ67" s="24" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="BA67" s="24" t="inlineStr">
-        <is>
-          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
-        </is>
-      </c>
-      <c r="BB67" s="24" t="inlineStr">
-        <is>
-          <t>flat_probability_shrinkage_toward_half</t>
-        </is>
-      </c>
-      <c r="BC67" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-totals-v3</t>
-        </is>
-      </c>
-      <c r="BD67" s="24" t="inlineStr">
-        <is>
-          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
-        </is>
-      </c>
-      <c r="BE67" s="24" t="inlineStr">
-        <is>
-          <t>v3</t>
-        </is>
-      </c>
-      <c r="BF67" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG67" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-paired-v1</t>
-        </is>
-      </c>
-      <c r="BH67" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="BI67" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ67" s="25" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="BK67" s="26" t="n">
-        <v>-108</v>
-      </c>
-      <c r="BL67" s="27" t="n">
-        <v>1.925926</v>
-      </c>
-      <c r="BM67" s="28" t="n">
-        <v>0.519231</v>
-      </c>
-      <c r="BN67" s="28" t="n">
-        <v>0.517413</v>
-      </c>
-      <c r="BO67" s="28" t="n"/>
-      <c r="BP67" s="25" t="n"/>
-      <c r="BQ67" s="27" t="n"/>
-      <c r="BR67" s="28" t="n"/>
-      <c r="BS67" s="28" t="n"/>
-      <c r="BT67" s="28" t="n"/>
-      <c r="BU67" s="25" t="n"/>
-      <c r="BV67" s="29" t="n"/>
-      <c r="BW67" s="24" t="n"/>
-      <c r="BX67" s="30" t="n"/>
-      <c r="BY67" s="27" t="n"/>
-      <c r="BZ67" s="24" t="n"/>
-      <c r="CA67" s="31" t="n"/>
-      <c r="CB67" s="24" t="n"/>
-      <c r="CC67" s="24" t="n"/>
-      <c r="CD67" s="24" t="n"/>
-      <c r="CE67" s="24" t="n"/>
-      <c r="CF67" s="24" t="n"/>
-      <c r="CG67" s="24" t="n"/>
-      <c r="CH67" s="24" t="n"/>
-      <c r="CI67" s="24" t="n"/>
-      <c r="CJ67" s="24" t="n"/>
-      <c r="CK67" s="24" t="n"/>
-      <c r="CL67" s="24" t="n"/>
-      <c r="CM67" s="24" t="n"/>
-      <c r="CN67" s="24" t="n"/>
-      <c r="CO67" s="24" t="n"/>
-      <c r="CP67" s="24" t="n"/>
-      <c r="CQ67" s="24" t="n"/>
-      <c r="CR67" s="24" t="n"/>
-      <c r="CS67" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="36" customHeight="1">
-      <c r="A68" s="24" t="inlineStr">
-        <is>
-          <t>121480e59be84c61</t>
-        </is>
-      </c>
-      <c r="B68" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="C68" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T23:10Z</t>
-        </is>
-      </c>
-      <c r="D68" s="24" t="inlineStr">
-        <is>
-          <t>401816401</t>
-        </is>
-      </c>
-      <c r="E68" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F68" s="24" t="inlineStr">
-        <is>
-          <t>Chicago White Sox</t>
-        </is>
-      </c>
-      <c r="G68" s="24" t="inlineStr">
-        <is>
-          <t>Boston Red Sox</t>
-        </is>
-      </c>
-      <c r="H68" s="24" t="inlineStr">
-        <is>
-          <t>spread</t>
-        </is>
-      </c>
-      <c r="I68" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J68" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K68" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L68" s="26" t="n">
-        <v>-167</v>
-      </c>
-      <c r="M68" s="27" t="n">
-        <v>1.598802</v>
-      </c>
-      <c r="N68" s="28" t="n">
-        <v>0.625468</v>
-      </c>
-      <c r="O68" s="28" t="n">
-        <v>0.633248</v>
-      </c>
-      <c r="P68" s="28" t="n">
-        <v>0.042131</v>
-      </c>
-      <c r="Q68" s="28" t="n">
-        <v>0.00778</v>
-      </c>
-      <c r="R68" s="26" t="n">
-        <v>30</v>
-      </c>
-      <c r="S68" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T68" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-margin-v3</t>
-        </is>
-      </c>
-      <c r="U68" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V68" s="24" t="n"/>
-      <c r="W68" s="26" t="n"/>
-      <c r="X68" s="26" t="n"/>
-      <c r="Y68" s="25" t="n"/>
-      <c r="Z68" s="26" t="n"/>
-      <c r="AA68" s="28" t="n"/>
-      <c r="AB68" s="28" t="n"/>
-      <c r="AC68" s="30" t="n"/>
-      <c r="AD68" s="24" t="n"/>
-      <c r="AE68" s="31" t="inlineStr">
-        <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.13-3.98; raw selected-side p=0.6956, calibrated p=0.6332.</t>
-        </is>
-      </c>
-      <c r="AF68" s="31" t="inlineStr">
-        <is>
-          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
-        </is>
-      </c>
-      <c r="AG68" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH68" s="24" t="n"/>
-      <c r="AI68" s="31" t="n"/>
-      <c r="AJ68" s="31" t="n"/>
-      <c r="AK68" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL68" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM68" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN68" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO68" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP68" s="24" t="inlineStr">
-        <is>
-          <t>mlb-cws</t>
-        </is>
-      </c>
-      <c r="AQ68" s="24" t="inlineStr">
-        <is>
-          <t>Chicago White Sox</t>
-        </is>
-      </c>
-      <c r="AR68" s="24" t="inlineStr">
-        <is>
-          <t>Chicago White Sox</t>
-        </is>
-      </c>
-      <c r="AS68" s="24" t="inlineStr">
-        <is>
-          <t>mlb-bos</t>
-        </is>
-      </c>
-      <c r="AT68" s="24" t="inlineStr">
-        <is>
-          <t>Boston Red Sox</t>
-        </is>
-      </c>
-      <c r="AU68" s="24" t="inlineStr">
-        <is>
-          <t>Boston Red Sox</t>
-        </is>
-      </c>
-      <c r="AV68" s="24" t="n"/>
-      <c r="AW68" s="24" t="n"/>
-      <c r="AX68" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY68" s="24" t="n"/>
-      <c r="AZ68" s="24" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="BA68" s="24" t="inlineStr">
-        <is>
-          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
-        </is>
-      </c>
-      <c r="BB68" s="24" t="inlineStr">
-        <is>
-          <t>flat_probability_shrinkage_toward_half</t>
-        </is>
-      </c>
-      <c r="BC68" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-margin-v3</t>
-        </is>
-      </c>
-      <c r="BD68" s="24" t="inlineStr">
-        <is>
-          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
-        </is>
-      </c>
-      <c r="BE68" s="24" t="inlineStr">
-        <is>
-          <t>v3</t>
-        </is>
-      </c>
-      <c r="BF68" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG68" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-paired-v1</t>
-        </is>
-      </c>
-      <c r="BH68" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="BI68" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ68" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BK68" s="26" t="n">
-        <v>-167</v>
-      </c>
-      <c r="BL68" s="27" t="n">
-        <v>1.598802</v>
-      </c>
-      <c r="BM68" s="28" t="n">
-        <v>0.625468</v>
-      </c>
-      <c r="BN68" s="28" t="n">
-        <v>0.621891</v>
-      </c>
-      <c r="BO68" s="28" t="n"/>
-      <c r="BP68" s="25" t="n"/>
-      <c r="BQ68" s="27" t="n"/>
-      <c r="BR68" s="28" t="n"/>
-      <c r="BS68" s="28" t="n"/>
-      <c r="BT68" s="28" t="n"/>
-      <c r="BU68" s="25" t="n"/>
-      <c r="BV68" s="29" t="n"/>
-      <c r="BW68" s="24" t="n"/>
-      <c r="BX68" s="30" t="n"/>
-      <c r="BY68" s="27" t="n"/>
-      <c r="BZ68" s="24" t="n"/>
-      <c r="CA68" s="31" t="n"/>
-      <c r="CB68" s="24" t="n"/>
-      <c r="CC68" s="24" t="n"/>
-      <c r="CD68" s="24" t="n"/>
-      <c r="CE68" s="24" t="n"/>
-      <c r="CF68" s="24" t="n"/>
-      <c r="CG68" s="24" t="n"/>
-      <c r="CH68" s="24" t="n"/>
-      <c r="CI68" s="24" t="n"/>
-      <c r="CJ68" s="24" t="n"/>
-      <c r="CK68" s="24" t="n"/>
-      <c r="CL68" s="24" t="n"/>
-      <c r="CM68" s="24" t="n"/>
-      <c r="CN68" s="24" t="n"/>
-      <c r="CO68" s="24" t="n"/>
-      <c r="CP68" s="24" t="n"/>
-      <c r="CQ68" s="24" t="n"/>
-      <c r="CR68" s="24" t="n"/>
-      <c r="CS68" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="36" customHeight="1">
-      <c r="A69" s="24" t="inlineStr">
-        <is>
-          <t>357bc9b9aa6f487b</t>
-        </is>
-      </c>
-      <c r="B69" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="C69" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T23:10Z</t>
-        </is>
-      </c>
-      <c r="D69" s="24" t="inlineStr">
-        <is>
-          <t>401816401</t>
-        </is>
-      </c>
-      <c r="E69" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F69" s="24" t="inlineStr">
-        <is>
-          <t>Chicago White Sox</t>
-        </is>
-      </c>
-      <c r="G69" s="24" t="inlineStr">
-        <is>
-          <t>Boston Red Sox</t>
-        </is>
-      </c>
-      <c r="H69" s="24" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="I69" s="24" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="J69" s="25" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="K69" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L69" s="26" t="n">
-        <v>-111</v>
-      </c>
-      <c r="M69" s="27" t="n">
-        <v>1.900901</v>
-      </c>
-      <c r="N69" s="28" t="n">
-        <v>0.526066</v>
-      </c>
-      <c r="O69" s="28" t="n">
-        <v>0.522381</v>
-      </c>
-      <c r="P69" s="28" t="n">
-        <v>0.042131</v>
-      </c>
-      <c r="Q69" s="28" t="n">
-        <v>-0.003685</v>
-      </c>
-      <c r="R69" s="26" t="n">
-        <v>25</v>
-      </c>
-      <c r="S69" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T69" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-totals-v3</t>
-        </is>
-      </c>
-      <c r="U69" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V69" s="24" t="n"/>
-      <c r="W69" s="26" t="n"/>
-      <c r="X69" s="26" t="n"/>
-      <c r="Y69" s="25" t="n"/>
-      <c r="Z69" s="26" t="n"/>
-      <c r="AA69" s="28" t="n"/>
-      <c r="AB69" s="28" t="n"/>
-      <c r="AC69" s="30" t="n"/>
-      <c r="AD69" s="24" t="n"/>
-      <c r="AE69" s="31" t="inlineStr">
-        <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.13-3.98; raw selected-side p=0.5667, calibrated p=0.5224.</t>
-        </is>
-      </c>
-      <c r="AF69" s="31" t="inlineStr">
-        <is>
-          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
-        </is>
-      </c>
-      <c r="AG69" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH69" s="24" t="n"/>
-      <c r="AI69" s="31" t="n"/>
-      <c r="AJ69" s="31" t="n"/>
-      <c r="AK69" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL69" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM69" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN69" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO69" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP69" s="24" t="inlineStr">
-        <is>
-          <t>mlb-cws</t>
-        </is>
-      </c>
-      <c r="AQ69" s="24" t="inlineStr">
-        <is>
-          <t>Chicago White Sox</t>
-        </is>
-      </c>
-      <c r="AR69" s="24" t="inlineStr">
-        <is>
-          <t>Chicago White Sox</t>
-        </is>
-      </c>
-      <c r="AS69" s="24" t="inlineStr">
-        <is>
-          <t>mlb-bos</t>
-        </is>
-      </c>
-      <c r="AT69" s="24" t="inlineStr">
-        <is>
-          <t>Boston Red Sox</t>
-        </is>
-      </c>
-      <c r="AU69" s="24" t="inlineStr">
-        <is>
-          <t>Boston Red Sox</t>
-        </is>
-      </c>
-      <c r="AV69" s="24" t="n"/>
-      <c r="AW69" s="24" t="n"/>
-      <c r="AX69" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY69" s="24" t="n"/>
-      <c r="AZ69" s="24" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="BA69" s="24" t="inlineStr">
-        <is>
-          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
-        </is>
-      </c>
-      <c r="BB69" s="24" t="inlineStr">
-        <is>
-          <t>flat_probability_shrinkage_toward_half</t>
-        </is>
-      </c>
-      <c r="BC69" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-totals-v3</t>
-        </is>
-      </c>
-      <c r="BD69" s="24" t="inlineStr">
-        <is>
-          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
-        </is>
-      </c>
-      <c r="BE69" s="24" t="inlineStr">
-        <is>
-          <t>v3</t>
-        </is>
-      </c>
-      <c r="BF69" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG69" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-paired-v1</t>
-        </is>
-      </c>
-      <c r="BH69" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="BI69" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ69" s="25" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="BK69" s="26" t="n">
-        <v>-111</v>
-      </c>
-      <c r="BL69" s="27" t="n">
-        <v>1.900901</v>
-      </c>
-      <c r="BM69" s="28" t="n">
-        <v>0.526066</v>
-      </c>
-      <c r="BN69" s="28" t="n">
-        <v>0.522388</v>
-      </c>
-      <c r="BO69" s="28" t="n"/>
-      <c r="BP69" s="25" t="n"/>
-      <c r="BQ69" s="27" t="n"/>
-      <c r="BR69" s="28" t="n"/>
-      <c r="BS69" s="28" t="n"/>
-      <c r="BT69" s="28" t="n"/>
-      <c r="BU69" s="25" t="n"/>
-      <c r="BV69" s="29" t="n"/>
-      <c r="BW69" s="24" t="n"/>
-      <c r="BX69" s="30" t="n"/>
-      <c r="BY69" s="27" t="n"/>
-      <c r="BZ69" s="24" t="n"/>
-      <c r="CA69" s="31" t="n"/>
-      <c r="CB69" s="24" t="n"/>
-      <c r="CC69" s="24" t="n"/>
-      <c r="CD69" s="24" t="n"/>
-      <c r="CE69" s="24" t="n"/>
-      <c r="CF69" s="24" t="n"/>
-      <c r="CG69" s="24" t="n"/>
-      <c r="CH69" s="24" t="n"/>
-      <c r="CI69" s="24" t="n"/>
-      <c r="CJ69" s="24" t="n"/>
-      <c r="CK69" s="24" t="n"/>
-      <c r="CL69" s="24" t="n"/>
-      <c r="CM69" s="24" t="n"/>
-      <c r="CN69" s="24" t="n"/>
-      <c r="CO69" s="24" t="n"/>
-      <c r="CP69" s="24" t="n"/>
-      <c r="CQ69" s="24" t="n"/>
-      <c r="CR69" s="24" t="n"/>
-      <c r="CS69" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="36" customHeight="1">
-      <c r="A70" s="24" t="inlineStr">
-        <is>
-          <t>eaf4c819130f4347</t>
-        </is>
-      </c>
-      <c r="B70" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="C70" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T23:15Z</t>
-        </is>
-      </c>
-      <c r="D70" s="24" t="inlineStr">
-        <is>
-          <t>401816402</t>
-        </is>
-      </c>
-      <c r="E70" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F70" s="24" t="inlineStr">
-        <is>
-          <t>Miami Marlins</t>
-        </is>
-      </c>
-      <c r="G70" s="24" t="inlineStr">
-        <is>
-          <t>Atlanta Braves</t>
-        </is>
-      </c>
-      <c r="H70" s="24" t="inlineStr">
-        <is>
-          <t>spread</t>
-        </is>
-      </c>
-      <c r="I70" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J70" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K70" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L70" s="26" t="n">
-        <v>-174</v>
-      </c>
-      <c r="M70" s="27" t="n">
-        <v>1.574713</v>
-      </c>
-      <c r="N70" s="28" t="n">
-        <v>0.635036</v>
-      </c>
-      <c r="O70" s="28" t="n">
-        <v>0.639551</v>
-      </c>
-      <c r="P70" s="28" t="n">
-        <v>0.042131</v>
-      </c>
-      <c r="Q70" s="28" t="n">
-        <v>0.004515</v>
-      </c>
-      <c r="R70" s="26" t="n">
-        <v>29</v>
-      </c>
-      <c r="S70" s="29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="T70" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-margin-v3</t>
-        </is>
-      </c>
-      <c r="U70" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V70" s="24" t="n"/>
-      <c r="W70" s="26" t="n"/>
-      <c r="X70" s="26" t="n"/>
-      <c r="Y70" s="25" t="n"/>
-      <c r="Z70" s="26" t="n"/>
-      <c r="AA70" s="28" t="n"/>
-      <c r="AB70" s="28" t="n"/>
-      <c r="AC70" s="30" t="n"/>
-      <c r="AD70" s="24" t="n"/>
-      <c r="AE70" s="31" t="inlineStr">
-        <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.38-4.11; raw selected-side p=0.7048, calibrated p=0.6396.</t>
-        </is>
-      </c>
-      <c r="AF70" s="31" t="inlineStr">
-        <is>
-          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
-        </is>
-      </c>
-      <c r="AG70" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH70" s="24" t="n"/>
-      <c r="AI70" s="31" t="n"/>
-      <c r="AJ70" s="31" t="n"/>
-      <c r="AK70" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL70" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM70" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN70" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO70" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP70" s="24" t="inlineStr">
-        <is>
-          <t>mlb-mia</t>
-        </is>
-      </c>
-      <c r="AQ70" s="24" t="inlineStr">
-        <is>
-          <t>Miami Marlins</t>
-        </is>
-      </c>
-      <c r="AR70" s="24" t="inlineStr">
-        <is>
-          <t>Miami Marlins</t>
-        </is>
-      </c>
-      <c r="AS70" s="24" t="inlineStr">
-        <is>
-          <t>mlb-atl</t>
-        </is>
-      </c>
-      <c r="AT70" s="24" t="inlineStr">
-        <is>
-          <t>Atlanta Braves</t>
-        </is>
-      </c>
-      <c r="AU70" s="24" t="inlineStr">
-        <is>
-          <t>Atlanta Braves</t>
-        </is>
-      </c>
-      <c r="AV70" s="24" t="n"/>
-      <c r="AW70" s="24" t="n"/>
-      <c r="AX70" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY70" s="24" t="n"/>
-      <c r="AZ70" s="24" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="BA70" s="24" t="inlineStr">
-        <is>
-          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
-        </is>
-      </c>
-      <c r="BB70" s="24" t="inlineStr">
-        <is>
-          <t>flat_probability_shrinkage_toward_half</t>
-        </is>
-      </c>
-      <c r="BC70" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-margin-v3</t>
-        </is>
-      </c>
-      <c r="BD70" s="24" t="inlineStr">
-        <is>
-          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
-        </is>
-      </c>
-      <c r="BE70" s="24" t="inlineStr">
-        <is>
-          <t>v3</t>
-        </is>
-      </c>
-      <c r="BF70" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG70" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-paired-v1</t>
-        </is>
-      </c>
-      <c r="BH70" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="BI70" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ70" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BK70" s="26" t="n">
-        <v>-174</v>
-      </c>
-      <c r="BL70" s="27" t="n">
-        <v>1.574713</v>
-      </c>
-      <c r="BM70" s="28" t="n">
-        <v>0.635036</v>
-      </c>
-      <c r="BN70" s="28" t="n">
-        <v>0.631841</v>
-      </c>
-      <c r="BO70" s="28" t="n"/>
-      <c r="BP70" s="25" t="n"/>
-      <c r="BQ70" s="27" t="n"/>
-      <c r="BR70" s="28" t="n"/>
-      <c r="BS70" s="28" t="n"/>
-      <c r="BT70" s="28" t="n"/>
-      <c r="BU70" s="25" t="n"/>
-      <c r="BV70" s="29" t="n"/>
-      <c r="BW70" s="24" t="n"/>
-      <c r="BX70" s="30" t="n"/>
-      <c r="BY70" s="27" t="n"/>
-      <c r="BZ70" s="24" t="n"/>
-      <c r="CA70" s="31" t="n"/>
-      <c r="CB70" s="24" t="n"/>
-      <c r="CC70" s="24" t="n"/>
-      <c r="CD70" s="24" t="n"/>
-      <c r="CE70" s="24" t="n"/>
-      <c r="CF70" s="24" t="n"/>
-      <c r="CG70" s="24" t="n"/>
-      <c r="CH70" s="24" t="n"/>
-      <c r="CI70" s="24" t="n"/>
-      <c r="CJ70" s="24" t="n"/>
-      <c r="CK70" s="24" t="n"/>
-      <c r="CL70" s="24" t="n"/>
-      <c r="CM70" s="24" t="n"/>
-      <c r="CN70" s="24" t="n"/>
-      <c r="CO70" s="24" t="n"/>
-      <c r="CP70" s="24" t="n"/>
-      <c r="CQ70" s="24" t="n"/>
-      <c r="CR70" s="24" t="n"/>
-      <c r="CS70" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="36" customHeight="1">
-      <c r="A71" s="24" t="inlineStr">
-        <is>
-          <t>b4aa3184686a4646</t>
-        </is>
-      </c>
-      <c r="B71" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="C71" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T23:15Z</t>
-        </is>
-      </c>
-      <c r="D71" s="24" t="inlineStr">
-        <is>
-          <t>401816402</t>
-        </is>
-      </c>
-      <c r="E71" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F71" s="24" t="inlineStr">
-        <is>
-          <t>Miami Marlins</t>
-        </is>
-      </c>
-      <c r="G71" s="24" t="inlineStr">
-        <is>
-          <t>Atlanta Braves</t>
-        </is>
-      </c>
-      <c r="H71" s="24" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="I71" s="24" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="J71" s="25" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="K71" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L71" s="26" t="n">
-        <v>108</v>
-      </c>
-      <c r="M71" s="27" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="N71" s="28" t="n">
-        <v>0.480769</v>
-      </c>
-      <c r="O71" s="28" t="n">
-        <v>0.513637</v>
-      </c>
-      <c r="P71" s="28" t="n">
-        <v>0.042131</v>
-      </c>
-      <c r="Q71" s="28" t="n">
-        <v>0.032868</v>
-      </c>
-      <c r="R71" s="26" t="n">
-        <v>43</v>
-      </c>
-      <c r="S71" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T71" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-totals-v3</t>
-        </is>
-      </c>
-      <c r="U71" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V71" s="24" t="n"/>
-      <c r="W71" s="26" t="n"/>
-      <c r="X71" s="26" t="n"/>
-      <c r="Y71" s="25" t="n"/>
-      <c r="Z71" s="26" t="n"/>
-      <c r="AA71" s="28" t="n"/>
-      <c r="AB71" s="28" t="n"/>
-      <c r="AC71" s="30" t="n"/>
-      <c r="AD71" s="24" t="n"/>
-      <c r="AE71" s="31" t="inlineStr">
-        <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.38-4.11; raw selected-side p=0.5315, calibrated p=0.5136.</t>
-        </is>
-      </c>
-      <c r="AF71" s="31" t="inlineStr">
-        <is>
-          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
-        </is>
-      </c>
-      <c r="AG71" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH71" s="24" t="n"/>
-      <c r="AI71" s="31" t="n"/>
-      <c r="AJ71" s="31" t="n"/>
-      <c r="AK71" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL71" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM71" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN71" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO71" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP71" s="24" t="inlineStr">
-        <is>
-          <t>mlb-mia</t>
-        </is>
-      </c>
-      <c r="AQ71" s="24" t="inlineStr">
-        <is>
-          <t>Miami Marlins</t>
-        </is>
-      </c>
-      <c r="AR71" s="24" t="inlineStr">
-        <is>
-          <t>Miami Marlins</t>
-        </is>
-      </c>
-      <c r="AS71" s="24" t="inlineStr">
-        <is>
-          <t>mlb-atl</t>
-        </is>
-      </c>
-      <c r="AT71" s="24" t="inlineStr">
-        <is>
-          <t>Atlanta Braves</t>
-        </is>
-      </c>
-      <c r="AU71" s="24" t="inlineStr">
-        <is>
-          <t>Atlanta Braves</t>
-        </is>
-      </c>
-      <c r="AV71" s="24" t="n"/>
-      <c r="AW71" s="24" t="n"/>
-      <c r="AX71" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY71" s="24" t="n"/>
-      <c r="AZ71" s="24" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="BA71" s="24" t="inlineStr">
-        <is>
-          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
-        </is>
-      </c>
-      <c r="BB71" s="24" t="inlineStr">
-        <is>
-          <t>flat_probability_shrinkage_toward_half</t>
-        </is>
-      </c>
-      <c r="BC71" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-totals-v3</t>
-        </is>
-      </c>
-      <c r="BD71" s="24" t="inlineStr">
-        <is>
-          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
-        </is>
-      </c>
-      <c r="BE71" s="24" t="inlineStr">
-        <is>
-          <t>v3</t>
-        </is>
-      </c>
-      <c r="BF71" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG71" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-paired-v1</t>
-        </is>
-      </c>
-      <c r="BH71" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="BI71" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ71" s="25" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="BK71" s="26" t="n">
-        <v>108</v>
-      </c>
-      <c r="BL71" s="27" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BM71" s="28" t="n">
-        <v>0.480769</v>
-      </c>
-      <c r="BN71" s="28" t="n">
-        <v>0.477612</v>
-      </c>
-      <c r="BO71" s="28" t="n"/>
-      <c r="BP71" s="25" t="n"/>
-      <c r="BQ71" s="27" t="n"/>
-      <c r="BR71" s="28" t="n"/>
-      <c r="BS71" s="28" t="n"/>
-      <c r="BT71" s="28" t="n"/>
-      <c r="BU71" s="25" t="n"/>
-      <c r="BV71" s="29" t="n"/>
-      <c r="BW71" s="24" t="n"/>
-      <c r="BX71" s="30" t="n"/>
-      <c r="BY71" s="27" t="n"/>
-      <c r="BZ71" s="24" t="n"/>
-      <c r="CA71" s="31" t="n"/>
-      <c r="CB71" s="24" t="n"/>
-      <c r="CC71" s="24" t="n"/>
-      <c r="CD71" s="24" t="n"/>
-      <c r="CE71" s="24" t="n"/>
-      <c r="CF71" s="24" t="n"/>
-      <c r="CG71" s="24" t="n"/>
-      <c r="CH71" s="24" t="n"/>
-      <c r="CI71" s="24" t="n"/>
-      <c r="CJ71" s="24" t="n"/>
-      <c r="CK71" s="24" t="n"/>
-      <c r="CL71" s="24" t="n"/>
-      <c r="CM71" s="24" t="n"/>
-      <c r="CN71" s="24" t="n"/>
-      <c r="CO71" s="24" t="n"/>
-      <c r="CP71" s="24" t="n"/>
-      <c r="CQ71" s="24" t="n"/>
-      <c r="CR71" s="24" t="n"/>
-      <c r="CS71" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="36" customHeight="1">
-      <c r="A72" s="24" t="inlineStr">
-        <is>
-          <t>6a8f0f1cb0614a33</t>
-        </is>
-      </c>
-      <c r="B72" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="C72" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T23:30Z</t>
-        </is>
-      </c>
-      <c r="D72" s="24" t="inlineStr">
-        <is>
-          <t>401816408</t>
-        </is>
-      </c>
-      <c r="E72" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F72" s="24" t="inlineStr">
-        <is>
-          <t>Pittsburgh Pirates</t>
-        </is>
-      </c>
-      <c r="G72" s="24" t="inlineStr">
-        <is>
-          <t>Milwaukee Brewers</t>
-        </is>
-      </c>
-      <c r="H72" s="24" t="inlineStr">
-        <is>
-          <t>spread</t>
-        </is>
-      </c>
-      <c r="I72" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J72" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K72" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L72" s="26" t="n">
-        <v>-178</v>
-      </c>
-      <c r="M72" s="27" t="n">
-        <v>1.561798</v>
-      </c>
-      <c r="N72" s="28" t="n">
-        <v>0.640288</v>
-      </c>
-      <c r="O72" s="28" t="n">
-        <v>0.586402</v>
-      </c>
-      <c r="P72" s="28" t="n">
-        <v>0.042131</v>
-      </c>
-      <c r="Q72" s="28" t="n">
-        <v>-0.053886</v>
-      </c>
-      <c r="R72" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S72" s="29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T72" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-margin-v3</t>
-        </is>
-      </c>
-      <c r="U72" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V72" s="24" t="n"/>
-      <c r="W72" s="26" t="n"/>
-      <c r="X72" s="26" t="n"/>
-      <c r="Y72" s="25" t="n"/>
-      <c r="Z72" s="26" t="n"/>
-      <c r="AA72" s="28" t="n"/>
-      <c r="AB72" s="28" t="n"/>
-      <c r="AC72" s="30" t="n"/>
-      <c r="AD72" s="24" t="n"/>
-      <c r="AE72" s="31" t="inlineStr">
-        <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.27-4.68; raw selected-side p=0.6268, calibrated p=0.5864.</t>
-        </is>
-      </c>
-      <c r="AF72" s="31" t="inlineStr">
-        <is>
-          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
-        </is>
-      </c>
-      <c r="AG72" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH72" s="24" t="n"/>
-      <c r="AI72" s="31" t="n"/>
-      <c r="AJ72" s="31" t="n"/>
-      <c r="AK72" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL72" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM72" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN72" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO72" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP72" s="24" t="inlineStr">
-        <is>
-          <t>mlb-pit</t>
-        </is>
-      </c>
-      <c r="AQ72" s="24" t="inlineStr">
-        <is>
-          <t>Pittsburgh Pirates</t>
-        </is>
-      </c>
-      <c r="AR72" s="24" t="inlineStr">
-        <is>
-          <t>Pittsburgh Pirates</t>
-        </is>
-      </c>
-      <c r="AS72" s="24" t="inlineStr">
-        <is>
-          <t>mlb-mil</t>
-        </is>
-      </c>
-      <c r="AT72" s="24" t="inlineStr">
-        <is>
-          <t>Milwaukee Brewers</t>
-        </is>
-      </c>
-      <c r="AU72" s="24" t="inlineStr">
-        <is>
-          <t>Milwaukee Brewers</t>
-        </is>
-      </c>
-      <c r="AV72" s="24" t="n"/>
-      <c r="AW72" s="24" t="n"/>
-      <c r="AX72" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY72" s="24" t="n"/>
-      <c r="AZ72" s="24" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="BA72" s="24" t="inlineStr">
-        <is>
-          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
-        </is>
-      </c>
-      <c r="BB72" s="24" t="inlineStr">
-        <is>
-          <t>flat_probability_shrinkage_toward_half</t>
-        </is>
-      </c>
-      <c r="BC72" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-margin-v3</t>
-        </is>
-      </c>
-      <c r="BD72" s="24" t="inlineStr">
-        <is>
-          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
-        </is>
-      </c>
-      <c r="BE72" s="24" t="inlineStr">
-        <is>
-          <t>v3</t>
-        </is>
-      </c>
-      <c r="BF72" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG72" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-paired-v1</t>
-        </is>
-      </c>
-      <c r="BH72" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="BI72" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ72" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BK72" s="26" t="n">
-        <v>-178</v>
-      </c>
-      <c r="BL72" s="27" t="n">
-        <v>1.561798</v>
-      </c>
-      <c r="BM72" s="28" t="n">
-        <v>0.640288</v>
-      </c>
-      <c r="BN72" s="28" t="n">
-        <v>0.636816</v>
-      </c>
-      <c r="BO72" s="28" t="n"/>
-      <c r="BP72" s="25" t="n"/>
-      <c r="BQ72" s="27" t="n"/>
-      <c r="BR72" s="28" t="n"/>
-      <c r="BS72" s="28" t="n"/>
-      <c r="BT72" s="28" t="n"/>
-      <c r="BU72" s="25" t="n"/>
-      <c r="BV72" s="29" t="n"/>
-      <c r="BW72" s="24" t="n"/>
-      <c r="BX72" s="30" t="n"/>
-      <c r="BY72" s="27" t="n"/>
-      <c r="BZ72" s="24" t="n"/>
-      <c r="CA72" s="31" t="n"/>
-      <c r="CB72" s="24" t="n"/>
-      <c r="CC72" s="24" t="n"/>
-      <c r="CD72" s="24" t="n"/>
-      <c r="CE72" s="24" t="n"/>
-      <c r="CF72" s="24" t="n"/>
-      <c r="CG72" s="24" t="n"/>
-      <c r="CH72" s="24" t="n"/>
-      <c r="CI72" s="24" t="n"/>
-      <c r="CJ72" s="24" t="n"/>
-      <c r="CK72" s="24" t="n"/>
-      <c r="CL72" s="24" t="n"/>
-      <c r="CM72" s="24" t="n"/>
-      <c r="CN72" s="24" t="n"/>
-      <c r="CO72" s="24" t="n"/>
-      <c r="CP72" s="24" t="n"/>
-      <c r="CQ72" s="24" t="n"/>
-      <c r="CR72" s="24" t="n"/>
-      <c r="CS72" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="36" customHeight="1">
-      <c r="A73" s="24" t="inlineStr">
-        <is>
-          <t>12d42c3262224698</t>
-        </is>
-      </c>
-      <c r="B73" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="C73" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T23:30Z</t>
-        </is>
-      </c>
-      <c r="D73" s="24" t="inlineStr">
-        <is>
-          <t>401816408</t>
-        </is>
-      </c>
-      <c r="E73" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F73" s="24" t="inlineStr">
-        <is>
-          <t>Pittsburgh Pirates</t>
-        </is>
-      </c>
-      <c r="G73" s="24" t="inlineStr">
-        <is>
-          <t>Milwaukee Brewers</t>
-        </is>
-      </c>
-      <c r="H73" s="24" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="I73" s="24" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="J73" s="25" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="K73" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L73" s="26" t="n">
-        <v>117</v>
-      </c>
-      <c r="M73" s="27" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="N73" s="28" t="n">
-        <v>0.460829</v>
-      </c>
-      <c r="O73" s="28" t="n">
-        <v>0.527398</v>
-      </c>
-      <c r="P73" s="28" t="n">
-        <v>0.042131</v>
-      </c>
-      <c r="Q73" s="28" t="n">
-        <v>0.066569</v>
-      </c>
-      <c r="R73" s="26" t="n">
-        <v>60</v>
-      </c>
-      <c r="S73" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T73" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-totals-v3</t>
-        </is>
-      </c>
-      <c r="U73" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V73" s="24" t="n"/>
-      <c r="W73" s="26" t="n"/>
-      <c r="X73" s="26" t="n"/>
-      <c r="Y73" s="25" t="n"/>
-      <c r="Z73" s="26" t="n"/>
-      <c r="AA73" s="28" t="n"/>
-      <c r="AB73" s="28" t="n"/>
-      <c r="AC73" s="30" t="n"/>
-      <c r="AD73" s="24" t="n"/>
-      <c r="AE73" s="31" t="inlineStr">
-        <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.27-4.68; raw selected-side p=0.5869, calibrated p=0.5274.</t>
-        </is>
-      </c>
-      <c r="AF73" s="31" t="inlineStr">
-        <is>
-          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
-        </is>
-      </c>
-      <c r="AG73" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH73" s="24" t="n"/>
-      <c r="AI73" s="31" t="n"/>
-      <c r="AJ73" s="31" t="n"/>
-      <c r="AK73" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL73" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM73" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN73" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO73" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP73" s="24" t="inlineStr">
-        <is>
-          <t>mlb-pit</t>
-        </is>
-      </c>
-      <c r="AQ73" s="24" t="inlineStr">
-        <is>
-          <t>Pittsburgh Pirates</t>
-        </is>
-      </c>
-      <c r="AR73" s="24" t="inlineStr">
-        <is>
-          <t>Pittsburgh Pirates</t>
-        </is>
-      </c>
-      <c r="AS73" s="24" t="inlineStr">
-        <is>
-          <t>mlb-mil</t>
-        </is>
-      </c>
-      <c r="AT73" s="24" t="inlineStr">
-        <is>
-          <t>Milwaukee Brewers</t>
-        </is>
-      </c>
-      <c r="AU73" s="24" t="inlineStr">
-        <is>
-          <t>Milwaukee Brewers</t>
-        </is>
-      </c>
-      <c r="AV73" s="24" t="n"/>
-      <c r="AW73" s="24" t="n"/>
-      <c r="AX73" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY73" s="24" t="n"/>
-      <c r="AZ73" s="24" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="BA73" s="24" t="inlineStr">
-        <is>
-          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
-        </is>
-      </c>
-      <c r="BB73" s="24" t="inlineStr">
-        <is>
-          <t>flat_probability_shrinkage_toward_half</t>
-        </is>
-      </c>
-      <c r="BC73" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-totals-v3</t>
-        </is>
-      </c>
-      <c r="BD73" s="24" t="inlineStr">
-        <is>
-          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
-        </is>
-      </c>
-      <c r="BE73" s="24" t="inlineStr">
-        <is>
-          <t>v3</t>
-        </is>
-      </c>
-      <c r="BF73" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG73" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-paired-v1</t>
-        </is>
-      </c>
-      <c r="BH73" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="BI73" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ73" s="25" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="BK73" s="26" t="n">
-        <v>117</v>
-      </c>
-      <c r="BL73" s="27" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BM73" s="28" t="n">
-        <v>0.460829</v>
-      </c>
-      <c r="BN73" s="28" t="n">
-        <v>0.457711</v>
-      </c>
-      <c r="BO73" s="28" t="n"/>
-      <c r="BP73" s="25" t="n"/>
-      <c r="BQ73" s="27" t="n"/>
-      <c r="BR73" s="28" t="n"/>
-      <c r="BS73" s="28" t="n"/>
-      <c r="BT73" s="28" t="n"/>
-      <c r="BU73" s="25" t="n"/>
-      <c r="BV73" s="29" t="n"/>
-      <c r="BW73" s="24" t="n"/>
-      <c r="BX73" s="30" t="n"/>
-      <c r="BY73" s="27" t="n"/>
-      <c r="BZ73" s="24" t="n"/>
-      <c r="CA73" s="31" t="n"/>
-      <c r="CB73" s="24" t="n"/>
-      <c r="CC73" s="24" t="n"/>
-      <c r="CD73" s="24" t="n"/>
-      <c r="CE73" s="24" t="n"/>
-      <c r="CF73" s="24" t="n"/>
-      <c r="CG73" s="24" t="n"/>
-      <c r="CH73" s="24" t="n"/>
-      <c r="CI73" s="24" t="n"/>
-      <c r="CJ73" s="24" t="n"/>
-      <c r="CK73" s="24" t="n"/>
-      <c r="CL73" s="24" t="n"/>
-      <c r="CM73" s="24" t="n"/>
-      <c r="CN73" s="24" t="n"/>
-      <c r="CO73" s="24" t="n"/>
-      <c r="CP73" s="24" t="n"/>
-      <c r="CQ73" s="24" t="n"/>
-      <c r="CR73" s="24" t="n"/>
-      <c r="CS73" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="36" customHeight="1">
-      <c r="A74" s="24" t="inlineStr">
-        <is>
-          <t>a440f9bcad354056</t>
-        </is>
-      </c>
-      <c r="B74" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="C74" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T23:40Z</t>
-        </is>
-      </c>
-      <c r="D74" s="24" t="inlineStr">
-        <is>
-          <t>401816407</t>
-        </is>
-      </c>
-      <c r="E74" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F74" s="24" t="inlineStr">
-        <is>
-          <t>Minnesota Twins</t>
-        </is>
-      </c>
-      <c r="G74" s="24" t="inlineStr">
-        <is>
-          <t>Kansas City Royals</t>
-        </is>
-      </c>
-      <c r="H74" s="24" t="inlineStr">
-        <is>
-          <t>spread</t>
-        </is>
-      </c>
-      <c r="I74" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J74" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K74" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L74" s="26" t="n">
-        <v>-178</v>
-      </c>
-      <c r="M74" s="27" t="n">
-        <v>1.561798</v>
-      </c>
-      <c r="N74" s="28" t="n">
-        <v>0.640288</v>
-      </c>
-      <c r="O74" s="28" t="n">
-        <v>0.648545</v>
-      </c>
-      <c r="P74" s="28" t="n">
-        <v>0.05172</v>
-      </c>
-      <c r="Q74" s="28" t="n">
-        <v>0.008257</v>
-      </c>
-      <c r="R74" s="26" t="n">
-        <v>25</v>
-      </c>
-      <c r="S74" s="29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="T74" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-margin-v3</t>
-        </is>
-      </c>
-      <c r="U74" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V74" s="24" t="n"/>
-      <c r="W74" s="26" t="n"/>
-      <c r="X74" s="26" t="n"/>
-      <c r="Y74" s="25" t="n"/>
-      <c r="Z74" s="26" t="n"/>
-      <c r="AA74" s="28" t="n"/>
-      <c r="AB74" s="28" t="n"/>
-      <c r="AC74" s="30" t="n"/>
-      <c r="AD74" s="24" t="n"/>
-      <c r="AE74" s="31" t="inlineStr">
-        <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.58-5.19; raw selected-side p=0.7180, calibrated p=0.6485.</t>
-        </is>
-      </c>
-      <c r="AF74" s="31" t="inlineStr">
-        <is>
-          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
-        </is>
-      </c>
-      <c r="AG74" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH74" s="24" t="n"/>
-      <c r="AI74" s="31" t="n"/>
-      <c r="AJ74" s="31" t="n"/>
-      <c r="AK74" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL74" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM74" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN74" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO74" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP74" s="24" t="inlineStr">
-        <is>
-          <t>mlb-min</t>
-        </is>
-      </c>
-      <c r="AQ74" s="24" t="inlineStr">
-        <is>
-          <t>Minnesota Twins</t>
-        </is>
-      </c>
-      <c r="AR74" s="24" t="inlineStr">
-        <is>
-          <t>Minnesota Twins</t>
-        </is>
-      </c>
-      <c r="AS74" s="24" t="inlineStr">
-        <is>
-          <t>mlb-kc</t>
-        </is>
-      </c>
-      <c r="AT74" s="24" t="inlineStr">
-        <is>
-          <t>Kansas City Royals</t>
-        </is>
-      </c>
-      <c r="AU74" s="24" t="inlineStr">
-        <is>
-          <t>Kansas City Royals</t>
-        </is>
-      </c>
-      <c r="AV74" s="24" t="n"/>
-      <c r="AW74" s="24" t="n"/>
-      <c r="AX74" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY74" s="24" t="n"/>
-      <c r="AZ74" s="24" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="BA74" s="24" t="inlineStr">
-        <is>
-          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
-        </is>
-      </c>
-      <c r="BB74" s="24" t="inlineStr">
-        <is>
-          <t>flat_probability_shrinkage_toward_half</t>
-        </is>
-      </c>
-      <c r="BC74" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-margin-v3</t>
-        </is>
-      </c>
-      <c r="BD74" s="24" t="inlineStr">
-        <is>
-          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
-        </is>
-      </c>
-      <c r="BE74" s="24" t="inlineStr">
-        <is>
-          <t>v3</t>
-        </is>
-      </c>
-      <c r="BF74" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG74" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-paired-v1</t>
-        </is>
-      </c>
-      <c r="BH74" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="BI74" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ74" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BK74" s="26" t="n">
-        <v>-178</v>
-      </c>
-      <c r="BL74" s="27" t="n">
-        <v>1.561798</v>
-      </c>
-      <c r="BM74" s="28" t="n">
-        <v>0.640288</v>
-      </c>
-      <c r="BN74" s="28" t="n">
-        <v>0.636816</v>
-      </c>
-      <c r="BO74" s="28" t="n"/>
-      <c r="BP74" s="25" t="n"/>
-      <c r="BQ74" s="27" t="n"/>
-      <c r="BR74" s="28" t="n"/>
-      <c r="BS74" s="28" t="n"/>
-      <c r="BT74" s="28" t="n"/>
-      <c r="BU74" s="25" t="n"/>
-      <c r="BV74" s="29" t="n"/>
-      <c r="BW74" s="24" t="n"/>
-      <c r="BX74" s="30" t="n"/>
-      <c r="BY74" s="27" t="n"/>
-      <c r="BZ74" s="24" t="n"/>
-      <c r="CA74" s="31" t="n"/>
-      <c r="CB74" s="24" t="n"/>
-      <c r="CC74" s="24" t="n"/>
-      <c r="CD74" s="24" t="n"/>
-      <c r="CE74" s="24" t="n"/>
-      <c r="CF74" s="24" t="n"/>
-      <c r="CG74" s="24" t="n"/>
-      <c r="CH74" s="24" t="n"/>
-      <c r="CI74" s="24" t="n"/>
-      <c r="CJ74" s="24" t="n"/>
-      <c r="CK74" s="24" t="n"/>
-      <c r="CL74" s="24" t="n"/>
-      <c r="CM74" s="24" t="n"/>
-      <c r="CN74" s="24" t="n"/>
-      <c r="CO74" s="24" t="n"/>
-      <c r="CP74" s="24" t="n"/>
-      <c r="CQ74" s="24" t="n"/>
-      <c r="CR74" s="24" t="n"/>
-      <c r="CS74" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="36" customHeight="1">
-      <c r="A75" s="24" t="inlineStr">
-        <is>
-          <t>2e8ee2437c3349dc</t>
-        </is>
-      </c>
-      <c r="B75" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="C75" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T23:40Z</t>
-        </is>
-      </c>
-      <c r="D75" s="24" t="inlineStr">
-        <is>
-          <t>401816407</t>
-        </is>
-      </c>
-      <c r="E75" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F75" s="24" t="inlineStr">
-        <is>
-          <t>Minnesota Twins</t>
-        </is>
-      </c>
-      <c r="G75" s="24" t="inlineStr">
-        <is>
-          <t>Kansas City Royals</t>
-        </is>
-      </c>
-      <c r="H75" s="24" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="I75" s="24" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="J75" s="25" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="K75" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L75" s="26" t="n">
-        <v>-111</v>
-      </c>
-      <c r="M75" s="27" t="n">
-        <v>1.900901</v>
-      </c>
-      <c r="N75" s="28" t="n">
-        <v>0.526066</v>
-      </c>
-      <c r="O75" s="28" t="n">
-        <v>0.524778</v>
-      </c>
-      <c r="P75" s="28" t="n">
-        <v>0.05172</v>
-      </c>
-      <c r="Q75" s="28" t="n">
-        <v>-0.001288</v>
-      </c>
-      <c r="R75" s="26" t="n">
-        <v>20</v>
-      </c>
-      <c r="S75" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T75" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-totals-v3</t>
-        </is>
-      </c>
-      <c r="U75" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V75" s="24" t="n"/>
-      <c r="W75" s="26" t="n"/>
-      <c r="X75" s="26" t="n"/>
-      <c r="Y75" s="25" t="n"/>
-      <c r="Z75" s="26" t="n"/>
-      <c r="AA75" s="28" t="n"/>
-      <c r="AB75" s="28" t="n"/>
-      <c r="AC75" s="30" t="n"/>
-      <c r="AD75" s="24" t="n"/>
-      <c r="AE75" s="31" t="inlineStr">
-        <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.58-5.19; raw selected-side p=0.5764, calibrated p=0.5248.</t>
-        </is>
-      </c>
-      <c r="AF75" s="31" t="inlineStr">
-        <is>
-          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
-        </is>
-      </c>
-      <c r="AG75" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH75" s="24" t="n"/>
-      <c r="AI75" s="31" t="n"/>
-      <c r="AJ75" s="31" t="n"/>
-      <c r="AK75" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL75" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM75" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN75" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO75" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP75" s="24" t="inlineStr">
-        <is>
-          <t>mlb-min</t>
-        </is>
-      </c>
-      <c r="AQ75" s="24" t="inlineStr">
-        <is>
-          <t>Minnesota Twins</t>
-        </is>
-      </c>
-      <c r="AR75" s="24" t="inlineStr">
-        <is>
-          <t>Minnesota Twins</t>
-        </is>
-      </c>
-      <c r="AS75" s="24" t="inlineStr">
-        <is>
-          <t>mlb-kc</t>
-        </is>
-      </c>
-      <c r="AT75" s="24" t="inlineStr">
-        <is>
-          <t>Kansas City Royals</t>
-        </is>
-      </c>
-      <c r="AU75" s="24" t="inlineStr">
-        <is>
-          <t>Kansas City Royals</t>
-        </is>
-      </c>
-      <c r="AV75" s="24" t="n"/>
-      <c r="AW75" s="24" t="n"/>
-      <c r="AX75" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY75" s="24" t="n"/>
-      <c r="AZ75" s="24" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="BA75" s="24" t="inlineStr">
-        <is>
-          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
-        </is>
-      </c>
-      <c r="BB75" s="24" t="inlineStr">
-        <is>
-          <t>flat_probability_shrinkage_toward_half</t>
-        </is>
-      </c>
-      <c r="BC75" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-totals-v3</t>
-        </is>
-      </c>
-      <c r="BD75" s="24" t="inlineStr">
-        <is>
-          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
-        </is>
-      </c>
-      <c r="BE75" s="24" t="inlineStr">
-        <is>
-          <t>v3</t>
-        </is>
-      </c>
-      <c r="BF75" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG75" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-paired-v1</t>
-        </is>
-      </c>
-      <c r="BH75" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="BI75" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ75" s="25" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="BK75" s="26" t="n">
-        <v>-111</v>
-      </c>
-      <c r="BL75" s="27" t="n">
-        <v>1.900901</v>
-      </c>
-      <c r="BM75" s="28" t="n">
-        <v>0.526066</v>
-      </c>
-      <c r="BN75" s="28" t="n">
-        <v>0.522388</v>
-      </c>
-      <c r="BO75" s="28" t="n"/>
-      <c r="BP75" s="25" t="n"/>
-      <c r="BQ75" s="27" t="n"/>
-      <c r="BR75" s="28" t="n"/>
-      <c r="BS75" s="28" t="n"/>
-      <c r="BT75" s="28" t="n"/>
-      <c r="BU75" s="25" t="n"/>
-      <c r="BV75" s="29" t="n"/>
-      <c r="BW75" s="24" t="n"/>
-      <c r="BX75" s="30" t="n"/>
-      <c r="BY75" s="27" t="n"/>
-      <c r="BZ75" s="24" t="n"/>
-      <c r="CA75" s="31" t="n"/>
-      <c r="CB75" s="24" t="n"/>
-      <c r="CC75" s="24" t="n"/>
-      <c r="CD75" s="24" t="n"/>
-      <c r="CE75" s="24" t="n"/>
-      <c r="CF75" s="24" t="n"/>
-      <c r="CG75" s="24" t="n"/>
-      <c r="CH75" s="24" t="n"/>
-      <c r="CI75" s="24" t="n"/>
-      <c r="CJ75" s="24" t="n"/>
-      <c r="CK75" s="24" t="n"/>
-      <c r="CL75" s="24" t="n"/>
-      <c r="CM75" s="24" t="n"/>
-      <c r="CN75" s="24" t="n"/>
-      <c r="CO75" s="24" t="n"/>
-      <c r="CP75" s="24" t="n"/>
-      <c r="CQ75" s="24" t="n"/>
-      <c r="CR75" s="24" t="n"/>
-      <c r="CS75" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="36" customHeight="1">
-      <c r="A76" s="24" t="inlineStr">
-        <is>
-          <t>782aabd620da42b0</t>
-        </is>
-      </c>
-      <c r="B76" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="C76" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-06T01:40Z</t>
-        </is>
-      </c>
-      <c r="D76" s="24" t="inlineStr">
-        <is>
-          <t>401816412</t>
-        </is>
-      </c>
-      <c r="E76" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F76" s="24" t="inlineStr">
-        <is>
-          <t>Detroit Tigers</t>
-        </is>
-      </c>
-      <c r="G76" s="24" t="inlineStr">
-        <is>
-          <t>Seattle Mariners</t>
-        </is>
-      </c>
-      <c r="H76" s="24" t="inlineStr">
-        <is>
-          <t>spread</t>
-        </is>
-      </c>
-      <c r="I76" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J76" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K76" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L76" s="26" t="n">
-        <v>-153</v>
-      </c>
-      <c r="M76" s="27" t="n">
-        <v>1.653595</v>
-      </c>
-      <c r="N76" s="28" t="n">
-        <v>0.604743</v>
-      </c>
-      <c r="O76" s="28" t="n">
-        <v>0.633554</v>
-      </c>
-      <c r="P76" s="28" t="n">
-        <v>0.042131</v>
-      </c>
-      <c r="Q76" s="28" t="n">
-        <v>0.028811</v>
-      </c>
-      <c r="R76" s="26" t="n">
-        <v>41</v>
-      </c>
-      <c r="S76" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T76" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-margin-v3</t>
-        </is>
-      </c>
-      <c r="U76" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V76" s="24" t="n"/>
-      <c r="W76" s="26" t="n"/>
-      <c r="X76" s="26" t="n"/>
-      <c r="Y76" s="25" t="n"/>
-      <c r="Z76" s="26" t="n"/>
-      <c r="AA76" s="28" t="n"/>
-      <c r="AB76" s="28" t="n"/>
-      <c r="AC76" s="30" t="n"/>
-      <c r="AD76" s="24" t="n"/>
-      <c r="AE76" s="31" t="inlineStr">
-        <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.87-4.56; raw selected-side p=0.6960, calibrated p=0.6336.</t>
-        </is>
-      </c>
-      <c r="AF76" s="31" t="inlineStr">
-        <is>
-          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
-        </is>
-      </c>
-      <c r="AG76" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH76" s="24" t="n"/>
-      <c r="AI76" s="31" t="n"/>
-      <c r="AJ76" s="31" t="n"/>
-      <c r="AK76" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL76" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM76" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN76" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO76" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP76" s="24" t="inlineStr">
-        <is>
-          <t>mlb-det</t>
-        </is>
-      </c>
-      <c r="AQ76" s="24" t="inlineStr">
-        <is>
-          <t>Detroit Tigers</t>
-        </is>
-      </c>
-      <c r="AR76" s="24" t="inlineStr">
-        <is>
-          <t>Detroit Tigers</t>
-        </is>
-      </c>
-      <c r="AS76" s="24" t="inlineStr">
-        <is>
-          <t>mlb-sea</t>
-        </is>
-      </c>
-      <c r="AT76" s="24" t="inlineStr">
-        <is>
-          <t>Seattle Mariners</t>
-        </is>
-      </c>
-      <c r="AU76" s="24" t="inlineStr">
-        <is>
-          <t>Seattle Mariners</t>
-        </is>
-      </c>
-      <c r="AV76" s="24" t="n"/>
-      <c r="AW76" s="24" t="n"/>
-      <c r="AX76" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY76" s="24" t="n"/>
-      <c r="AZ76" s="24" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="BA76" s="24" t="inlineStr">
-        <is>
-          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
-        </is>
-      </c>
-      <c r="BB76" s="24" t="inlineStr">
-        <is>
-          <t>flat_probability_shrinkage_toward_half</t>
-        </is>
-      </c>
-      <c r="BC76" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-margin-v3</t>
-        </is>
-      </c>
-      <c r="BD76" s="24" t="inlineStr">
-        <is>
-          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
-        </is>
-      </c>
-      <c r="BE76" s="24" t="inlineStr">
-        <is>
-          <t>v3</t>
-        </is>
-      </c>
-      <c r="BF76" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG76" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-paired-v1</t>
-        </is>
-      </c>
-      <c r="BH76" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="BI76" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ76" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BK76" s="26" t="n">
-        <v>-153</v>
-      </c>
-      <c r="BL76" s="27" t="n">
-        <v>1.653595</v>
-      </c>
-      <c r="BM76" s="28" t="n">
-        <v>0.604743</v>
-      </c>
-      <c r="BN76" s="28" t="n">
-        <v>0.60199</v>
-      </c>
-      <c r="BO76" s="28" t="n"/>
-      <c r="BP76" s="25" t="n"/>
-      <c r="BQ76" s="27" t="n"/>
-      <c r="BR76" s="28" t="n"/>
-      <c r="BS76" s="28" t="n"/>
-      <c r="BT76" s="28" t="n"/>
-      <c r="BU76" s="25" t="n"/>
-      <c r="BV76" s="29" t="n"/>
-      <c r="BW76" s="24" t="n"/>
-      <c r="BX76" s="30" t="n"/>
-      <c r="BY76" s="27" t="n"/>
-      <c r="BZ76" s="24" t="n"/>
-      <c r="CA76" s="31" t="n"/>
-      <c r="CB76" s="24" t="n"/>
-      <c r="CC76" s="24" t="n"/>
-      <c r="CD76" s="24" t="n"/>
-      <c r="CE76" s="24" t="n"/>
-      <c r="CF76" s="24" t="n"/>
-      <c r="CG76" s="24" t="n"/>
-      <c r="CH76" s="24" t="n"/>
-      <c r="CI76" s="24" t="n"/>
-      <c r="CJ76" s="24" t="n"/>
-      <c r="CK76" s="24" t="n"/>
-      <c r="CL76" s="24" t="n"/>
-      <c r="CM76" s="24" t="n"/>
-      <c r="CN76" s="24" t="n"/>
-      <c r="CO76" s="24" t="n"/>
-      <c r="CP76" s="24" t="n"/>
-      <c r="CQ76" s="24" t="n"/>
-      <c r="CR76" s="24" t="n"/>
-      <c r="CS76" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="36" customHeight="1">
-      <c r="A77" s="24" t="inlineStr">
-        <is>
-          <t>53ea51af68e84e54</t>
-        </is>
-      </c>
-      <c r="B77" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="C77" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-06T01:40Z</t>
-        </is>
-      </c>
-      <c r="D77" s="24" t="inlineStr">
-        <is>
-          <t>401816412</t>
-        </is>
-      </c>
-      <c r="E77" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F77" s="24" t="inlineStr">
-        <is>
-          <t>Detroit Tigers</t>
-        </is>
-      </c>
-      <c r="G77" s="24" t="inlineStr">
-        <is>
-          <t>Seattle Mariners</t>
-        </is>
-      </c>
-      <c r="H77" s="24" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="I77" s="24" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="J77" s="25" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="K77" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L77" s="26" t="n">
-        <v>-102</v>
-      </c>
-      <c r="M77" s="27" t="n">
-        <v>1.980392</v>
-      </c>
-      <c r="N77" s="28" t="n">
-        <v>0.50495</v>
-      </c>
-      <c r="O77" s="28" t="n">
-        <v>0.537173</v>
-      </c>
-      <c r="P77" s="28" t="n">
-        <v>0.042131</v>
-      </c>
-      <c r="Q77" s="28" t="n">
-        <v>0.032223</v>
-      </c>
-      <c r="R77" s="26" t="n">
-        <v>42</v>
-      </c>
-      <c r="S77" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T77" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-totals-v3</t>
-        </is>
-      </c>
-      <c r="U77" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V77" s="24" t="n"/>
-      <c r="W77" s="26" t="n"/>
-      <c r="X77" s="26" t="n"/>
-      <c r="Y77" s="25" t="n"/>
-      <c r="Z77" s="26" t="n"/>
-      <c r="AA77" s="28" t="n"/>
-      <c r="AB77" s="28" t="n"/>
-      <c r="AC77" s="30" t="n"/>
-      <c r="AD77" s="24" t="n"/>
-      <c r="AE77" s="31" t="inlineStr">
-        <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.87-4.56; raw selected-side p=0.6263, calibrated p=0.5372.</t>
-        </is>
-      </c>
-      <c r="AF77" s="31" t="inlineStr">
-        <is>
-          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
-        </is>
-      </c>
-      <c r="AG77" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH77" s="24" t="n"/>
-      <c r="AI77" s="31" t="n"/>
-      <c r="AJ77" s="31" t="n"/>
-      <c r="AK77" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL77" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM77" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN77" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO77" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP77" s="24" t="inlineStr">
-        <is>
-          <t>mlb-det</t>
-        </is>
-      </c>
-      <c r="AQ77" s="24" t="inlineStr">
-        <is>
-          <t>Detroit Tigers</t>
-        </is>
-      </c>
-      <c r="AR77" s="24" t="inlineStr">
-        <is>
-          <t>Detroit Tigers</t>
-        </is>
-      </c>
-      <c r="AS77" s="24" t="inlineStr">
-        <is>
-          <t>mlb-sea</t>
-        </is>
-      </c>
-      <c r="AT77" s="24" t="inlineStr">
-        <is>
-          <t>Seattle Mariners</t>
-        </is>
-      </c>
-      <c r="AU77" s="24" t="inlineStr">
-        <is>
-          <t>Seattle Mariners</t>
-        </is>
-      </c>
-      <c r="AV77" s="24" t="n"/>
-      <c r="AW77" s="24" t="n"/>
-      <c r="AX77" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY77" s="24" t="n"/>
-      <c r="AZ77" s="24" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="BA77" s="24" t="inlineStr">
-        <is>
-          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
-        </is>
-      </c>
-      <c r="BB77" s="24" t="inlineStr">
-        <is>
-          <t>flat_probability_shrinkage_toward_half</t>
-        </is>
-      </c>
-      <c r="BC77" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-totals-v3</t>
-        </is>
-      </c>
-      <c r="BD77" s="24" t="inlineStr">
-        <is>
-          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
-        </is>
-      </c>
-      <c r="BE77" s="24" t="inlineStr">
-        <is>
-          <t>v3</t>
-        </is>
-      </c>
-      <c r="BF77" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG77" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-paired-v1</t>
-        </is>
-      </c>
-      <c r="BH77" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="BI77" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ77" s="25" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="BK77" s="26" t="n">
-        <v>-102</v>
-      </c>
-      <c r="BL77" s="27" t="n">
-        <v>1.980392</v>
-      </c>
-      <c r="BM77" s="28" t="n">
-        <v>0.50495</v>
-      </c>
-      <c r="BN77" s="28" t="n">
-        <v>0.502488</v>
-      </c>
-      <c r="BO77" s="28" t="n"/>
-      <c r="BP77" s="25" t="n"/>
-      <c r="BQ77" s="27" t="n"/>
-      <c r="BR77" s="28" t="n"/>
-      <c r="BS77" s="28" t="n"/>
-      <c r="BT77" s="28" t="n"/>
-      <c r="BU77" s="25" t="n"/>
-      <c r="BV77" s="29" t="n"/>
-      <c r="BW77" s="24" t="n"/>
-      <c r="BX77" s="30" t="n"/>
-      <c r="BY77" s="27" t="n"/>
-      <c r="BZ77" s="24" t="n"/>
-      <c r="CA77" s="31" t="n"/>
-      <c r="CB77" s="24" t="n"/>
-      <c r="CC77" s="24" t="n"/>
-      <c r="CD77" s="24" t="n"/>
-      <c r="CE77" s="24" t="n"/>
-      <c r="CF77" s="24" t="n"/>
-      <c r="CG77" s="24" t="n"/>
-      <c r="CH77" s="24" t="n"/>
-      <c r="CI77" s="24" t="n"/>
-      <c r="CJ77" s="24" t="n"/>
-      <c r="CK77" s="24" t="n"/>
-      <c r="CL77" s="24" t="n"/>
-      <c r="CM77" s="24" t="n"/>
-      <c r="CN77" s="24" t="n"/>
-      <c r="CO77" s="24" t="n"/>
-      <c r="CP77" s="24" t="n"/>
-      <c r="CQ77" s="24" t="n"/>
-      <c r="CR77" s="24" t="n"/>
-      <c r="CS77" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="36" customHeight="1">
-      <c r="A78" s="24" t="inlineStr">
-        <is>
-          <t>ccd69ef788fa45c5</t>
-        </is>
-      </c>
-      <c r="B78" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="C78" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-06T01:40Z</t>
-        </is>
-      </c>
-      <c r="D78" s="24" t="inlineStr">
-        <is>
-          <t>401816413</t>
-        </is>
-      </c>
-      <c r="E78" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F78" s="24" t="inlineStr">
-        <is>
-          <t>San Diego Padres</t>
-        </is>
-      </c>
-      <c r="G78" s="24" t="inlineStr">
-        <is>
-          <t>Arizona Diamondbacks</t>
-        </is>
-      </c>
-      <c r="H78" s="24" t="inlineStr">
-        <is>
-          <t>spread</t>
-        </is>
-      </c>
-      <c r="I78" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J78" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K78" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L78" s="26" t="n">
-        <v>-141</v>
-      </c>
-      <c r="M78" s="27" t="n">
-        <v>1.70922</v>
-      </c>
-      <c r="N78" s="28" t="n">
-        <v>0.585062</v>
-      </c>
-      <c r="O78" s="28" t="n">
-        <v>0.5781230000000001</v>
-      </c>
-      <c r="P78" s="28" t="n">
-        <v>0.05172</v>
-      </c>
-      <c r="Q78" s="28" t="n">
-        <v>-0.006939</v>
-      </c>
-      <c r="R78" s="26" t="n">
-        <v>17</v>
-      </c>
-      <c r="S78" s="29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T78" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-margin-v3</t>
-        </is>
-      </c>
-      <c r="U78" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V78" s="24" t="n"/>
-      <c r="W78" s="26" t="n"/>
-      <c r="X78" s="26" t="n"/>
-      <c r="Y78" s="25" t="n"/>
-      <c r="Z78" s="26" t="n"/>
-      <c r="AA78" s="28" t="n"/>
-      <c r="AB78" s="28" t="n"/>
-      <c r="AC78" s="30" t="n"/>
-      <c r="AD78" s="24" t="n"/>
-      <c r="AE78" s="31" t="inlineStr">
-        <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.83-4.33; raw selected-side p=0.6147, calibrated p=0.5781.</t>
-        </is>
-      </c>
-      <c r="AF78" s="31" t="inlineStr">
-        <is>
-          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
-        </is>
-      </c>
-      <c r="AG78" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH78" s="24" t="n"/>
-      <c r="AI78" s="31" t="n"/>
-      <c r="AJ78" s="31" t="n"/>
-      <c r="AK78" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL78" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM78" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN78" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO78" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP78" s="24" t="inlineStr">
-        <is>
-          <t>mlb-sd</t>
-        </is>
-      </c>
-      <c r="AQ78" s="24" t="inlineStr">
-        <is>
-          <t>San Diego Padres</t>
-        </is>
-      </c>
-      <c r="AR78" s="24" t="inlineStr">
-        <is>
-          <t>San Diego Padres</t>
-        </is>
-      </c>
-      <c r="AS78" s="24" t="inlineStr">
-        <is>
-          <t>mlb-ari</t>
-        </is>
-      </c>
-      <c r="AT78" s="24" t="inlineStr">
-        <is>
-          <t>Arizona Diamondbacks</t>
-        </is>
-      </c>
-      <c r="AU78" s="24" t="inlineStr">
-        <is>
-          <t>Arizona Diamondbacks</t>
-        </is>
-      </c>
-      <c r="AV78" s="24" t="n"/>
-      <c r="AW78" s="24" t="n"/>
-      <c r="AX78" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY78" s="24" t="n"/>
-      <c r="AZ78" s="24" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="BA78" s="24" t="inlineStr">
-        <is>
-          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
-        </is>
-      </c>
-      <c r="BB78" s="24" t="inlineStr">
-        <is>
-          <t>flat_probability_shrinkage_toward_half</t>
-        </is>
-      </c>
-      <c r="BC78" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-margin-v3</t>
-        </is>
-      </c>
-      <c r="BD78" s="24" t="inlineStr">
-        <is>
-          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
-        </is>
-      </c>
-      <c r="BE78" s="24" t="inlineStr">
-        <is>
-          <t>v3</t>
-        </is>
-      </c>
-      <c r="BF78" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG78" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-paired-v1</t>
-        </is>
-      </c>
-      <c r="BH78" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="BI78" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ78" s="25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BK78" s="26" t="n">
-        <v>-141</v>
-      </c>
-      <c r="BL78" s="27" t="n">
-        <v>1.70922</v>
-      </c>
-      <c r="BM78" s="28" t="n">
-        <v>0.585062</v>
-      </c>
-      <c r="BN78" s="28" t="n">
-        <v>0.58209</v>
-      </c>
-      <c r="BO78" s="28" t="n"/>
-      <c r="BP78" s="25" t="n"/>
-      <c r="BQ78" s="27" t="n"/>
-      <c r="BR78" s="28" t="n"/>
-      <c r="BS78" s="28" t="n"/>
-      <c r="BT78" s="28" t="n"/>
-      <c r="BU78" s="25" t="n"/>
-      <c r="BV78" s="29" t="n"/>
-      <c r="BW78" s="24" t="n"/>
-      <c r="BX78" s="30" t="n"/>
-      <c r="BY78" s="27" t="n"/>
-      <c r="BZ78" s="24" t="n"/>
-      <c r="CA78" s="31" t="n"/>
-      <c r="CB78" s="24" t="n"/>
-      <c r="CC78" s="24" t="n"/>
-      <c r="CD78" s="24" t="n"/>
-      <c r="CE78" s="24" t="n"/>
-      <c r="CF78" s="24" t="n"/>
-      <c r="CG78" s="24" t="n"/>
-      <c r="CH78" s="24" t="n"/>
-      <c r="CI78" s="24" t="n"/>
-      <c r="CJ78" s="24" t="n"/>
-      <c r="CK78" s="24" t="n"/>
-      <c r="CL78" s="24" t="n"/>
-      <c r="CM78" s="24" t="n"/>
-      <c r="CN78" s="24" t="n"/>
-      <c r="CO78" s="24" t="n"/>
-      <c r="CP78" s="24" t="n"/>
-      <c r="CQ78" s="24" t="n"/>
-      <c r="CR78" s="24" t="n"/>
-      <c r="CS78" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="36" customHeight="1">
-      <c r="A79" s="24" t="inlineStr">
-        <is>
-          <t>002f58116035474e</t>
-        </is>
-      </c>
-      <c r="B79" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="C79" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-06T01:40Z</t>
-        </is>
-      </c>
-      <c r="D79" s="24" t="inlineStr">
-        <is>
-          <t>401816413</t>
-        </is>
-      </c>
-      <c r="E79" s="24" t="inlineStr">
-        <is>
-          <t>MLB</t>
-        </is>
-      </c>
-      <c r="F79" s="24" t="inlineStr">
-        <is>
-          <t>San Diego Padres</t>
-        </is>
-      </c>
-      <c r="G79" s="24" t="inlineStr">
-        <is>
-          <t>Arizona Diamondbacks</t>
-        </is>
-      </c>
-      <c r="H79" s="24" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="I79" s="24" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="J79" s="25" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="K79" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L79" s="26" t="n">
-        <v>-120</v>
-      </c>
-      <c r="M79" s="27" t="n">
-        <v>1.833333</v>
-      </c>
-      <c r="N79" s="28" t="n">
-        <v>0.545455</v>
-      </c>
-      <c r="O79" s="28" t="n">
-        <v>0.526914</v>
-      </c>
-      <c r="P79" s="28" t="n">
-        <v>0.05172</v>
-      </c>
-      <c r="Q79" s="28" t="n">
-        <v>-0.018541</v>
-      </c>
-      <c r="R79" s="26" t="n">
-        <v>11</v>
-      </c>
-      <c r="S79" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T79" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-totals-v3</t>
-        </is>
-      </c>
-      <c r="U79" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V79" s="24" t="n"/>
-      <c r="W79" s="26" t="n"/>
-      <c r="X79" s="26" t="n"/>
-      <c r="Y79" s="25" t="n"/>
-      <c r="Z79" s="26" t="n"/>
-      <c r="AA79" s="28" t="n"/>
-      <c r="AB79" s="28" t="n"/>
-      <c r="AC79" s="30" t="n"/>
-      <c r="AD79" s="24" t="n"/>
-      <c r="AE79" s="31" t="inlineStr">
-        <is>
-          <t>Measured Edge Totals: Trend Engine projected 4.83-4.33; raw selected-side p=0.5850, calibrated p=0.5269.</t>
-        </is>
-      </c>
-      <c r="AF79" s="31" t="inlineStr">
-        <is>
-          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
-        </is>
-      </c>
-      <c r="AG79" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH79" s="24" t="n"/>
-      <c r="AI79" s="31" t="n"/>
-      <c r="AJ79" s="31" t="n"/>
-      <c r="AK79" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL79" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM79" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN79" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO79" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP79" s="24" t="inlineStr">
-        <is>
-          <t>mlb-sd</t>
-        </is>
-      </c>
-      <c r="AQ79" s="24" t="inlineStr">
-        <is>
-          <t>San Diego Padres</t>
-        </is>
-      </c>
-      <c r="AR79" s="24" t="inlineStr">
-        <is>
-          <t>San Diego Padres</t>
-        </is>
-      </c>
-      <c r="AS79" s="24" t="inlineStr">
-        <is>
-          <t>mlb-ari</t>
-        </is>
-      </c>
-      <c r="AT79" s="24" t="inlineStr">
-        <is>
-          <t>Arizona Diamondbacks</t>
-        </is>
-      </c>
-      <c r="AU79" s="24" t="inlineStr">
-        <is>
-          <t>Arizona Diamondbacks</t>
-        </is>
-      </c>
-      <c r="AV79" s="24" t="n"/>
-      <c r="AW79" s="24" t="n"/>
-      <c r="AX79" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY79" s="24" t="n"/>
-      <c r="AZ79" s="24" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="BA79" s="24" t="inlineStr">
-        <is>
-          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
-        </is>
-      </c>
-      <c r="BB79" s="24" t="inlineStr">
-        <is>
-          <t>flat_probability_shrinkage_toward_half</t>
-        </is>
-      </c>
-      <c r="BC79" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-totals-v3</t>
-        </is>
-      </c>
-      <c r="BD79" s="24" t="inlineStr">
-        <is>
-          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
-        </is>
-      </c>
-      <c r="BE79" s="24" t="inlineStr">
-        <is>
-          <t>v3</t>
-        </is>
-      </c>
-      <c r="BF79" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG79" s="24" t="inlineStr">
-        <is>
-          <t>measured-edge-paired-v1</t>
-        </is>
-      </c>
-      <c r="BH79" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-05T13:54:46.877508Z</t>
-        </is>
-      </c>
-      <c r="BI79" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ79" s="25" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="BK79" s="26" t="n">
-        <v>-120</v>
-      </c>
-      <c r="BL79" s="27" t="n">
-        <v>1.833333</v>
-      </c>
-      <c r="BM79" s="28" t="n">
-        <v>0.545455</v>
-      </c>
-      <c r="BN79" s="28" t="n">
-        <v>0.542289</v>
-      </c>
-      <c r="BO79" s="28" t="n"/>
-      <c r="BP79" s="25" t="n"/>
-      <c r="BQ79" s="27" t="n"/>
-      <c r="BR79" s="28" t="n"/>
-      <c r="BS79" s="28" t="n"/>
-      <c r="BT79" s="28" t="n"/>
-      <c r="BU79" s="25" t="n"/>
-      <c r="BV79" s="29" t="n"/>
-      <c r="BW79" s="24" t="n"/>
-      <c r="BX79" s="30" t="n"/>
-      <c r="BY79" s="27" t="n"/>
-      <c r="BZ79" s="24" t="n"/>
-      <c r="CA79" s="31" t="n"/>
-      <c r="CB79" s="24" t="n"/>
-      <c r="CC79" s="24" t="n"/>
-      <c r="CD79" s="24" t="n"/>
-      <c r="CE79" s="24" t="n"/>
-      <c r="CF79" s="24" t="n"/>
-      <c r="CG79" s="24" t="n"/>
-      <c r="CH79" s="24" t="n"/>
-      <c r="CI79" s="24" t="n"/>
-      <c r="CJ79" s="24" t="n"/>
-      <c r="CK79" s="24" t="n"/>
-      <c r="CL79" s="24" t="n"/>
-      <c r="CM79" s="24" t="n"/>
-      <c r="CN79" s="24" t="n"/>
-      <c r="CO79" s="24" t="n"/>
-      <c r="CP79" s="24" t="n"/>
-      <c r="CQ79" s="24" t="n"/>
-      <c r="CR79" s="24" t="n"/>
-      <c r="CS79" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
         </is>
       </c>
     </row>

--- a/data/main/mlb.xlsx
+++ b/data/main/mlb.xlsx
@@ -15273,12 +15273,12 @@
     <row r="47" ht="36" customHeight="1">
       <c r="A47" s="24" t="inlineStr">
         <is>
-          <t>9581ac3086d84147</t>
+          <t>d806739b5e2e4a59</t>
         </is>
       </c>
       <c r="B47" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:22:19.501521Z</t>
+          <t>2026-08-07T18:29:28.691575Z</t>
         </is>
       </c>
       <c r="C47" s="24" t="inlineStr">
@@ -15334,16 +15334,16 @@
         <v>0.509804</v>
       </c>
       <c r="O47" s="28" t="n">
-        <v>0.655325</v>
+        <v>0.65788</v>
       </c>
       <c r="P47" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q47" s="28" t="n">
-        <v>0.145521</v>
+        <v>0.148076</v>
       </c>
       <c r="R47" s="26" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="S47" s="29" t="n">
         <v>1.75</v>
@@ -15369,7 +15369,7 @@
       <c r="AD47" s="24" t="n"/>
       <c r="AE47" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.08-4.72; raw selected-side p=0.7279, calibrated p=0.6553.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.08-4.72; raw selected-side p=0.7317, calibrated p=0.6579.</t>
         </is>
       </c>
       <c r="AF47" s="31" t="inlineStr">
@@ -15488,7 +15488,7 @@
       </c>
       <c r="BH47" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:22:19.501521Z</t>
+          <t>2026-08-07T18:29:28.691575Z</t>
         </is>
       </c>
       <c r="BI47" s="24" t="inlineStr">
@@ -15509,7 +15509,7 @@
         <v>0.509804</v>
       </c>
       <c r="BN47" s="28" t="n">
-        <v>0.507463</v>
+        <v>0.50495</v>
       </c>
       <c r="BO47" s="28" t="n"/>
       <c r="BP47" s="25" t="n"/>
@@ -15550,12 +15550,12 @@
     <row r="48" ht="36" customHeight="1">
       <c r="A48" s="24" t="inlineStr">
         <is>
-          <t>3b3245b6b87e40d5</t>
+          <t>28e5bf581f78421f</t>
         </is>
       </c>
       <c r="B48" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:22:19.501521Z</t>
+          <t>2026-08-07T18:29:28.691575Z</t>
         </is>
       </c>
       <c r="C48" s="24" t="inlineStr">
@@ -15611,16 +15611,16 @@
         <v>0.5</v>
       </c>
       <c r="O48" s="28" t="n">
-        <v>0.627047</v>
+        <v>0.627183</v>
       </c>
       <c r="P48" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q48" s="28" t="n">
-        <v>0.127047</v>
+        <v>0.127183</v>
       </c>
       <c r="R48" s="26" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="S48" s="29" t="n">
         <v>1.5</v>
@@ -15646,7 +15646,7 @@
       <c r="AD48" s="24" t="n"/>
       <c r="AE48" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 4.62-4.87; raw selected-side p=0.6865, calibrated p=0.6270.</t>
+          <t>Measured Edge Margin: Trend Engine projected 4.62-4.87; raw selected-side p=0.6866, calibrated p=0.6272.</t>
         </is>
       </c>
       <c r="AF48" s="31" t="inlineStr">
@@ -15765,7 +15765,7 @@
       </c>
       <c r="BH48" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:22:19.501521Z</t>
+          <t>2026-08-07T18:29:28.691575Z</t>
         </is>
       </c>
       <c r="BI48" s="24" t="inlineStr">

--- a/data/main/mlb.xlsx
+++ b/data/main/mlb.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS74" headerRowCount="1">
-  <autoFilter ref="A1:CS74"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS76" headerRowCount="1">
+  <autoFilter ref="A1:CS76"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$74)</f>
+        <f>COUNTA('Picks'!$A$2:$A$76)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$74,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$76,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$74,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$76,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$74,"settled",'Picks'!$V$2:$V$74,"win")+COUNTIFS('Picks'!$U$2:$U$74,"settled",'Picks'!$V$2:$V$74,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$76,"settled",'Picks'!$V$2:$V$76,"win")+COUNTIFS('Picks'!$U$2:$U$76,"settled",'Picks'!$V$2:$V$76,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$74,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$76,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$74,"&gt;0",'Picks'!$V$2:$V$74,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$74,"&gt;0",'Picks'!$V$2:$V$74,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$76,"&gt;0",'Picks'!$V$2:$V$76,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$76,"&gt;0",'Picks'!$V$2:$V$76,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$74,"&gt;0",'Picks'!$V$2:$V$74,"win")/(COUNTIFS('Picks'!$BX$2:$BX$74,"&gt;0",'Picks'!$V$2:$V$74,"win")+COUNTIFS('Picks'!$BX$2:$BX$74,"&gt;0",'Picks'!$V$2:$V$74,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$76,"&gt;0",'Picks'!$V$2:$V$76,"win")/(COUNTIFS('Picks'!$BX$2:$BX$76,"&gt;0",'Picks'!$V$2:$V$76,"win")+COUNTIFS('Picks'!$BX$2:$BX$76,"&gt;0",'Picks'!$V$2:$V$76,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$74)/SUM('Picks'!$BX$2:$BX$74),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$76)/SUM('Picks'!$BX$2:$BX$76),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$74)</f>
+        <f>SUM('Picks'!$BY$2:$BY$76)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$74,"&lt;&gt;",'Picks'!$AB$2:$AB$74),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$76,"&lt;&gt;",'Picks'!$AB$2:$AB$76),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$74,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$74,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$76,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$76,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$74,'Picks'!$AM$2:$AM$74,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$76,'Picks'!$AM$2:$AM$76,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$74,$A14,'Picks'!$U$2:$U$74,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$76,$A14,'Picks'!$U$2:$U$76,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$74,$A14,'Picks'!$U$2:$U$74,"settled",'Picks'!$V$2:$V$74,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$76,$A14,'Picks'!$U$2:$U$76,"settled",'Picks'!$V$2:$V$76,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$74,$A14,'Picks'!$U$2:$U$74,"settled",'Picks'!$V$2:$V$74,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$76,$A14,'Picks'!$U$2:$U$76,"settled",'Picks'!$V$2:$V$76,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$74,'Picks'!$H$2:$H$74,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$76,'Picks'!$H$2:$H$76,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$74,'Picks'!$H$2:$H$74,$A14,'Picks'!$U$2:$U$74,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$76,'Picks'!$H$2:$H$76,$A14,'Picks'!$U$2:$U$76,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$74,$A15,'Picks'!$U$2:$U$74,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$76,$A15,'Picks'!$U$2:$U$76,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$74,$A15,'Picks'!$U$2:$U$74,"settled",'Picks'!$V$2:$V$74,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$76,$A15,'Picks'!$U$2:$U$76,"settled",'Picks'!$V$2:$V$76,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$74,$A15,'Picks'!$U$2:$U$74,"settled",'Picks'!$V$2:$V$74,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$76,$A15,'Picks'!$U$2:$U$76,"settled",'Picks'!$V$2:$V$76,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$74,'Picks'!$H$2:$H$74,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$76,'Picks'!$H$2:$H$76,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$74,'Picks'!$H$2:$H$74,$A15,'Picks'!$U$2:$U$74,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$76,'Picks'!$H$2:$H$76,$A15,'Picks'!$U$2:$U$76,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$74,$A16,'Picks'!$U$2:$U$74,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$76,$A16,'Picks'!$U$2:$U$76,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$74,$A16,'Picks'!$U$2:$U$74,"settled",'Picks'!$V$2:$V$74,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$76,$A16,'Picks'!$U$2:$U$76,"settled",'Picks'!$V$2:$V$76,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$74,$A16,'Picks'!$U$2:$U$74,"settled",'Picks'!$V$2:$V$74,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$76,$A16,'Picks'!$U$2:$U$76,"settled",'Picks'!$V$2:$V$76,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$74,'Picks'!$H$2:$H$74,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$76,'Picks'!$H$2:$H$76,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$74,'Picks'!$H$2:$H$74,$A16,'Picks'!$U$2:$U$74,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$76,'Picks'!$H$2:$H$76,$A16,'Picks'!$U$2:$U$76,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS74"/>
+  <dimension ref="A1:CS76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -23234,6 +23234,612 @@
         </is>
       </c>
     </row>
+    <row r="75" ht="36" customHeight="1">
+      <c r="A75" s="24" t="inlineStr">
+        <is>
+          <t>77cf66ca7401476e</t>
+        </is>
+      </c>
+      <c r="B75" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T19:33:23.759021Z</t>
+        </is>
+      </c>
+      <c r="C75" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T15:40:00-0400</t>
+        </is>
+      </c>
+      <c r="D75" s="24" t="inlineStr">
+        <is>
+          <t>401816503</t>
+        </is>
+      </c>
+      <c r="E75" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F75" s="24" t="inlineStr">
+        <is>
+          <t>Colorado Rockies</t>
+        </is>
+      </c>
+      <c r="G75" s="24" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="H75" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I75" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J75" s="25" t="n"/>
+      <c r="K75" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L75" s="26" t="n">
+        <v>-160</v>
+      </c>
+      <c r="M75" s="27" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="N75" s="28" t="n">
+        <v>0.615385</v>
+      </c>
+      <c r="O75" s="28" t="n">
+        <v>0.644989</v>
+      </c>
+      <c r="P75" s="28" t="n"/>
+      <c r="Q75" s="28" t="n">
+        <v>0.029604</v>
+      </c>
+      <c r="R75" s="26" t="n">
+        <v>37</v>
+      </c>
+      <c r="S75" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T75" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="U75" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V75" s="24" t="n"/>
+      <c r="W75" s="26" t="n"/>
+      <c r="X75" s="26" t="n"/>
+      <c r="Y75" s="25" t="n"/>
+      <c r="Z75" s="26" t="n"/>
+      <c r="AA75" s="28" t="n"/>
+      <c r="AB75" s="28" t="n"/>
+      <c r="AC75" s="30" t="n"/>
+      <c r="AD75" s="24" t="n"/>
+      <c r="AE75" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.6197; executable ask 0.6150 (aec-mlb-col-az-2026-08-12); model edge vs ask +0.0300.</t>
+        </is>
+      </c>
+      <c r="AF75" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG75" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH75" s="24" t="n"/>
+      <c r="AI75" s="31" t="n"/>
+      <c r="AJ75" s="31" t="n"/>
+      <c r="AK75" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL75" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM75" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN75" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO75" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP75" s="24" t="inlineStr">
+        <is>
+          <t>mlb-col</t>
+        </is>
+      </c>
+      <c r="AQ75" s="24" t="inlineStr">
+        <is>
+          <t>Colorado Rockies</t>
+        </is>
+      </c>
+      <c r="AR75" s="24" t="inlineStr">
+        <is>
+          <t>Colorado Rockies</t>
+        </is>
+      </c>
+      <c r="AS75" s="24" t="inlineStr">
+        <is>
+          <t>mlb-ari</t>
+        </is>
+      </c>
+      <c r="AT75" s="24" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="AU75" s="24" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="AV75" s="24" t="n"/>
+      <c r="AW75" s="24" t="n"/>
+      <c r="AX75" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY75" s="24" t="n"/>
+      <c r="AZ75" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA75" s="24" t="inlineStr">
+        <is>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
+        </is>
+      </c>
+      <c r="BB75" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC75" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="BD75" s="24" t="inlineStr">
+        <is>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
+        </is>
+      </c>
+      <c r="BE75" s="24" t="inlineStr">
+        <is>
+          <t>02d0a106d2db5aa1</t>
+        </is>
+      </c>
+      <c r="BF75" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG75" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="BH75" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:41:22.389910Z</t>
+        </is>
+      </c>
+      <c r="BI75" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ75" s="25" t="n"/>
+      <c r="BK75" s="26" t="n">
+        <v>-160</v>
+      </c>
+      <c r="BL75" s="27" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="BM75" s="28" t="n">
+        <v>0.615385</v>
+      </c>
+      <c r="BN75" s="28" t="n">
+        <v>0.61194</v>
+      </c>
+      <c r="BO75" s="28" t="n"/>
+      <c r="BP75" s="25" t="n"/>
+      <c r="BQ75" s="27" t="n"/>
+      <c r="BR75" s="28" t="n"/>
+      <c r="BS75" s="28" t="n"/>
+      <c r="BT75" s="28" t="n"/>
+      <c r="BU75" s="25" t="n"/>
+      <c r="BV75" s="29" t="n"/>
+      <c r="BW75" s="24" t="n"/>
+      <c r="BX75" s="30" t="n"/>
+      <c r="BY75" s="27" t="n"/>
+      <c r="BZ75" s="24" t="n"/>
+      <c r="CA75" s="31" t="n"/>
+      <c r="CB75" s="24" t="n"/>
+      <c r="CC75" s="24" t="inlineStr">
+        <is>
+          <t>0.6955480628</t>
+        </is>
+      </c>
+      <c r="CD75" s="24" t="inlineStr">
+        <is>
+          <t>0.591178</t>
+        </is>
+      </c>
+      <c r="CE75" s="24" t="inlineStr">
+        <is>
+          <t>1.097</t>
+        </is>
+      </c>
+      <c r="CF75" s="24" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="CG75" s="24" t="n"/>
+      <c r="CH75" s="24" t="n"/>
+      <c r="CI75" s="24" t="n"/>
+      <c r="CJ75" s="24" t="inlineStr">
+        <is>
+          <t>1.07916</t>
+        </is>
+      </c>
+      <c r="CK75" s="24" t="n"/>
+      <c r="CL75" s="24" t="inlineStr">
+        <is>
+          <t>-0.135632</t>
+        </is>
+      </c>
+      <c r="CM75" s="24" t="inlineStr">
+        <is>
+          <t>-4.622</t>
+        </is>
+      </c>
+      <c r="CN75" s="24" t="n"/>
+      <c r="CO75" s="24" t="n"/>
+      <c r="CP75" s="24" t="n"/>
+      <c r="CQ75" s="24" t="n"/>
+      <c r="CR75" s="24" t="inlineStr">
+        <is>
+          <t>0.644989</t>
+        </is>
+      </c>
+      <c r="CS75" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="36" customHeight="1">
+      <c r="A76" s="24" t="inlineStr">
+        <is>
+          <t>f1dda80aa5124cd6</t>
+        </is>
+      </c>
+      <c r="B76" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T19:33:23.759021Z</t>
+        </is>
+      </c>
+      <c r="C76" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T22:10:00-0400</t>
+        </is>
+      </c>
+      <c r="D76" s="24" t="inlineStr">
+        <is>
+          <t>401816505</t>
+        </is>
+      </c>
+      <c r="E76" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F76" s="24" t="inlineStr">
+        <is>
+          <t>Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="G76" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="H76" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I76" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J76" s="25" t="n"/>
+      <c r="K76" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L76" s="26" t="n">
+        <v>-199</v>
+      </c>
+      <c r="M76" s="27" t="n">
+        <v>1.502513</v>
+      </c>
+      <c r="N76" s="28" t="n">
+        <v>0.665552</v>
+      </c>
+      <c r="O76" s="28" t="n">
+        <v>0.636517</v>
+      </c>
+      <c r="P76" s="28" t="n"/>
+      <c r="Q76" s="28" t="n">
+        <v>-0.029035</v>
+      </c>
+      <c r="R76" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="S76" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T76" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="U76" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V76" s="24" t="n"/>
+      <c r="W76" s="26" t="n"/>
+      <c r="X76" s="26" t="n"/>
+      <c r="Y76" s="25" t="n"/>
+      <c r="Z76" s="26" t="n"/>
+      <c r="AA76" s="28" t="n"/>
+      <c r="AB76" s="28" t="n"/>
+      <c r="AC76" s="30" t="n"/>
+      <c r="AD76" s="24" t="n"/>
+      <c r="AE76" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.6197; executable ask 0.6650 (aec-mlb-kc-lad-2026-08-12); model edge vs ask -0.0285.</t>
+        </is>
+      </c>
+      <c r="AF76" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG76" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH76" s="24" t="n"/>
+      <c r="AI76" s="31" t="n"/>
+      <c r="AJ76" s="31" t="n"/>
+      <c r="AK76" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL76" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM76" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN76" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO76" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP76" s="24" t="inlineStr">
+        <is>
+          <t>mlb-kc</t>
+        </is>
+      </c>
+      <c r="AQ76" s="24" t="inlineStr">
+        <is>
+          <t>Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="AR76" s="24" t="inlineStr">
+        <is>
+          <t>Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="AS76" s="24" t="inlineStr">
+        <is>
+          <t>mlb-lad</t>
+        </is>
+      </c>
+      <c r="AT76" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="AU76" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="AV76" s="24" t="n"/>
+      <c r="AW76" s="24" t="n"/>
+      <c r="AX76" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY76" s="24" t="n"/>
+      <c r="AZ76" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA76" s="24" t="inlineStr">
+        <is>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
+        </is>
+      </c>
+      <c r="BB76" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC76" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="BD76" s="24" t="inlineStr">
+        <is>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
+        </is>
+      </c>
+      <c r="BE76" s="24" t="inlineStr">
+        <is>
+          <t>dc4da9831907af6e</t>
+        </is>
+      </c>
+      <c r="BF76" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG76" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="BH76" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:41:29.212213Z</t>
+        </is>
+      </c>
+      <c r="BI76" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ76" s="25" t="n"/>
+      <c r="BK76" s="26" t="n">
+        <v>-199</v>
+      </c>
+      <c r="BL76" s="27" t="n">
+        <v>1.502513</v>
+      </c>
+      <c r="BM76" s="28" t="n">
+        <v>0.665552</v>
+      </c>
+      <c r="BN76" s="28" t="n">
+        <v>0.6616919999999999</v>
+      </c>
+      <c r="BO76" s="28" t="n"/>
+      <c r="BP76" s="25" t="n"/>
+      <c r="BQ76" s="27" t="n"/>
+      <c r="BR76" s="28" t="n"/>
+      <c r="BS76" s="28" t="n"/>
+      <c r="BT76" s="28" t="n"/>
+      <c r="BU76" s="25" t="n"/>
+      <c r="BV76" s="29" t="n"/>
+      <c r="BW76" s="24" t="n"/>
+      <c r="BX76" s="30" t="n"/>
+      <c r="BY76" s="27" t="n"/>
+      <c r="BZ76" s="24" t="n"/>
+      <c r="CA76" s="31" t="n"/>
+      <c r="CB76" s="24" t="n"/>
+      <c r="CC76" s="24" t="inlineStr">
+        <is>
+          <t>0.6733890599</t>
+        </is>
+      </c>
+      <c r="CD76" s="24" t="inlineStr">
+        <is>
+          <t>-0.257437</t>
+        </is>
+      </c>
+      <c r="CE76" s="24" t="inlineStr">
+        <is>
+          <t>1.026</t>
+        </is>
+      </c>
+      <c r="CF76" s="24" t="inlineStr">
+        <is>
+          <t>1.0008</t>
+        </is>
+      </c>
+      <c r="CG76" s="24" t="n"/>
+      <c r="CH76" s="24" t="n"/>
+      <c r="CI76" s="24" t="n"/>
+      <c r="CJ76" s="24" t="inlineStr">
+        <is>
+          <t>-0.554899</t>
+        </is>
+      </c>
+      <c r="CK76" s="24" t="n"/>
+      <c r="CL76" s="24" t="inlineStr">
+        <is>
+          <t>-0.273728</t>
+        </is>
+      </c>
+      <c r="CM76" s="24" t="inlineStr">
+        <is>
+          <t>-2.8699</t>
+        </is>
+      </c>
+      <c r="CN76" s="24" t="n"/>
+      <c r="CO76" s="24" t="n"/>
+      <c r="CP76" s="24" t="n"/>
+      <c r="CQ76" s="24" t="n"/>
+      <c r="CR76" s="24" t="inlineStr">
+        <is>
+          <t>0.636517</t>
+        </is>
+      </c>
+      <c r="CS76" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
